--- a/tempetoto2026_invulformulier.xlsx
+++ b/tempetoto2026_invulformulier.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -78,6 +78,11 @@
       <b val="1"/>
       <color rgb="00B22234"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00444444"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -428,7 +433,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -457,21 +462,27 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -515,16 +526,13 @@
     <xf numFmtId="0" fontId="0" fillId="47" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="48" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="49" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="50" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="50" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1482,7 +1490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O193"/>
+  <dimension ref="A1:O203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1491,15 +1499,15 @@
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="5" customWidth="1" min="7" max="7"/>
-    <col width="2" customWidth="1" min="8" max="8"/>
-    <col width="2" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="10"/>
     <col width="2" customWidth="1" min="11" max="11"/>
     <col width="17" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="5" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1595,45 +1603,45 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
+    <row r="14" ht="40" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>•  Vul ALLE 72 groepswedstrijden in als '2-1' (thuis–uit, uitslag na 90 min). Dit zijn de lichtblauwe vakjes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
+          <t>1.  Vul ALLE 72 groepswedstrijden in als '2-1' (thuis–uit, uitslag na 90 min). Dit zijn de lichtblauwe vakjes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="40" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>•  Vul ook de VOORAF-sectie in: kampioen, verrassing, deceptie, topscorer, goals en kaarten.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
+          <t>2.  Vul ook de VOORAF-sectie in: kampioen, verrassing, deceptie, topscorer, goals en kaarten.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>•  Groepswinnaar, runner-up en beste nummers 3 worden AUTOMATISCH berekend uit je scores — je hoeft die niet in te vullen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
+          <t>3.  Groepswinnaar, runner-up en beste nummers 3 worden AUTOMATISCH berekend uit je scores — je hoeft die niet in te vullen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="40" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>•  Knock-out voorspellingen (grijs) vul je pas in na de groepsfase, vóór elke volgende ronde.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
+          <t>4.  Knock-out voorspellingen (grijs) vul je pas in na de groepsfase, vóór elke volgende ronde.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="40" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>•  Wijzigen van groepsfase-voorspellingen kan niet meer nadat het WK begonnen is.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
+          <t>5.  Wijzigen van groepsfase-voorspellingen kan niet meer nadat het WK begonnen is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="40" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>•  In principe worden de FIFA WK-regels aangehouden. Bij twijfel beslist de organisator.</t>
+          <t>6.  In principe worden de FIFA WK-regels aangehouden. Bij twijfel beslist de organisator.</t>
         </is>
       </c>
     </row>
@@ -1645,646 +1653,387 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>Groepswedstrijden:</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
+    </row>
+    <row r="23" ht="40" customHeight="1">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>Goede toto (winst/gelijkspel/verlies): 3 pt.  Goede uitslag: +2 pt.</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>Knock-outrondes:</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr">
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>Goede toto [+ goede uitslag]: R32 5[+3] · R16 7[+4] · KF 9[+5] · HF 11[+6] · F 13[+7] pt.  Uitslag na 90 min telt.</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>Doorgaan (top-2):</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
+    </row>
+    <row r="27" ht="40" customHeight="1">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>Per goed voorspeld land dat 1e of 2e eindigt in zijn groep: 3 pt.</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>Beste nummers 3:</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+    </row>
+    <row r="29" ht="40" customHeight="1">
+      <c r="B29" s="11" t="inlineStr">
         <is>
           <t>Per goed voorspelde nummer 3 die doorgaat: 3 pt  (8 plekken totaal).</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="5" t="inlineStr">
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>Kampioen:</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
+    </row>
+    <row r="31" ht="40" customHeight="1">
+      <c r="B31" s="11" t="inlineStr">
         <is>
           <t>Verliezend finalist voorspeld: 16 pt.  Kampioen exact: 40 pt.</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t>Topscorer:</t>
         </is>
       </c>
-      <c r="E27" s="8" t="inlineStr">
+    </row>
+    <row r="33" ht="40" customHeight="1">
+      <c r="B33" s="11" t="inlineStr">
         <is>
           <t>3e op topscorerslijst: 9 pt · 2e: 18 pt · 1e: 35 pt.  Exact aantal goals: +8 pt.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>Totaal goals:</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t>Exact goed: 25 pt.  Per goal verschil: -1 pt.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>Verrassing:</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t>Land buiten top-12 · punten schalen met hoe ver het komt (R16→winnaar) én hoe laag FIFA-gerankt. Zie tabel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>Deceptie:</t>
-        </is>
-      </c>
-      <c r="E30" s="8" t="inlineStr">
-        <is>
-          <t>Land uit top-12 · punten schalen met hoe vroeg het uitvalt (groepsfase=meest) én hoe hoog gerankt. Zie tabel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>Gele/rode kaarten:</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="inlineStr">
-        <is>
-          <t>Exact goed: 12 pt.  Per kaart verschil: -1 pt.  Geel en rood apart.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="8" customHeight="1"/>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>▶  GROEPSWEDSTRIJDEN  ·  vul in als '2-1' (thuis–uit, na 90 min)  ·  lichtblauwe vakjes invullen</t>
         </is>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="10" t="inlineStr">
         <is>
+          <t>Totaal goals:</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="40" customHeight="1">
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>Exact goed: 25 pt.  Per goal verschil: -1 pt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>Verrassing:</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="40" customHeight="1">
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>Land buiten top-12 · punten schalen met hoe ver het komt (R16→winnaar) én hoe laag FIFA-gerankt. Zie tabel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>Deceptie:</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="40" customHeight="1">
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>Land uit top-12 · punten schalen met hoe vroeg het uitvalt (groepsfase=meest) én hoe hoog gerankt. Zie tabel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>Gele/rode kaarten:</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="40" customHeight="1">
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>Exact goed: 12 pt.  Per kaart verschil: -1 pt.  Geel en rood apart.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="8" customHeight="1"/>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>▶  GROEPSWEDSTRIJDEN  ·  vul in als '2-1' (thuis–uit, na 90 min)  ·  lichtblauwe vakjes invullen</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="16" customHeight="1">
+      <c r="A44" s="12" t="inlineStr">
+        <is>
           <t>Groep A</t>
         </is>
       </c>
-      <c r="E34" s="11" t="inlineStr">
+      <c r="E44" s="13" t="inlineStr">
         <is>
           <t>voorsp.</t>
         </is>
       </c>
-      <c r="F34" s="11" t="inlineStr">
+      <c r="F44" s="13" t="inlineStr">
         <is>
           <t>uitslag</t>
         </is>
       </c>
-      <c r="G34" s="11" t="inlineStr">
+      <c r="G44" s="13" t="inlineStr">
         <is>
           <t>pt.</t>
         </is>
       </c>
-      <c r="I34" s="10" t="inlineStr">
+      <c r="I44" s="12" t="inlineStr">
         <is>
           <t>Groep B</t>
         </is>
       </c>
-      <c r="M34" s="11" t="inlineStr">
+      <c r="M44" s="13" t="inlineStr">
         <is>
           <t>voorsp.</t>
         </is>
       </c>
-      <c r="N34" s="11" t="inlineStr">
+      <c r="N44" s="13" t="inlineStr">
         <is>
           <t>uitslag</t>
         </is>
       </c>
-      <c r="O34" s="11" t="inlineStr">
+      <c r="O44" s="13" t="inlineStr">
         <is>
           <t>pt.</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="17" customHeight="1">
-      <c r="A35" s="12" t="n"/>
-      <c r="B35" s="13" t="inlineStr">
+    <row r="45" ht="17" customHeight="1">
+      <c r="A45" s="14" t="n"/>
+      <c r="B45" s="15" t="inlineStr">
         <is>
           <t>Mexico</t>
         </is>
       </c>
-      <c r="C35" s="14" t="n"/>
-      <c r="D35" s="15" t="inlineStr">
+      <c r="C45" s="16" t="n"/>
+      <c r="D45" s="17" t="inlineStr">
         <is>
           <t>Zuid-Afrika</t>
         </is>
       </c>
-      <c r="E35" s="6" t="n"/>
-      <c r="F35" s="16" t="inlineStr"/>
-      <c r="G35" s="16" t="inlineStr"/>
-      <c r="I35" s="17" t="n"/>
-      <c r="J35" s="13" t="inlineStr">
+      <c r="E45" s="6" t="n"/>
+      <c r="F45" s="18" t="inlineStr"/>
+      <c r="G45" s="18" t="inlineStr"/>
+      <c r="I45" s="19" t="n"/>
+      <c r="J45" s="15" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="K35" s="18" t="n"/>
-      <c r="L35" s="15" t="inlineStr">
+      <c r="K45" s="20" t="n"/>
+      <c r="L45" s="17" t="inlineStr">
         <is>
           <t>Zwitserland</t>
         </is>
       </c>
-      <c r="M35" s="6" t="n"/>
-      <c r="N35" s="16" t="inlineStr"/>
-      <c r="O35" s="16" t="inlineStr"/>
-    </row>
-    <row r="36" ht="17" customHeight="1">
-      <c r="A36" s="19" t="n"/>
-      <c r="B36" s="13" t="inlineStr">
+      <c r="M45" s="6" t="n"/>
+      <c r="N45" s="18" t="inlineStr"/>
+      <c r="O45" s="18" t="inlineStr"/>
+    </row>
+    <row r="46" ht="17" customHeight="1">
+      <c r="A46" s="21" t="n"/>
+      <c r="B46" s="15" t="inlineStr">
         <is>
           <t>Zuid-Korea</t>
         </is>
       </c>
-      <c r="C36" s="20" t="n"/>
-      <c r="D36" s="15" t="inlineStr">
+      <c r="C46" s="22" t="n"/>
+      <c r="D46" s="17" t="inlineStr">
         <is>
           <t>Tsjechië</t>
         </is>
       </c>
-      <c r="E36" s="6" t="n"/>
-      <c r="F36" s="16" t="inlineStr"/>
-      <c r="G36" s="16" t="inlineStr"/>
-      <c r="I36" s="21" t="n"/>
-      <c r="J36" s="13" t="inlineStr">
+      <c r="E46" s="6" t="n"/>
+      <c r="F46" s="18" t="inlineStr"/>
+      <c r="G46" s="18" t="inlineStr"/>
+      <c r="I46" s="23" t="n"/>
+      <c r="J46" s="15" t="inlineStr">
         <is>
           <t>Qatar</t>
         </is>
       </c>
-      <c r="K36" s="22" t="n"/>
-      <c r="L36" s="15" t="inlineStr">
+      <c r="K46" s="24" t="n"/>
+      <c r="L46" s="17" t="inlineStr">
         <is>
           <t>Bosnië-Herzegovina</t>
         </is>
       </c>
-      <c r="M36" s="6" t="n"/>
-      <c r="N36" s="16" t="inlineStr"/>
-      <c r="O36" s="16" t="inlineStr"/>
-    </row>
-    <row r="37" ht="17" customHeight="1">
-      <c r="A37" s="12" t="n"/>
-      <c r="B37" s="13" t="inlineStr">
+      <c r="M46" s="6" t="n"/>
+      <c r="N46" s="18" t="inlineStr"/>
+      <c r="O46" s="18" t="inlineStr"/>
+    </row>
+    <row r="47" ht="17" customHeight="1">
+      <c r="A47" s="14" t="n"/>
+      <c r="B47" s="15" t="inlineStr">
         <is>
           <t>Mexico</t>
         </is>
       </c>
-      <c r="C37" s="19" t="n"/>
-      <c r="D37" s="15" t="inlineStr">
+      <c r="C47" s="21" t="n"/>
+      <c r="D47" s="17" t="inlineStr">
         <is>
           <t>Zuid-Korea</t>
         </is>
       </c>
-      <c r="E37" s="6" t="n"/>
-      <c r="F37" s="16" t="inlineStr"/>
-      <c r="G37" s="16" t="inlineStr"/>
-      <c r="I37" s="17" t="n"/>
-      <c r="J37" s="13" t="inlineStr">
+      <c r="E47" s="6" t="n"/>
+      <c r="F47" s="18" t="inlineStr"/>
+      <c r="G47" s="18" t="inlineStr"/>
+      <c r="I47" s="19" t="n"/>
+      <c r="J47" s="15" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="K37" s="21" t="n"/>
-      <c r="L37" s="15" t="inlineStr">
+      <c r="K47" s="23" t="n"/>
+      <c r="L47" s="17" t="inlineStr">
         <is>
           <t>Qatar</t>
         </is>
       </c>
-      <c r="M37" s="6" t="n"/>
-      <c r="N37" s="16" t="inlineStr"/>
-      <c r="O37" s="16" t="inlineStr"/>
-    </row>
-    <row r="38" ht="17" customHeight="1">
-      <c r="A38" s="20" t="n"/>
-      <c r="B38" s="13" t="inlineStr">
+      <c r="M47" s="6" t="n"/>
+      <c r="N47" s="18" t="inlineStr"/>
+      <c r="O47" s="18" t="inlineStr"/>
+    </row>
+    <row r="48" ht="17" customHeight="1">
+      <c r="A48" s="22" t="n"/>
+      <c r="B48" s="15" t="inlineStr">
         <is>
           <t>Tsjechië</t>
         </is>
       </c>
-      <c r="C38" s="14" t="n"/>
-      <c r="D38" s="15" t="inlineStr">
+      <c r="C48" s="16" t="n"/>
+      <c r="D48" s="17" t="inlineStr">
         <is>
           <t>Zuid-Afrika</t>
         </is>
       </c>
-      <c r="E38" s="6" t="n"/>
-      <c r="F38" s="16" t="inlineStr"/>
-      <c r="G38" s="16" t="inlineStr"/>
-      <c r="I38" s="22" t="n"/>
-      <c r="J38" s="13" t="inlineStr">
+      <c r="E48" s="6" t="n"/>
+      <c r="F48" s="18" t="inlineStr"/>
+      <c r="G48" s="18" t="inlineStr"/>
+      <c r="I48" s="24" t="n"/>
+      <c r="J48" s="15" t="inlineStr">
         <is>
           <t>Bosnië-Herzegovina</t>
         </is>
       </c>
-      <c r="K38" s="18" t="n"/>
-      <c r="L38" s="15" t="inlineStr">
+      <c r="K48" s="20" t="n"/>
+      <c r="L48" s="17" t="inlineStr">
         <is>
           <t>Zwitserland</t>
         </is>
       </c>
-      <c r="M38" s="6" t="n"/>
-      <c r="N38" s="16" t="inlineStr"/>
-      <c r="O38" s="16" t="inlineStr"/>
-    </row>
-    <row r="39" ht="17" customHeight="1">
-      <c r="A39" s="20" t="n"/>
-      <c r="B39" s="13" t="inlineStr">
+      <c r="M48" s="6" t="n"/>
+      <c r="N48" s="18" t="inlineStr"/>
+      <c r="O48" s="18" t="inlineStr"/>
+    </row>
+    <row r="49" ht="17" customHeight="1">
+      <c r="A49" s="22" t="n"/>
+      <c r="B49" s="15" t="inlineStr">
         <is>
           <t>Tsjechië</t>
         </is>
       </c>
-      <c r="C39" s="12" t="n"/>
-      <c r="D39" s="15" t="inlineStr">
+      <c r="C49" s="14" t="n"/>
+      <c r="D49" s="17" t="inlineStr">
         <is>
           <t>Mexico</t>
         </is>
       </c>
-      <c r="E39" s="6" t="n"/>
-      <c r="F39" s="16" t="inlineStr"/>
-      <c r="G39" s="16" t="inlineStr"/>
-      <c r="I39" s="22" t="n"/>
-      <c r="J39" s="13" t="inlineStr">
+      <c r="E49" s="6" t="n"/>
+      <c r="F49" s="18" t="inlineStr"/>
+      <c r="G49" s="18" t="inlineStr"/>
+      <c r="I49" s="24" t="n"/>
+      <c r="J49" s="15" t="inlineStr">
         <is>
           <t>Bosnië-Herzegovina</t>
         </is>
       </c>
-      <c r="K39" s="17" t="n"/>
-      <c r="L39" s="15" t="inlineStr">
+      <c r="K49" s="19" t="n"/>
+      <c r="L49" s="17" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="M39" s="6" t="n"/>
-      <c r="N39" s="16" t="inlineStr"/>
-      <c r="O39" s="16" t="inlineStr"/>
-    </row>
-    <row r="40" ht="17" customHeight="1">
-      <c r="A40" s="14" t="n"/>
-      <c r="B40" s="13" t="inlineStr">
+      <c r="M49" s="6" t="n"/>
+      <c r="N49" s="18" t="inlineStr"/>
+      <c r="O49" s="18" t="inlineStr"/>
+    </row>
+    <row r="50" ht="17" customHeight="1">
+      <c r="A50" s="16" t="n"/>
+      <c r="B50" s="15" t="inlineStr">
         <is>
           <t>Zuid-Afrika</t>
         </is>
       </c>
-      <c r="C40" s="19" t="n"/>
-      <c r="D40" s="15" t="inlineStr">
+      <c r="C50" s="21" t="n"/>
+      <c r="D50" s="17" t="inlineStr">
         <is>
           <t>Zuid-Korea</t>
         </is>
       </c>
-      <c r="E40" s="6" t="n"/>
-      <c r="F40" s="16" t="inlineStr"/>
-      <c r="G40" s="16" t="inlineStr"/>
-      <c r="I40" s="18" t="n"/>
-      <c r="J40" s="13" t="inlineStr">
+      <c r="E50" s="6" t="n"/>
+      <c r="F50" s="18" t="inlineStr"/>
+      <c r="G50" s="18" t="inlineStr"/>
+      <c r="I50" s="20" t="n"/>
+      <c r="J50" s="15" t="inlineStr">
         <is>
           <t>Zwitserland</t>
         </is>
       </c>
-      <c r="K40" s="21" t="n"/>
-      <c r="L40" s="15" t="inlineStr">
+      <c r="K50" s="23" t="n"/>
+      <c r="L50" s="17" t="inlineStr">
         <is>
           <t>Qatar</t>
         </is>
       </c>
-      <c r="M40" s="6" t="n"/>
-      <c r="N40" s="16" t="inlineStr"/>
-      <c r="O40" s="16" t="inlineStr"/>
-    </row>
-    <row r="41" ht="17" customHeight="1">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>Groepswinnaar:</t>
-        </is>
-      </c>
-      <c r="E41" s="16" t="inlineStr">
-        <is>
-          <t>↳ automatisch berekend</t>
-        </is>
-      </c>
-      <c r="I41" s="5" t="inlineStr">
-        <is>
-          <t>Groepswinnaar:</t>
-        </is>
-      </c>
-      <c r="M41" s="16" t="inlineStr">
-        <is>
-          <t>↳ automatisch berekend</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="17" customHeight="1">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>Runner-up:</t>
-        </is>
-      </c>
-      <c r="E42" s="16" t="inlineStr">
-        <is>
-          <t>↳ automatisch berekend</t>
-        </is>
-      </c>
-      <c r="I42" s="5" t="inlineStr">
-        <is>
-          <t>Runner-up:</t>
-        </is>
-      </c>
-      <c r="M42" s="16" t="inlineStr">
-        <is>
-          <t>↳ automatisch berekend</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="6" customHeight="1"/>
-    <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="10" t="inlineStr">
-        <is>
-          <t>Groep C</t>
-        </is>
-      </c>
-      <c r="E44" s="11" t="inlineStr">
-        <is>
-          <t>voorsp.</t>
-        </is>
-      </c>
-      <c r="F44" s="11" t="inlineStr">
-        <is>
-          <t>uitslag</t>
-        </is>
-      </c>
-      <c r="G44" s="11" t="inlineStr">
-        <is>
-          <t>pt.</t>
-        </is>
-      </c>
-      <c r="I44" s="10" t="inlineStr">
-        <is>
-          <t>Groep D</t>
-        </is>
-      </c>
-      <c r="M44" s="11" t="inlineStr">
-        <is>
-          <t>voorsp.</t>
-        </is>
-      </c>
-      <c r="N44" s="11" t="inlineStr">
-        <is>
-          <t>uitslag</t>
-        </is>
-      </c>
-      <c r="O44" s="11" t="inlineStr">
-        <is>
-          <t>pt.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="17" customHeight="1">
-      <c r="A45" s="23" t="n"/>
-      <c r="B45" s="13" t="inlineStr">
-        <is>
-          <t>Brazilië</t>
-        </is>
-      </c>
-      <c r="C45" s="24" t="n"/>
-      <c r="D45" s="15" t="inlineStr">
-        <is>
-          <t>Marokko</t>
-        </is>
-      </c>
-      <c r="E45" s="6" t="n"/>
-      <c r="F45" s="16" t="inlineStr"/>
-      <c r="G45" s="16" t="inlineStr"/>
-      <c r="I45" s="25" t="n"/>
-      <c r="J45" s="13" t="inlineStr">
-        <is>
-          <t>Verenigde Staten</t>
-        </is>
-      </c>
-      <c r="K45" s="26" t="n"/>
-      <c r="L45" s="15" t="inlineStr">
-        <is>
-          <t>Paraguay</t>
-        </is>
-      </c>
-      <c r="M45" s="6" t="n"/>
-      <c r="N45" s="16" t="inlineStr"/>
-      <c r="O45" s="16" t="inlineStr"/>
-    </row>
-    <row r="46" ht="17" customHeight="1">
-      <c r="A46" s="27" t="n"/>
-      <c r="B46" s="13" t="inlineStr">
-        <is>
-          <t>Haïti</t>
-        </is>
-      </c>
-      <c r="C46" s="28" t="n"/>
-      <c r="D46" s="15" t="inlineStr">
-        <is>
-          <t>Schotland</t>
-        </is>
-      </c>
-      <c r="E46" s="6" t="n"/>
-      <c r="F46" s="16" t="inlineStr"/>
-      <c r="G46" s="16" t="inlineStr"/>
-      <c r="I46" s="29" t="n"/>
-      <c r="J46" s="13" t="inlineStr">
-        <is>
-          <t>Australië</t>
-        </is>
-      </c>
-      <c r="K46" s="30" t="n"/>
-      <c r="L46" s="15" t="inlineStr">
-        <is>
-          <t>Turkije</t>
-        </is>
-      </c>
-      <c r="M46" s="6" t="n"/>
-      <c r="N46" s="16" t="inlineStr"/>
-      <c r="O46" s="16" t="inlineStr"/>
-    </row>
-    <row r="47" ht="17" customHeight="1">
-      <c r="A47" s="23" t="n"/>
-      <c r="B47" s="13" t="inlineStr">
-        <is>
-          <t>Brazilië</t>
-        </is>
-      </c>
-      <c r="C47" s="27" t="n"/>
-      <c r="D47" s="15" t="inlineStr">
-        <is>
-          <t>Haïti</t>
-        </is>
-      </c>
-      <c r="E47" s="6" t="n"/>
-      <c r="F47" s="16" t="inlineStr"/>
-      <c r="G47" s="16" t="inlineStr"/>
-      <c r="I47" s="25" t="n"/>
-      <c r="J47" s="13" t="inlineStr">
-        <is>
-          <t>Verenigde Staten</t>
-        </is>
-      </c>
-      <c r="K47" s="29" t="n"/>
-      <c r="L47" s="15" t="inlineStr">
-        <is>
-          <t>Australië</t>
-        </is>
-      </c>
-      <c r="M47" s="6" t="n"/>
-      <c r="N47" s="16" t="inlineStr"/>
-      <c r="O47" s="16" t="inlineStr"/>
-    </row>
-    <row r="48" ht="17" customHeight="1">
-      <c r="A48" s="28" t="n"/>
-      <c r="B48" s="13" t="inlineStr">
-        <is>
-          <t>Schotland</t>
-        </is>
-      </c>
-      <c r="C48" s="24" t="n"/>
-      <c r="D48" s="15" t="inlineStr">
-        <is>
-          <t>Marokko</t>
-        </is>
-      </c>
-      <c r="E48" s="6" t="n"/>
-      <c r="F48" s="16" t="inlineStr"/>
-      <c r="G48" s="16" t="inlineStr"/>
-      <c r="I48" s="30" t="n"/>
-      <c r="J48" s="13" t="inlineStr">
-        <is>
-          <t>Turkije</t>
-        </is>
-      </c>
-      <c r="K48" s="26" t="n"/>
-      <c r="L48" s="15" t="inlineStr">
-        <is>
-          <t>Paraguay</t>
-        </is>
-      </c>
-      <c r="M48" s="6" t="n"/>
-      <c r="N48" s="16" t="inlineStr"/>
-      <c r="O48" s="16" t="inlineStr"/>
-    </row>
-    <row r="49" ht="17" customHeight="1">
-      <c r="A49" s="28" t="n"/>
-      <c r="B49" s="13" t="inlineStr">
-        <is>
-          <t>Schotland</t>
-        </is>
-      </c>
-      <c r="C49" s="23" t="n"/>
-      <c r="D49" s="15" t="inlineStr">
-        <is>
-          <t>Brazilië</t>
-        </is>
-      </c>
-      <c r="E49" s="6" t="n"/>
-      <c r="F49" s="16" t="inlineStr"/>
-      <c r="G49" s="16" t="inlineStr"/>
-      <c r="I49" s="30" t="n"/>
-      <c r="J49" s="13" t="inlineStr">
-        <is>
-          <t>Turkije</t>
-        </is>
-      </c>
-      <c r="K49" s="25" t="n"/>
-      <c r="L49" s="15" t="inlineStr">
-        <is>
-          <t>Verenigde Staten</t>
-        </is>
-      </c>
-      <c r="M49" s="6" t="n"/>
-      <c r="N49" s="16" t="inlineStr"/>
-      <c r="O49" s="16" t="inlineStr"/>
-    </row>
-    <row r="50" ht="17" customHeight="1">
-      <c r="A50" s="24" t="n"/>
-      <c r="B50" s="13" t="inlineStr">
-        <is>
-          <t>Marokko</t>
-        </is>
-      </c>
-      <c r="C50" s="27" t="n"/>
-      <c r="D50" s="15" t="inlineStr">
-        <is>
-          <t>Haïti</t>
-        </is>
-      </c>
-      <c r="E50" s="6" t="n"/>
-      <c r="F50" s="16" t="inlineStr"/>
-      <c r="G50" s="16" t="inlineStr"/>
-      <c r="I50" s="26" t="n"/>
-      <c r="J50" s="13" t="inlineStr">
-        <is>
-          <t>Paraguay</t>
-        </is>
-      </c>
-      <c r="K50" s="29" t="n"/>
-      <c r="L50" s="15" t="inlineStr">
-        <is>
-          <t>Australië</t>
-        </is>
-      </c>
       <c r="M50" s="6" t="n"/>
-      <c r="N50" s="16" t="inlineStr"/>
-      <c r="O50" s="16" t="inlineStr"/>
+      <c r="N50" s="18" t="inlineStr"/>
+      <c r="O50" s="18" t="inlineStr"/>
     </row>
     <row r="51" ht="17" customHeight="1">
       <c r="A51" s="5" t="inlineStr">
@@ -2292,9 +2041,9 @@
           <t>Groepswinnaar:</t>
         </is>
       </c>
-      <c r="E51" s="16" t="inlineStr">
-        <is>
-          <t>↳ automatisch berekend</t>
+      <c r="E51" s="18" t="inlineStr">
+        <is>
+          <t>↳ niet invullen</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
@@ -2302,9 +2051,9 @@
           <t>Groepswinnaar:</t>
         </is>
       </c>
-      <c r="M51" s="16" t="inlineStr">
-        <is>
-          <t>↳ automatisch berekend</t>
+      <c r="M51" s="18" t="inlineStr">
+        <is>
+          <t>↳ niet invullen</t>
         </is>
       </c>
     </row>
@@ -2314,9 +2063,9 @@
           <t>Runner-up:</t>
         </is>
       </c>
-      <c r="E52" s="16" t="inlineStr">
-        <is>
-          <t>↳ automatisch berekend</t>
+      <c r="E52" s="18" t="inlineStr">
+        <is>
+          <t>↳ niet invullen</t>
         </is>
       </c>
       <c r="I52" s="5" t="inlineStr">
@@ -2324,246 +2073,246 @@
           <t>Runner-up:</t>
         </is>
       </c>
-      <c r="M52" s="16" t="inlineStr">
-        <is>
-          <t>↳ automatisch berekend</t>
+      <c r="M52" s="18" t="inlineStr">
+        <is>
+          <t>↳ niet invullen</t>
         </is>
       </c>
     </row>
     <row r="53" ht="6" customHeight="1"/>
     <row r="54" ht="16" customHeight="1">
-      <c r="A54" s="10" t="inlineStr">
-        <is>
-          <t>Groep E</t>
-        </is>
-      </c>
-      <c r="E54" s="11" t="inlineStr">
+      <c r="A54" s="12" t="inlineStr">
+        <is>
+          <t>Groep C</t>
+        </is>
+      </c>
+      <c r="E54" s="13" t="inlineStr">
         <is>
           <t>voorsp.</t>
         </is>
       </c>
-      <c r="F54" s="11" t="inlineStr">
+      <c r="F54" s="13" t="inlineStr">
         <is>
           <t>uitslag</t>
         </is>
       </c>
-      <c r="G54" s="11" t="inlineStr">
+      <c r="G54" s="13" t="inlineStr">
         <is>
           <t>pt.</t>
         </is>
       </c>
-      <c r="I54" s="10" t="inlineStr">
-        <is>
-          <t>Groep F</t>
-        </is>
-      </c>
-      <c r="M54" s="11" t="inlineStr">
+      <c r="I54" s="12" t="inlineStr">
+        <is>
+          <t>Groep D</t>
+        </is>
+      </c>
+      <c r="M54" s="13" t="inlineStr">
         <is>
           <t>voorsp.</t>
         </is>
       </c>
-      <c r="N54" s="11" t="inlineStr">
+      <c r="N54" s="13" t="inlineStr">
         <is>
           <t>uitslag</t>
         </is>
       </c>
-      <c r="O54" s="11" t="inlineStr">
+      <c r="O54" s="13" t="inlineStr">
         <is>
           <t>pt.</t>
         </is>
       </c>
     </row>
     <row r="55" ht="17" customHeight="1">
-      <c r="A55" s="18" t="n"/>
-      <c r="B55" s="13" t="inlineStr">
-        <is>
-          <t>Duitsland</t>
-        </is>
-      </c>
-      <c r="C55" s="31" t="n"/>
-      <c r="D55" s="15" t="inlineStr">
-        <is>
-          <t>Curaçao</t>
+      <c r="A55" s="25" t="n"/>
+      <c r="B55" s="15" t="inlineStr">
+        <is>
+          <t>Brazilië</t>
+        </is>
+      </c>
+      <c r="C55" s="26" t="n"/>
+      <c r="D55" s="17" t="inlineStr">
+        <is>
+          <t>Marokko</t>
         </is>
       </c>
       <c r="E55" s="6" t="n"/>
-      <c r="F55" s="16" t="inlineStr"/>
-      <c r="G55" s="16" t="inlineStr"/>
-      <c r="I55" s="32" t="n"/>
-      <c r="J55" s="13" t="inlineStr">
-        <is>
-          <t>Nederland</t>
-        </is>
-      </c>
-      <c r="K55" s="33" t="n"/>
-      <c r="L55" s="15" t="inlineStr">
-        <is>
-          <t>Japan</t>
+      <c r="F55" s="18" t="inlineStr"/>
+      <c r="G55" s="18" t="inlineStr"/>
+      <c r="I55" s="27" t="n"/>
+      <c r="J55" s="15" t="inlineStr">
+        <is>
+          <t>Verenigde Staten</t>
+        </is>
+      </c>
+      <c r="K55" s="28" t="n"/>
+      <c r="L55" s="17" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="M55" s="6" t="n"/>
-      <c r="N55" s="16" t="inlineStr"/>
-      <c r="O55" s="16" t="inlineStr"/>
+      <c r="N55" s="18" t="inlineStr"/>
+      <c r="O55" s="18" t="inlineStr"/>
     </row>
     <row r="56" ht="17" customHeight="1">
-      <c r="A56" s="34" t="n"/>
-      <c r="B56" s="13" t="inlineStr">
-        <is>
-          <t>Ivoorkust</t>
-        </is>
-      </c>
-      <c r="C56" s="35" t="n"/>
-      <c r="D56" s="15" t="inlineStr">
-        <is>
-          <t>Ecuador</t>
+      <c r="A56" s="29" t="n"/>
+      <c r="B56" s="15" t="inlineStr">
+        <is>
+          <t>Haïti</t>
+        </is>
+      </c>
+      <c r="C56" s="30" t="n"/>
+      <c r="D56" s="17" t="inlineStr">
+        <is>
+          <t>Schotland</t>
         </is>
       </c>
       <c r="E56" s="6" t="n"/>
-      <c r="F56" s="16" t="inlineStr"/>
-      <c r="G56" s="16" t="inlineStr"/>
-      <c r="I56" s="36" t="n"/>
-      <c r="J56" s="13" t="inlineStr">
-        <is>
-          <t>Zweden</t>
-        </is>
-      </c>
-      <c r="K56" s="30" t="n"/>
-      <c r="L56" s="15" t="inlineStr">
-        <is>
-          <t>Tunesië</t>
+      <c r="F56" s="18" t="inlineStr"/>
+      <c r="G56" s="18" t="inlineStr"/>
+      <c r="I56" s="31" t="n"/>
+      <c r="J56" s="15" t="inlineStr">
+        <is>
+          <t>Australië</t>
+        </is>
+      </c>
+      <c r="K56" s="32" t="n"/>
+      <c r="L56" s="17" t="inlineStr">
+        <is>
+          <t>Turkije</t>
         </is>
       </c>
       <c r="M56" s="6" t="n"/>
-      <c r="N56" s="16" t="inlineStr"/>
-      <c r="O56" s="16" t="inlineStr"/>
+      <c r="N56" s="18" t="inlineStr"/>
+      <c r="O56" s="18" t="inlineStr"/>
     </row>
     <row r="57" ht="17" customHeight="1">
-      <c r="A57" s="18" t="n"/>
-      <c r="B57" s="13" t="inlineStr">
-        <is>
-          <t>Duitsland</t>
-        </is>
-      </c>
-      <c r="C57" s="34" t="n"/>
-      <c r="D57" s="15" t="inlineStr">
-        <is>
-          <t>Ivoorkust</t>
+      <c r="A57" s="25" t="n"/>
+      <c r="B57" s="15" t="inlineStr">
+        <is>
+          <t>Brazilië</t>
+        </is>
+      </c>
+      <c r="C57" s="29" t="n"/>
+      <c r="D57" s="17" t="inlineStr">
+        <is>
+          <t>Haïti</t>
         </is>
       </c>
       <c r="E57" s="6" t="n"/>
-      <c r="F57" s="16" t="inlineStr"/>
-      <c r="G57" s="16" t="inlineStr"/>
-      <c r="I57" s="32" t="n"/>
-      <c r="J57" s="13" t="inlineStr">
-        <is>
-          <t>Nederland</t>
-        </is>
-      </c>
-      <c r="K57" s="36" t="n"/>
-      <c r="L57" s="15" t="inlineStr">
-        <is>
-          <t>Zweden</t>
+      <c r="F57" s="18" t="inlineStr"/>
+      <c r="G57" s="18" t="inlineStr"/>
+      <c r="I57" s="27" t="n"/>
+      <c r="J57" s="15" t="inlineStr">
+        <is>
+          <t>Verenigde Staten</t>
+        </is>
+      </c>
+      <c r="K57" s="31" t="n"/>
+      <c r="L57" s="17" t="inlineStr">
+        <is>
+          <t>Australië</t>
         </is>
       </c>
       <c r="M57" s="6" t="n"/>
-      <c r="N57" s="16" t="inlineStr"/>
-      <c r="O57" s="16" t="inlineStr"/>
+      <c r="N57" s="18" t="inlineStr"/>
+      <c r="O57" s="18" t="inlineStr"/>
     </row>
     <row r="58" ht="17" customHeight="1">
-      <c r="A58" s="35" t="n"/>
-      <c r="B58" s="13" t="inlineStr">
-        <is>
-          <t>Ecuador</t>
-        </is>
-      </c>
-      <c r="C58" s="31" t="n"/>
-      <c r="D58" s="15" t="inlineStr">
-        <is>
-          <t>Curaçao</t>
+      <c r="A58" s="30" t="n"/>
+      <c r="B58" s="15" t="inlineStr">
+        <is>
+          <t>Schotland</t>
+        </is>
+      </c>
+      <c r="C58" s="26" t="n"/>
+      <c r="D58" s="17" t="inlineStr">
+        <is>
+          <t>Marokko</t>
         </is>
       </c>
       <c r="E58" s="6" t="n"/>
-      <c r="F58" s="16" t="inlineStr"/>
-      <c r="G58" s="16" t="inlineStr"/>
-      <c r="I58" s="30" t="n"/>
-      <c r="J58" s="13" t="inlineStr">
-        <is>
-          <t>Tunesië</t>
-        </is>
-      </c>
-      <c r="K58" s="33" t="n"/>
-      <c r="L58" s="15" t="inlineStr">
-        <is>
-          <t>Japan</t>
+      <c r="F58" s="18" t="inlineStr"/>
+      <c r="G58" s="18" t="inlineStr"/>
+      <c r="I58" s="32" t="n"/>
+      <c r="J58" s="15" t="inlineStr">
+        <is>
+          <t>Turkije</t>
+        </is>
+      </c>
+      <c r="K58" s="28" t="n"/>
+      <c r="L58" s="17" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="M58" s="6" t="n"/>
-      <c r="N58" s="16" t="inlineStr"/>
-      <c r="O58" s="16" t="inlineStr"/>
+      <c r="N58" s="18" t="inlineStr"/>
+      <c r="O58" s="18" t="inlineStr"/>
     </row>
     <row r="59" ht="17" customHeight="1">
-      <c r="A59" s="35" t="n"/>
-      <c r="B59" s="13" t="inlineStr">
-        <is>
-          <t>Ecuador</t>
-        </is>
-      </c>
-      <c r="C59" s="18" t="n"/>
-      <c r="D59" s="15" t="inlineStr">
-        <is>
-          <t>Duitsland</t>
+      <c r="A59" s="30" t="n"/>
+      <c r="B59" s="15" t="inlineStr">
+        <is>
+          <t>Schotland</t>
+        </is>
+      </c>
+      <c r="C59" s="25" t="n"/>
+      <c r="D59" s="17" t="inlineStr">
+        <is>
+          <t>Brazilië</t>
         </is>
       </c>
       <c r="E59" s="6" t="n"/>
-      <c r="F59" s="16" t="inlineStr"/>
-      <c r="G59" s="16" t="inlineStr"/>
-      <c r="I59" s="30" t="n"/>
-      <c r="J59" s="13" t="inlineStr">
-        <is>
-          <t>Tunesië</t>
-        </is>
-      </c>
-      <c r="K59" s="32" t="n"/>
-      <c r="L59" s="15" t="inlineStr">
-        <is>
-          <t>Nederland</t>
+      <c r="F59" s="18" t="inlineStr"/>
+      <c r="G59" s="18" t="inlineStr"/>
+      <c r="I59" s="32" t="n"/>
+      <c r="J59" s="15" t="inlineStr">
+        <is>
+          <t>Turkije</t>
+        </is>
+      </c>
+      <c r="K59" s="27" t="n"/>
+      <c r="L59" s="17" t="inlineStr">
+        <is>
+          <t>Verenigde Staten</t>
         </is>
       </c>
       <c r="M59" s="6" t="n"/>
-      <c r="N59" s="16" t="inlineStr"/>
-      <c r="O59" s="16" t="inlineStr"/>
+      <c r="N59" s="18" t="inlineStr"/>
+      <c r="O59" s="18" t="inlineStr"/>
     </row>
     <row r="60" ht="17" customHeight="1">
-      <c r="A60" s="31" t="n"/>
-      <c r="B60" s="13" t="inlineStr">
-        <is>
-          <t>Curaçao</t>
-        </is>
-      </c>
-      <c r="C60" s="34" t="n"/>
-      <c r="D60" s="15" t="inlineStr">
-        <is>
-          <t>Ivoorkust</t>
+      <c r="A60" s="26" t="n"/>
+      <c r="B60" s="15" t="inlineStr">
+        <is>
+          <t>Marokko</t>
+        </is>
+      </c>
+      <c r="C60" s="29" t="n"/>
+      <c r="D60" s="17" t="inlineStr">
+        <is>
+          <t>Haïti</t>
         </is>
       </c>
       <c r="E60" s="6" t="n"/>
-      <c r="F60" s="16" t="inlineStr"/>
-      <c r="G60" s="16" t="inlineStr"/>
-      <c r="I60" s="33" t="n"/>
-      <c r="J60" s="13" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="K60" s="36" t="n"/>
-      <c r="L60" s="15" t="inlineStr">
-        <is>
-          <t>Zweden</t>
+      <c r="F60" s="18" t="inlineStr"/>
+      <c r="G60" s="18" t="inlineStr"/>
+      <c r="I60" s="28" t="n"/>
+      <c r="J60" s="15" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+      <c r="K60" s="31" t="n"/>
+      <c r="L60" s="17" t="inlineStr">
+        <is>
+          <t>Australië</t>
         </is>
       </c>
       <c r="M60" s="6" t="n"/>
-      <c r="N60" s="16" t="inlineStr"/>
-      <c r="O60" s="16" t="inlineStr"/>
+      <c r="N60" s="18" t="inlineStr"/>
+      <c r="O60" s="18" t="inlineStr"/>
     </row>
     <row r="61" ht="17" customHeight="1">
       <c r="A61" s="5" t="inlineStr">
@@ -2571,9 +2320,9 @@
           <t>Groepswinnaar:</t>
         </is>
       </c>
-      <c r="E61" s="16" t="inlineStr">
-        <is>
-          <t>↳ automatisch berekend</t>
+      <c r="E61" s="18" t="inlineStr">
+        <is>
+          <t>↳ niet invullen</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr">
@@ -2581,9 +2330,9 @@
           <t>Groepswinnaar:</t>
         </is>
       </c>
-      <c r="M61" s="16" t="inlineStr">
-        <is>
-          <t>↳ automatisch berekend</t>
+      <c r="M61" s="18" t="inlineStr">
+        <is>
+          <t>↳ niet invullen</t>
         </is>
       </c>
     </row>
@@ -2593,9 +2342,9 @@
           <t>Runner-up:</t>
         </is>
       </c>
-      <c r="E62" s="16" t="inlineStr">
-        <is>
-          <t>↳ automatisch berekend</t>
+      <c r="E62" s="18" t="inlineStr">
+        <is>
+          <t>↳ niet invullen</t>
         </is>
       </c>
       <c r="I62" s="5" t="inlineStr">
@@ -2603,246 +2352,246 @@
           <t>Runner-up:</t>
         </is>
       </c>
-      <c r="M62" s="16" t="inlineStr">
-        <is>
-          <t>↳ automatisch berekend</t>
+      <c r="M62" s="18" t="inlineStr">
+        <is>
+          <t>↳ niet invullen</t>
         </is>
       </c>
     </row>
     <row r="63" ht="6" customHeight="1"/>
     <row r="64" ht="16" customHeight="1">
-      <c r="A64" s="10" t="inlineStr">
-        <is>
-          <t>Groep G</t>
-        </is>
-      </c>
-      <c r="E64" s="11" t="inlineStr">
+      <c r="A64" s="12" t="inlineStr">
+        <is>
+          <t>Groep E</t>
+        </is>
+      </c>
+      <c r="E64" s="13" t="inlineStr">
         <is>
           <t>voorsp.</t>
         </is>
       </c>
-      <c r="F64" s="11" t="inlineStr">
+      <c r="F64" s="13" t="inlineStr">
         <is>
           <t>uitslag</t>
         </is>
       </c>
-      <c r="G64" s="11" t="inlineStr">
+      <c r="G64" s="13" t="inlineStr">
         <is>
           <t>pt.</t>
         </is>
       </c>
-      <c r="I64" s="10" t="inlineStr">
-        <is>
-          <t>Groep H</t>
-        </is>
-      </c>
-      <c r="M64" s="11" t="inlineStr">
+      <c r="I64" s="12" t="inlineStr">
+        <is>
+          <t>Groep F</t>
+        </is>
+      </c>
+      <c r="M64" s="13" t="inlineStr">
         <is>
           <t>voorsp.</t>
         </is>
       </c>
-      <c r="N64" s="11" t="inlineStr">
+      <c r="N64" s="13" t="inlineStr">
         <is>
           <t>uitslag</t>
         </is>
       </c>
-      <c r="O64" s="11" t="inlineStr">
+      <c r="O64" s="13" t="inlineStr">
         <is>
           <t>pt.</t>
         </is>
       </c>
     </row>
     <row r="65" ht="17" customHeight="1">
-      <c r="A65" s="37" t="n"/>
-      <c r="B65" s="13" t="inlineStr">
-        <is>
-          <t>België</t>
-        </is>
-      </c>
-      <c r="C65" s="38" t="n"/>
-      <c r="D65" s="15" t="inlineStr">
-        <is>
-          <t>Egypte</t>
+      <c r="A65" s="20" t="n"/>
+      <c r="B65" s="15" t="inlineStr">
+        <is>
+          <t>Duitsland</t>
+        </is>
+      </c>
+      <c r="C65" s="33" t="n"/>
+      <c r="D65" s="17" t="inlineStr">
+        <is>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="E65" s="6" t="n"/>
-      <c r="F65" s="16" t="inlineStr"/>
-      <c r="G65" s="16" t="inlineStr"/>
-      <c r="I65" s="39" t="n"/>
-      <c r="J65" s="13" t="inlineStr">
-        <is>
-          <t>Spanje</t>
-        </is>
-      </c>
-      <c r="K65" s="40" t="n"/>
-      <c r="L65" s="15" t="inlineStr">
-        <is>
-          <t>Kaapverdië</t>
+      <c r="F65" s="18" t="inlineStr"/>
+      <c r="G65" s="18" t="inlineStr"/>
+      <c r="I65" s="34" t="n"/>
+      <c r="J65" s="15" t="inlineStr">
+        <is>
+          <t>Nederland</t>
+        </is>
+      </c>
+      <c r="K65" s="35" t="n"/>
+      <c r="L65" s="17" t="inlineStr">
+        <is>
+          <t>Japan</t>
         </is>
       </c>
       <c r="M65" s="6" t="n"/>
-      <c r="N65" s="16" t="inlineStr"/>
-      <c r="O65" s="16" t="inlineStr"/>
+      <c r="N65" s="18" t="inlineStr"/>
+      <c r="O65" s="18" t="inlineStr"/>
     </row>
     <row r="66" ht="17" customHeight="1">
-      <c r="A66" s="41" t="n"/>
-      <c r="B66" s="13" t="inlineStr">
-        <is>
-          <t>Iran</t>
-        </is>
-      </c>
-      <c r="C66" s="42" t="n"/>
-      <c r="D66" s="15" t="inlineStr">
-        <is>
-          <t>Nieuw-Zeeland</t>
+      <c r="A66" s="36" t="n"/>
+      <c r="B66" s="15" t="inlineStr">
+        <is>
+          <t>Ivoorkust</t>
+        </is>
+      </c>
+      <c r="C66" s="37" t="n"/>
+      <c r="D66" s="17" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="E66" s="6" t="n"/>
-      <c r="F66" s="16" t="inlineStr"/>
-      <c r="G66" s="16" t="inlineStr"/>
-      <c r="I66" s="43" t="n"/>
-      <c r="J66" s="13" t="inlineStr">
-        <is>
-          <t>Saoedi-Arabië</t>
-        </is>
-      </c>
-      <c r="K66" s="44" t="n"/>
-      <c r="L66" s="15" t="inlineStr">
-        <is>
-          <t>Uruguay</t>
+      <c r="F66" s="18" t="inlineStr"/>
+      <c r="G66" s="18" t="inlineStr"/>
+      <c r="I66" s="38" t="n"/>
+      <c r="J66" s="15" t="inlineStr">
+        <is>
+          <t>Zweden</t>
+        </is>
+      </c>
+      <c r="K66" s="32" t="n"/>
+      <c r="L66" s="17" t="inlineStr">
+        <is>
+          <t>Tunesië</t>
         </is>
       </c>
       <c r="M66" s="6" t="n"/>
-      <c r="N66" s="16" t="inlineStr"/>
-      <c r="O66" s="16" t="inlineStr"/>
+      <c r="N66" s="18" t="inlineStr"/>
+      <c r="O66" s="18" t="inlineStr"/>
     </row>
     <row r="67" ht="17" customHeight="1">
-      <c r="A67" s="37" t="n"/>
-      <c r="B67" s="13" t="inlineStr">
-        <is>
-          <t>België</t>
-        </is>
-      </c>
-      <c r="C67" s="41" t="n"/>
-      <c r="D67" s="15" t="inlineStr">
-        <is>
-          <t>Iran</t>
+      <c r="A67" s="20" t="n"/>
+      <c r="B67" s="15" t="inlineStr">
+        <is>
+          <t>Duitsland</t>
+        </is>
+      </c>
+      <c r="C67" s="36" t="n"/>
+      <c r="D67" s="17" t="inlineStr">
+        <is>
+          <t>Ivoorkust</t>
         </is>
       </c>
       <c r="E67" s="6" t="n"/>
-      <c r="F67" s="16" t="inlineStr"/>
-      <c r="G67" s="16" t="inlineStr"/>
-      <c r="I67" s="39" t="n"/>
-      <c r="J67" s="13" t="inlineStr">
-        <is>
-          <t>Spanje</t>
-        </is>
-      </c>
-      <c r="K67" s="43" t="n"/>
-      <c r="L67" s="15" t="inlineStr">
-        <is>
-          <t>Saoedi-Arabië</t>
+      <c r="F67" s="18" t="inlineStr"/>
+      <c r="G67" s="18" t="inlineStr"/>
+      <c r="I67" s="34" t="n"/>
+      <c r="J67" s="15" t="inlineStr">
+        <is>
+          <t>Nederland</t>
+        </is>
+      </c>
+      <c r="K67" s="38" t="n"/>
+      <c r="L67" s="17" t="inlineStr">
+        <is>
+          <t>Zweden</t>
         </is>
       </c>
       <c r="M67" s="6" t="n"/>
-      <c r="N67" s="16" t="inlineStr"/>
-      <c r="O67" s="16" t="inlineStr"/>
+      <c r="N67" s="18" t="inlineStr"/>
+      <c r="O67" s="18" t="inlineStr"/>
     </row>
     <row r="68" ht="17" customHeight="1">
-      <c r="A68" s="42" t="n"/>
-      <c r="B68" s="13" t="inlineStr">
-        <is>
-          <t>Nieuw-Zeeland</t>
-        </is>
-      </c>
-      <c r="C68" s="38" t="n"/>
-      <c r="D68" s="15" t="inlineStr">
-        <is>
-          <t>Egypte</t>
+      <c r="A68" s="37" t="n"/>
+      <c r="B68" s="15" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="C68" s="33" t="n"/>
+      <c r="D68" s="17" t="inlineStr">
+        <is>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="E68" s="6" t="n"/>
-      <c r="F68" s="16" t="inlineStr"/>
-      <c r="G68" s="16" t="inlineStr"/>
-      <c r="I68" s="44" t="n"/>
-      <c r="J68" s="13" t="inlineStr">
-        <is>
-          <t>Uruguay</t>
-        </is>
-      </c>
-      <c r="K68" s="40" t="n"/>
-      <c r="L68" s="15" t="inlineStr">
-        <is>
-          <t>Kaapverdië</t>
+      <c r="F68" s="18" t="inlineStr"/>
+      <c r="G68" s="18" t="inlineStr"/>
+      <c r="I68" s="32" t="n"/>
+      <c r="J68" s="15" t="inlineStr">
+        <is>
+          <t>Tunesië</t>
+        </is>
+      </c>
+      <c r="K68" s="35" t="n"/>
+      <c r="L68" s="17" t="inlineStr">
+        <is>
+          <t>Japan</t>
         </is>
       </c>
       <c r="M68" s="6" t="n"/>
-      <c r="N68" s="16" t="inlineStr"/>
-      <c r="O68" s="16" t="inlineStr"/>
+      <c r="N68" s="18" t="inlineStr"/>
+      <c r="O68" s="18" t="inlineStr"/>
     </row>
     <row r="69" ht="17" customHeight="1">
-      <c r="A69" s="42" t="n"/>
-      <c r="B69" s="13" t="inlineStr">
-        <is>
-          <t>Nieuw-Zeeland</t>
-        </is>
-      </c>
-      <c r="C69" s="37" t="n"/>
-      <c r="D69" s="15" t="inlineStr">
-        <is>
-          <t>België</t>
+      <c r="A69" s="37" t="n"/>
+      <c r="B69" s="15" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="C69" s="20" t="n"/>
+      <c r="D69" s="17" t="inlineStr">
+        <is>
+          <t>Duitsland</t>
         </is>
       </c>
       <c r="E69" s="6" t="n"/>
-      <c r="F69" s="16" t="inlineStr"/>
-      <c r="G69" s="16" t="inlineStr"/>
-      <c r="I69" s="44" t="n"/>
-      <c r="J69" s="13" t="inlineStr">
-        <is>
-          <t>Uruguay</t>
-        </is>
-      </c>
-      <c r="K69" s="39" t="n"/>
-      <c r="L69" s="15" t="inlineStr">
-        <is>
-          <t>Spanje</t>
+      <c r="F69" s="18" t="inlineStr"/>
+      <c r="G69" s="18" t="inlineStr"/>
+      <c r="I69" s="32" t="n"/>
+      <c r="J69" s="15" t="inlineStr">
+        <is>
+          <t>Tunesië</t>
+        </is>
+      </c>
+      <c r="K69" s="34" t="n"/>
+      <c r="L69" s="17" t="inlineStr">
+        <is>
+          <t>Nederland</t>
         </is>
       </c>
       <c r="M69" s="6" t="n"/>
-      <c r="N69" s="16" t="inlineStr"/>
-      <c r="O69" s="16" t="inlineStr"/>
+      <c r="N69" s="18" t="inlineStr"/>
+      <c r="O69" s="18" t="inlineStr"/>
     </row>
     <row r="70" ht="17" customHeight="1">
-      <c r="A70" s="38" t="n"/>
-      <c r="B70" s="13" t="inlineStr">
-        <is>
-          <t>Egypte</t>
-        </is>
-      </c>
-      <c r="C70" s="41" t="n"/>
-      <c r="D70" s="15" t="inlineStr">
-        <is>
-          <t>Iran</t>
+      <c r="A70" s="33" t="n"/>
+      <c r="B70" s="15" t="inlineStr">
+        <is>
+          <t>Curaçao</t>
+        </is>
+      </c>
+      <c r="C70" s="36" t="n"/>
+      <c r="D70" s="17" t="inlineStr">
+        <is>
+          <t>Ivoorkust</t>
         </is>
       </c>
       <c r="E70" s="6" t="n"/>
-      <c r="F70" s="16" t="inlineStr"/>
-      <c r="G70" s="16" t="inlineStr"/>
-      <c r="I70" s="40" t="n"/>
-      <c r="J70" s="13" t="inlineStr">
-        <is>
-          <t>Kaapverdië</t>
-        </is>
-      </c>
-      <c r="K70" s="43" t="n"/>
-      <c r="L70" s="15" t="inlineStr">
-        <is>
-          <t>Saoedi-Arabië</t>
+      <c r="F70" s="18" t="inlineStr"/>
+      <c r="G70" s="18" t="inlineStr"/>
+      <c r="I70" s="35" t="n"/>
+      <c r="J70" s="15" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="K70" s="38" t="n"/>
+      <c r="L70" s="17" t="inlineStr">
+        <is>
+          <t>Zweden</t>
         </is>
       </c>
       <c r="M70" s="6" t="n"/>
-      <c r="N70" s="16" t="inlineStr"/>
-      <c r="O70" s="16" t="inlineStr"/>
+      <c r="N70" s="18" t="inlineStr"/>
+      <c r="O70" s="18" t="inlineStr"/>
     </row>
     <row r="71" ht="17" customHeight="1">
       <c r="A71" s="5" t="inlineStr">
@@ -2850,9 +2599,9 @@
           <t>Groepswinnaar:</t>
         </is>
       </c>
-      <c r="E71" s="16" t="inlineStr">
-        <is>
-          <t>↳ automatisch berekend</t>
+      <c r="E71" s="18" t="inlineStr">
+        <is>
+          <t>↳ niet invullen</t>
         </is>
       </c>
       <c r="I71" s="5" t="inlineStr">
@@ -2860,9 +2609,9 @@
           <t>Groepswinnaar:</t>
         </is>
       </c>
-      <c r="M71" s="16" t="inlineStr">
-        <is>
-          <t>↳ automatisch berekend</t>
+      <c r="M71" s="18" t="inlineStr">
+        <is>
+          <t>↳ niet invullen</t>
         </is>
       </c>
     </row>
@@ -2872,9 +2621,9 @@
           <t>Runner-up:</t>
         </is>
       </c>
-      <c r="E72" s="16" t="inlineStr">
-        <is>
-          <t>↳ automatisch berekend</t>
+      <c r="E72" s="18" t="inlineStr">
+        <is>
+          <t>↳ niet invullen</t>
         </is>
       </c>
       <c r="I72" s="5" t="inlineStr">
@@ -2882,246 +2631,246 @@
           <t>Runner-up:</t>
         </is>
       </c>
-      <c r="M72" s="16" t="inlineStr">
-        <is>
-          <t>↳ automatisch berekend</t>
+      <c r="M72" s="18" t="inlineStr">
+        <is>
+          <t>↳ niet invullen</t>
         </is>
       </c>
     </row>
     <row r="73" ht="6" customHeight="1"/>
     <row r="74" ht="16" customHeight="1">
-      <c r="A74" s="10" t="inlineStr">
-        <is>
-          <t>Groep I</t>
-        </is>
-      </c>
-      <c r="E74" s="11" t="inlineStr">
+      <c r="A74" s="12" t="inlineStr">
+        <is>
+          <t>Groep G</t>
+        </is>
+      </c>
+      <c r="E74" s="13" t="inlineStr">
         <is>
           <t>voorsp.</t>
         </is>
       </c>
-      <c r="F74" s="11" t="inlineStr">
+      <c r="F74" s="13" t="inlineStr">
         <is>
           <t>uitslag</t>
         </is>
       </c>
-      <c r="G74" s="11" t="inlineStr">
+      <c r="G74" s="13" t="inlineStr">
         <is>
           <t>pt.</t>
         </is>
       </c>
-      <c r="I74" s="10" t="inlineStr">
-        <is>
-          <t>Groep J</t>
-        </is>
-      </c>
-      <c r="M74" s="11" t="inlineStr">
+      <c r="I74" s="12" t="inlineStr">
+        <is>
+          <t>Groep H</t>
+        </is>
+      </c>
+      <c r="M74" s="13" t="inlineStr">
         <is>
           <t>voorsp.</t>
         </is>
       </c>
-      <c r="N74" s="11" t="inlineStr">
+      <c r="N74" s="13" t="inlineStr">
         <is>
           <t>uitslag</t>
         </is>
       </c>
-      <c r="O74" s="11" t="inlineStr">
+      <c r="O74" s="13" t="inlineStr">
         <is>
           <t>pt.</t>
         </is>
       </c>
     </row>
     <row r="75" ht="17" customHeight="1">
-      <c r="A75" s="45" t="n"/>
-      <c r="B75" s="13" t="inlineStr">
-        <is>
-          <t>Frankrijk</t>
-        </is>
-      </c>
-      <c r="C75" s="46" t="n"/>
-      <c r="D75" s="15" t="inlineStr">
-        <is>
-          <t>Senegal</t>
+      <c r="A75" s="39" t="n"/>
+      <c r="B75" s="15" t="inlineStr">
+        <is>
+          <t>België</t>
+        </is>
+      </c>
+      <c r="C75" s="40" t="n"/>
+      <c r="D75" s="17" t="inlineStr">
+        <is>
+          <t>Egypte</t>
         </is>
       </c>
       <c r="E75" s="6" t="n"/>
-      <c r="F75" s="16" t="inlineStr"/>
-      <c r="G75" s="16" t="inlineStr"/>
-      <c r="I75" s="47" t="n"/>
-      <c r="J75" s="13" t="inlineStr">
-        <is>
-          <t>Argentinië</t>
-        </is>
-      </c>
-      <c r="K75" s="48" t="n"/>
-      <c r="L75" s="15" t="inlineStr">
-        <is>
-          <t>Algerije</t>
+      <c r="F75" s="18" t="inlineStr"/>
+      <c r="G75" s="18" t="inlineStr"/>
+      <c r="I75" s="41" t="n"/>
+      <c r="J75" s="15" t="inlineStr">
+        <is>
+          <t>Spanje</t>
+        </is>
+      </c>
+      <c r="K75" s="42" t="n"/>
+      <c r="L75" s="17" t="inlineStr">
+        <is>
+          <t>Kaapverdië</t>
         </is>
       </c>
       <c r="M75" s="6" t="n"/>
-      <c r="N75" s="16" t="inlineStr"/>
-      <c r="O75" s="16" t="inlineStr"/>
+      <c r="N75" s="18" t="inlineStr"/>
+      <c r="O75" s="18" t="inlineStr"/>
     </row>
     <row r="76" ht="17" customHeight="1">
-      <c r="A76" s="49" t="n"/>
-      <c r="B76" s="13" t="inlineStr">
-        <is>
-          <t>Noorwegen</t>
-        </is>
-      </c>
-      <c r="C76" s="30" t="n"/>
-      <c r="D76" s="15" t="inlineStr">
-        <is>
-          <t>Irak</t>
+      <c r="A76" s="43" t="n"/>
+      <c r="B76" s="15" t="inlineStr">
+        <is>
+          <t>Iran</t>
+        </is>
+      </c>
+      <c r="C76" s="44" t="n"/>
+      <c r="D76" s="17" t="inlineStr">
+        <is>
+          <t>Nieuw-Zeeland</t>
         </is>
       </c>
       <c r="E76" s="6" t="n"/>
-      <c r="F76" s="16" t="inlineStr"/>
-      <c r="G76" s="16" t="inlineStr"/>
-      <c r="I76" s="50" t="n"/>
-      <c r="J76" s="13" t="inlineStr">
-        <is>
-          <t>Oostenrijk</t>
-        </is>
-      </c>
-      <c r="K76" s="18" t="n"/>
-      <c r="L76" s="15" t="inlineStr">
-        <is>
-          <t>Jordanië</t>
+      <c r="F76" s="18" t="inlineStr"/>
+      <c r="G76" s="18" t="inlineStr"/>
+      <c r="I76" s="45" t="n"/>
+      <c r="J76" s="15" t="inlineStr">
+        <is>
+          <t>Saoedi-Arabië</t>
+        </is>
+      </c>
+      <c r="K76" s="46" t="n"/>
+      <c r="L76" s="17" t="inlineStr">
+        <is>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="M76" s="6" t="n"/>
-      <c r="N76" s="16" t="inlineStr"/>
-      <c r="O76" s="16" t="inlineStr"/>
+      <c r="N76" s="18" t="inlineStr"/>
+      <c r="O76" s="18" t="inlineStr"/>
     </row>
     <row r="77" ht="17" customHeight="1">
-      <c r="A77" s="45" t="n"/>
-      <c r="B77" s="13" t="inlineStr">
-        <is>
-          <t>Frankrijk</t>
-        </is>
-      </c>
-      <c r="C77" s="49" t="n"/>
-      <c r="D77" s="15" t="inlineStr">
-        <is>
-          <t>Noorwegen</t>
+      <c r="A77" s="39" t="n"/>
+      <c r="B77" s="15" t="inlineStr">
+        <is>
+          <t>België</t>
+        </is>
+      </c>
+      <c r="C77" s="43" t="n"/>
+      <c r="D77" s="17" t="inlineStr">
+        <is>
+          <t>Iran</t>
         </is>
       </c>
       <c r="E77" s="6" t="n"/>
-      <c r="F77" s="16" t="inlineStr"/>
-      <c r="G77" s="16" t="inlineStr"/>
-      <c r="I77" s="47" t="n"/>
-      <c r="J77" s="13" t="inlineStr">
-        <is>
-          <t>Argentinië</t>
-        </is>
-      </c>
-      <c r="K77" s="50" t="n"/>
-      <c r="L77" s="15" t="inlineStr">
-        <is>
-          <t>Oostenrijk</t>
+      <c r="F77" s="18" t="inlineStr"/>
+      <c r="G77" s="18" t="inlineStr"/>
+      <c r="I77" s="41" t="n"/>
+      <c r="J77" s="15" t="inlineStr">
+        <is>
+          <t>Spanje</t>
+        </is>
+      </c>
+      <c r="K77" s="45" t="n"/>
+      <c r="L77" s="17" t="inlineStr">
+        <is>
+          <t>Saoedi-Arabië</t>
         </is>
       </c>
       <c r="M77" s="6" t="n"/>
-      <c r="N77" s="16" t="inlineStr"/>
-      <c r="O77" s="16" t="inlineStr"/>
+      <c r="N77" s="18" t="inlineStr"/>
+      <c r="O77" s="18" t="inlineStr"/>
     </row>
     <row r="78" ht="17" customHeight="1">
-      <c r="A78" s="30" t="n"/>
-      <c r="B78" s="13" t="inlineStr">
-        <is>
-          <t>Irak</t>
-        </is>
-      </c>
-      <c r="C78" s="46" t="n"/>
-      <c r="D78" s="15" t="inlineStr">
-        <is>
-          <t>Senegal</t>
+      <c r="A78" s="44" t="n"/>
+      <c r="B78" s="15" t="inlineStr">
+        <is>
+          <t>Nieuw-Zeeland</t>
+        </is>
+      </c>
+      <c r="C78" s="40" t="n"/>
+      <c r="D78" s="17" t="inlineStr">
+        <is>
+          <t>Egypte</t>
         </is>
       </c>
       <c r="E78" s="6" t="n"/>
-      <c r="F78" s="16" t="inlineStr"/>
-      <c r="G78" s="16" t="inlineStr"/>
-      <c r="I78" s="18" t="n"/>
-      <c r="J78" s="13" t="inlineStr">
-        <is>
-          <t>Jordanië</t>
-        </is>
-      </c>
-      <c r="K78" s="48" t="n"/>
-      <c r="L78" s="15" t="inlineStr">
-        <is>
-          <t>Algerije</t>
+      <c r="F78" s="18" t="inlineStr"/>
+      <c r="G78" s="18" t="inlineStr"/>
+      <c r="I78" s="46" t="n"/>
+      <c r="J78" s="15" t="inlineStr">
+        <is>
+          <t>Uruguay</t>
+        </is>
+      </c>
+      <c r="K78" s="42" t="n"/>
+      <c r="L78" s="17" t="inlineStr">
+        <is>
+          <t>Kaapverdië</t>
         </is>
       </c>
       <c r="M78" s="6" t="n"/>
-      <c r="N78" s="16" t="inlineStr"/>
-      <c r="O78" s="16" t="inlineStr"/>
+      <c r="N78" s="18" t="inlineStr"/>
+      <c r="O78" s="18" t="inlineStr"/>
     </row>
     <row r="79" ht="17" customHeight="1">
-      <c r="A79" s="30" t="n"/>
-      <c r="B79" s="13" t="inlineStr">
-        <is>
-          <t>Irak</t>
-        </is>
-      </c>
-      <c r="C79" s="45" t="n"/>
-      <c r="D79" s="15" t="inlineStr">
-        <is>
-          <t>Frankrijk</t>
+      <c r="A79" s="44" t="n"/>
+      <c r="B79" s="15" t="inlineStr">
+        <is>
+          <t>Nieuw-Zeeland</t>
+        </is>
+      </c>
+      <c r="C79" s="39" t="n"/>
+      <c r="D79" s="17" t="inlineStr">
+        <is>
+          <t>België</t>
         </is>
       </c>
       <c r="E79" s="6" t="n"/>
-      <c r="F79" s="16" t="inlineStr"/>
-      <c r="G79" s="16" t="inlineStr"/>
-      <c r="I79" s="18" t="n"/>
-      <c r="J79" s="13" t="inlineStr">
-        <is>
-          <t>Jordanië</t>
-        </is>
-      </c>
-      <c r="K79" s="47" t="n"/>
-      <c r="L79" s="15" t="inlineStr">
-        <is>
-          <t>Argentinië</t>
+      <c r="F79" s="18" t="inlineStr"/>
+      <c r="G79" s="18" t="inlineStr"/>
+      <c r="I79" s="46" t="n"/>
+      <c r="J79" s="15" t="inlineStr">
+        <is>
+          <t>Uruguay</t>
+        </is>
+      </c>
+      <c r="K79" s="41" t="n"/>
+      <c r="L79" s="17" t="inlineStr">
+        <is>
+          <t>Spanje</t>
         </is>
       </c>
       <c r="M79" s="6" t="n"/>
-      <c r="N79" s="16" t="inlineStr"/>
-      <c r="O79" s="16" t="inlineStr"/>
+      <c r="N79" s="18" t="inlineStr"/>
+      <c r="O79" s="18" t="inlineStr"/>
     </row>
     <row r="80" ht="17" customHeight="1">
-      <c r="A80" s="46" t="n"/>
-      <c r="B80" s="13" t="inlineStr">
-        <is>
-          <t>Senegal</t>
-        </is>
-      </c>
-      <c r="C80" s="49" t="n"/>
-      <c r="D80" s="15" t="inlineStr">
-        <is>
-          <t>Noorwegen</t>
+      <c r="A80" s="40" t="n"/>
+      <c r="B80" s="15" t="inlineStr">
+        <is>
+          <t>Egypte</t>
+        </is>
+      </c>
+      <c r="C80" s="43" t="n"/>
+      <c r="D80" s="17" t="inlineStr">
+        <is>
+          <t>Iran</t>
         </is>
       </c>
       <c r="E80" s="6" t="n"/>
-      <c r="F80" s="16" t="inlineStr"/>
-      <c r="G80" s="16" t="inlineStr"/>
-      <c r="I80" s="48" t="n"/>
-      <c r="J80" s="13" t="inlineStr">
-        <is>
-          <t>Algerije</t>
-        </is>
-      </c>
-      <c r="K80" s="50" t="n"/>
-      <c r="L80" s="15" t="inlineStr">
-        <is>
-          <t>Oostenrijk</t>
+      <c r="F80" s="18" t="inlineStr"/>
+      <c r="G80" s="18" t="inlineStr"/>
+      <c r="I80" s="42" t="n"/>
+      <c r="J80" s="15" t="inlineStr">
+        <is>
+          <t>Kaapverdië</t>
+        </is>
+      </c>
+      <c r="K80" s="45" t="n"/>
+      <c r="L80" s="17" t="inlineStr">
+        <is>
+          <t>Saoedi-Arabië</t>
         </is>
       </c>
       <c r="M80" s="6" t="n"/>
-      <c r="N80" s="16" t="inlineStr"/>
-      <c r="O80" s="16" t="inlineStr"/>
+      <c r="N80" s="18" t="inlineStr"/>
+      <c r="O80" s="18" t="inlineStr"/>
     </row>
     <row r="81" ht="17" customHeight="1">
       <c r="A81" s="5" t="inlineStr">
@@ -3129,9 +2878,9 @@
           <t>Groepswinnaar:</t>
         </is>
       </c>
-      <c r="E81" s="16" t="inlineStr">
-        <is>
-          <t>↳ automatisch berekend</t>
+      <c r="E81" s="18" t="inlineStr">
+        <is>
+          <t>↳ niet invullen</t>
         </is>
       </c>
       <c r="I81" s="5" t="inlineStr">
@@ -3139,9 +2888,9 @@
           <t>Groepswinnaar:</t>
         </is>
       </c>
-      <c r="M81" s="16" t="inlineStr">
-        <is>
-          <t>↳ automatisch berekend</t>
+      <c r="M81" s="18" t="inlineStr">
+        <is>
+          <t>↳ niet invullen</t>
         </is>
       </c>
     </row>
@@ -3151,9 +2900,9 @@
           <t>Runner-up:</t>
         </is>
       </c>
-      <c r="E82" s="16" t="inlineStr">
-        <is>
-          <t>↳ automatisch berekend</t>
+      <c r="E82" s="18" t="inlineStr">
+        <is>
+          <t>↳ niet invullen</t>
         </is>
       </c>
       <c r="I82" s="5" t="inlineStr">
@@ -3161,246 +2910,246 @@
           <t>Runner-up:</t>
         </is>
       </c>
-      <c r="M82" s="16" t="inlineStr">
-        <is>
-          <t>↳ automatisch berekend</t>
+      <c r="M82" s="18" t="inlineStr">
+        <is>
+          <t>↳ niet invullen</t>
         </is>
       </c>
     </row>
     <row r="83" ht="6" customHeight="1"/>
     <row r="84" ht="16" customHeight="1">
-      <c r="A84" s="10" t="inlineStr">
-        <is>
-          <t>Groep K</t>
-        </is>
-      </c>
-      <c r="E84" s="11" t="inlineStr">
+      <c r="A84" s="12" t="inlineStr">
+        <is>
+          <t>Groep I</t>
+        </is>
+      </c>
+      <c r="E84" s="13" t="inlineStr">
         <is>
           <t>voorsp.</t>
         </is>
       </c>
-      <c r="F84" s="11" t="inlineStr">
+      <c r="F84" s="13" t="inlineStr">
         <is>
           <t>uitslag</t>
         </is>
       </c>
-      <c r="G84" s="11" t="inlineStr">
+      <c r="G84" s="13" t="inlineStr">
         <is>
           <t>pt.</t>
         </is>
       </c>
-      <c r="I84" s="10" t="inlineStr">
-        <is>
-          <t>Groep L</t>
-        </is>
-      </c>
-      <c r="M84" s="11" t="inlineStr">
+      <c r="I84" s="12" t="inlineStr">
+        <is>
+          <t>Groep J</t>
+        </is>
+      </c>
+      <c r="M84" s="13" t="inlineStr">
         <is>
           <t>voorsp.</t>
         </is>
       </c>
-      <c r="N84" s="11" t="inlineStr">
+      <c r="N84" s="13" t="inlineStr">
         <is>
           <t>uitslag</t>
         </is>
       </c>
-      <c r="O84" s="11" t="inlineStr">
+      <c r="O84" s="13" t="inlineStr">
         <is>
           <t>pt.</t>
         </is>
       </c>
     </row>
     <row r="85" ht="17" customHeight="1">
-      <c r="A85" s="51" t="n"/>
-      <c r="B85" s="13" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="C85" s="52" t="n"/>
-      <c r="D85" s="15" t="inlineStr">
-        <is>
-          <t>DR Congo</t>
+      <c r="A85" s="47" t="n"/>
+      <c r="B85" s="15" t="inlineStr">
+        <is>
+          <t>Frankrijk</t>
+        </is>
+      </c>
+      <c r="C85" s="48" t="n"/>
+      <c r="D85" s="17" t="inlineStr">
+        <is>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="E85" s="6" t="n"/>
-      <c r="F85" s="16" t="inlineStr"/>
-      <c r="G85" s="16" t="inlineStr"/>
-      <c r="I85" s="53" t="n"/>
-      <c r="J85" s="13" t="inlineStr">
-        <is>
-          <t>Engeland</t>
-        </is>
-      </c>
-      <c r="K85" s="54" t="n"/>
-      <c r="L85" s="15" t="inlineStr">
-        <is>
-          <t>Kroatië</t>
+      <c r="F85" s="18" t="inlineStr"/>
+      <c r="G85" s="18" t="inlineStr"/>
+      <c r="I85" s="49" t="n"/>
+      <c r="J85" s="15" t="inlineStr">
+        <is>
+          <t>Argentinië</t>
+        </is>
+      </c>
+      <c r="K85" s="50" t="n"/>
+      <c r="L85" s="17" t="inlineStr">
+        <is>
+          <t>Algerije</t>
         </is>
       </c>
       <c r="M85" s="6" t="n"/>
-      <c r="N85" s="16" t="inlineStr"/>
-      <c r="O85" s="16" t="inlineStr"/>
+      <c r="N85" s="18" t="inlineStr"/>
+      <c r="O85" s="18" t="inlineStr"/>
     </row>
     <row r="86" ht="17" customHeight="1">
-      <c r="A86" s="55" t="n"/>
-      <c r="B86" s="13" t="inlineStr">
-        <is>
-          <t>Oezbekistan</t>
-        </is>
-      </c>
-      <c r="C86" s="56" t="n"/>
-      <c r="D86" s="15" t="inlineStr">
-        <is>
-          <t>Colombia</t>
+      <c r="A86" s="51" t="n"/>
+      <c r="B86" s="15" t="inlineStr">
+        <is>
+          <t>Noorwegen</t>
+        </is>
+      </c>
+      <c r="C86" s="32" t="n"/>
+      <c r="D86" s="17" t="inlineStr">
+        <is>
+          <t>Irak</t>
         </is>
       </c>
       <c r="E86" s="6" t="n"/>
-      <c r="F86" s="16" t="inlineStr"/>
-      <c r="G86" s="16" t="inlineStr"/>
-      <c r="I86" s="57" t="n"/>
-      <c r="J86" s="13" t="inlineStr">
-        <is>
-          <t>Ghana</t>
-        </is>
-      </c>
-      <c r="K86" s="30" t="n"/>
-      <c r="L86" s="15" t="inlineStr">
-        <is>
-          <t>Panama</t>
+      <c r="F86" s="18" t="inlineStr"/>
+      <c r="G86" s="18" t="inlineStr"/>
+      <c r="I86" s="52" t="n"/>
+      <c r="J86" s="15" t="inlineStr">
+        <is>
+          <t>Oostenrijk</t>
+        </is>
+      </c>
+      <c r="K86" s="20" t="n"/>
+      <c r="L86" s="17" t="inlineStr">
+        <is>
+          <t>Jordanië</t>
         </is>
       </c>
       <c r="M86" s="6" t="n"/>
-      <c r="N86" s="16" t="inlineStr"/>
-      <c r="O86" s="16" t="inlineStr"/>
+      <c r="N86" s="18" t="inlineStr"/>
+      <c r="O86" s="18" t="inlineStr"/>
     </row>
     <row r="87" ht="17" customHeight="1">
-      <c r="A87" s="51" t="n"/>
-      <c r="B87" s="13" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="C87" s="55" t="n"/>
-      <c r="D87" s="15" t="inlineStr">
-        <is>
-          <t>Oezbekistan</t>
+      <c r="A87" s="47" t="n"/>
+      <c r="B87" s="15" t="inlineStr">
+        <is>
+          <t>Frankrijk</t>
+        </is>
+      </c>
+      <c r="C87" s="51" t="n"/>
+      <c r="D87" s="17" t="inlineStr">
+        <is>
+          <t>Noorwegen</t>
         </is>
       </c>
       <c r="E87" s="6" t="n"/>
-      <c r="F87" s="16" t="inlineStr"/>
-      <c r="G87" s="16" t="inlineStr"/>
-      <c r="I87" s="53" t="n"/>
-      <c r="J87" s="13" t="inlineStr">
-        <is>
-          <t>Engeland</t>
-        </is>
-      </c>
-      <c r="K87" s="57" t="n"/>
-      <c r="L87" s="15" t="inlineStr">
-        <is>
-          <t>Ghana</t>
+      <c r="F87" s="18" t="inlineStr"/>
+      <c r="G87" s="18" t="inlineStr"/>
+      <c r="I87" s="49" t="n"/>
+      <c r="J87" s="15" t="inlineStr">
+        <is>
+          <t>Argentinië</t>
+        </is>
+      </c>
+      <c r="K87" s="52" t="n"/>
+      <c r="L87" s="17" t="inlineStr">
+        <is>
+          <t>Oostenrijk</t>
         </is>
       </c>
       <c r="M87" s="6" t="n"/>
-      <c r="N87" s="16" t="inlineStr"/>
-      <c r="O87" s="16" t="inlineStr"/>
+      <c r="N87" s="18" t="inlineStr"/>
+      <c r="O87" s="18" t="inlineStr"/>
     </row>
     <row r="88" ht="17" customHeight="1">
-      <c r="A88" s="56" t="n"/>
-      <c r="B88" s="13" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="C88" s="52" t="n"/>
-      <c r="D88" s="15" t="inlineStr">
-        <is>
-          <t>DR Congo</t>
+      <c r="A88" s="32" t="n"/>
+      <c r="B88" s="15" t="inlineStr">
+        <is>
+          <t>Irak</t>
+        </is>
+      </c>
+      <c r="C88" s="48" t="n"/>
+      <c r="D88" s="17" t="inlineStr">
+        <is>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="E88" s="6" t="n"/>
-      <c r="F88" s="16" t="inlineStr"/>
-      <c r="G88" s="16" t="inlineStr"/>
-      <c r="I88" s="30" t="n"/>
-      <c r="J88" s="13" t="inlineStr">
-        <is>
-          <t>Panama</t>
-        </is>
-      </c>
-      <c r="K88" s="54" t="n"/>
-      <c r="L88" s="15" t="inlineStr">
-        <is>
-          <t>Kroatië</t>
+      <c r="F88" s="18" t="inlineStr"/>
+      <c r="G88" s="18" t="inlineStr"/>
+      <c r="I88" s="20" t="n"/>
+      <c r="J88" s="15" t="inlineStr">
+        <is>
+          <t>Jordanië</t>
+        </is>
+      </c>
+      <c r="K88" s="50" t="n"/>
+      <c r="L88" s="17" t="inlineStr">
+        <is>
+          <t>Algerije</t>
         </is>
       </c>
       <c r="M88" s="6" t="n"/>
-      <c r="N88" s="16" t="inlineStr"/>
-      <c r="O88" s="16" t="inlineStr"/>
+      <c r="N88" s="18" t="inlineStr"/>
+      <c r="O88" s="18" t="inlineStr"/>
     </row>
     <row r="89" ht="17" customHeight="1">
-      <c r="A89" s="56" t="n"/>
-      <c r="B89" s="13" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="C89" s="51" t="n"/>
-      <c r="D89" s="15" t="inlineStr">
-        <is>
-          <t>Portugal</t>
+      <c r="A89" s="32" t="n"/>
+      <c r="B89" s="15" t="inlineStr">
+        <is>
+          <t>Irak</t>
+        </is>
+      </c>
+      <c r="C89" s="47" t="n"/>
+      <c r="D89" s="17" t="inlineStr">
+        <is>
+          <t>Frankrijk</t>
         </is>
       </c>
       <c r="E89" s="6" t="n"/>
-      <c r="F89" s="16" t="inlineStr"/>
-      <c r="G89" s="16" t="inlineStr"/>
-      <c r="I89" s="30" t="n"/>
-      <c r="J89" s="13" t="inlineStr">
-        <is>
-          <t>Panama</t>
-        </is>
-      </c>
-      <c r="K89" s="53" t="n"/>
-      <c r="L89" s="15" t="inlineStr">
-        <is>
-          <t>Engeland</t>
+      <c r="F89" s="18" t="inlineStr"/>
+      <c r="G89" s="18" t="inlineStr"/>
+      <c r="I89" s="20" t="n"/>
+      <c r="J89" s="15" t="inlineStr">
+        <is>
+          <t>Jordanië</t>
+        </is>
+      </c>
+      <c r="K89" s="49" t="n"/>
+      <c r="L89" s="17" t="inlineStr">
+        <is>
+          <t>Argentinië</t>
         </is>
       </c>
       <c r="M89" s="6" t="n"/>
-      <c r="N89" s="16" t="inlineStr"/>
-      <c r="O89" s="16" t="inlineStr"/>
+      <c r="N89" s="18" t="inlineStr"/>
+      <c r="O89" s="18" t="inlineStr"/>
     </row>
     <row r="90" ht="17" customHeight="1">
-      <c r="A90" s="52" t="n"/>
-      <c r="B90" s="13" t="inlineStr">
-        <is>
-          <t>DR Congo</t>
-        </is>
-      </c>
-      <c r="C90" s="55" t="n"/>
-      <c r="D90" s="15" t="inlineStr">
-        <is>
-          <t>Oezbekistan</t>
+      <c r="A90" s="48" t="n"/>
+      <c r="B90" s="15" t="inlineStr">
+        <is>
+          <t>Senegal</t>
+        </is>
+      </c>
+      <c r="C90" s="51" t="n"/>
+      <c r="D90" s="17" t="inlineStr">
+        <is>
+          <t>Noorwegen</t>
         </is>
       </c>
       <c r="E90" s="6" t="n"/>
-      <c r="F90" s="16" t="inlineStr"/>
-      <c r="G90" s="16" t="inlineStr"/>
-      <c r="I90" s="54" t="n"/>
-      <c r="J90" s="13" t="inlineStr">
-        <is>
-          <t>Kroatië</t>
-        </is>
-      </c>
-      <c r="K90" s="57" t="n"/>
-      <c r="L90" s="15" t="inlineStr">
-        <is>
-          <t>Ghana</t>
+      <c r="F90" s="18" t="inlineStr"/>
+      <c r="G90" s="18" t="inlineStr"/>
+      <c r="I90" s="50" t="n"/>
+      <c r="J90" s="15" t="inlineStr">
+        <is>
+          <t>Algerije</t>
+        </is>
+      </c>
+      <c r="K90" s="52" t="n"/>
+      <c r="L90" s="17" t="inlineStr">
+        <is>
+          <t>Oostenrijk</t>
         </is>
       </c>
       <c r="M90" s="6" t="n"/>
-      <c r="N90" s="16" t="inlineStr"/>
-      <c r="O90" s="16" t="inlineStr"/>
+      <c r="N90" s="18" t="inlineStr"/>
+      <c r="O90" s="18" t="inlineStr"/>
     </row>
     <row r="91" ht="17" customHeight="1">
       <c r="A91" s="5" t="inlineStr">
@@ -3408,9 +3157,9 @@
           <t>Groepswinnaar:</t>
         </is>
       </c>
-      <c r="E91" s="16" t="inlineStr">
-        <is>
-          <t>↳ automatisch berekend</t>
+      <c r="E91" s="18" t="inlineStr">
+        <is>
+          <t>↳ niet invullen</t>
         </is>
       </c>
       <c r="I91" s="5" t="inlineStr">
@@ -3418,9 +3167,9 @@
           <t>Groepswinnaar:</t>
         </is>
       </c>
-      <c r="M91" s="16" t="inlineStr">
-        <is>
-          <t>↳ automatisch berekend</t>
+      <c r="M91" s="18" t="inlineStr">
+        <is>
+          <t>↳ niet invullen</t>
         </is>
       </c>
     </row>
@@ -3430,9 +3179,9 @@
           <t>Runner-up:</t>
         </is>
       </c>
-      <c r="E92" s="16" t="inlineStr">
-        <is>
-          <t>↳ automatisch berekend</t>
+      <c r="E92" s="18" t="inlineStr">
+        <is>
+          <t>↳ niet invullen</t>
         </is>
       </c>
       <c r="I92" s="5" t="inlineStr">
@@ -3440,1494 +3189,1773 @@
           <t>Runner-up:</t>
         </is>
       </c>
-      <c r="M92" s="16" t="inlineStr">
-        <is>
-          <t>↳ automatisch berekend</t>
+      <c r="M92" s="18" t="inlineStr">
+        <is>
+          <t>↳ niet invullen</t>
         </is>
       </c>
     </row>
     <row r="93" ht="6" customHeight="1"/>
-    <row r="94" ht="8" customHeight="1"/>
-    <row r="95" ht="18" customHeight="1">
-      <c r="A95" s="4" t="inlineStr">
-        <is>
-          <t>▶  BESTE 8 NUMMERS 3  ·  automatisch berekend uit je groepsscores — niets invullen</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="30" customHeight="1">
-      <c r="A96" s="58" t="inlineStr">
-        <is>
-          <t>De 8 beste nummers 3 worden automatisch bepaald op basis van de punten en het doelsaldo van de nummer-3-landen in jouw groepsvoorspellingen. Je hoeft hier zelf niets in te vullen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="8" customHeight="1"/>
-    <row r="98" ht="18" customHeight="1">
-      <c r="A98" s="4" t="inlineStr">
+    <row r="94" ht="16" customHeight="1">
+      <c r="A94" s="12" t="inlineStr">
+        <is>
+          <t>Groep K</t>
+        </is>
+      </c>
+      <c r="E94" s="13" t="inlineStr">
+        <is>
+          <t>voorsp.</t>
+        </is>
+      </c>
+      <c r="F94" s="13" t="inlineStr">
+        <is>
+          <t>uitslag</t>
+        </is>
+      </c>
+      <c r="G94" s="13" t="inlineStr">
+        <is>
+          <t>pt.</t>
+        </is>
+      </c>
+      <c r="I94" s="12" t="inlineStr">
+        <is>
+          <t>Groep L</t>
+        </is>
+      </c>
+      <c r="M94" s="13" t="inlineStr">
+        <is>
+          <t>voorsp.</t>
+        </is>
+      </c>
+      <c r="N94" s="13" t="inlineStr">
+        <is>
+          <t>uitslag</t>
+        </is>
+      </c>
+      <c r="O94" s="13" t="inlineStr">
+        <is>
+          <t>pt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="17" customHeight="1">
+      <c r="A95" s="53" t="n"/>
+      <c r="B95" s="15" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="C95" s="54" t="n"/>
+      <c r="D95" s="17" t="inlineStr">
+        <is>
+          <t>DR Congo</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="n"/>
+      <c r="F95" s="18" t="inlineStr"/>
+      <c r="G95" s="18" t="inlineStr"/>
+      <c r="I95" s="55" t="n"/>
+      <c r="J95" s="15" t="inlineStr">
+        <is>
+          <t>Engeland</t>
+        </is>
+      </c>
+      <c r="K95" s="56" t="n"/>
+      <c r="L95" s="17" t="inlineStr">
+        <is>
+          <t>Kroatië</t>
+        </is>
+      </c>
+      <c r="M95" s="6" t="n"/>
+      <c r="N95" s="18" t="inlineStr"/>
+      <c r="O95" s="18" t="inlineStr"/>
+    </row>
+    <row r="96" ht="17" customHeight="1">
+      <c r="A96" s="57" t="n"/>
+      <c r="B96" s="15" t="inlineStr">
+        <is>
+          <t>Oezbekistan</t>
+        </is>
+      </c>
+      <c r="C96" s="58" t="n"/>
+      <c r="D96" s="17" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="E96" s="6" t="n"/>
+      <c r="F96" s="18" t="inlineStr"/>
+      <c r="G96" s="18" t="inlineStr"/>
+      <c r="I96" s="59" t="n"/>
+      <c r="J96" s="15" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="K96" s="32" t="n"/>
+      <c r="L96" s="17" t="inlineStr">
+        <is>
+          <t>Panama</t>
+        </is>
+      </c>
+      <c r="M96" s="6" t="n"/>
+      <c r="N96" s="18" t="inlineStr"/>
+      <c r="O96" s="18" t="inlineStr"/>
+    </row>
+    <row r="97" ht="17" customHeight="1">
+      <c r="A97" s="53" t="n"/>
+      <c r="B97" s="15" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="C97" s="57" t="n"/>
+      <c r="D97" s="17" t="inlineStr">
+        <is>
+          <t>Oezbekistan</t>
+        </is>
+      </c>
+      <c r="E97" s="6" t="n"/>
+      <c r="F97" s="18" t="inlineStr"/>
+      <c r="G97" s="18" t="inlineStr"/>
+      <c r="I97" s="55" t="n"/>
+      <c r="J97" s="15" t="inlineStr">
+        <is>
+          <t>Engeland</t>
+        </is>
+      </c>
+      <c r="K97" s="59" t="n"/>
+      <c r="L97" s="17" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="M97" s="6" t="n"/>
+      <c r="N97" s="18" t="inlineStr"/>
+      <c r="O97" s="18" t="inlineStr"/>
+    </row>
+    <row r="98" ht="17" customHeight="1">
+      <c r="A98" s="58" t="n"/>
+      <c r="B98" s="15" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="C98" s="54" t="n"/>
+      <c r="D98" s="17" t="inlineStr">
+        <is>
+          <t>DR Congo</t>
+        </is>
+      </c>
+      <c r="E98" s="6" t="n"/>
+      <c r="F98" s="18" t="inlineStr"/>
+      <c r="G98" s="18" t="inlineStr"/>
+      <c r="I98" s="32" t="n"/>
+      <c r="J98" s="15" t="inlineStr">
+        <is>
+          <t>Panama</t>
+        </is>
+      </c>
+      <c r="K98" s="56" t="n"/>
+      <c r="L98" s="17" t="inlineStr">
+        <is>
+          <t>Kroatië</t>
+        </is>
+      </c>
+      <c r="M98" s="6" t="n"/>
+      <c r="N98" s="18" t="inlineStr"/>
+      <c r="O98" s="18" t="inlineStr"/>
+    </row>
+    <row r="99" ht="17" customHeight="1">
+      <c r="A99" s="58" t="n"/>
+      <c r="B99" s="15" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="C99" s="53" t="n"/>
+      <c r="D99" s="17" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E99" s="6" t="n"/>
+      <c r="F99" s="18" t="inlineStr"/>
+      <c r="G99" s="18" t="inlineStr"/>
+      <c r="I99" s="32" t="n"/>
+      <c r="J99" s="15" t="inlineStr">
+        <is>
+          <t>Panama</t>
+        </is>
+      </c>
+      <c r="K99" s="55" t="n"/>
+      <c r="L99" s="17" t="inlineStr">
+        <is>
+          <t>Engeland</t>
+        </is>
+      </c>
+      <c r="M99" s="6" t="n"/>
+      <c r="N99" s="18" t="inlineStr"/>
+      <c r="O99" s="18" t="inlineStr"/>
+    </row>
+    <row r="100" ht="17" customHeight="1">
+      <c r="A100" s="54" t="n"/>
+      <c r="B100" s="15" t="inlineStr">
+        <is>
+          <t>DR Congo</t>
+        </is>
+      </c>
+      <c r="C100" s="57" t="n"/>
+      <c r="D100" s="17" t="inlineStr">
+        <is>
+          <t>Oezbekistan</t>
+        </is>
+      </c>
+      <c r="E100" s="6" t="n"/>
+      <c r="F100" s="18" t="inlineStr"/>
+      <c r="G100" s="18" t="inlineStr"/>
+      <c r="I100" s="56" t="n"/>
+      <c r="J100" s="15" t="inlineStr">
+        <is>
+          <t>Kroatië</t>
+        </is>
+      </c>
+      <c r="K100" s="59" t="n"/>
+      <c r="L100" s="17" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="M100" s="6" t="n"/>
+      <c r="N100" s="18" t="inlineStr"/>
+      <c r="O100" s="18" t="inlineStr"/>
+    </row>
+    <row r="101" ht="17" customHeight="1">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>Groepswinnaar:</t>
+        </is>
+      </c>
+      <c r="E101" s="18" t="inlineStr">
+        <is>
+          <t>↳ niet invullen</t>
+        </is>
+      </c>
+      <c r="I101" s="5" t="inlineStr">
+        <is>
+          <t>Groepswinnaar:</t>
+        </is>
+      </c>
+      <c r="M101" s="18" t="inlineStr">
+        <is>
+          <t>↳ niet invullen</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="17" customHeight="1">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>Runner-up:</t>
+        </is>
+      </c>
+      <c r="E102" s="18" t="inlineStr">
+        <is>
+          <t>↳ niet invullen</t>
+        </is>
+      </c>
+      <c r="I102" s="5" t="inlineStr">
+        <is>
+          <t>Runner-up:</t>
+        </is>
+      </c>
+      <c r="M102" s="18" t="inlineStr">
+        <is>
+          <t>↳ niet invullen</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="6" customHeight="1"/>
+    <row r="104" ht="8" customHeight="1"/>
+    <row r="105" ht="18" customHeight="1">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>▶  BESTE 8 NUMMERS 3  ·  niet invullen — wordt na inlevering door de agent berekend</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="40" customHeight="1">
+      <c r="A106" s="60" t="inlineStr">
+        <is>
+          <t>De 8 beste nummers 3 worden na inlevering van dit formulier automatisch berekend op basis van de punten en het doelsaldo van de nummer-3-landen in jouw groepsscores. De Excel zelf rekent dit NIET uit — je hoeft hier niets in te vullen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="8" customHeight="1"/>
+    <row r="108" ht="18" customHeight="1">
+      <c r="A108" s="4" t="inlineStr">
         <is>
           <t>▶  KNOCK-OUT  ·  grijze vakjes — invullen na de groepsfase, vóór elke ronde</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="16" customHeight="1">
-      <c r="A99" s="59" t="inlineStr">
+    <row r="109" ht="16" customHeight="1">
+      <c r="A109" s="10" t="inlineStr">
         <is>
           <t>Ronde van 32  ·  toto 5 pt / exact +3 pt</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="16" customHeight="1">
-      <c r="A100" s="60" t="inlineStr">
+    <row r="110" ht="16" customHeight="1">
+      <c r="A110" s="61" t="inlineStr">
         <is>
           <t>2A  –  2B</t>
         </is>
       </c>
-      <c r="E100" s="16" t="inlineStr"/>
-      <c r="F100" s="16" t="inlineStr"/>
-      <c r="G100" s="16" t="inlineStr"/>
-    </row>
-    <row r="101" ht="16" customHeight="1">
-      <c r="A101" s="60" t="inlineStr">
+      <c r="E110" s="18" t="inlineStr"/>
+      <c r="F110" s="18" t="inlineStr"/>
+      <c r="G110" s="18" t="inlineStr"/>
+    </row>
+    <row r="111" ht="16" customHeight="1">
+      <c r="A111" s="61" t="inlineStr">
         <is>
           <t>1E  –  3e (A/B/C/D/F)</t>
         </is>
       </c>
-      <c r="E101" s="16" t="inlineStr"/>
-      <c r="F101" s="16" t="inlineStr"/>
-      <c r="G101" s="16" t="inlineStr"/>
-    </row>
-    <row r="102" ht="16" customHeight="1">
-      <c r="A102" s="60" t="inlineStr">
+      <c r="E111" s="18" t="inlineStr"/>
+      <c r="F111" s="18" t="inlineStr"/>
+      <c r="G111" s="18" t="inlineStr"/>
+    </row>
+    <row r="112" ht="16" customHeight="1">
+      <c r="A112" s="61" t="inlineStr">
         <is>
           <t>1F  –  2C</t>
         </is>
       </c>
-      <c r="E102" s="16" t="inlineStr"/>
-      <c r="F102" s="16" t="inlineStr"/>
-      <c r="G102" s="16" t="inlineStr"/>
-    </row>
-    <row r="103" ht="16" customHeight="1">
-      <c r="A103" s="60" t="inlineStr">
+      <c r="E112" s="18" t="inlineStr"/>
+      <c r="F112" s="18" t="inlineStr"/>
+      <c r="G112" s="18" t="inlineStr"/>
+    </row>
+    <row r="113" ht="16" customHeight="1">
+      <c r="A113" s="61" t="inlineStr">
         <is>
           <t>1C  –  2F</t>
         </is>
       </c>
-      <c r="E103" s="16" t="inlineStr"/>
-      <c r="F103" s="16" t="inlineStr"/>
-      <c r="G103" s="16" t="inlineStr"/>
-    </row>
-    <row r="104" ht="16" customHeight="1">
-      <c r="A104" s="60" t="inlineStr">
+      <c r="E113" s="18" t="inlineStr"/>
+      <c r="F113" s="18" t="inlineStr"/>
+      <c r="G113" s="18" t="inlineStr"/>
+    </row>
+    <row r="114" ht="16" customHeight="1">
+      <c r="A114" s="61" t="inlineStr">
         <is>
           <t>1I  –  3e (C/D/F/G/H)</t>
         </is>
       </c>
-      <c r="E104" s="16" t="inlineStr"/>
-      <c r="F104" s="16" t="inlineStr"/>
-      <c r="G104" s="16" t="inlineStr"/>
-    </row>
-    <row r="105" ht="16" customHeight="1">
-      <c r="A105" s="60" t="inlineStr">
+      <c r="E114" s="18" t="inlineStr"/>
+      <c r="F114" s="18" t="inlineStr"/>
+      <c r="G114" s="18" t="inlineStr"/>
+    </row>
+    <row r="115" ht="16" customHeight="1">
+      <c r="A115" s="61" t="inlineStr">
         <is>
           <t>2E  –  2I</t>
         </is>
       </c>
-      <c r="E105" s="16" t="inlineStr"/>
-      <c r="F105" s="16" t="inlineStr"/>
-      <c r="G105" s="16" t="inlineStr"/>
-    </row>
-    <row r="106" ht="16" customHeight="1">
-      <c r="A106" s="60" t="inlineStr">
+      <c r="E115" s="18" t="inlineStr"/>
+      <c r="F115" s="18" t="inlineStr"/>
+      <c r="G115" s="18" t="inlineStr"/>
+    </row>
+    <row r="116" ht="16" customHeight="1">
+      <c r="A116" s="61" t="inlineStr">
         <is>
           <t>1A  –  3e (C/E/F/H/I)</t>
         </is>
       </c>
-      <c r="E106" s="16" t="inlineStr"/>
-      <c r="F106" s="16" t="inlineStr"/>
-      <c r="G106" s="16" t="inlineStr"/>
-    </row>
-    <row r="107" ht="16" customHeight="1">
-      <c r="A107" s="60" t="inlineStr">
+      <c r="E116" s="18" t="inlineStr"/>
+      <c r="F116" s="18" t="inlineStr"/>
+      <c r="G116" s="18" t="inlineStr"/>
+    </row>
+    <row r="117" ht="16" customHeight="1">
+      <c r="A117" s="61" t="inlineStr">
         <is>
           <t>1L  –  3e (E/H/I/J/K)</t>
         </is>
       </c>
-      <c r="E107" s="16" t="inlineStr"/>
-      <c r="F107" s="16" t="inlineStr"/>
-      <c r="G107" s="16" t="inlineStr"/>
-    </row>
-    <row r="108" ht="16" customHeight="1">
-      <c r="A108" s="60" t="inlineStr">
+      <c r="E117" s="18" t="inlineStr"/>
+      <c r="F117" s="18" t="inlineStr"/>
+      <c r="G117" s="18" t="inlineStr"/>
+    </row>
+    <row r="118" ht="16" customHeight="1">
+      <c r="A118" s="61" t="inlineStr">
         <is>
           <t>1D  –  3e (B/E/F/I/J)</t>
         </is>
       </c>
-      <c r="E108" s="16" t="inlineStr"/>
-      <c r="F108" s="16" t="inlineStr"/>
-      <c r="G108" s="16" t="inlineStr"/>
-    </row>
-    <row r="109" ht="16" customHeight="1">
-      <c r="A109" s="60" t="inlineStr">
+      <c r="E118" s="18" t="inlineStr"/>
+      <c r="F118" s="18" t="inlineStr"/>
+      <c r="G118" s="18" t="inlineStr"/>
+    </row>
+    <row r="119" ht="16" customHeight="1">
+      <c r="A119" s="61" t="inlineStr">
         <is>
           <t>1G  –  3e (A/E/H/I/J)</t>
         </is>
       </c>
-      <c r="E109" s="16" t="inlineStr"/>
-      <c r="F109" s="16" t="inlineStr"/>
-      <c r="G109" s="16" t="inlineStr"/>
-    </row>
-    <row r="110" ht="16" customHeight="1">
-      <c r="A110" s="60" t="inlineStr">
+      <c r="E119" s="18" t="inlineStr"/>
+      <c r="F119" s="18" t="inlineStr"/>
+      <c r="G119" s="18" t="inlineStr"/>
+    </row>
+    <row r="120" ht="16" customHeight="1">
+      <c r="A120" s="61" t="inlineStr">
         <is>
           <t>2K  –  2L</t>
         </is>
       </c>
-      <c r="E110" s="16" t="inlineStr"/>
-      <c r="F110" s="16" t="inlineStr"/>
-      <c r="G110" s="16" t="inlineStr"/>
-    </row>
-    <row r="111" ht="16" customHeight="1">
-      <c r="A111" s="60" t="inlineStr">
+      <c r="E120" s="18" t="inlineStr"/>
+      <c r="F120" s="18" t="inlineStr"/>
+      <c r="G120" s="18" t="inlineStr"/>
+    </row>
+    <row r="121" ht="16" customHeight="1">
+      <c r="A121" s="61" t="inlineStr">
         <is>
           <t>1H  –  2J</t>
         </is>
       </c>
-      <c r="E111" s="16" t="inlineStr"/>
-      <c r="F111" s="16" t="inlineStr"/>
-      <c r="G111" s="16" t="inlineStr"/>
-    </row>
-    <row r="112" ht="16" customHeight="1">
-      <c r="A112" s="60" t="inlineStr">
+      <c r="E121" s="18" t="inlineStr"/>
+      <c r="F121" s="18" t="inlineStr"/>
+      <c r="G121" s="18" t="inlineStr"/>
+    </row>
+    <row r="122" ht="16" customHeight="1">
+      <c r="A122" s="61" t="inlineStr">
         <is>
           <t>1B  –  3e (E/F/G/I/J)</t>
         </is>
       </c>
-      <c r="E112" s="16" t="inlineStr"/>
-      <c r="F112" s="16" t="inlineStr"/>
-      <c r="G112" s="16" t="inlineStr"/>
-    </row>
-    <row r="113" ht="16" customHeight="1">
-      <c r="A113" s="60" t="inlineStr">
+      <c r="E122" s="18" t="inlineStr"/>
+      <c r="F122" s="18" t="inlineStr"/>
+      <c r="G122" s="18" t="inlineStr"/>
+    </row>
+    <row r="123" ht="16" customHeight="1">
+      <c r="A123" s="61" t="inlineStr">
         <is>
           <t>1J  –  2H</t>
         </is>
       </c>
-      <c r="E113" s="16" t="inlineStr"/>
-      <c r="F113" s="16" t="inlineStr"/>
-      <c r="G113" s="16" t="inlineStr"/>
-    </row>
-    <row r="114" ht="16" customHeight="1">
-      <c r="A114" s="60" t="inlineStr">
+      <c r="E123" s="18" t="inlineStr"/>
+      <c r="F123" s="18" t="inlineStr"/>
+      <c r="G123" s="18" t="inlineStr"/>
+    </row>
+    <row r="124" ht="16" customHeight="1">
+      <c r="A124" s="61" t="inlineStr">
         <is>
           <t>1K  –  3e (D/E/I/J/L)</t>
         </is>
       </c>
-      <c r="E114" s="16" t="inlineStr"/>
-      <c r="F114" s="16" t="inlineStr"/>
-      <c r="G114" s="16" t="inlineStr"/>
-    </row>
-    <row r="115" ht="16" customHeight="1">
-      <c r="A115" s="60" t="inlineStr">
+      <c r="E124" s="18" t="inlineStr"/>
+      <c r="F124" s="18" t="inlineStr"/>
+      <c r="G124" s="18" t="inlineStr"/>
+    </row>
+    <row r="125" ht="16" customHeight="1">
+      <c r="A125" s="61" t="inlineStr">
         <is>
           <t>2D  –  2G</t>
         </is>
       </c>
-      <c r="E115" s="16" t="inlineStr"/>
-      <c r="F115" s="16" t="inlineStr"/>
-      <c r="G115" s="16" t="inlineStr"/>
-    </row>
-    <row r="116" ht="6" customHeight="1"/>
-    <row r="117" ht="16" customHeight="1">
-      <c r="A117" s="59" t="inlineStr">
-        <is>
-          <t>Ronde van 16  ·  toto 7 pt / exact +4 pt</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="16" customHeight="1">
-      <c r="A118" s="60" t="inlineStr">
-        <is>
-          <t>W32-2  –  W32-5</t>
-        </is>
-      </c>
-      <c r="E118" s="16" t="inlineStr"/>
-      <c r="F118" s="16" t="inlineStr"/>
-      <c r="G118" s="16" t="inlineStr"/>
-    </row>
-    <row r="119" ht="16" customHeight="1">
-      <c r="A119" s="60" t="inlineStr">
-        <is>
-          <t>W32-1  –  W32-3</t>
-        </is>
-      </c>
-      <c r="E119" s="16" t="inlineStr"/>
-      <c r="F119" s="16" t="inlineStr"/>
-      <c r="G119" s="16" t="inlineStr"/>
-    </row>
-    <row r="120" ht="16" customHeight="1">
-      <c r="A120" s="60" t="inlineStr">
-        <is>
-          <t>W32-4  –  W32-6</t>
-        </is>
-      </c>
-      <c r="E120" s="16" t="inlineStr"/>
-      <c r="F120" s="16" t="inlineStr"/>
-      <c r="G120" s="16" t="inlineStr"/>
-    </row>
-    <row r="121" ht="16" customHeight="1">
-      <c r="A121" s="60" t="inlineStr">
-        <is>
-          <t>W32-7  –  W32-8</t>
-        </is>
-      </c>
-      <c r="E121" s="16" t="inlineStr"/>
-      <c r="F121" s="16" t="inlineStr"/>
-      <c r="G121" s="16" t="inlineStr"/>
-    </row>
-    <row r="122" ht="16" customHeight="1">
-      <c r="A122" s="60" t="inlineStr">
-        <is>
-          <t>W32-11  –  W32-12</t>
-        </is>
-      </c>
-      <c r="E122" s="16" t="inlineStr"/>
-      <c r="F122" s="16" t="inlineStr"/>
-      <c r="G122" s="16" t="inlineStr"/>
-    </row>
-    <row r="123" ht="16" customHeight="1">
-      <c r="A123" s="60" t="inlineStr">
-        <is>
-          <t>W32-9  –  W32-10</t>
-        </is>
-      </c>
-      <c r="E123" s="16" t="inlineStr"/>
-      <c r="F123" s="16" t="inlineStr"/>
-      <c r="G123" s="16" t="inlineStr"/>
-    </row>
-    <row r="124" ht="16" customHeight="1">
-      <c r="A124" s="60" t="inlineStr">
-        <is>
-          <t>W32-14  –  W32-16</t>
-        </is>
-      </c>
-      <c r="E124" s="16" t="inlineStr"/>
-      <c r="F124" s="16" t="inlineStr"/>
-      <c r="G124" s="16" t="inlineStr"/>
-    </row>
-    <row r="125" ht="16" customHeight="1">
-      <c r="A125" s="60" t="inlineStr">
-        <is>
-          <t>W32-13  –  W32-15</t>
-        </is>
-      </c>
-      <c r="E125" s="16" t="inlineStr"/>
-      <c r="F125" s="16" t="inlineStr"/>
-      <c r="G125" s="16" t="inlineStr"/>
+      <c r="E125" s="18" t="inlineStr"/>
+      <c r="F125" s="18" t="inlineStr"/>
+      <c r="G125" s="18" t="inlineStr"/>
     </row>
     <row r="126" ht="6" customHeight="1"/>
     <row r="127" ht="16" customHeight="1">
-      <c r="A127" s="59" t="inlineStr">
-        <is>
-          <t>Kwartfinales  ·  toto 9 pt / exact +5 pt</t>
+      <c r="A127" s="10" t="inlineStr">
+        <is>
+          <t>Ronde van 16  ·  toto 7 pt / exact +4 pt</t>
         </is>
       </c>
     </row>
     <row r="128" ht="16" customHeight="1">
-      <c r="A128" s="60" t="inlineStr">
-        <is>
-          <t>W16-1  –  W16-2</t>
-        </is>
-      </c>
-      <c r="E128" s="16" t="inlineStr"/>
-      <c r="F128" s="16" t="inlineStr"/>
-      <c r="G128" s="16" t="inlineStr"/>
+      <c r="A128" s="61" t="inlineStr">
+        <is>
+          <t>W32-2  –  W32-5</t>
+        </is>
+      </c>
+      <c r="E128" s="18" t="inlineStr"/>
+      <c r="F128" s="18" t="inlineStr"/>
+      <c r="G128" s="18" t="inlineStr"/>
     </row>
     <row r="129" ht="16" customHeight="1">
-      <c r="A129" s="60" t="inlineStr">
-        <is>
-          <t>W16-5  –  W16-6</t>
-        </is>
-      </c>
-      <c r="E129" s="16" t="inlineStr"/>
-      <c r="F129" s="16" t="inlineStr"/>
-      <c r="G129" s="16" t="inlineStr"/>
+      <c r="A129" s="61" t="inlineStr">
+        <is>
+          <t>W32-1  –  W32-3</t>
+        </is>
+      </c>
+      <c r="E129" s="18" t="inlineStr"/>
+      <c r="F129" s="18" t="inlineStr"/>
+      <c r="G129" s="18" t="inlineStr"/>
     </row>
     <row r="130" ht="16" customHeight="1">
-      <c r="A130" s="60" t="inlineStr">
-        <is>
-          <t>W16-3  –  W16-4</t>
-        </is>
-      </c>
-      <c r="E130" s="16" t="inlineStr"/>
-      <c r="F130" s="16" t="inlineStr"/>
-      <c r="G130" s="16" t="inlineStr"/>
+      <c r="A130" s="61" t="inlineStr">
+        <is>
+          <t>W32-4  –  W32-6</t>
+        </is>
+      </c>
+      <c r="E130" s="18" t="inlineStr"/>
+      <c r="F130" s="18" t="inlineStr"/>
+      <c r="G130" s="18" t="inlineStr"/>
     </row>
     <row r="131" ht="16" customHeight="1">
-      <c r="A131" s="60" t="inlineStr">
-        <is>
-          <t>W16-7  –  W16-8</t>
-        </is>
-      </c>
-      <c r="E131" s="16" t="inlineStr"/>
-      <c r="F131" s="16" t="inlineStr"/>
-      <c r="G131" s="16" t="inlineStr"/>
-    </row>
-    <row r="132" ht="6" customHeight="1"/>
+      <c r="A131" s="61" t="inlineStr">
+        <is>
+          <t>W32-7  –  W32-8</t>
+        </is>
+      </c>
+      <c r="E131" s="18" t="inlineStr"/>
+      <c r="F131" s="18" t="inlineStr"/>
+      <c r="G131" s="18" t="inlineStr"/>
+    </row>
+    <row r="132" ht="16" customHeight="1">
+      <c r="A132" s="61" t="inlineStr">
+        <is>
+          <t>W32-11  –  W32-12</t>
+        </is>
+      </c>
+      <c r="E132" s="18" t="inlineStr"/>
+      <c r="F132" s="18" t="inlineStr"/>
+      <c r="G132" s="18" t="inlineStr"/>
+    </row>
     <row r="133" ht="16" customHeight="1">
-      <c r="A133" s="59" t="inlineStr">
-        <is>
-          <t>Halve finales  ·  toto 11 pt / exact +6 pt</t>
-        </is>
-      </c>
+      <c r="A133" s="61" t="inlineStr">
+        <is>
+          <t>W32-9  –  W32-10</t>
+        </is>
+      </c>
+      <c r="E133" s="18" t="inlineStr"/>
+      <c r="F133" s="18" t="inlineStr"/>
+      <c r="G133" s="18" t="inlineStr"/>
     </row>
     <row r="134" ht="16" customHeight="1">
-      <c r="A134" s="60" t="inlineStr">
-        <is>
-          <t>WKF-1  –  WKF-2</t>
-        </is>
-      </c>
-      <c r="E134" s="16" t="inlineStr"/>
-      <c r="F134" s="16" t="inlineStr"/>
-      <c r="G134" s="16" t="inlineStr"/>
+      <c r="A134" s="61" t="inlineStr">
+        <is>
+          <t>W32-14  –  W32-16</t>
+        </is>
+      </c>
+      <c r="E134" s="18" t="inlineStr"/>
+      <c r="F134" s="18" t="inlineStr"/>
+      <c r="G134" s="18" t="inlineStr"/>
     </row>
     <row r="135" ht="16" customHeight="1">
-      <c r="A135" s="60" t="inlineStr">
-        <is>
-          <t>WKF-3  –  WKF-4</t>
-        </is>
-      </c>
-      <c r="E135" s="16" t="inlineStr"/>
-      <c r="F135" s="16" t="inlineStr"/>
-      <c r="G135" s="16" t="inlineStr"/>
+      <c r="A135" s="61" t="inlineStr">
+        <is>
+          <t>W32-13  –  W32-15</t>
+        </is>
+      </c>
+      <c r="E135" s="18" t="inlineStr"/>
+      <c r="F135" s="18" t="inlineStr"/>
+      <c r="G135" s="18" t="inlineStr"/>
     </row>
     <row r="136" ht="6" customHeight="1"/>
     <row r="137" ht="16" customHeight="1">
-      <c r="A137" s="59" t="inlineStr">
+      <c r="A137" s="10" t="inlineStr">
+        <is>
+          <t>Kwartfinales  ·  toto 9 pt / exact +5 pt</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="16" customHeight="1">
+      <c r="A138" s="61" t="inlineStr">
+        <is>
+          <t>W16-1  –  W16-2</t>
+        </is>
+      </c>
+      <c r="E138" s="18" t="inlineStr"/>
+      <c r="F138" s="18" t="inlineStr"/>
+      <c r="G138" s="18" t="inlineStr"/>
+    </row>
+    <row r="139" ht="16" customHeight="1">
+      <c r="A139" s="61" t="inlineStr">
+        <is>
+          <t>W16-5  –  W16-6</t>
+        </is>
+      </c>
+      <c r="E139" s="18" t="inlineStr"/>
+      <c r="F139" s="18" t="inlineStr"/>
+      <c r="G139" s="18" t="inlineStr"/>
+    </row>
+    <row r="140" ht="16" customHeight="1">
+      <c r="A140" s="61" t="inlineStr">
+        <is>
+          <t>W16-3  –  W16-4</t>
+        </is>
+      </c>
+      <c r="E140" s="18" t="inlineStr"/>
+      <c r="F140" s="18" t="inlineStr"/>
+      <c r="G140" s="18" t="inlineStr"/>
+    </row>
+    <row r="141" ht="16" customHeight="1">
+      <c r="A141" s="61" t="inlineStr">
+        <is>
+          <t>W16-7  –  W16-8</t>
+        </is>
+      </c>
+      <c r="E141" s="18" t="inlineStr"/>
+      <c r="F141" s="18" t="inlineStr"/>
+      <c r="G141" s="18" t="inlineStr"/>
+    </row>
+    <row r="142" ht="6" customHeight="1"/>
+    <row r="143" ht="16" customHeight="1">
+      <c r="A143" s="10" t="inlineStr">
+        <is>
+          <t>Halve finales  ·  toto 11 pt / exact +6 pt</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="16" customHeight="1">
+      <c r="A144" s="61" t="inlineStr">
+        <is>
+          <t>WKF-1  –  WKF-2</t>
+        </is>
+      </c>
+      <c r="E144" s="18" t="inlineStr"/>
+      <c r="F144" s="18" t="inlineStr"/>
+      <c r="G144" s="18" t="inlineStr"/>
+    </row>
+    <row r="145" ht="16" customHeight="1">
+      <c r="A145" s="61" t="inlineStr">
+        <is>
+          <t>WKF-3  –  WKF-4</t>
+        </is>
+      </c>
+      <c r="E145" s="18" t="inlineStr"/>
+      <c r="F145" s="18" t="inlineStr"/>
+      <c r="G145" s="18" t="inlineStr"/>
+    </row>
+    <row r="146" ht="6" customHeight="1"/>
+    <row r="147" ht="16" customHeight="1">
+      <c r="A147" s="10" t="inlineStr">
         <is>
           <t>Finale  ·  toto 13 pt / exact +7 pt</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="16" customHeight="1">
-      <c r="A138" s="60" t="inlineStr">
+    <row r="148" ht="16" customHeight="1">
+      <c r="A148" s="61" t="inlineStr">
         <is>
           <t>WHF-1  –  WHF-2</t>
         </is>
       </c>
-      <c r="E138" s="16" t="inlineStr"/>
-      <c r="F138" s="16" t="inlineStr"/>
-      <c r="G138" s="16" t="inlineStr"/>
-    </row>
-    <row r="139" ht="6" customHeight="1"/>
-    <row r="140" ht="8" customHeight="1"/>
-    <row r="141" ht="18" customHeight="1">
-      <c r="A141" s="4" t="inlineStr">
+      <c r="E148" s="18" t="inlineStr"/>
+      <c r="F148" s="18" t="inlineStr"/>
+      <c r="G148" s="18" t="inlineStr"/>
+    </row>
+    <row r="149" ht="6" customHeight="1"/>
+    <row r="150" ht="8" customHeight="1"/>
+    <row r="151" ht="18" customHeight="1">
+      <c r="A151" s="4" t="inlineStr">
         <is>
           <t>▶  VERRASSING — kies een land BUITEN de top-12 · punten schalen met ranking en ronde</t>
         </is>
       </c>
     </row>
-    <row r="142" ht="14" customHeight="1">
-      <c r="A142" s="11" t="inlineStr">
+    <row r="152" ht="14" customHeight="1">
+      <c r="A152" s="13" t="inlineStr">
         <is>
           <t>Land (outsider)</t>
         </is>
       </c>
-      <c r="E142" s="11" t="inlineStr">
+      <c r="E152" s="13" t="inlineStr">
         <is>
           <t>R16</t>
         </is>
       </c>
-      <c r="F142" s="11" t="inlineStr">
+      <c r="F152" s="13" t="inlineStr">
         <is>
           <t>KF</t>
         </is>
       </c>
-      <c r="G142" s="11" t="inlineStr">
+      <c r="G152" s="13" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="H142" s="11" t="inlineStr">
+      <c r="H152" s="13" t="inlineStr">
         <is>
           <t>Finale</t>
         </is>
       </c>
-      <c r="I142" s="11" t="inlineStr">
+      <c r="I152" s="13" t="inlineStr">
         <is>
           <t>Winnaar</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="15" customHeight="1">
-      <c r="A143" s="13" t="inlineStr">
+    <row r="153" ht="15" customHeight="1">
+      <c r="A153" s="15" t="inlineStr">
         <is>
           <t>Senegal</t>
         </is>
       </c>
-      <c r="E143" s="61" t="n">
+      <c r="E153" s="62" t="n">
         <v>7</v>
       </c>
-      <c r="F143" s="61" t="n">
+      <c r="F153" s="62" t="n">
         <v>12</v>
       </c>
-      <c r="G143" s="61" t="n">
+      <c r="G153" s="62" t="n">
         <v>19</v>
       </c>
-      <c r="H143" s="61" t="n">
+      <c r="H153" s="62" t="n">
         <v>26</v>
       </c>
-      <c r="I143" s="61" t="n">
+      <c r="I153" s="62" t="n">
         <v>34</v>
       </c>
     </row>
-    <row r="144" ht="15" customHeight="1">
-      <c r="A144" s="13" t="inlineStr">
+    <row r="154" ht="15" customHeight="1">
+      <c r="A154" s="15" t="inlineStr">
         <is>
           <t>Mexico</t>
         </is>
       </c>
-      <c r="E144" s="61" t="n">
+      <c r="E154" s="62" t="n">
         <v>7</v>
       </c>
-      <c r="F144" s="61" t="n">
+      <c r="F154" s="62" t="n">
         <v>13</v>
       </c>
-      <c r="G144" s="61" t="n">
+      <c r="G154" s="62" t="n">
         <v>19</v>
       </c>
-      <c r="H144" s="61" t="n">
+      <c r="H154" s="62" t="n">
         <v>27</v>
       </c>
-      <c r="I144" s="61" t="n">
+      <c r="I154" s="62" t="n">
         <v>35</v>
       </c>
     </row>
-    <row r="145" ht="15" customHeight="1">
-      <c r="A145" s="13" t="inlineStr">
+    <row r="155" ht="15" customHeight="1">
+      <c r="A155" s="15" t="inlineStr">
         <is>
           <t>Verenigde Staten</t>
         </is>
       </c>
-      <c r="E145" s="61" t="n">
+      <c r="E155" s="62" t="n">
         <v>8</v>
       </c>
-      <c r="F145" s="61" t="n">
+      <c r="F155" s="62" t="n">
         <v>13</v>
       </c>
-      <c r="G145" s="61" t="n">
+      <c r="G155" s="62" t="n">
         <v>20</v>
       </c>
-      <c r="H145" s="61" t="n">
+      <c r="H155" s="62" t="n">
         <v>27</v>
       </c>
-      <c r="I145" s="61" t="n">
+      <c r="I155" s="62" t="n">
         <v>36</v>
       </c>
     </row>
-    <row r="146" ht="15" customHeight="1">
-      <c r="A146" s="13" t="inlineStr">
+    <row r="156" ht="15" customHeight="1">
+      <c r="A156" s="15" t="inlineStr">
         <is>
           <t>Uruguay</t>
         </is>
       </c>
-      <c r="E146" s="61" t="n">
+      <c r="E156" s="62" t="n">
         <v>8</v>
       </c>
-      <c r="F146" s="61" t="n">
+      <c r="F156" s="62" t="n">
         <v>14</v>
       </c>
-      <c r="G146" s="61" t="n">
+      <c r="G156" s="62" t="n">
         <v>20</v>
       </c>
-      <c r="H146" s="61" t="n">
+      <c r="H156" s="62" t="n">
         <v>28</v>
       </c>
-      <c r="I146" s="61" t="n">
+      <c r="I156" s="62" t="n">
         <v>37</v>
       </c>
     </row>
-    <row r="147" ht="15" customHeight="1">
-      <c r="A147" s="13" t="inlineStr">
+    <row r="157" ht="15" customHeight="1">
+      <c r="A157" s="15" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="E147" s="61" t="n">
+      <c r="E157" s="62" t="n">
         <v>8</v>
       </c>
-      <c r="F147" s="61" t="n">
+      <c r="F157" s="62" t="n">
         <v>14</v>
       </c>
-      <c r="G147" s="61" t="n">
+      <c r="G157" s="62" t="n">
         <v>21</v>
       </c>
-      <c r="H147" s="61" t="n">
+      <c r="H157" s="62" t="n">
         <v>29</v>
       </c>
-      <c r="I147" s="61" t="n">
+      <c r="I157" s="62" t="n">
         <v>38</v>
       </c>
     </row>
-    <row r="148" ht="15" customHeight="1">
-      <c r="A148" s="13" t="inlineStr">
+    <row r="158" ht="15" customHeight="1">
+      <c r="A158" s="15" t="inlineStr">
         <is>
           <t>Zwitserland</t>
         </is>
       </c>
-      <c r="E148" s="61" t="n">
+      <c r="E158" s="62" t="n">
         <v>8</v>
       </c>
-      <c r="F148" s="61" t="n">
+      <c r="F158" s="62" t="n">
         <v>14</v>
       </c>
-      <c r="G148" s="61" t="n">
+      <c r="G158" s="62" t="n">
         <v>21</v>
       </c>
-      <c r="H148" s="61" t="n">
+      <c r="H158" s="62" t="n">
         <v>30</v>
       </c>
-      <c r="I148" s="61" t="n">
+      <c r="I158" s="62" t="n">
         <v>39</v>
       </c>
     </row>
-    <row r="149" ht="15" customHeight="1">
-      <c r="A149" s="13" t="inlineStr">
+    <row r="159" ht="15" customHeight="1">
+      <c r="A159" s="15" t="inlineStr">
         <is>
           <t>Iran</t>
         </is>
       </c>
-      <c r="E149" s="61" t="n">
+      <c r="E159" s="62" t="n">
         <v>9</v>
       </c>
-      <c r="F149" s="61" t="n">
+      <c r="F159" s="62" t="n">
         <v>15</v>
       </c>
-      <c r="G149" s="61" t="n">
+      <c r="G159" s="62" t="n">
         <v>22</v>
       </c>
-      <c r="H149" s="61" t="n">
+      <c r="H159" s="62" t="n">
         <v>31</v>
       </c>
-      <c r="I149" s="61" t="n">
+      <c r="I159" s="62" t="n">
         <v>41</v>
       </c>
     </row>
-    <row r="150" ht="15" customHeight="1">
-      <c r="A150" s="13" t="inlineStr">
+    <row r="160" ht="15" customHeight="1">
+      <c r="A160" s="15" t="inlineStr">
         <is>
           <t>Oostenrijk</t>
         </is>
       </c>
-      <c r="E150" s="61" t="n">
+      <c r="E160" s="62" t="n">
         <v>9</v>
       </c>
-      <c r="F150" s="61" t="n">
+      <c r="F160" s="62" t="n">
         <v>15</v>
       </c>
-      <c r="G150" s="61" t="n">
+      <c r="G160" s="62" t="n">
         <v>23</v>
       </c>
-      <c r="H150" s="61" t="n">
+      <c r="H160" s="62" t="n">
         <v>32</v>
       </c>
-      <c r="I150" s="61" t="n">
+      <c r="I160" s="62" t="n">
         <v>42</v>
       </c>
     </row>
-    <row r="151" ht="15" customHeight="1">
-      <c r="A151" s="13" t="inlineStr">
+    <row r="161" ht="15" customHeight="1">
+      <c r="A161" s="15" t="inlineStr">
         <is>
           <t>Zuid-Korea</t>
         </is>
       </c>
-      <c r="E151" s="61" t="n">
+      <c r="E161" s="62" t="n">
         <v>9</v>
       </c>
-      <c r="F151" s="61" t="n">
+      <c r="F161" s="62" t="n">
         <v>16</v>
       </c>
-      <c r="G151" s="61" t="n">
+      <c r="G161" s="62" t="n">
         <v>23</v>
       </c>
-      <c r="H151" s="61" t="n">
+      <c r="H161" s="62" t="n">
         <v>32</v>
       </c>
-      <c r="I151" s="61" t="n">
+      <c r="I161" s="62" t="n">
         <v>43</v>
       </c>
     </row>
-    <row r="152" ht="15" customHeight="1">
-      <c r="A152" s="13" t="inlineStr">
+    <row r="162" ht="15" customHeight="1">
+      <c r="A162" s="15" t="inlineStr">
         <is>
           <t>Australië</t>
         </is>
       </c>
-      <c r="E152" s="61" t="n">
+      <c r="E162" s="62" t="n">
         <v>9</v>
       </c>
-      <c r="F152" s="61" t="n">
+      <c r="F162" s="62" t="n">
         <v>16</v>
       </c>
-      <c r="G152" s="61" t="n">
+      <c r="G162" s="62" t="n">
         <v>24</v>
       </c>
-      <c r="H152" s="61" t="n">
+      <c r="H162" s="62" t="n">
         <v>33</v>
       </c>
-      <c r="I152" s="61" t="n">
+      <c r="I162" s="62" t="n">
         <v>43</v>
       </c>
     </row>
-    <row r="153" ht="15" customHeight="1">
-      <c r="A153" s="13" t="inlineStr">
+    <row r="163" ht="15" customHeight="1">
+      <c r="A163" s="15" t="inlineStr">
         <is>
           <t>Ecuador</t>
         </is>
       </c>
-      <c r="E153" s="61" t="n">
+      <c r="E163" s="62" t="n">
         <v>9</v>
       </c>
-      <c r="F153" s="61" t="n">
+      <c r="F163" s="62" t="n">
         <v>16</v>
       </c>
-      <c r="G153" s="61" t="n">
+      <c r="G163" s="62" t="n">
         <v>24</v>
       </c>
-      <c r="H153" s="61" t="n">
+      <c r="H163" s="62" t="n">
         <v>34</v>
       </c>
-      <c r="I153" s="61" t="n">
+      <c r="I163" s="62" t="n">
         <v>44</v>
       </c>
     </row>
-    <row r="154" ht="15" customHeight="1">
-      <c r="A154" s="13" t="inlineStr">
+    <row r="164" ht="15" customHeight="1">
+      <c r="A164" s="15" t="inlineStr">
         <is>
           <t>Noorwegen</t>
         </is>
       </c>
-      <c r="E154" s="61" t="n">
+      <c r="E164" s="62" t="n">
         <v>10</v>
       </c>
-      <c r="F154" s="61" t="n">
+      <c r="F164" s="62" t="n">
         <v>16</v>
       </c>
-      <c r="G154" s="61" t="n">
+      <c r="G164" s="62" t="n">
         <v>25</v>
       </c>
-      <c r="H154" s="61" t="n">
+      <c r="H164" s="62" t="n">
         <v>34</v>
       </c>
-      <c r="I154" s="61" t="n">
+      <c r="I164" s="62" t="n">
         <v>45</v>
       </c>
     </row>
-    <row r="155" ht="15" customHeight="1">
-      <c r="A155" s="13" t="inlineStr">
+    <row r="165" ht="15" customHeight="1">
+      <c r="A165" s="15" t="inlineStr">
         <is>
           <t>Panama</t>
         </is>
       </c>
-      <c r="E155" s="61" t="n">
+      <c r="E165" s="62" t="n">
         <v>10</v>
       </c>
-      <c r="F155" s="61" t="n">
+      <c r="F165" s="62" t="n">
         <v>17</v>
       </c>
-      <c r="G155" s="61" t="n">
+      <c r="G165" s="62" t="n">
         <v>26</v>
       </c>
-      <c r="H155" s="61" t="n">
+      <c r="H165" s="62" t="n">
         <v>36</v>
       </c>
-      <c r="I155" s="61" t="n">
+      <c r="I165" s="62" t="n">
         <v>48</v>
       </c>
     </row>
-    <row r="156" ht="15" customHeight="1">
-      <c r="A156" s="13" t="inlineStr">
+    <row r="166" ht="15" customHeight="1">
+      <c r="A166" s="15" t="inlineStr">
         <is>
           <t>Egypte</t>
         </is>
       </c>
-      <c r="E156" s="61" t="n">
+      <c r="E166" s="62" t="n">
         <v>10</v>
       </c>
-      <c r="F156" s="61" t="n">
+      <c r="F166" s="62" t="n">
         <v>18</v>
       </c>
-      <c r="G156" s="61" t="n">
+      <c r="G166" s="62" t="n">
         <v>27</v>
       </c>
-      <c r="H156" s="61" t="n">
+      <c r="H166" s="62" t="n">
         <v>37</v>
       </c>
-      <c r="I156" s="61" t="n">
+      <c r="I166" s="62" t="n">
         <v>49</v>
       </c>
     </row>
-    <row r="157" ht="15" customHeight="1">
-      <c r="A157" s="13" t="inlineStr">
+    <row r="167" ht="15" customHeight="1">
+      <c r="A167" s="15" t="inlineStr">
         <is>
           <t>Algerije</t>
         </is>
       </c>
-      <c r="E157" s="61" t="n">
+      <c r="E167" s="62" t="n">
         <v>11</v>
       </c>
-      <c r="F157" s="61" t="n">
+      <c r="F167" s="62" t="n">
         <v>19</v>
       </c>
-      <c r="G157" s="61" t="n">
+      <c r="G167" s="62" t="n">
         <v>28</v>
       </c>
-      <c r="H157" s="61" t="n">
+      <c r="H167" s="62" t="n">
         <v>40</v>
       </c>
-      <c r="I157" s="61" t="n">
+      <c r="I167" s="62" t="n">
         <v>52</v>
       </c>
     </row>
-    <row r="158" ht="15" customHeight="1">
-      <c r="A158" s="13" t="inlineStr">
+    <row r="168" ht="15" customHeight="1">
+      <c r="A168" s="15" t="inlineStr">
         <is>
           <t>Paraguay</t>
         </is>
       </c>
-      <c r="E158" s="61" t="n">
+      <c r="E168" s="62" t="n">
         <v>11</v>
       </c>
-      <c r="F158" s="61" t="n">
+      <c r="F168" s="62" t="n">
         <v>19</v>
       </c>
-      <c r="G158" s="61" t="n">
+      <c r="G168" s="62" t="n">
         <v>29</v>
       </c>
-      <c r="H158" s="61" t="n">
+      <c r="H168" s="62" t="n">
         <v>41</v>
       </c>
-      <c r="I158" s="61" t="n">
+      <c r="I168" s="62" t="n">
         <v>53</v>
       </c>
     </row>
-    <row r="159" ht="15" customHeight="1">
-      <c r="A159" s="13" t="inlineStr">
+    <row r="169" ht="15" customHeight="1">
+      <c r="A169" s="15" t="inlineStr">
         <is>
           <t>Ivoorkust</t>
         </is>
       </c>
-      <c r="E159" s="61" t="n">
+      <c r="E169" s="62" t="n">
         <v>12</v>
       </c>
-      <c r="F159" s="61" t="n">
+      <c r="F169" s="62" t="n">
         <v>20</v>
       </c>
-      <c r="G159" s="61" t="n">
+      <c r="G169" s="62" t="n">
         <v>30</v>
       </c>
-      <c r="H159" s="61" t="n">
+      <c r="H169" s="62" t="n">
         <v>41</v>
       </c>
-      <c r="I159" s="61" t="n">
+      <c r="I169" s="62" t="n">
         <v>55</v>
       </c>
     </row>
-    <row r="160" ht="15" customHeight="1">
-      <c r="A160" s="13" t="inlineStr">
+    <row r="170" ht="15" customHeight="1">
+      <c r="A170" s="15" t="inlineStr">
         <is>
           <t>Tunesië</t>
         </is>
       </c>
-      <c r="E160" s="61" t="n">
+      <c r="E170" s="62" t="n">
         <v>12</v>
       </c>
-      <c r="F160" s="61" t="n">
+      <c r="F170" s="62" t="n">
         <v>20</v>
       </c>
-      <c r="G160" s="61" t="n">
+      <c r="G170" s="62" t="n">
         <v>30</v>
       </c>
-      <c r="H160" s="61" t="n">
+      <c r="H170" s="62" t="n">
         <v>42</v>
       </c>
-      <c r="I160" s="61" t="n">
+      <c r="I170" s="62" t="n">
         <v>55</v>
       </c>
     </row>
-    <row r="161" ht="15" customHeight="1">
-      <c r="A161" s="13" t="inlineStr">
+    <row r="171" ht="15" customHeight="1">
+      <c r="A171" s="15" t="inlineStr">
         <is>
           <t>Schotland</t>
         </is>
       </c>
-      <c r="E161" s="61" t="n">
+      <c r="E171" s="62" t="n">
         <v>12</v>
       </c>
-      <c r="F161" s="61" t="n">
+      <c r="F171" s="62" t="n">
         <v>20</v>
       </c>
-      <c r="G161" s="61" t="n">
+      <c r="G171" s="62" t="n">
         <v>31</v>
       </c>
-      <c r="H161" s="61" t="n">
+      <c r="H171" s="62" t="n">
         <v>42</v>
       </c>
-      <c r="I161" s="61" t="n">
+      <c r="I171" s="62" t="n">
         <v>56</v>
       </c>
     </row>
-    <row r="162" ht="15" customHeight="1">
-      <c r="A162" s="13" t="inlineStr">
+    <row r="172" ht="15" customHeight="1">
+      <c r="A172" s="15" t="inlineStr">
         <is>
           <t>Zweden</t>
         </is>
       </c>
-      <c r="E162" s="61" t="n">
+      <c r="E172" s="62" t="n">
         <v>12</v>
       </c>
-      <c r="F162" s="61" t="n">
+      <c r="F172" s="62" t="n">
         <v>21</v>
       </c>
-      <c r="G162" s="61" t="n">
+      <c r="G172" s="62" t="n">
         <v>31</v>
       </c>
-      <c r="H162" s="61" t="n">
+      <c r="H172" s="62" t="n">
         <v>43</v>
       </c>
-      <c r="I162" s="61" t="n">
+      <c r="I172" s="62" t="n">
         <v>57</v>
       </c>
     </row>
-    <row r="163" ht="15" customHeight="1">
-      <c r="A163" s="13" t="inlineStr">
+    <row r="173" ht="15" customHeight="1">
+      <c r="A173" s="15" t="inlineStr">
         <is>
           <t>Tsjechië</t>
         </is>
       </c>
-      <c r="E163" s="61" t="n">
+      <c r="E173" s="62" t="n">
         <v>12</v>
       </c>
-      <c r="F163" s="61" t="n">
+      <c r="F173" s="62" t="n">
         <v>21</v>
       </c>
-      <c r="G163" s="61" t="n">
+      <c r="G173" s="62" t="n">
         <v>31</v>
       </c>
-      <c r="H163" s="61" t="n">
+      <c r="H173" s="62" t="n">
         <v>43</v>
       </c>
-      <c r="I163" s="61" t="n">
+      <c r="I173" s="62" t="n">
         <v>57</v>
       </c>
     </row>
-    <row r="164" ht="15" customHeight="1">
-      <c r="A164" s="13" t="inlineStr">
+    <row r="174" ht="15" customHeight="1">
+      <c r="A174" s="15" t="inlineStr">
         <is>
           <t>Qatar</t>
         </is>
       </c>
-      <c r="E164" s="61" t="n">
+      <c r="E174" s="62" t="n">
         <v>13</v>
       </c>
-      <c r="F164" s="61" t="n">
+      <c r="F174" s="62" t="n">
         <v>22</v>
       </c>
-      <c r="G164" s="61" t="n">
+      <c r="G174" s="62" t="n">
         <v>33</v>
       </c>
-      <c r="H164" s="61" t="n">
+      <c r="H174" s="62" t="n">
         <v>46</v>
       </c>
-      <c r="I164" s="61" t="n">
+      <c r="I174" s="62" t="n">
         <v>61</v>
       </c>
     </row>
-    <row r="165" ht="15" customHeight="1">
-      <c r="A165" s="13" t="inlineStr">
+    <row r="175" ht="15" customHeight="1">
+      <c r="A175" s="15" t="inlineStr">
         <is>
           <t>Oezbekistan</t>
         </is>
       </c>
-      <c r="E165" s="61" t="n">
+      <c r="E175" s="62" t="n">
         <v>13</v>
       </c>
-      <c r="F165" s="61" t="n">
+      <c r="F175" s="62" t="n">
         <v>23</v>
       </c>
-      <c r="G165" s="61" t="n">
+      <c r="G175" s="62" t="n">
         <v>34</v>
       </c>
-      <c r="H165" s="61" t="n">
+      <c r="H175" s="62" t="n">
         <v>47</v>
       </c>
-      <c r="I165" s="61" t="n">
+      <c r="I175" s="62" t="n">
         <v>63</v>
       </c>
     </row>
-    <row r="166" ht="15" customHeight="1">
-      <c r="A166" s="13" t="inlineStr">
+    <row r="176" ht="15" customHeight="1">
+      <c r="A176" s="15" t="inlineStr">
         <is>
           <t>DR Congo</t>
         </is>
       </c>
-      <c r="E166" s="61" t="n">
+      <c r="E176" s="62" t="n">
         <v>14</v>
       </c>
-      <c r="F166" s="61" t="n">
+      <c r="F176" s="62" t="n">
         <v>23</v>
       </c>
-      <c r="G166" s="61" t="n">
+      <c r="G176" s="62" t="n">
         <v>35</v>
       </c>
-      <c r="H166" s="61" t="n">
+      <c r="H176" s="62" t="n">
         <v>48</v>
       </c>
-      <c r="I166" s="61" t="n">
+      <c r="I176" s="62" t="n">
         <v>64</v>
       </c>
     </row>
-    <row r="167" ht="15" customHeight="1">
-      <c r="A167" s="13" t="inlineStr">
+    <row r="177" ht="15" customHeight="1">
+      <c r="A177" s="15" t="inlineStr">
         <is>
           <t>Saoedi-Arabië</t>
         </is>
       </c>
-      <c r="E167" s="61" t="n">
+      <c r="E177" s="62" t="n">
         <v>14</v>
       </c>
-      <c r="F167" s="61" t="n">
+      <c r="F177" s="62" t="n">
         <v>24</v>
       </c>
-      <c r="G167" s="61" t="n">
+      <c r="G177" s="62" t="n">
         <v>35</v>
       </c>
-      <c r="H167" s="61" t="n">
+      <c r="H177" s="62" t="n">
         <v>49</v>
       </c>
-      <c r="I167" s="61" t="n">
+      <c r="I177" s="62" t="n">
         <v>65</v>
       </c>
     </row>
-    <row r="168" ht="15" customHeight="1">
-      <c r="A168" s="13" t="inlineStr">
+    <row r="178" ht="15" customHeight="1">
+      <c r="A178" s="15" t="inlineStr">
         <is>
           <t>Irak</t>
         </is>
       </c>
-      <c r="E168" s="61" t="n">
+      <c r="E178" s="62" t="n">
         <v>14</v>
       </c>
-      <c r="F168" s="61" t="n">
+      <c r="F178" s="62" t="n">
         <v>24</v>
       </c>
-      <c r="G168" s="61" t="n">
+      <c r="G178" s="62" t="n">
         <v>36</v>
       </c>
-      <c r="H168" s="61" t="n">
+      <c r="H178" s="62" t="n">
         <v>49</v>
       </c>
-      <c r="I168" s="61" t="n">
+      <c r="I178" s="62" t="n">
         <v>65</v>
       </c>
     </row>
-    <row r="169" ht="15" customHeight="1">
-      <c r="A169" s="13" t="inlineStr">
+    <row r="179" ht="15" customHeight="1">
+      <c r="A179" s="15" t="inlineStr">
         <is>
           <t>Zuid-Afrika</t>
         </is>
       </c>
-      <c r="E169" s="61" t="n">
+      <c r="E179" s="62" t="n">
         <v>14</v>
       </c>
-      <c r="F169" s="61" t="n">
+      <c r="F179" s="62" t="n">
         <v>24</v>
       </c>
-      <c r="G169" s="61" t="n">
+      <c r="G179" s="62" t="n">
         <v>36</v>
       </c>
-      <c r="H169" s="61" t="n">
+      <c r="H179" s="62" t="n">
         <v>50</v>
       </c>
-      <c r="I169" s="61" t="n">
+      <c r="I179" s="62" t="n">
         <v>66</v>
       </c>
     </row>
-    <row r="170" ht="15" customHeight="1">
-      <c r="A170" s="13" t="inlineStr">
+    <row r="180" ht="15" customHeight="1">
+      <c r="A180" s="15" t="inlineStr">
         <is>
           <t>Jordanië</t>
         </is>
       </c>
-      <c r="E170" s="61" t="n">
+      <c r="E180" s="62" t="n">
         <v>14</v>
       </c>
-      <c r="F170" s="61" t="n">
+      <c r="F180" s="62" t="n">
         <v>25</v>
       </c>
-      <c r="G170" s="61" t="n">
+      <c r="G180" s="62" t="n">
         <v>37</v>
       </c>
-      <c r="H170" s="61" t="n">
+      <c r="H180" s="62" t="n">
         <v>51</v>
       </c>
-      <c r="I170" s="61" t="n">
+      <c r="I180" s="62" t="n">
         <v>68</v>
       </c>
     </row>
-    <row r="171" ht="15" customHeight="1">
-      <c r="A171" s="13" t="inlineStr">
+    <row r="181" ht="15" customHeight="1">
+      <c r="A181" s="15" t="inlineStr">
         <is>
           <t>Kaapverdië</t>
         </is>
       </c>
-      <c r="E171" s="61" t="n">
+      <c r="E181" s="62" t="n">
         <v>15</v>
       </c>
-      <c r="F171" s="61" t="n">
+      <c r="F181" s="62" t="n">
         <v>26</v>
       </c>
-      <c r="G171" s="61" t="n">
+      <c r="G181" s="62" t="n">
         <v>38</v>
       </c>
-      <c r="H171" s="61" t="n">
+      <c r="H181" s="62" t="n">
         <v>53</v>
       </c>
-      <c r="I171" s="61" t="n">
+      <c r="I181" s="62" t="n">
         <v>70</v>
       </c>
     </row>
-    <row r="172" ht="15" customHeight="1">
-      <c r="A172" s="13" t="inlineStr">
+    <row r="182" ht="15" customHeight="1">
+      <c r="A182" s="15" t="inlineStr">
         <is>
           <t>Ghana</t>
         </is>
       </c>
-      <c r="E172" s="61" t="n">
+      <c r="E182" s="62" t="n">
         <v>15</v>
       </c>
-      <c r="F172" s="61" t="n">
+      <c r="F182" s="62" t="n">
         <v>26</v>
       </c>
-      <c r="G172" s="61" t="n">
+      <c r="G182" s="62" t="n">
         <v>39</v>
       </c>
-      <c r="H172" s="61" t="n">
+      <c r="H182" s="62" t="n">
         <v>54</v>
       </c>
-      <c r="I172" s="61" t="n">
+      <c r="I182" s="62" t="n">
         <v>72</v>
       </c>
     </row>
-    <row r="173" ht="15" customHeight="1">
-      <c r="A173" s="13" t="inlineStr">
+    <row r="183" ht="15" customHeight="1">
+      <c r="A183" s="15" t="inlineStr">
         <is>
           <t>Bosnië-Herzegovina</t>
         </is>
       </c>
-      <c r="E173" s="61" t="n">
+      <c r="E183" s="62" t="n">
         <v>15</v>
       </c>
-      <c r="F173" s="61" t="n">
+      <c r="F183" s="62" t="n">
         <v>26</v>
       </c>
-      <c r="G173" s="61" t="n">
+      <c r="G183" s="62" t="n">
         <v>39</v>
       </c>
-      <c r="H173" s="61" t="n">
+      <c r="H183" s="62" t="n">
         <v>55</v>
       </c>
-      <c r="I173" s="61" t="n">
+      <c r="I183" s="62" t="n">
         <v>72</v>
       </c>
     </row>
-    <row r="174" ht="15" customHeight="1">
-      <c r="A174" s="13" t="inlineStr">
+    <row r="184" ht="15" customHeight="1">
+      <c r="A184" s="15" t="inlineStr">
         <is>
           <t>Haïti</t>
         </is>
       </c>
-      <c r="E174" s="61" t="n">
+      <c r="E184" s="62" t="n">
         <v>16</v>
       </c>
-      <c r="F174" s="61" t="n">
+      <c r="F184" s="62" t="n">
         <v>28</v>
       </c>
-      <c r="G174" s="61" t="n">
+      <c r="G184" s="62" t="n">
         <v>41</v>
       </c>
-      <c r="H174" s="61" t="n">
+      <c r="H184" s="62" t="n">
         <v>58</v>
       </c>
-      <c r="I174" s="61" t="n">
+      <c r="I184" s="62" t="n">
         <v>76</v>
       </c>
     </row>
-    <row r="175" ht="15" customHeight="1">
-      <c r="A175" s="13" t="inlineStr">
+    <row r="185" ht="15" customHeight="1">
+      <c r="A185" s="15" t="inlineStr">
         <is>
           <t>Nieuw-Zeeland</t>
         </is>
       </c>
-      <c r="E175" s="61" t="n">
+      <c r="E185" s="62" t="n">
         <v>16</v>
       </c>
-      <c r="F175" s="61" t="n">
+      <c r="F185" s="62" t="n">
         <v>28</v>
       </c>
-      <c r="G175" s="61" t="n">
+      <c r="G185" s="62" t="n">
         <v>42</v>
       </c>
-      <c r="H175" s="61" t="n">
+      <c r="H185" s="62" t="n">
         <v>59</v>
       </c>
-      <c r="I175" s="61" t="n">
+      <c r="I185" s="62" t="n">
         <v>77</v>
       </c>
     </row>
-    <row r="176" ht="15" customHeight="1">
-      <c r="A176" s="13" t="inlineStr">
+    <row r="186" ht="15" customHeight="1">
+      <c r="A186" s="15" t="inlineStr">
         <is>
           <t>Curaçao</t>
         </is>
       </c>
-      <c r="E176" s="61" t="n">
+      <c r="E186" s="62" t="n">
         <v>17</v>
       </c>
-      <c r="F176" s="61" t="n">
+      <c r="F186" s="62" t="n">
         <v>29</v>
       </c>
-      <c r="G176" s="61" t="n">
+      <c r="G186" s="62" t="n">
         <v>43</v>
       </c>
-      <c r="H176" s="61" t="n">
+      <c r="H186" s="62" t="n">
         <v>60</v>
       </c>
-      <c r="I176" s="61" t="n">
+      <c r="I186" s="62" t="n">
         <v>79</v>
       </c>
     </row>
-    <row r="177" ht="15" customHeight="1">
-      <c r="A177" s="13" t="inlineStr">
+    <row r="187" ht="15" customHeight="1">
+      <c r="A187" s="15" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="E177" s="61" t="n">
+      <c r="E187" s="62" t="n">
         <v>13</v>
       </c>
-      <c r="F177" s="61" t="n">
+      <c r="F187" s="62" t="n">
         <v>22</v>
       </c>
-      <c r="G177" s="61" t="n">
+      <c r="G187" s="62" t="n">
         <v>33</v>
       </c>
-      <c r="H177" s="61" t="n">
+      <c r="H187" s="62" t="n">
         <v>46</v>
       </c>
-      <c r="I177" s="61" t="n">
+      <c r="I187" s="62" t="n">
         <v>61</v>
       </c>
     </row>
-    <row r="178" ht="15" customHeight="1">
-      <c r="A178" s="13" t="inlineStr">
+    <row r="188" ht="15" customHeight="1">
+      <c r="A188" s="15" t="inlineStr">
         <is>
           <t>Turkije</t>
         </is>
       </c>
-      <c r="E178" s="61" t="n">
+      <c r="E188" s="62" t="n">
         <v>13</v>
       </c>
-      <c r="F178" s="61" t="n">
+      <c r="F188" s="62" t="n">
         <v>22</v>
       </c>
-      <c r="G178" s="61" t="n">
+      <c r="G188" s="62" t="n">
         <v>33</v>
       </c>
-      <c r="H178" s="61" t="n">
+      <c r="H188" s="62" t="n">
         <v>46</v>
       </c>
-      <c r="I178" s="61" t="n">
+      <c r="I188" s="62" t="n">
         <v>61</v>
       </c>
     </row>
-    <row r="179" ht="8" customHeight="1"/>
-    <row r="180" ht="18" customHeight="1">
-      <c r="A180" s="4" t="inlineStr">
+    <row r="189" ht="8" customHeight="1"/>
+    <row r="190" ht="18" customHeight="1">
+      <c r="A190" s="4" t="inlineStr">
         <is>
           <t>▶  DECEPTIE — kies een land UIT de top-12 · punten schalen met ranking en uitvalsronde</t>
         </is>
       </c>
     </row>
-    <row r="181" ht="14" customHeight="1">
-      <c r="A181" s="11" t="inlineStr">
+    <row r="191" ht="14" customHeight="1">
+      <c r="A191" s="13" t="inlineStr">
         <is>
           <t>Land (favoriet)</t>
         </is>
       </c>
-      <c r="E181" s="11" t="inlineStr">
+      <c r="E191" s="13" t="inlineStr">
         <is>
           <t>KF</t>
         </is>
       </c>
-      <c r="F181" s="11" t="inlineStr">
+      <c r="F191" s="13" t="inlineStr">
         <is>
           <t>R16</t>
         </is>
       </c>
-      <c r="G181" s="11" t="inlineStr">
+      <c r="G191" s="13" t="inlineStr">
         <is>
           <t>R32</t>
         </is>
       </c>
-      <c r="H181" s="11" t="inlineStr">
+      <c r="H191" s="13" t="inlineStr">
         <is>
           <t>Groep eruit</t>
         </is>
       </c>
     </row>
-    <row r="182" ht="15" customHeight="1">
-      <c r="A182" s="13" t="inlineStr">
+    <row r="192" ht="15" customHeight="1">
+      <c r="A192" s="15" t="inlineStr">
         <is>
           <t>Frankrijk</t>
         </is>
       </c>
-      <c r="E182" s="61" t="n">
+      <c r="E192" s="62" t="n">
         <v>8</v>
       </c>
-      <c r="F182" s="61" t="n">
+      <c r="F192" s="62" t="n">
         <v>14</v>
       </c>
-      <c r="G182" s="61" t="n">
+      <c r="G192" s="62" t="n">
         <v>20</v>
       </c>
-      <c r="H182" s="61" t="n">
+      <c r="H192" s="62" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="183" ht="15" customHeight="1">
-      <c r="A183" s="13" t="inlineStr">
+    <row r="193" ht="15" customHeight="1">
+      <c r="A193" s="15" t="inlineStr">
         <is>
           <t>Spanje</t>
         </is>
       </c>
-      <c r="E183" s="61" t="n">
+      <c r="E193" s="62" t="n">
         <v>7</v>
       </c>
-      <c r="F183" s="61" t="n">
+      <c r="F193" s="62" t="n">
         <v>13</v>
       </c>
-      <c r="G183" s="61" t="n">
+      <c r="G193" s="62" t="n">
         <v>19</v>
       </c>
-      <c r="H183" s="61" t="n">
+      <c r="H193" s="62" t="n">
         <v>28</v>
       </c>
     </row>
-    <row r="184" ht="15" customHeight="1">
-      <c r="A184" s="13" t="inlineStr">
+    <row r="194" ht="15" customHeight="1">
+      <c r="A194" s="15" t="inlineStr">
         <is>
           <t>Argentinië</t>
         </is>
       </c>
-      <c r="E184" s="61" t="n">
+      <c r="E194" s="62" t="n">
         <v>6</v>
       </c>
-      <c r="F184" s="61" t="n">
+      <c r="F194" s="62" t="n">
         <v>12</v>
       </c>
-      <c r="G184" s="61" t="n">
+      <c r="G194" s="62" t="n">
         <v>17</v>
       </c>
-      <c r="H184" s="61" t="n">
+      <c r="H194" s="62" t="n">
         <v>26</v>
       </c>
     </row>
-    <row r="185" ht="15" customHeight="1">
-      <c r="A185" s="13" t="inlineStr">
+    <row r="195" ht="15" customHeight="1">
+      <c r="A195" s="15" t="inlineStr">
         <is>
           <t>Engeland</t>
         </is>
       </c>
-      <c r="E185" s="61" t="n">
+      <c r="E195" s="62" t="n">
         <v>6</v>
       </c>
-      <c r="F185" s="61" t="n">
+      <c r="F195" s="62" t="n">
         <v>11</v>
       </c>
-      <c r="G185" s="61" t="n">
+      <c r="G195" s="62" t="n">
         <v>16</v>
       </c>
-      <c r="H185" s="61" t="n">
+      <c r="H195" s="62" t="n">
         <v>24</v>
       </c>
     </row>
-    <row r="186" ht="15" customHeight="1">
-      <c r="A186" s="13" t="inlineStr">
+    <row r="196" ht="15" customHeight="1">
+      <c r="A196" s="15" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="E186" s="61" t="n">
+      <c r="E196" s="62" t="n">
         <v>6</v>
       </c>
-      <c r="F186" s="61" t="n">
+      <c r="F196" s="62" t="n">
         <v>10</v>
       </c>
-      <c r="G186" s="61" t="n">
+      <c r="G196" s="62" t="n">
         <v>15</v>
       </c>
-      <c r="H186" s="61" t="n">
+      <c r="H196" s="62" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="187" ht="15" customHeight="1">
-      <c r="A187" s="13" t="inlineStr">
+    <row r="197" ht="15" customHeight="1">
+      <c r="A197" s="15" t="inlineStr">
         <is>
           <t>Brazilië</t>
         </is>
       </c>
-      <c r="E187" s="61" t="n">
+      <c r="E197" s="62" t="n">
         <v>5</v>
       </c>
-      <c r="F187" s="61" t="n">
+      <c r="F197" s="62" t="n">
         <v>9</v>
       </c>
-      <c r="G187" s="61" t="n">
+      <c r="G197" s="62" t="n">
         <v>13</v>
       </c>
-      <c r="H187" s="61" t="n">
+      <c r="H197" s="62" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="188" ht="15" customHeight="1">
-      <c r="A188" s="13" t="inlineStr">
+    <row r="198" ht="15" customHeight="1">
+      <c r="A198" s="15" t="inlineStr">
         <is>
           <t>Nederland</t>
         </is>
       </c>
-      <c r="E188" s="61" t="n">
+      <c r="E198" s="62" t="n">
         <v>4</v>
       </c>
-      <c r="F188" s="61" t="n">
+      <c r="F198" s="62" t="n">
         <v>8</v>
       </c>
-      <c r="G188" s="61" t="n">
+      <c r="G198" s="62" t="n">
         <v>12</v>
       </c>
-      <c r="H188" s="61" t="n">
+      <c r="H198" s="62" t="n">
         <v>18</v>
       </c>
     </row>
-    <row r="189" ht="15" customHeight="1">
-      <c r="A189" s="13" t="inlineStr">
+    <row r="199" ht="15" customHeight="1">
+      <c r="A199" s="15" t="inlineStr">
         <is>
           <t>Marokko</t>
         </is>
       </c>
-      <c r="E189" s="61" t="n">
+      <c r="E199" s="62" t="n">
         <v>4</v>
       </c>
-      <c r="F189" s="61" t="n">
+      <c r="F199" s="62" t="n">
         <v>7</v>
       </c>
-      <c r="G189" s="61" t="n">
+      <c r="G199" s="62" t="n">
         <v>11</v>
       </c>
-      <c r="H189" s="61" t="n">
+      <c r="H199" s="62" t="n">
         <v>16</v>
       </c>
     </row>
-    <row r="190" ht="15" customHeight="1">
-      <c r="A190" s="13" t="inlineStr">
+    <row r="200" ht="15" customHeight="1">
+      <c r="A200" s="15" t="inlineStr">
         <is>
           <t>België</t>
         </is>
       </c>
-      <c r="E190" s="61" t="n">
+      <c r="E200" s="62" t="n">
         <v>4</v>
       </c>
-      <c r="F190" s="61" t="n">
+      <c r="F200" s="62" t="n">
         <v>6</v>
       </c>
-      <c r="G190" s="61" t="n">
+      <c r="G200" s="62" t="n">
         <v>9</v>
       </c>
-      <c r="H190" s="61" t="n">
+      <c r="H200" s="62" t="n">
         <v>14</v>
       </c>
     </row>
-    <row r="191" ht="15" customHeight="1">
-      <c r="A191" s="13" t="inlineStr">
+    <row r="201" ht="15" customHeight="1">
+      <c r="A201" s="15" t="inlineStr">
         <is>
           <t>Duitsland</t>
         </is>
       </c>
-      <c r="E191" s="61" t="n">
+      <c r="E201" s="62" t="n">
         <v>3</v>
       </c>
-      <c r="F191" s="61" t="n">
+      <c r="F201" s="62" t="n">
         <v>6</v>
       </c>
-      <c r="G191" s="61" t="n">
+      <c r="G201" s="62" t="n">
         <v>8</v>
       </c>
-      <c r="H191" s="61" t="n">
+      <c r="H201" s="62" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="192" ht="15" customHeight="1">
-      <c r="A192" s="13" t="inlineStr">
+    <row r="202" ht="15" customHeight="1">
+      <c r="A202" s="15" t="inlineStr">
         <is>
           <t>Kroatië</t>
         </is>
       </c>
-      <c r="E192" s="61" t="n">
+      <c r="E202" s="62" t="n">
         <v>2</v>
       </c>
-      <c r="F192" s="61" t="n">
+      <c r="F202" s="62" t="n">
         <v>5</v>
       </c>
-      <c r="G192" s="61" t="n">
+      <c r="G202" s="62" t="n">
         <v>7</v>
       </c>
-      <c r="H192" s="61" t="n">
+      <c r="H202" s="62" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="193" ht="15" customHeight="1">
-      <c r="A193" s="13" t="inlineStr">
+    <row r="203" ht="15" customHeight="1">
+      <c r="A203" s="15" t="inlineStr">
         <is>
           <t>Colombia</t>
         </is>
       </c>
-      <c r="E193" s="61" t="n">
+      <c r="E203" s="62" t="n">
         <v>2</v>
       </c>
-      <c r="F193" s="61" t="n">
+      <c r="F203" s="62" t="n">
         <v>3</v>
       </c>
-      <c r="G193" s="61" t="n">
+      <c r="G203" s="62" t="n">
         <v>4</v>
       </c>
-      <c r="H193" s="61" t="n">
+      <c r="H203" s="62" t="n">
         <v>6</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="192">
+  <mergeCells count="200">
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A150:D150"/>
+    <mergeCell ref="B41:O41"/>
+    <mergeCell ref="B35:O35"/>
     <mergeCell ref="A144:D144"/>
     <mergeCell ref="A159:D159"/>
     <mergeCell ref="A122:D122"/>
     <mergeCell ref="A72:D72"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="A133:O133"/>
+    <mergeCell ref="B25:O25"/>
     <mergeCell ref="A134:D134"/>
+    <mergeCell ref="A200:D200"/>
     <mergeCell ref="A81:D81"/>
-    <mergeCell ref="E24:O24"/>
     <mergeCell ref="A112:D112"/>
     <mergeCell ref="A152:D152"/>
     <mergeCell ref="A121:D121"/>
@@ -4935,178 +4963,186 @@
     <mergeCell ref="A161:D161"/>
     <mergeCell ref="A3:O3"/>
     <mergeCell ref="A44:D44"/>
-    <mergeCell ref="A95:O95"/>
-    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="B27:O27"/>
+    <mergeCell ref="A202:D202"/>
     <mergeCell ref="A176:D176"/>
     <mergeCell ref="A114:D114"/>
     <mergeCell ref="E1:F1"/>
-    <mergeCell ref="M41:O41"/>
     <mergeCell ref="A64:D64"/>
     <mergeCell ref="I81:L81"/>
+    <mergeCell ref="A32:O32"/>
     <mergeCell ref="A186:D186"/>
-    <mergeCell ref="A24:D24"/>
     <mergeCell ref="A51:D51"/>
-    <mergeCell ref="A107:D107"/>
     <mergeCell ref="A178:D178"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="A106:O106"/>
     <mergeCell ref="E81:G81"/>
-    <mergeCell ref="A96:O96"/>
+    <mergeCell ref="A38:O38"/>
     <mergeCell ref="A13:O13"/>
     <mergeCell ref="A124:D124"/>
+    <mergeCell ref="B29:O29"/>
     <mergeCell ref="A54:D54"/>
     <mergeCell ref="A7:D7"/>
-    <mergeCell ref="E27:O27"/>
-    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="B37:O37"/>
     <mergeCell ref="A172:D172"/>
+    <mergeCell ref="A40:O40"/>
     <mergeCell ref="A164:D164"/>
-    <mergeCell ref="A108:D108"/>
     <mergeCell ref="A15:O15"/>
-    <mergeCell ref="E42:G42"/>
-    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A24:O24"/>
     <mergeCell ref="A154:D154"/>
-    <mergeCell ref="A149:D149"/>
     <mergeCell ref="M52:O52"/>
     <mergeCell ref="A163:D163"/>
     <mergeCell ref="A101:D101"/>
     <mergeCell ref="E92:G92"/>
-    <mergeCell ref="E22:O22"/>
-    <mergeCell ref="A42:D42"/>
+    <mergeCell ref="A195:D195"/>
     <mergeCell ref="I52:L52"/>
     <mergeCell ref="A188:D188"/>
+    <mergeCell ref="A141:D141"/>
     <mergeCell ref="A16:O16"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="A99:O99"/>
     <mergeCell ref="A135:D135"/>
     <mergeCell ref="I44:L44"/>
     <mergeCell ref="A62:D62"/>
+    <mergeCell ref="A108:O108"/>
     <mergeCell ref="A125:D125"/>
-    <mergeCell ref="A190:D190"/>
     <mergeCell ref="A18:O18"/>
-    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="I94:L94"/>
+    <mergeCell ref="A117:D117"/>
+    <mergeCell ref="E6:G6"/>
     <mergeCell ref="A111:D111"/>
-    <mergeCell ref="E23:O23"/>
+    <mergeCell ref="A199:D199"/>
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="I84:L84"/>
     <mergeCell ref="A167:D167"/>
-    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A151:O151"/>
     <mergeCell ref="E61:G61"/>
-    <mergeCell ref="A141:O141"/>
-    <mergeCell ref="A142:D142"/>
     <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A22:O22"/>
     <mergeCell ref="A182:D182"/>
     <mergeCell ref="A191:D191"/>
     <mergeCell ref="A169:D169"/>
     <mergeCell ref="M72:O72"/>
     <mergeCell ref="I61:L61"/>
     <mergeCell ref="E72:G72"/>
-    <mergeCell ref="E41:G41"/>
     <mergeCell ref="A61:D61"/>
+    <mergeCell ref="A190:O190"/>
+    <mergeCell ref="A28:O28"/>
     <mergeCell ref="A153:D153"/>
     <mergeCell ref="A162:D162"/>
     <mergeCell ref="M71:O71"/>
     <mergeCell ref="I54:L54"/>
     <mergeCell ref="A128:D128"/>
     <mergeCell ref="I72:L72"/>
-    <mergeCell ref="I41:L41"/>
     <mergeCell ref="A127:O127"/>
     <mergeCell ref="A177:D177"/>
-    <mergeCell ref="E26:O26"/>
+    <mergeCell ref="A30:O30"/>
     <mergeCell ref="E71:G71"/>
     <mergeCell ref="A192:D192"/>
     <mergeCell ref="I71:L71"/>
     <mergeCell ref="A74:D74"/>
-    <mergeCell ref="A105:D105"/>
-    <mergeCell ref="A98:O98"/>
     <mergeCell ref="A145:D145"/>
-    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A139:D139"/>
+    <mergeCell ref="E8:G8"/>
     <mergeCell ref="G1:K1"/>
-    <mergeCell ref="E25:O25"/>
+    <mergeCell ref="A179:D179"/>
     <mergeCell ref="A71:D71"/>
     <mergeCell ref="E82:G82"/>
     <mergeCell ref="A129:D129"/>
-    <mergeCell ref="I42:L42"/>
+    <mergeCell ref="A194:D194"/>
+    <mergeCell ref="A203:D203"/>
+    <mergeCell ref="A116:D116"/>
     <mergeCell ref="A181:D181"/>
+    <mergeCell ref="E10:G10"/>
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="A91:D91"/>
     <mergeCell ref="A137:O137"/>
     <mergeCell ref="A131:D131"/>
     <mergeCell ref="I82:L82"/>
-    <mergeCell ref="A100:D100"/>
     <mergeCell ref="A184:D184"/>
+    <mergeCell ref="A140:D140"/>
     <mergeCell ref="A171:D171"/>
-    <mergeCell ref="A109:D109"/>
     <mergeCell ref="A52:D52"/>
     <mergeCell ref="A165:D165"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="A180:D180"/>
+    <mergeCell ref="B31:O31"/>
     <mergeCell ref="A10:D10"/>
     <mergeCell ref="A115:D115"/>
     <mergeCell ref="A155:D155"/>
     <mergeCell ref="A102:D102"/>
     <mergeCell ref="A173:D173"/>
+    <mergeCell ref="E11:G11"/>
     <mergeCell ref="I74:L74"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="M42:O42"/>
-    <mergeCell ref="A143:D143"/>
-    <mergeCell ref="E29:O29"/>
-    <mergeCell ref="A33:O33"/>
+    <mergeCell ref="B39:O39"/>
     <mergeCell ref="A92:D92"/>
     <mergeCell ref="A157:D157"/>
     <mergeCell ref="A166:D166"/>
     <mergeCell ref="M61:O61"/>
     <mergeCell ref="A17:O17"/>
+    <mergeCell ref="B23:O23"/>
     <mergeCell ref="M62:O62"/>
+    <mergeCell ref="A109:O109"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="E31:O31"/>
-    <mergeCell ref="A103:D103"/>
-    <mergeCell ref="A180:O180"/>
+    <mergeCell ref="A94:D94"/>
     <mergeCell ref="A168:D168"/>
+    <mergeCell ref="E102:G102"/>
     <mergeCell ref="A19:O19"/>
-    <mergeCell ref="A117:O117"/>
+    <mergeCell ref="A34:O34"/>
+    <mergeCell ref="A133:D133"/>
+    <mergeCell ref="A143:O143"/>
     <mergeCell ref="A193:D193"/>
     <mergeCell ref="E62:G62"/>
     <mergeCell ref="A120:D120"/>
-    <mergeCell ref="A104:D104"/>
+    <mergeCell ref="A36:O36"/>
+    <mergeCell ref="E4:G4"/>
     <mergeCell ref="A113:D113"/>
     <mergeCell ref="I62:L62"/>
     <mergeCell ref="M51:O51"/>
     <mergeCell ref="M82:O82"/>
     <mergeCell ref="E51:G51"/>
     <mergeCell ref="A185:D185"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A106:D106"/>
     <mergeCell ref="I64:L64"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="I51:L51"/>
-    <mergeCell ref="A147:D147"/>
     <mergeCell ref="A156:D156"/>
     <mergeCell ref="A170:D170"/>
     <mergeCell ref="A21:O21"/>
-    <mergeCell ref="I34:L34"/>
+    <mergeCell ref="A105:O105"/>
+    <mergeCell ref="A26:O26"/>
+    <mergeCell ref="A130:D130"/>
     <mergeCell ref="A14:O14"/>
-    <mergeCell ref="A130:D130"/>
+    <mergeCell ref="M101:O101"/>
+    <mergeCell ref="A201:D201"/>
     <mergeCell ref="A148:D148"/>
     <mergeCell ref="A82:D82"/>
-    <mergeCell ref="E28:O28"/>
+    <mergeCell ref="E101:G101"/>
     <mergeCell ref="M91:O91"/>
     <mergeCell ref="E91:G91"/>
     <mergeCell ref="A123:D123"/>
     <mergeCell ref="A138:D138"/>
+    <mergeCell ref="A147:O147"/>
+    <mergeCell ref="A132:D132"/>
+    <mergeCell ref="A197:D197"/>
     <mergeCell ref="A110:D110"/>
-    <mergeCell ref="A146:D146"/>
+    <mergeCell ref="A43:O43"/>
+    <mergeCell ref="I101:L101"/>
     <mergeCell ref="A6:D6"/>
     <mergeCell ref="A119:D119"/>
-    <mergeCell ref="E30:O30"/>
     <mergeCell ref="I91:L91"/>
+    <mergeCell ref="M102:O102"/>
     <mergeCell ref="A187:D187"/>
-    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A196:D196"/>
     <mergeCell ref="A174:D174"/>
     <mergeCell ref="A183:D183"/>
     <mergeCell ref="A84:D84"/>
     <mergeCell ref="M92:O92"/>
     <mergeCell ref="A118:D118"/>
-    <mergeCell ref="A189:D189"/>
     <mergeCell ref="A158:D158"/>
     <mergeCell ref="E52:G52"/>
+    <mergeCell ref="I102:L102"/>
+    <mergeCell ref="A198:D198"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="B33:O33"/>
     <mergeCell ref="I92:L92"/>
-    <mergeCell ref="A151:D151"/>
     <mergeCell ref="A160:D160"/>
     <mergeCell ref="A175:D175"/>
   </mergeCells>

--- a/tempetoto2026_invulformulier.xlsx
+++ b/tempetoto2026_invulformulier.xlsx
@@ -1490,7 +1490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O203"/>
+  <dimension ref="A1:O208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -3505,20 +3505,27 @@
         </is>
       </c>
     </row>
-    <row r="110" ht="16" customHeight="1">
-      <c r="A110" s="61" t="inlineStr">
-        <is>
-          <t>2A  –  2B</t>
-        </is>
-      </c>
-      <c r="E110" s="18" t="inlineStr"/>
-      <c r="F110" s="18" t="inlineStr"/>
-      <c r="G110" s="18" t="inlineStr"/>
+    <row r="110" ht="14" customHeight="1">
+      <c r="E110" s="13" t="inlineStr">
+        <is>
+          <t>voorsp.</t>
+        </is>
+      </c>
+      <c r="F110" s="13" t="inlineStr">
+        <is>
+          <t>uitslag</t>
+        </is>
+      </c>
+      <c r="G110" s="13" t="inlineStr">
+        <is>
+          <t>pt.</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="16" customHeight="1">
       <c r="A111" s="61" t="inlineStr">
         <is>
-          <t>1E  –  3e (A/B/C/D/F)</t>
+          <t>2A  –  2B</t>
         </is>
       </c>
       <c r="E111" s="18" t="inlineStr"/>
@@ -3528,7 +3535,7 @@
     <row r="112" ht="16" customHeight="1">
       <c r="A112" s="61" t="inlineStr">
         <is>
-          <t>1F  –  2C</t>
+          <t>1E  –  3e (A/B/C/D/F)</t>
         </is>
       </c>
       <c r="E112" s="18" t="inlineStr"/>
@@ -3538,7 +3545,7 @@
     <row r="113" ht="16" customHeight="1">
       <c r="A113" s="61" t="inlineStr">
         <is>
-          <t>1C  –  2F</t>
+          <t>1F  –  2C</t>
         </is>
       </c>
       <c r="E113" s="18" t="inlineStr"/>
@@ -3548,7 +3555,7 @@
     <row r="114" ht="16" customHeight="1">
       <c r="A114" s="61" t="inlineStr">
         <is>
-          <t>1I  –  3e (C/D/F/G/H)</t>
+          <t>1C  –  2F</t>
         </is>
       </c>
       <c r="E114" s="18" t="inlineStr"/>
@@ -3558,7 +3565,7 @@
     <row r="115" ht="16" customHeight="1">
       <c r="A115" s="61" t="inlineStr">
         <is>
-          <t>2E  –  2I</t>
+          <t>1I  –  3e (C/D/F/G/H)</t>
         </is>
       </c>
       <c r="E115" s="18" t="inlineStr"/>
@@ -3568,7 +3575,7 @@
     <row r="116" ht="16" customHeight="1">
       <c r="A116" s="61" t="inlineStr">
         <is>
-          <t>1A  –  3e (C/E/F/H/I)</t>
+          <t>2E  –  2I</t>
         </is>
       </c>
       <c r="E116" s="18" t="inlineStr"/>
@@ -3578,7 +3585,7 @@
     <row r="117" ht="16" customHeight="1">
       <c r="A117" s="61" t="inlineStr">
         <is>
-          <t>1L  –  3e (E/H/I/J/K)</t>
+          <t>1A  –  3e (C/E/F/H/I)</t>
         </is>
       </c>
       <c r="E117" s="18" t="inlineStr"/>
@@ -3588,7 +3595,7 @@
     <row r="118" ht="16" customHeight="1">
       <c r="A118" s="61" t="inlineStr">
         <is>
-          <t>1D  –  3e (B/E/F/I/J)</t>
+          <t>1L  –  3e (E/H/I/J/K)</t>
         </is>
       </c>
       <c r="E118" s="18" t="inlineStr"/>
@@ -3598,7 +3605,7 @@
     <row r="119" ht="16" customHeight="1">
       <c r="A119" s="61" t="inlineStr">
         <is>
-          <t>1G  –  3e (A/E/H/I/J)</t>
+          <t>1D  –  3e (B/E/F/I/J)</t>
         </is>
       </c>
       <c r="E119" s="18" t="inlineStr"/>
@@ -3608,7 +3615,7 @@
     <row r="120" ht="16" customHeight="1">
       <c r="A120" s="61" t="inlineStr">
         <is>
-          <t>2K  –  2L</t>
+          <t>1G  –  3e (A/E/H/I/J)</t>
         </is>
       </c>
       <c r="E120" s="18" t="inlineStr"/>
@@ -3618,7 +3625,7 @@
     <row r="121" ht="16" customHeight="1">
       <c r="A121" s="61" t="inlineStr">
         <is>
-          <t>1H  –  2J</t>
+          <t>2K  –  2L</t>
         </is>
       </c>
       <c r="E121" s="18" t="inlineStr"/>
@@ -3628,7 +3635,7 @@
     <row r="122" ht="16" customHeight="1">
       <c r="A122" s="61" t="inlineStr">
         <is>
-          <t>1B  –  3e (E/F/G/I/J)</t>
+          <t>1H  –  2J</t>
         </is>
       </c>
       <c r="E122" s="18" t="inlineStr"/>
@@ -3638,7 +3645,7 @@
     <row r="123" ht="16" customHeight="1">
       <c r="A123" s="61" t="inlineStr">
         <is>
-          <t>1J  –  2H</t>
+          <t>1B  –  3e (E/F/G/I/J)</t>
         </is>
       </c>
       <c r="E123" s="18" t="inlineStr"/>
@@ -3648,7 +3655,7 @@
     <row r="124" ht="16" customHeight="1">
       <c r="A124" s="61" t="inlineStr">
         <is>
-          <t>1K  –  3e (D/E/I/J/L)</t>
+          <t>1J  –  2H</t>
         </is>
       </c>
       <c r="E124" s="18" t="inlineStr"/>
@@ -3658,45 +3665,52 @@
     <row r="125" ht="16" customHeight="1">
       <c r="A125" s="61" t="inlineStr">
         <is>
-          <t>2D  –  2G</t>
+          <t>1K  –  3e (D/E/I/J/L)</t>
         </is>
       </c>
       <c r="E125" s="18" t="inlineStr"/>
       <c r="F125" s="18" t="inlineStr"/>
       <c r="G125" s="18" t="inlineStr"/>
     </row>
-    <row r="126" ht="6" customHeight="1"/>
-    <row r="127" ht="16" customHeight="1">
-      <c r="A127" s="10" t="inlineStr">
+    <row r="126" ht="16" customHeight="1">
+      <c r="A126" s="61" t="inlineStr">
+        <is>
+          <t>2D  –  2G</t>
+        </is>
+      </c>
+      <c r="E126" s="18" t="inlineStr"/>
+      <c r="F126" s="18" t="inlineStr"/>
+      <c r="G126" s="18" t="inlineStr"/>
+    </row>
+    <row r="127" ht="6" customHeight="1"/>
+    <row r="128" ht="16" customHeight="1">
+      <c r="A128" s="10" t="inlineStr">
         <is>
           <t>Ronde van 16  ·  toto 7 pt / exact +4 pt</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="16" customHeight="1">
-      <c r="A128" s="61" t="inlineStr">
-        <is>
-          <t>W32-2  –  W32-5</t>
-        </is>
-      </c>
-      <c r="E128" s="18" t="inlineStr"/>
-      <c r="F128" s="18" t="inlineStr"/>
-      <c r="G128" s="18" t="inlineStr"/>
-    </row>
-    <row r="129" ht="16" customHeight="1">
-      <c r="A129" s="61" t="inlineStr">
-        <is>
-          <t>W32-1  –  W32-3</t>
-        </is>
-      </c>
-      <c r="E129" s="18" t="inlineStr"/>
-      <c r="F129" s="18" t="inlineStr"/>
-      <c r="G129" s="18" t="inlineStr"/>
+    <row r="129" ht="14" customHeight="1">
+      <c r="E129" s="13" t="inlineStr">
+        <is>
+          <t>voorsp.</t>
+        </is>
+      </c>
+      <c r="F129" s="13" t="inlineStr">
+        <is>
+          <t>uitslag</t>
+        </is>
+      </c>
+      <c r="G129" s="13" t="inlineStr">
+        <is>
+          <t>pt.</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="16" customHeight="1">
       <c r="A130" s="61" t="inlineStr">
         <is>
-          <t>W32-4  –  W32-6</t>
+          <t>W32-2  –  W32-5</t>
         </is>
       </c>
       <c r="E130" s="18" t="inlineStr"/>
@@ -3706,7 +3720,7 @@
     <row r="131" ht="16" customHeight="1">
       <c r="A131" s="61" t="inlineStr">
         <is>
-          <t>W32-7  –  W32-8</t>
+          <t>W32-1  –  W32-3</t>
         </is>
       </c>
       <c r="E131" s="18" t="inlineStr"/>
@@ -3716,7 +3730,7 @@
     <row r="132" ht="16" customHeight="1">
       <c r="A132" s="61" t="inlineStr">
         <is>
-          <t>W32-11  –  W32-12</t>
+          <t>W32-4  –  W32-6</t>
         </is>
       </c>
       <c r="E132" s="18" t="inlineStr"/>
@@ -3726,7 +3740,7 @@
     <row r="133" ht="16" customHeight="1">
       <c r="A133" s="61" t="inlineStr">
         <is>
-          <t>W32-9  –  W32-10</t>
+          <t>W32-7  –  W32-8</t>
         </is>
       </c>
       <c r="E133" s="18" t="inlineStr"/>
@@ -3736,7 +3750,7 @@
     <row r="134" ht="16" customHeight="1">
       <c r="A134" s="61" t="inlineStr">
         <is>
-          <t>W32-14  –  W32-16</t>
+          <t>W32-11  –  W32-12</t>
         </is>
       </c>
       <c r="E134" s="18" t="inlineStr"/>
@@ -3746,1200 +3760,1271 @@
     <row r="135" ht="16" customHeight="1">
       <c r="A135" s="61" t="inlineStr">
         <is>
-          <t>W32-13  –  W32-15</t>
+          <t>W32-9  –  W32-10</t>
         </is>
       </c>
       <c r="E135" s="18" t="inlineStr"/>
       <c r="F135" s="18" t="inlineStr"/>
       <c r="G135" s="18" t="inlineStr"/>
     </row>
-    <row r="136" ht="6" customHeight="1"/>
+    <row r="136" ht="16" customHeight="1">
+      <c r="A136" s="61" t="inlineStr">
+        <is>
+          <t>W32-14  –  W32-16</t>
+        </is>
+      </c>
+      <c r="E136" s="18" t="inlineStr"/>
+      <c r="F136" s="18" t="inlineStr"/>
+      <c r="G136" s="18" t="inlineStr"/>
+    </row>
     <row r="137" ht="16" customHeight="1">
-      <c r="A137" s="10" t="inlineStr">
+      <c r="A137" s="61" t="inlineStr">
+        <is>
+          <t>W32-13  –  W32-15</t>
+        </is>
+      </c>
+      <c r="E137" s="18" t="inlineStr"/>
+      <c r="F137" s="18" t="inlineStr"/>
+      <c r="G137" s="18" t="inlineStr"/>
+    </row>
+    <row r="138" ht="6" customHeight="1"/>
+    <row r="139" ht="16" customHeight="1">
+      <c r="A139" s="10" t="inlineStr">
         <is>
           <t>Kwartfinales  ·  toto 9 pt / exact +5 pt</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="16" customHeight="1">
-      <c r="A138" s="61" t="inlineStr">
-        <is>
-          <t>W16-1  –  W16-2</t>
-        </is>
-      </c>
-      <c r="E138" s="18" t="inlineStr"/>
-      <c r="F138" s="18" t="inlineStr"/>
-      <c r="G138" s="18" t="inlineStr"/>
-    </row>
-    <row r="139" ht="16" customHeight="1">
-      <c r="A139" s="61" t="inlineStr">
-        <is>
-          <t>W16-5  –  W16-6</t>
-        </is>
-      </c>
-      <c r="E139" s="18" t="inlineStr"/>
-      <c r="F139" s="18" t="inlineStr"/>
-      <c r="G139" s="18" t="inlineStr"/>
-    </row>
-    <row r="140" ht="16" customHeight="1">
-      <c r="A140" s="61" t="inlineStr">
-        <is>
-          <t>W16-3  –  W16-4</t>
-        </is>
-      </c>
-      <c r="E140" s="18" t="inlineStr"/>
-      <c r="F140" s="18" t="inlineStr"/>
-      <c r="G140" s="18" t="inlineStr"/>
+    <row r="140" ht="14" customHeight="1">
+      <c r="E140" s="13" t="inlineStr">
+        <is>
+          <t>voorsp.</t>
+        </is>
+      </c>
+      <c r="F140" s="13" t="inlineStr">
+        <is>
+          <t>uitslag</t>
+        </is>
+      </c>
+      <c r="G140" s="13" t="inlineStr">
+        <is>
+          <t>pt.</t>
+        </is>
+      </c>
     </row>
     <row r="141" ht="16" customHeight="1">
       <c r="A141" s="61" t="inlineStr">
         <is>
-          <t>W16-7  –  W16-8</t>
+          <t>W16-1  –  W16-2</t>
         </is>
       </c>
       <c r="E141" s="18" t="inlineStr"/>
       <c r="F141" s="18" t="inlineStr"/>
       <c r="G141" s="18" t="inlineStr"/>
     </row>
-    <row r="142" ht="6" customHeight="1"/>
+    <row r="142" ht="16" customHeight="1">
+      <c r="A142" s="61" t="inlineStr">
+        <is>
+          <t>W16-5  –  W16-6</t>
+        </is>
+      </c>
+      <c r="E142" s="18" t="inlineStr"/>
+      <c r="F142" s="18" t="inlineStr"/>
+      <c r="G142" s="18" t="inlineStr"/>
+    </row>
     <row r="143" ht="16" customHeight="1">
-      <c r="A143" s="10" t="inlineStr">
-        <is>
-          <t>Halve finales  ·  toto 11 pt / exact +6 pt</t>
-        </is>
-      </c>
+      <c r="A143" s="61" t="inlineStr">
+        <is>
+          <t>W16-3  –  W16-4</t>
+        </is>
+      </c>
+      <c r="E143" s="18" t="inlineStr"/>
+      <c r="F143" s="18" t="inlineStr"/>
+      <c r="G143" s="18" t="inlineStr"/>
     </row>
     <row r="144" ht="16" customHeight="1">
       <c r="A144" s="61" t="inlineStr">
         <is>
-          <t>WKF-1  –  WKF-2</t>
+          <t>W16-7  –  W16-8</t>
         </is>
       </c>
       <c r="E144" s="18" t="inlineStr"/>
       <c r="F144" s="18" t="inlineStr"/>
       <c r="G144" s="18" t="inlineStr"/>
     </row>
-    <row r="145" ht="16" customHeight="1">
-      <c r="A145" s="61" t="inlineStr">
-        <is>
-          <t>WKF-3  –  WKF-4</t>
-        </is>
-      </c>
-      <c r="E145" s="18" t="inlineStr"/>
-      <c r="F145" s="18" t="inlineStr"/>
-      <c r="G145" s="18" t="inlineStr"/>
-    </row>
-    <row r="146" ht="6" customHeight="1"/>
-    <row r="147" ht="16" customHeight="1">
-      <c r="A147" s="10" t="inlineStr">
-        <is>
-          <t>Finale  ·  toto 13 pt / exact +7 pt</t>
+    <row r="145" ht="6" customHeight="1"/>
+    <row r="146" ht="16" customHeight="1">
+      <c r="A146" s="10" t="inlineStr">
+        <is>
+          <t>Halve finales  ·  toto 11 pt / exact +6 pt</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="14" customHeight="1">
+      <c r="E147" s="13" t="inlineStr">
+        <is>
+          <t>voorsp.</t>
+        </is>
+      </c>
+      <c r="F147" s="13" t="inlineStr">
+        <is>
+          <t>uitslag</t>
+        </is>
+      </c>
+      <c r="G147" s="13" t="inlineStr">
+        <is>
+          <t>pt.</t>
         </is>
       </c>
     </row>
     <row r="148" ht="16" customHeight="1">
       <c r="A148" s="61" t="inlineStr">
         <is>
-          <t>WHF-1  –  WHF-2</t>
+          <t>WKF-1  –  WKF-2</t>
         </is>
       </c>
       <c r="E148" s="18" t="inlineStr"/>
       <c r="F148" s="18" t="inlineStr"/>
       <c r="G148" s="18" t="inlineStr"/>
     </row>
-    <row r="149" ht="6" customHeight="1"/>
-    <row r="150" ht="8" customHeight="1"/>
-    <row r="151" ht="18" customHeight="1">
-      <c r="A151" s="4" t="inlineStr">
+    <row r="149" ht="16" customHeight="1">
+      <c r="A149" s="61" t="inlineStr">
+        <is>
+          <t>WKF-3  –  WKF-4</t>
+        </is>
+      </c>
+      <c r="E149" s="18" t="inlineStr"/>
+      <c r="F149" s="18" t="inlineStr"/>
+      <c r="G149" s="18" t="inlineStr"/>
+    </row>
+    <row r="150" ht="6" customHeight="1"/>
+    <row r="151" ht="16" customHeight="1">
+      <c r="A151" s="10" t="inlineStr">
+        <is>
+          <t>Finale  ·  toto 13 pt / exact +7 pt</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="14" customHeight="1">
+      <c r="E152" s="13" t="inlineStr">
+        <is>
+          <t>voorsp.</t>
+        </is>
+      </c>
+      <c r="F152" s="13" t="inlineStr">
+        <is>
+          <t>uitslag</t>
+        </is>
+      </c>
+      <c r="G152" s="13" t="inlineStr">
+        <is>
+          <t>pt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="16" customHeight="1">
+      <c r="A153" s="61" t="inlineStr">
+        <is>
+          <t>WHF-1  –  WHF-2</t>
+        </is>
+      </c>
+      <c r="E153" s="18" t="inlineStr"/>
+      <c r="F153" s="18" t="inlineStr"/>
+      <c r="G153" s="18" t="inlineStr"/>
+    </row>
+    <row r="154" ht="6" customHeight="1"/>
+    <row r="155" ht="8" customHeight="1"/>
+    <row r="156" ht="18" customHeight="1">
+      <c r="A156" s="4" t="inlineStr">
         <is>
           <t>▶  VERRASSING — kies een land BUITEN de top-12 · punten schalen met ranking en ronde</t>
         </is>
       </c>
     </row>
-    <row r="152" ht="14" customHeight="1">
-      <c r="A152" s="13" t="inlineStr">
+    <row r="157" ht="14" customHeight="1">
+      <c r="A157" s="13" t="inlineStr">
         <is>
           <t>Land (outsider)</t>
         </is>
       </c>
-      <c r="E152" s="13" t="inlineStr">
+      <c r="E157" s="13" t="inlineStr">
         <is>
           <t>R16</t>
         </is>
       </c>
-      <c r="F152" s="13" t="inlineStr">
+      <c r="F157" s="13" t="inlineStr">
         <is>
           <t>KF</t>
         </is>
       </c>
-      <c r="G152" s="13" t="inlineStr">
+      <c r="G157" s="13" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="H152" s="13" t="inlineStr">
+      <c r="H157" s="13" t="inlineStr">
         <is>
           <t>Finale</t>
         </is>
       </c>
-      <c r="I152" s="13" t="inlineStr">
+      <c r="I157" s="13" t="inlineStr">
         <is>
           <t>Winnaar</t>
         </is>
-      </c>
-    </row>
-    <row r="153" ht="15" customHeight="1">
-      <c r="A153" s="15" t="inlineStr">
-        <is>
-          <t>Senegal</t>
-        </is>
-      </c>
-      <c r="E153" s="62" t="n">
-        <v>7</v>
-      </c>
-      <c r="F153" s="62" t="n">
-        <v>12</v>
-      </c>
-      <c r="G153" s="62" t="n">
-        <v>19</v>
-      </c>
-      <c r="H153" s="62" t="n">
-        <v>26</v>
-      </c>
-      <c r="I153" s="62" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="154" ht="15" customHeight="1">
-      <c r="A154" s="15" t="inlineStr">
-        <is>
-          <t>Mexico</t>
-        </is>
-      </c>
-      <c r="E154" s="62" t="n">
-        <v>7</v>
-      </c>
-      <c r="F154" s="62" t="n">
-        <v>13</v>
-      </c>
-      <c r="G154" s="62" t="n">
-        <v>19</v>
-      </c>
-      <c r="H154" s="62" t="n">
-        <v>27</v>
-      </c>
-      <c r="I154" s="62" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="155" ht="15" customHeight="1">
-      <c r="A155" s="15" t="inlineStr">
-        <is>
-          <t>Verenigde Staten</t>
-        </is>
-      </c>
-      <c r="E155" s="62" t="n">
-        <v>8</v>
-      </c>
-      <c r="F155" s="62" t="n">
-        <v>13</v>
-      </c>
-      <c r="G155" s="62" t="n">
-        <v>20</v>
-      </c>
-      <c r="H155" s="62" t="n">
-        <v>27</v>
-      </c>
-      <c r="I155" s="62" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="156" ht="15" customHeight="1">
-      <c r="A156" s="15" t="inlineStr">
-        <is>
-          <t>Uruguay</t>
-        </is>
-      </c>
-      <c r="E156" s="62" t="n">
-        <v>8</v>
-      </c>
-      <c r="F156" s="62" t="n">
-        <v>14</v>
-      </c>
-      <c r="G156" s="62" t="n">
-        <v>20</v>
-      </c>
-      <c r="H156" s="62" t="n">
-        <v>28</v>
-      </c>
-      <c r="I156" s="62" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="157" ht="15" customHeight="1">
-      <c r="A157" s="15" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="E157" s="62" t="n">
-        <v>8</v>
-      </c>
-      <c r="F157" s="62" t="n">
-        <v>14</v>
-      </c>
-      <c r="G157" s="62" t="n">
-        <v>21</v>
-      </c>
-      <c r="H157" s="62" t="n">
-        <v>29</v>
-      </c>
-      <c r="I157" s="62" t="n">
-        <v>38</v>
       </c>
     </row>
     <row r="158" ht="15" customHeight="1">
       <c r="A158" s="15" t="inlineStr">
         <is>
-          <t>Zwitserland</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="E158" s="62" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F158" s="62" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G158" s="62" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H158" s="62" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I158" s="62" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="159" ht="15" customHeight="1">
       <c r="A159" s="15" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="E159" s="62" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F159" s="62" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G159" s="62" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H159" s="62" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I159" s="62" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="160" ht="15" customHeight="1">
       <c r="A160" s="15" t="inlineStr">
         <is>
-          <t>Oostenrijk</t>
+          <t>Verenigde Staten</t>
         </is>
       </c>
       <c r="E160" s="62" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F160" s="62" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G160" s="62" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H160" s="62" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="I160" s="62" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="161" ht="15" customHeight="1">
       <c r="A161" s="15" t="inlineStr">
         <is>
-          <t>Zuid-Korea</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="E161" s="62" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F161" s="62" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G161" s="62" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H161" s="62" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I161" s="62" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="162" ht="15" customHeight="1">
       <c r="A162" s="15" t="inlineStr">
         <is>
-          <t>Australië</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="E162" s="62" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F162" s="62" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G162" s="62" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H162" s="62" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I162" s="62" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="163" ht="15" customHeight="1">
       <c r="A163" s="15" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Zwitserland</t>
         </is>
       </c>
       <c r="E163" s="62" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F163" s="62" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G163" s="62" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H163" s="62" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I163" s="62" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="164" ht="15" customHeight="1">
       <c r="A164" s="15" t="inlineStr">
         <is>
-          <t>Noorwegen</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="E164" s="62" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F164" s="62" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G164" s="62" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H164" s="62" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I164" s="62" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="165" ht="15" customHeight="1">
       <c r="A165" s="15" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Oostenrijk</t>
         </is>
       </c>
       <c r="E165" s="62" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F165" s="62" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G165" s="62" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H165" s="62" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I165" s="62" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="166" ht="15" customHeight="1">
       <c r="A166" s="15" t="inlineStr">
         <is>
-          <t>Egypte</t>
+          <t>Zuid-Korea</t>
         </is>
       </c>
       <c r="E166" s="62" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F166" s="62" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G166" s="62" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="H166" s="62" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="I166" s="62" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="167" ht="15" customHeight="1">
       <c r="A167" s="15" t="inlineStr">
         <is>
-          <t>Algerije</t>
+          <t>Australië</t>
         </is>
       </c>
       <c r="E167" s="62" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F167" s="62" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G167" s="62" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H167" s="62" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="I167" s="62" t="n">
-        <v>52</v>
+        <v>43</v>
       </c>
     </row>
     <row r="168" ht="15" customHeight="1">
       <c r="A168" s="15" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="E168" s="62" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F168" s="62" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G168" s="62" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="H168" s="62" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I168" s="62" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
     </row>
     <row r="169" ht="15" customHeight="1">
       <c r="A169" s="15" t="inlineStr">
         <is>
-          <t>Ivoorkust</t>
+          <t>Noorwegen</t>
         </is>
       </c>
       <c r="E169" s="62" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F169" s="62" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G169" s="62" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H169" s="62" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I169" s="62" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
     </row>
     <row r="170" ht="15" customHeight="1">
       <c r="A170" s="15" t="inlineStr">
         <is>
-          <t>Tunesië</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="E170" s="62" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F170" s="62" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G170" s="62" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="H170" s="62" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="I170" s="62" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
     </row>
     <row r="171" ht="15" customHeight="1">
       <c r="A171" s="15" t="inlineStr">
         <is>
-          <t>Schotland</t>
+          <t>Egypte</t>
         </is>
       </c>
       <c r="E171" s="62" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F171" s="62" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G171" s="62" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="H171" s="62" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="I171" s="62" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
     </row>
     <row r="172" ht="15" customHeight="1">
       <c r="A172" s="15" t="inlineStr">
         <is>
-          <t>Zweden</t>
+          <t>Algerije</t>
         </is>
       </c>
       <c r="E172" s="62" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F172" s="62" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G172" s="62" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H172" s="62" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="I172" s="62" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="173" ht="15" customHeight="1">
       <c r="A173" s="15" t="inlineStr">
         <is>
-          <t>Tsjechië</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="E173" s="62" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F173" s="62" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G173" s="62" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H173" s="62" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I173" s="62" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="174" ht="15" customHeight="1">
       <c r="A174" s="15" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Ivoorkust</t>
         </is>
       </c>
       <c r="E174" s="62" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F174" s="62" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G174" s="62" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H174" s="62" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="I174" s="62" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="175" ht="15" customHeight="1">
       <c r="A175" s="15" t="inlineStr">
         <is>
-          <t>Oezbekistan</t>
+          <t>Tunesië</t>
         </is>
       </c>
       <c r="E175" s="62" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F175" s="62" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G175" s="62" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H175" s="62" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I175" s="62" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="176" ht="15" customHeight="1">
       <c r="A176" s="15" t="inlineStr">
         <is>
-          <t>DR Congo</t>
+          <t>Schotland</t>
         </is>
       </c>
       <c r="E176" s="62" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F176" s="62" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G176" s="62" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H176" s="62" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I176" s="62" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
     </row>
     <row r="177" ht="15" customHeight="1">
       <c r="A177" s="15" t="inlineStr">
         <is>
-          <t>Saoedi-Arabië</t>
+          <t>Zweden</t>
         </is>
       </c>
       <c r="E177" s="62" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F177" s="62" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G177" s="62" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H177" s="62" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="I177" s="62" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="178" ht="15" customHeight="1">
       <c r="A178" s="15" t="inlineStr">
         <is>
-          <t>Irak</t>
+          <t>Tsjechië</t>
         </is>
       </c>
       <c r="E178" s="62" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F178" s="62" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G178" s="62" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H178" s="62" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="I178" s="62" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="179" ht="15" customHeight="1">
       <c r="A179" s="15" t="inlineStr">
         <is>
-          <t>Zuid-Afrika</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="E179" s="62" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F179" s="62" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G179" s="62" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H179" s="62" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="I179" s="62" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="180" ht="15" customHeight="1">
       <c r="A180" s="15" t="inlineStr">
         <is>
-          <t>Jordanië</t>
+          <t>Oezbekistan</t>
         </is>
       </c>
       <c r="E180" s="62" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F180" s="62" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G180" s="62" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="H180" s="62" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="I180" s="62" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="181" ht="15" customHeight="1">
       <c r="A181" s="15" t="inlineStr">
         <is>
-          <t>Kaapverdië</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="E181" s="62" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F181" s="62" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G181" s="62" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H181" s="62" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="I181" s="62" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="182" ht="15" customHeight="1">
       <c r="A182" s="15" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Saoedi-Arabië</t>
         </is>
       </c>
       <c r="E182" s="62" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F182" s="62" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G182" s="62" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="H182" s="62" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="I182" s="62" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
     </row>
     <row r="183" ht="15" customHeight="1">
       <c r="A183" s="15" t="inlineStr">
         <is>
-          <t>Bosnië-Herzegovina</t>
+          <t>Irak</t>
         </is>
       </c>
       <c r="E183" s="62" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F183" s="62" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G183" s="62" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H183" s="62" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="I183" s="62" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
     </row>
     <row r="184" ht="15" customHeight="1">
       <c r="A184" s="15" t="inlineStr">
         <is>
-          <t>Haïti</t>
+          <t>Zuid-Afrika</t>
         </is>
       </c>
       <c r="E184" s="62" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F184" s="62" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G184" s="62" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="H184" s="62" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="I184" s="62" t="n">
-        <v>76</v>
+        <v>66</v>
       </c>
     </row>
     <row r="185" ht="15" customHeight="1">
       <c r="A185" s="15" t="inlineStr">
         <is>
-          <t>Nieuw-Zeeland</t>
+          <t>Jordanië</t>
         </is>
       </c>
       <c r="E185" s="62" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F185" s="62" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G185" s="62" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H185" s="62" t="n">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="I185" s="62" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
     </row>
     <row r="186" ht="15" customHeight="1">
       <c r="A186" s="15" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Kaapverdië</t>
         </is>
       </c>
       <c r="E186" s="62" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F186" s="62" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G186" s="62" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H186" s="62" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="I186" s="62" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
     </row>
     <row r="187" ht="15" customHeight="1">
       <c r="A187" s="15" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="E187" s="62" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F187" s="62" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G187" s="62" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H187" s="62" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="I187" s="62" t="n">
-        <v>61</v>
+        <v>72</v>
       </c>
     </row>
     <row r="188" ht="15" customHeight="1">
       <c r="A188" s="15" t="inlineStr">
         <is>
-          <t>Turkije</t>
+          <t>Bosnië-Herzegovina</t>
         </is>
       </c>
       <c r="E188" s="62" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F188" s="62" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G188" s="62" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H188" s="62" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="I188" s="62" t="n">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="189" ht="8" customHeight="1"/>
-    <row r="190" ht="18" customHeight="1">
-      <c r="A190" s="4" t="inlineStr">
-        <is>
-          <t>▶  DECEPTIE — kies een land UIT de top-12 · punten schalen met ranking en uitvalsronde</t>
-        </is>
-      </c>
-    </row>
-    <row r="191" ht="14" customHeight="1">
-      <c r="A191" s="13" t="inlineStr">
-        <is>
-          <t>Land (favoriet)</t>
-        </is>
-      </c>
-      <c r="E191" s="13" t="inlineStr">
-        <is>
-          <t>KF</t>
-        </is>
-      </c>
-      <c r="F191" s="13" t="inlineStr">
-        <is>
-          <t>R16</t>
-        </is>
-      </c>
-      <c r="G191" s="13" t="inlineStr">
-        <is>
-          <t>R32</t>
-        </is>
-      </c>
-      <c r="H191" s="13" t="inlineStr">
-        <is>
-          <t>Groep eruit</t>
-        </is>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="189" ht="15" customHeight="1">
+      <c r="A189" s="15" t="inlineStr">
+        <is>
+          <t>Haïti</t>
+        </is>
+      </c>
+      <c r="E189" s="62" t="n">
+        <v>16</v>
+      </c>
+      <c r="F189" s="62" t="n">
+        <v>28</v>
+      </c>
+      <c r="G189" s="62" t="n">
+        <v>41</v>
+      </c>
+      <c r="H189" s="62" t="n">
+        <v>58</v>
+      </c>
+      <c r="I189" s="62" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="190" ht="15" customHeight="1">
+      <c r="A190" s="15" t="inlineStr">
+        <is>
+          <t>Nieuw-Zeeland</t>
+        </is>
+      </c>
+      <c r="E190" s="62" t="n">
+        <v>16</v>
+      </c>
+      <c r="F190" s="62" t="n">
+        <v>28</v>
+      </c>
+      <c r="G190" s="62" t="n">
+        <v>42</v>
+      </c>
+      <c r="H190" s="62" t="n">
+        <v>59</v>
+      </c>
+      <c r="I190" s="62" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="191" ht="15" customHeight="1">
+      <c r="A191" s="15" t="inlineStr">
+        <is>
+          <t>Curaçao</t>
+        </is>
+      </c>
+      <c r="E191" s="62" t="n">
+        <v>17</v>
+      </c>
+      <c r="F191" s="62" t="n">
+        <v>29</v>
+      </c>
+      <c r="G191" s="62" t="n">
+        <v>43</v>
+      </c>
+      <c r="H191" s="62" t="n">
+        <v>60</v>
+      </c>
+      <c r="I191" s="62" t="n">
+        <v>79</v>
       </c>
     </row>
     <row r="192" ht="15" customHeight="1">
       <c r="A192" s="15" t="inlineStr">
         <is>
-          <t>Frankrijk</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E192" s="62" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F192" s="62" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G192" s="62" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="H192" s="62" t="n">
-        <v>30</v>
+        <v>46</v>
+      </c>
+      <c r="I192" s="62" t="n">
+        <v>61</v>
       </c>
     </row>
     <row r="193" ht="15" customHeight="1">
       <c r="A193" s="15" t="inlineStr">
         <is>
-          <t>Spanje</t>
+          <t>Turkije</t>
         </is>
       </c>
       <c r="E193" s="62" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F193" s="62" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G193" s="62" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="H193" s="62" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="194" ht="15" customHeight="1">
-      <c r="A194" s="15" t="inlineStr">
-        <is>
-          <t>Argentinië</t>
-        </is>
-      </c>
-      <c r="E194" s="62" t="n">
-        <v>6</v>
-      </c>
-      <c r="F194" s="62" t="n">
-        <v>12</v>
-      </c>
-      <c r="G194" s="62" t="n">
-        <v>17</v>
-      </c>
-      <c r="H194" s="62" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="195" ht="15" customHeight="1">
-      <c r="A195" s="15" t="inlineStr">
-        <is>
-          <t>Engeland</t>
-        </is>
-      </c>
-      <c r="E195" s="62" t="n">
-        <v>6</v>
-      </c>
-      <c r="F195" s="62" t="n">
-        <v>11</v>
-      </c>
-      <c r="G195" s="62" t="n">
-        <v>16</v>
-      </c>
-      <c r="H195" s="62" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="196" ht="15" customHeight="1">
-      <c r="A196" s="15" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="E196" s="62" t="n">
-        <v>6</v>
-      </c>
-      <c r="F196" s="62" t="n">
-        <v>10</v>
-      </c>
-      <c r="G196" s="62" t="n">
-        <v>15</v>
-      </c>
-      <c r="H196" s="62" t="n">
-        <v>22</v>
+        <v>46</v>
+      </c>
+      <c r="I193" s="62" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="194" ht="8" customHeight="1"/>
+    <row r="195" ht="18" customHeight="1">
+      <c r="A195" s="4" t="inlineStr">
+        <is>
+          <t>▶  DECEPTIE — kies een land UIT de top-12 · punten schalen met ranking en uitvalsronde</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="14" customHeight="1">
+      <c r="A196" s="13" t="inlineStr">
+        <is>
+          <t>Land (favoriet)</t>
+        </is>
+      </c>
+      <c r="E196" s="13" t="inlineStr">
+        <is>
+          <t>KF</t>
+        </is>
+      </c>
+      <c r="F196" s="13" t="inlineStr">
+        <is>
+          <t>R16</t>
+        </is>
+      </c>
+      <c r="G196" s="13" t="inlineStr">
+        <is>
+          <t>R32</t>
+        </is>
+      </c>
+      <c r="H196" s="13" t="inlineStr">
+        <is>
+          <t>Groep eruit</t>
+        </is>
       </c>
     </row>
     <row r="197" ht="15" customHeight="1">
       <c r="A197" s="15" t="inlineStr">
         <is>
-          <t>Brazilië</t>
+          <t>Frankrijk</t>
         </is>
       </c>
       <c r="E197" s="62" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F197" s="62" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G197" s="62" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H197" s="62" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="198" ht="15" customHeight="1">
       <c r="A198" s="15" t="inlineStr">
         <is>
-          <t>Nederland</t>
+          <t>Spanje</t>
         </is>
       </c>
       <c r="E198" s="62" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F198" s="62" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G198" s="62" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H198" s="62" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
     <row r="199" ht="15" customHeight="1">
       <c r="A199" s="15" t="inlineStr">
         <is>
-          <t>Marokko</t>
+          <t>Argentinië</t>
         </is>
       </c>
       <c r="E199" s="62" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F199" s="62" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G199" s="62" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H199" s="62" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="200" ht="15" customHeight="1">
       <c r="A200" s="15" t="inlineStr">
         <is>
-          <t>België</t>
+          <t>Engeland</t>
         </is>
       </c>
       <c r="E200" s="62" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F200" s="62" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G200" s="62" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="H200" s="62" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="201" ht="15" customHeight="1">
       <c r="A201" s="15" t="inlineStr">
         <is>
-          <t>Duitsland</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="E201" s="62" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F201" s="62" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G201" s="62" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H201" s="62" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="202" ht="15" customHeight="1">
       <c r="A202" s="15" t="inlineStr">
         <is>
-          <t>Kroatië</t>
+          <t>Brazilië</t>
         </is>
       </c>
       <c r="E202" s="62" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F202" s="62" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G202" s="62" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H202" s="62" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="203" ht="15" customHeight="1">
       <c r="A203" s="15" t="inlineStr">
         <is>
+          <t>Nederland</t>
+        </is>
+      </c>
+      <c r="E203" s="62" t="n">
+        <v>4</v>
+      </c>
+      <c r="F203" s="62" t="n">
+        <v>8</v>
+      </c>
+      <c r="G203" s="62" t="n">
+        <v>12</v>
+      </c>
+      <c r="H203" s="62" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="204" ht="15" customHeight="1">
+      <c r="A204" s="15" t="inlineStr">
+        <is>
+          <t>Marokko</t>
+        </is>
+      </c>
+      <c r="E204" s="62" t="n">
+        <v>4</v>
+      </c>
+      <c r="F204" s="62" t="n">
+        <v>7</v>
+      </c>
+      <c r="G204" s="62" t="n">
+        <v>11</v>
+      </c>
+      <c r="H204" s="62" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="205" ht="15" customHeight="1">
+      <c r="A205" s="15" t="inlineStr">
+        <is>
+          <t>België</t>
+        </is>
+      </c>
+      <c r="E205" s="62" t="n">
+        <v>4</v>
+      </c>
+      <c r="F205" s="62" t="n">
+        <v>6</v>
+      </c>
+      <c r="G205" s="62" t="n">
+        <v>9</v>
+      </c>
+      <c r="H205" s="62" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="206" ht="15" customHeight="1">
+      <c r="A206" s="15" t="inlineStr">
+        <is>
+          <t>Duitsland</t>
+        </is>
+      </c>
+      <c r="E206" s="62" t="n">
+        <v>3</v>
+      </c>
+      <c r="F206" s="62" t="n">
+        <v>6</v>
+      </c>
+      <c r="G206" s="62" t="n">
+        <v>8</v>
+      </c>
+      <c r="H206" s="62" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="207" ht="15" customHeight="1">
+      <c r="A207" s="15" t="inlineStr">
+        <is>
+          <t>Kroatië</t>
+        </is>
+      </c>
+      <c r="E207" s="62" t="n">
+        <v>2</v>
+      </c>
+      <c r="F207" s="62" t="n">
+        <v>5</v>
+      </c>
+      <c r="G207" s="62" t="n">
+        <v>7</v>
+      </c>
+      <c r="H207" s="62" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="208" ht="15" customHeight="1">
+      <c r="A208" s="15" t="inlineStr">
+        <is>
           <t>Colombia</t>
         </is>
       </c>
-      <c r="E203" s="62" t="n">
+      <c r="E208" s="62" t="n">
         <v>2</v>
       </c>
-      <c r="F203" s="62" t="n">
+      <c r="F208" s="62" t="n">
         <v>3</v>
       </c>
-      <c r="G203" s="62" t="n">
+      <c r="G208" s="62" t="n">
         <v>4</v>
       </c>
-      <c r="H203" s="62" t="n">
+      <c r="H208" s="62" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4957,7 +5042,6 @@
     <mergeCell ref="A200:D200"/>
     <mergeCell ref="A81:D81"/>
     <mergeCell ref="A112:D112"/>
-    <mergeCell ref="A152:D152"/>
     <mergeCell ref="A121:D121"/>
     <mergeCell ref="M81:O81"/>
     <mergeCell ref="A161:D161"/>
@@ -4989,21 +5073,25 @@
     <mergeCell ref="A164:D164"/>
     <mergeCell ref="A15:O15"/>
     <mergeCell ref="A24:O24"/>
-    <mergeCell ref="A154:D154"/>
+    <mergeCell ref="A149:D149"/>
     <mergeCell ref="M52:O52"/>
     <mergeCell ref="A163:D163"/>
     <mergeCell ref="A101:D101"/>
     <mergeCell ref="E92:G92"/>
-    <mergeCell ref="A195:D195"/>
+    <mergeCell ref="A204:D204"/>
+    <mergeCell ref="A146:O146"/>
     <mergeCell ref="I52:L52"/>
     <mergeCell ref="A188:D188"/>
+    <mergeCell ref="A126:D126"/>
     <mergeCell ref="A141:D141"/>
     <mergeCell ref="A16:O16"/>
     <mergeCell ref="A135:D135"/>
+    <mergeCell ref="A206:D206"/>
     <mergeCell ref="I44:L44"/>
     <mergeCell ref="A62:D62"/>
     <mergeCell ref="A108:O108"/>
     <mergeCell ref="A125:D125"/>
+    <mergeCell ref="A190:D190"/>
     <mergeCell ref="A18:O18"/>
     <mergeCell ref="I94:L94"/>
     <mergeCell ref="A117:D117"/>
@@ -5015,6 +5103,7 @@
     <mergeCell ref="A167:D167"/>
     <mergeCell ref="A151:O151"/>
     <mergeCell ref="E61:G61"/>
+    <mergeCell ref="A142:D142"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="A22:O22"/>
     <mergeCell ref="A182:D182"/>
@@ -5024,41 +5113,35 @@
     <mergeCell ref="I61:L61"/>
     <mergeCell ref="E72:G72"/>
     <mergeCell ref="A61:D61"/>
-    <mergeCell ref="A190:O190"/>
     <mergeCell ref="A28:O28"/>
     <mergeCell ref="A153:D153"/>
     <mergeCell ref="A162:D162"/>
     <mergeCell ref="M71:O71"/>
     <mergeCell ref="I54:L54"/>
-    <mergeCell ref="A128:D128"/>
     <mergeCell ref="I72:L72"/>
-    <mergeCell ref="A127:O127"/>
+    <mergeCell ref="A137:D137"/>
     <mergeCell ref="A177:D177"/>
+    <mergeCell ref="A208:D208"/>
     <mergeCell ref="A30:O30"/>
     <mergeCell ref="E71:G71"/>
+    <mergeCell ref="A136:D136"/>
     <mergeCell ref="A192:D192"/>
     <mergeCell ref="I71:L71"/>
     <mergeCell ref="A74:D74"/>
-    <mergeCell ref="A145:D145"/>
-    <mergeCell ref="A139:D139"/>
     <mergeCell ref="E8:G8"/>
     <mergeCell ref="G1:K1"/>
     <mergeCell ref="A179:D179"/>
     <mergeCell ref="A71:D71"/>
     <mergeCell ref="E82:G82"/>
-    <mergeCell ref="A129:D129"/>
-    <mergeCell ref="A194:D194"/>
     <mergeCell ref="A203:D203"/>
     <mergeCell ref="A116:D116"/>
     <mergeCell ref="A181:D181"/>
     <mergeCell ref="E10:G10"/>
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="A91:D91"/>
-    <mergeCell ref="A137:O137"/>
+    <mergeCell ref="A184:D184"/>
     <mergeCell ref="A131:D131"/>
     <mergeCell ref="I82:L82"/>
-    <mergeCell ref="A184:D184"/>
-    <mergeCell ref="A140:D140"/>
     <mergeCell ref="A171:D171"/>
     <mergeCell ref="A52:D52"/>
     <mergeCell ref="A165:D165"/>
@@ -5067,12 +5150,14 @@
     <mergeCell ref="B31:O31"/>
     <mergeCell ref="A10:D10"/>
     <mergeCell ref="A115:D115"/>
-    <mergeCell ref="A155:D155"/>
+    <mergeCell ref="A139:O139"/>
     <mergeCell ref="A102:D102"/>
     <mergeCell ref="A173:D173"/>
     <mergeCell ref="E11:G11"/>
     <mergeCell ref="I74:L74"/>
     <mergeCell ref="B39:O39"/>
+    <mergeCell ref="A195:O195"/>
+    <mergeCell ref="A143:D143"/>
     <mergeCell ref="A92:D92"/>
     <mergeCell ref="A157:D157"/>
     <mergeCell ref="A166:D166"/>
@@ -5080,15 +5165,16 @@
     <mergeCell ref="A17:O17"/>
     <mergeCell ref="B23:O23"/>
     <mergeCell ref="M62:O62"/>
+    <mergeCell ref="A207:D207"/>
     <mergeCell ref="A109:O109"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A94:D94"/>
     <mergeCell ref="A168:D168"/>
     <mergeCell ref="E102:G102"/>
     <mergeCell ref="A19:O19"/>
+    <mergeCell ref="A205:D205"/>
     <mergeCell ref="A34:O34"/>
     <mergeCell ref="A133:D133"/>
-    <mergeCell ref="A143:O143"/>
     <mergeCell ref="A193:D193"/>
     <mergeCell ref="E62:G62"/>
     <mergeCell ref="A120:D120"/>
@@ -5102,8 +5188,8 @@
     <mergeCell ref="A185:D185"/>
     <mergeCell ref="I64:L64"/>
     <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A128:O128"/>
     <mergeCell ref="I51:L51"/>
-    <mergeCell ref="A156:D156"/>
     <mergeCell ref="A170:D170"/>
     <mergeCell ref="A21:O21"/>
     <mergeCell ref="A105:O105"/>
@@ -5118,12 +5204,10 @@
     <mergeCell ref="M91:O91"/>
     <mergeCell ref="E91:G91"/>
     <mergeCell ref="A123:D123"/>
-    <mergeCell ref="A138:D138"/>
-    <mergeCell ref="A147:O147"/>
     <mergeCell ref="A132:D132"/>
     <mergeCell ref="A197:D197"/>
-    <mergeCell ref="A110:D110"/>
     <mergeCell ref="A43:O43"/>
+    <mergeCell ref="A156:O156"/>
     <mergeCell ref="I101:L101"/>
     <mergeCell ref="A6:D6"/>
     <mergeCell ref="A119:D119"/>
@@ -5136,6 +5220,7 @@
     <mergeCell ref="A84:D84"/>
     <mergeCell ref="M92:O92"/>
     <mergeCell ref="A118:D118"/>
+    <mergeCell ref="A189:D189"/>
     <mergeCell ref="A158:D158"/>
     <mergeCell ref="E52:G52"/>
     <mergeCell ref="I102:L102"/>

--- a/tempetoto2026_invulformulier.xlsx
+++ b/tempetoto2026_invulformulier.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="16">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,14 +29,8 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="000A1F47"/>
-      <sz val="16"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
       <color rgb="002A5298"/>
-      <sz val="12"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -61,12 +55,6 @@
       <b val="1"/>
       <color rgb="000A2A55"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="002A5298"/>
-      <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -433,56 +421,53 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -526,13 +511,13 @@
     <xf numFmtId="0" fontId="0" fillId="47" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="48" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="49" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="50" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="50" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -609,6 +594,36 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="11430000" cy="3543300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1490,7 +1505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O208"/>
+  <dimension ref="A6:O213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1510,3738 +1525,3738 @@
     <col width="11" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>TEMPETOTO 2026</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>Naam:</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="n"/>
-    </row>
-    <row r="2" ht="8" customHeight="1"/>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
+    <row r="1" ht="56" customHeight="1"/>
+    <row r="2" ht="56" customHeight="1"/>
+    <row r="3" ht="56" customHeight="1"/>
+    <row r="4" ht="56" customHeight="1"/>
+    <row r="5" ht="56" customHeight="1"/>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Naam deelnemer:</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n"/>
+    </row>
+    <row r="7" ht="8" customHeight="1"/>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>▶  VOORAF INVULLEN  ·  deadline vóór de eerste wedstrijd</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Kampioen:</t>
         </is>
       </c>
-      <c r="E4" s="6" t="n"/>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="E9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Verrassing  (outsider, buiten top-12):</t>
         </is>
       </c>
-      <c r="E5" s="6" t="n"/>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="E10" s="5" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Deceptie  (favoriet, uit top-12):</t>
         </is>
       </c>
-      <c r="E6" s="6" t="n"/>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="E11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Topscorer  (naam speler):</t>
         </is>
       </c>
-      <c r="E7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="E12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>↳ Verwacht aantal goals topscorer:</t>
         </is>
       </c>
-      <c r="E8" s="6" t="n"/>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="E13" s="5" t="n"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Totaal goals  (heel WK):</t>
         </is>
       </c>
-      <c r="E9" s="6" t="n"/>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="E14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Gele kaarten  (totaal WK):</t>
         </is>
       </c>
-      <c r="E10" s="6" t="n"/>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="E15" s="5" t="n"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Rode kaarten  (totaal WK):</t>
         </is>
       </c>
-      <c r="E11" s="6" t="n"/>
-    </row>
-    <row r="12" ht="8" customHeight="1"/>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="E16" s="5" t="n"/>
+    </row>
+    <row r="17" ht="8" customHeight="1"/>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>Spelregels:</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="40" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
+    <row r="19" ht="40" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>1.  Vul ALLE 72 groepswedstrijden in als '2-1' (thuis–uit, uitslag na 90 min). Dit zijn de lichtblauwe vakjes.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="40" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+    <row r="20" ht="40" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>2.  Vul ook de VOORAF-sectie in: kampioen, verrassing, deceptie, topscorer, goals en kaarten.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="40" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
+    <row r="21" ht="40" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>3.  Groepswinnaar, runner-up en beste nummers 3 worden AUTOMATISCH berekend uit je scores — je hoeft die niet in te vullen.</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="40" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>4.  Knock-out voorspellingen (grijs) vul je pas in na de groepsfase, vóór elke volgende ronde.</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="40" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>5.  Wijzigen van groepsfase-voorspellingen kan niet meer nadat het WK begonnen is.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="40" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>6.  In principe worden de FIFA WK-regels aangehouden. Bij twijfel beslist de organisator.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="8" customHeight="1"/>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="9" t="inlineStr">
+    <row r="25" ht="8" customHeight="1"/>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>Puntentelling:</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="10" t="inlineStr">
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>Groepswedstrijden:</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="40" customHeight="1">
-      <c r="B23" s="11" t="inlineStr">
+    <row r="28" ht="40" customHeight="1">
+      <c r="B28" s="10" t="inlineStr">
         <is>
           <t>Goede toto (winst/gelijkspel/verlies): 3 pt.  Goede uitslag: +2 pt.</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="10" t="inlineStr">
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>Knock-outrondes:</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="40" customHeight="1">
-      <c r="B25" s="11" t="inlineStr">
+    <row r="30" ht="40" customHeight="1">
+      <c r="B30" s="10" t="inlineStr">
         <is>
           <t>Goede toto [+ goede uitslag]: R32 5[+3] · R16 7[+4] · KF 9[+5] · HF 11[+6] · F 13[+7] pt.  Uitslag na 90 min telt.</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="10" t="inlineStr">
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>Doorgaan (top-2):</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="40" customHeight="1">
-      <c r="B27" s="11" t="inlineStr">
+    <row r="32" ht="40" customHeight="1">
+      <c r="B32" s="10" t="inlineStr">
         <is>
           <t>Per goed voorspeld land dat 1e of 2e eindigt in zijn groep: 3 pt.</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="10" t="inlineStr">
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t>Beste nummers 3:</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="40" customHeight="1">
-      <c r="B29" s="11" t="inlineStr">
+    <row r="34" ht="40" customHeight="1">
+      <c r="B34" s="10" t="inlineStr">
         <is>
           <t>Per goed voorspelde nummer 3 die doorgaat: 3 pt  (8 plekken totaal).</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="10" t="inlineStr">
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="9" t="inlineStr">
         <is>
           <t>Kampioen:</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="40" customHeight="1">
-      <c r="B31" s="11" t="inlineStr">
+    <row r="36" ht="40" customHeight="1">
+      <c r="B36" s="10" t="inlineStr">
         <is>
           <t>Verliezend finalist voorspeld: 16 pt.  Kampioen exact: 40 pt.</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="10" t="inlineStr">
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>Topscorer:</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="40" customHeight="1">
-      <c r="B33" s="11" t="inlineStr">
+    <row r="38" ht="40" customHeight="1">
+      <c r="B38" s="10" t="inlineStr">
         <is>
           <t>3e op topscorerslijst: 9 pt · 2e: 18 pt · 1e: 35 pt.  Exact aantal goals: +8 pt.</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="10" t="inlineStr">
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="9" t="inlineStr">
         <is>
           <t>Totaal goals:</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="40" customHeight="1">
-      <c r="B35" s="11" t="inlineStr">
+    <row r="40" ht="40" customHeight="1">
+      <c r="B40" s="10" t="inlineStr">
         <is>
           <t>Exact goed: 25 pt.  Per goal verschil: -1 pt.</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="10" t="inlineStr">
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="9" t="inlineStr">
         <is>
           <t>Verrassing:</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="40" customHeight="1">
-      <c r="B37" s="11" t="inlineStr">
+    <row r="42" ht="40" customHeight="1">
+      <c r="B42" s="10" t="inlineStr">
         <is>
           <t>Land buiten top-12 · punten schalen met hoe ver het komt (R16→winnaar) én hoe laag FIFA-gerankt. Zie tabel.</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="10" t="inlineStr">
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="9" t="inlineStr">
         <is>
           <t>Deceptie:</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="40" customHeight="1">
-      <c r="B39" s="11" t="inlineStr">
+    <row r="44" ht="40" customHeight="1">
+      <c r="B44" s="10" t="inlineStr">
         <is>
           <t>Land uit top-12 · punten schalen met hoe vroeg het uitvalt (groepsfase=meest) én hoe hoog gerankt. Zie tabel.</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="10" t="inlineStr">
+    <row r="45" ht="16" customHeight="1">
+      <c r="A45" s="9" t="inlineStr">
         <is>
           <t>Gele/rode kaarten:</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="40" customHeight="1">
-      <c r="B41" s="11" t="inlineStr">
+    <row r="46" ht="40" customHeight="1">
+      <c r="B46" s="10" t="inlineStr">
         <is>
           <t>Exact goed: 12 pt.  Per kaart verschil: -1 pt.  Geel en rood apart.</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="8" customHeight="1"/>
-    <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="4" t="inlineStr">
+    <row r="47" ht="8" customHeight="1"/>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>▶  GROEPSWEDSTRIJDEN  ·  vul in als '2-1' (thuis–uit, na 90 min)  ·  lichtblauwe vakjes invullen</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="12" t="inlineStr">
+    <row r="49" ht="16" customHeight="1">
+      <c r="A49" s="11" t="inlineStr">
         <is>
           <t>Groep A</t>
         </is>
       </c>
-      <c r="E44" s="13" t="inlineStr">
+      <c r="E49" s="12" t="inlineStr">
         <is>
           <t>voorsp.</t>
         </is>
       </c>
-      <c r="F44" s="13" t="inlineStr">
+      <c r="F49" s="12" t="inlineStr">
         <is>
           <t>uitslag</t>
         </is>
       </c>
-      <c r="G44" s="13" t="inlineStr">
+      <c r="G49" s="12" t="inlineStr">
         <is>
           <t>pt.</t>
         </is>
       </c>
-      <c r="I44" s="12" t="inlineStr">
+      <c r="I49" s="11" t="inlineStr">
         <is>
           <t>Groep B</t>
         </is>
       </c>
-      <c r="M44" s="13" t="inlineStr">
+      <c r="M49" s="12" t="inlineStr">
         <is>
           <t>voorsp.</t>
         </is>
       </c>
-      <c r="N44" s="13" t="inlineStr">
+      <c r="N49" s="12" t="inlineStr">
         <is>
           <t>uitslag</t>
         </is>
       </c>
-      <c r="O44" s="13" t="inlineStr">
+      <c r="O49" s="12" t="inlineStr">
         <is>
           <t>pt.</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="17" customHeight="1">
-      <c r="A45" s="14" t="n"/>
-      <c r="B45" s="15" t="inlineStr">
+    <row r="50" ht="17" customHeight="1">
+      <c r="A50" s="13" t="n"/>
+      <c r="B50" s="14" t="inlineStr">
         <is>
           <t>Mexico</t>
         </is>
       </c>
-      <c r="C45" s="16" t="n"/>
-      <c r="D45" s="17" t="inlineStr">
+      <c r="C50" s="15" t="n"/>
+      <c r="D50" s="16" t="inlineStr">
         <is>
           <t>Zuid-Afrika</t>
         </is>
       </c>
-      <c r="E45" s="6" t="n"/>
-      <c r="F45" s="18" t="inlineStr"/>
-      <c r="G45" s="18" t="inlineStr"/>
-      <c r="I45" s="19" t="n"/>
-      <c r="J45" s="15" t="inlineStr">
+      <c r="E50" s="5" t="n"/>
+      <c r="F50" s="17" t="inlineStr"/>
+      <c r="G50" s="17" t="inlineStr"/>
+      <c r="I50" s="18" t="n"/>
+      <c r="J50" s="14" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="K45" s="20" t="n"/>
-      <c r="L45" s="17" t="inlineStr">
+      <c r="K50" s="19" t="n"/>
+      <c r="L50" s="16" t="inlineStr">
         <is>
           <t>Zwitserland</t>
         </is>
       </c>
-      <c r="M45" s="6" t="n"/>
-      <c r="N45" s="18" t="inlineStr"/>
-      <c r="O45" s="18" t="inlineStr"/>
-    </row>
-    <row r="46" ht="17" customHeight="1">
-      <c r="A46" s="21" t="n"/>
-      <c r="B46" s="15" t="inlineStr">
+      <c r="M50" s="5" t="n"/>
+      <c r="N50" s="17" t="inlineStr"/>
+      <c r="O50" s="17" t="inlineStr"/>
+    </row>
+    <row r="51" ht="17" customHeight="1">
+      <c r="A51" s="20" t="n"/>
+      <c r="B51" s="14" t="inlineStr">
         <is>
           <t>Zuid-Korea</t>
         </is>
       </c>
-      <c r="C46" s="22" t="n"/>
-      <c r="D46" s="17" t="inlineStr">
+      <c r="C51" s="21" t="n"/>
+      <c r="D51" s="16" t="inlineStr">
         <is>
           <t>Tsjechië</t>
         </is>
       </c>
-      <c r="E46" s="6" t="n"/>
-      <c r="F46" s="18" t="inlineStr"/>
-      <c r="G46" s="18" t="inlineStr"/>
-      <c r="I46" s="23" t="n"/>
-      <c r="J46" s="15" t="inlineStr">
+      <c r="E51" s="5" t="n"/>
+      <c r="F51" s="17" t="inlineStr"/>
+      <c r="G51" s="17" t="inlineStr"/>
+      <c r="I51" s="22" t="n"/>
+      <c r="J51" s="14" t="inlineStr">
         <is>
           <t>Qatar</t>
         </is>
       </c>
-      <c r="K46" s="24" t="n"/>
-      <c r="L46" s="17" t="inlineStr">
+      <c r="K51" s="23" t="n"/>
+      <c r="L51" s="16" t="inlineStr">
         <is>
           <t>Bosnië-Herzegovina</t>
         </is>
       </c>
-      <c r="M46" s="6" t="n"/>
-      <c r="N46" s="18" t="inlineStr"/>
-      <c r="O46" s="18" t="inlineStr"/>
-    </row>
-    <row r="47" ht="17" customHeight="1">
-      <c r="A47" s="14" t="n"/>
-      <c r="B47" s="15" t="inlineStr">
+      <c r="M51" s="5" t="n"/>
+      <c r="N51" s="17" t="inlineStr"/>
+      <c r="O51" s="17" t="inlineStr"/>
+    </row>
+    <row r="52" ht="17" customHeight="1">
+      <c r="A52" s="13" t="n"/>
+      <c r="B52" s="14" t="inlineStr">
         <is>
           <t>Mexico</t>
         </is>
       </c>
-      <c r="C47" s="21" t="n"/>
-      <c r="D47" s="17" t="inlineStr">
+      <c r="C52" s="20" t="n"/>
+      <c r="D52" s="16" t="inlineStr">
         <is>
           <t>Zuid-Korea</t>
         </is>
       </c>
-      <c r="E47" s="6" t="n"/>
-      <c r="F47" s="18" t="inlineStr"/>
-      <c r="G47" s="18" t="inlineStr"/>
-      <c r="I47" s="19" t="n"/>
-      <c r="J47" s="15" t="inlineStr">
+      <c r="E52" s="5" t="n"/>
+      <c r="F52" s="17" t="inlineStr"/>
+      <c r="G52" s="17" t="inlineStr"/>
+      <c r="I52" s="18" t="n"/>
+      <c r="J52" s="14" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="K47" s="23" t="n"/>
-      <c r="L47" s="17" t="inlineStr">
+      <c r="K52" s="22" t="n"/>
+      <c r="L52" s="16" t="inlineStr">
         <is>
           <t>Qatar</t>
         </is>
       </c>
-      <c r="M47" s="6" t="n"/>
-      <c r="N47" s="18" t="inlineStr"/>
-      <c r="O47" s="18" t="inlineStr"/>
-    </row>
-    <row r="48" ht="17" customHeight="1">
-      <c r="A48" s="22" t="n"/>
-      <c r="B48" s="15" t="inlineStr">
+      <c r="M52" s="5" t="n"/>
+      <c r="N52" s="17" t="inlineStr"/>
+      <c r="O52" s="17" t="inlineStr"/>
+    </row>
+    <row r="53" ht="17" customHeight="1">
+      <c r="A53" s="21" t="n"/>
+      <c r="B53" s="14" t="inlineStr">
         <is>
           <t>Tsjechië</t>
         </is>
       </c>
-      <c r="C48" s="16" t="n"/>
-      <c r="D48" s="17" t="inlineStr">
+      <c r="C53" s="15" t="n"/>
+      <c r="D53" s="16" t="inlineStr">
         <is>
           <t>Zuid-Afrika</t>
         </is>
       </c>
-      <c r="E48" s="6" t="n"/>
-      <c r="F48" s="18" t="inlineStr"/>
-      <c r="G48" s="18" t="inlineStr"/>
-      <c r="I48" s="24" t="n"/>
-      <c r="J48" s="15" t="inlineStr">
+      <c r="E53" s="5" t="n"/>
+      <c r="F53" s="17" t="inlineStr"/>
+      <c r="G53" s="17" t="inlineStr"/>
+      <c r="I53" s="23" t="n"/>
+      <c r="J53" s="14" t="inlineStr">
         <is>
           <t>Bosnië-Herzegovina</t>
         </is>
       </c>
-      <c r="K48" s="20" t="n"/>
-      <c r="L48" s="17" t="inlineStr">
+      <c r="K53" s="19" t="n"/>
+      <c r="L53" s="16" t="inlineStr">
         <is>
           <t>Zwitserland</t>
         </is>
       </c>
-      <c r="M48" s="6" t="n"/>
-      <c r="N48" s="18" t="inlineStr"/>
-      <c r="O48" s="18" t="inlineStr"/>
-    </row>
-    <row r="49" ht="17" customHeight="1">
-      <c r="A49" s="22" t="n"/>
-      <c r="B49" s="15" t="inlineStr">
+      <c r="M53" s="5" t="n"/>
+      <c r="N53" s="17" t="inlineStr"/>
+      <c r="O53" s="17" t="inlineStr"/>
+    </row>
+    <row r="54" ht="17" customHeight="1">
+      <c r="A54" s="21" t="n"/>
+      <c r="B54" s="14" t="inlineStr">
         <is>
           <t>Tsjechië</t>
         </is>
       </c>
-      <c r="C49" s="14" t="n"/>
-      <c r="D49" s="17" t="inlineStr">
+      <c r="C54" s="13" t="n"/>
+      <c r="D54" s="16" t="inlineStr">
         <is>
           <t>Mexico</t>
         </is>
       </c>
-      <c r="E49" s="6" t="n"/>
-      <c r="F49" s="18" t="inlineStr"/>
-      <c r="G49" s="18" t="inlineStr"/>
-      <c r="I49" s="24" t="n"/>
-      <c r="J49" s="15" t="inlineStr">
+      <c r="E54" s="5" t="n"/>
+      <c r="F54" s="17" t="inlineStr"/>
+      <c r="G54" s="17" t="inlineStr"/>
+      <c r="I54" s="23" t="n"/>
+      <c r="J54" s="14" t="inlineStr">
         <is>
           <t>Bosnië-Herzegovina</t>
         </is>
       </c>
-      <c r="K49" s="19" t="n"/>
-      <c r="L49" s="17" t="inlineStr">
+      <c r="K54" s="18" t="n"/>
+      <c r="L54" s="16" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="M49" s="6" t="n"/>
-      <c r="N49" s="18" t="inlineStr"/>
-      <c r="O49" s="18" t="inlineStr"/>
-    </row>
-    <row r="50" ht="17" customHeight="1">
-      <c r="A50" s="16" t="n"/>
-      <c r="B50" s="15" t="inlineStr">
+      <c r="M54" s="5" t="n"/>
+      <c r="N54" s="17" t="inlineStr"/>
+      <c r="O54" s="17" t="inlineStr"/>
+    </row>
+    <row r="55" ht="17" customHeight="1">
+      <c r="A55" s="15" t="n"/>
+      <c r="B55" s="14" t="inlineStr">
         <is>
           <t>Zuid-Afrika</t>
         </is>
       </c>
-      <c r="C50" s="21" t="n"/>
-      <c r="D50" s="17" t="inlineStr">
+      <c r="C55" s="20" t="n"/>
+      <c r="D55" s="16" t="inlineStr">
         <is>
           <t>Zuid-Korea</t>
         </is>
       </c>
-      <c r="E50" s="6" t="n"/>
-      <c r="F50" s="18" t="inlineStr"/>
-      <c r="G50" s="18" t="inlineStr"/>
-      <c r="I50" s="20" t="n"/>
-      <c r="J50" s="15" t="inlineStr">
+      <c r="E55" s="5" t="n"/>
+      <c r="F55" s="17" t="inlineStr"/>
+      <c r="G55" s="17" t="inlineStr"/>
+      <c r="I55" s="19" t="n"/>
+      <c r="J55" s="14" t="inlineStr">
         <is>
           <t>Zwitserland</t>
         </is>
       </c>
-      <c r="K50" s="23" t="n"/>
-      <c r="L50" s="17" t="inlineStr">
+      <c r="K55" s="22" t="n"/>
+      <c r="L55" s="16" t="inlineStr">
         <is>
           <t>Qatar</t>
         </is>
       </c>
-      <c r="M50" s="6" t="n"/>
-      <c r="N50" s="18" t="inlineStr"/>
-      <c r="O50" s="18" t="inlineStr"/>
-    </row>
-    <row r="51" ht="17" customHeight="1">
-      <c r="A51" s="5" t="inlineStr">
+      <c r="M55" s="5" t="n"/>
+      <c r="N55" s="17" t="inlineStr"/>
+      <c r="O55" s="17" t="inlineStr"/>
+    </row>
+    <row r="56" ht="17" customHeight="1">
+      <c r="A56" s="4" t="inlineStr">
         <is>
           <t>Groepswinnaar:</t>
         </is>
       </c>
-      <c r="E51" s="18" t="inlineStr">
+      <c r="E56" s="17" t="inlineStr">
         <is>
           <t>↳ niet invullen</t>
         </is>
       </c>
-      <c r="I51" s="5" t="inlineStr">
+      <c r="I56" s="4" t="inlineStr">
         <is>
           <t>Groepswinnaar:</t>
         </is>
       </c>
-      <c r="M51" s="18" t="inlineStr">
+      <c r="M56" s="17" t="inlineStr">
         <is>
           <t>↳ niet invullen</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="17" customHeight="1">
-      <c r="A52" s="5" t="inlineStr">
+    <row r="57" ht="17" customHeight="1">
+      <c r="A57" s="4" t="inlineStr">
         <is>
           <t>Runner-up:</t>
         </is>
       </c>
-      <c r="E52" s="18" t="inlineStr">
+      <c r="E57" s="17" t="inlineStr">
         <is>
           <t>↳ niet invullen</t>
         </is>
       </c>
-      <c r="I52" s="5" t="inlineStr">
+      <c r="I57" s="4" t="inlineStr">
         <is>
           <t>Runner-up:</t>
         </is>
       </c>
-      <c r="M52" s="18" t="inlineStr">
+      <c r="M57" s="17" t="inlineStr">
         <is>
           <t>↳ niet invullen</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="6" customHeight="1"/>
-    <row r="54" ht="16" customHeight="1">
-      <c r="A54" s="12" t="inlineStr">
+    <row r="58" ht="6" customHeight="1"/>
+    <row r="59" ht="16" customHeight="1">
+      <c r="A59" s="11" t="inlineStr">
         <is>
           <t>Groep C</t>
         </is>
       </c>
-      <c r="E54" s="13" t="inlineStr">
+      <c r="E59" s="12" t="inlineStr">
         <is>
           <t>voorsp.</t>
         </is>
       </c>
-      <c r="F54" s="13" t="inlineStr">
+      <c r="F59" s="12" t="inlineStr">
         <is>
           <t>uitslag</t>
         </is>
       </c>
-      <c r="G54" s="13" t="inlineStr">
+      <c r="G59" s="12" t="inlineStr">
         <is>
           <t>pt.</t>
         </is>
       </c>
-      <c r="I54" s="12" t="inlineStr">
+      <c r="I59" s="11" t="inlineStr">
         <is>
           <t>Groep D</t>
         </is>
       </c>
-      <c r="M54" s="13" t="inlineStr">
+      <c r="M59" s="12" t="inlineStr">
         <is>
           <t>voorsp.</t>
         </is>
       </c>
-      <c r="N54" s="13" t="inlineStr">
+      <c r="N59" s="12" t="inlineStr">
         <is>
           <t>uitslag</t>
         </is>
       </c>
-      <c r="O54" s="13" t="inlineStr">
+      <c r="O59" s="12" t="inlineStr">
         <is>
           <t>pt.</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="17" customHeight="1">
-      <c r="A55" s="25" t="n"/>
-      <c r="B55" s="15" t="inlineStr">
+    <row r="60" ht="17" customHeight="1">
+      <c r="A60" s="24" t="n"/>
+      <c r="B60" s="14" t="inlineStr">
         <is>
           <t>Brazilië</t>
         </is>
       </c>
-      <c r="C55" s="26" t="n"/>
-      <c r="D55" s="17" t="inlineStr">
+      <c r="C60" s="25" t="n"/>
+      <c r="D60" s="16" t="inlineStr">
         <is>
           <t>Marokko</t>
         </is>
       </c>
-      <c r="E55" s="6" t="n"/>
-      <c r="F55" s="18" t="inlineStr"/>
-      <c r="G55" s="18" t="inlineStr"/>
-      <c r="I55" s="27" t="n"/>
-      <c r="J55" s="15" t="inlineStr">
+      <c r="E60" s="5" t="n"/>
+      <c r="F60" s="17" t="inlineStr"/>
+      <c r="G60" s="17" t="inlineStr"/>
+      <c r="I60" s="26" t="n"/>
+      <c r="J60" s="14" t="inlineStr">
         <is>
           <t>Verenigde Staten</t>
         </is>
       </c>
-      <c r="K55" s="28" t="n"/>
-      <c r="L55" s="17" t="inlineStr">
+      <c r="K60" s="27" t="n"/>
+      <c r="L60" s="16" t="inlineStr">
         <is>
           <t>Paraguay</t>
         </is>
       </c>
-      <c r="M55" s="6" t="n"/>
-      <c r="N55" s="18" t="inlineStr"/>
-      <c r="O55" s="18" t="inlineStr"/>
-    </row>
-    <row r="56" ht="17" customHeight="1">
-      <c r="A56" s="29" t="n"/>
-      <c r="B56" s="15" t="inlineStr">
+      <c r="M60" s="5" t="n"/>
+      <c r="N60" s="17" t="inlineStr"/>
+      <c r="O60" s="17" t="inlineStr"/>
+    </row>
+    <row r="61" ht="17" customHeight="1">
+      <c r="A61" s="28" t="n"/>
+      <c r="B61" s="14" t="inlineStr">
         <is>
           <t>Haïti</t>
         </is>
       </c>
-      <c r="C56" s="30" t="n"/>
-      <c r="D56" s="17" t="inlineStr">
+      <c r="C61" s="29" t="n"/>
+      <c r="D61" s="16" t="inlineStr">
         <is>
           <t>Schotland</t>
         </is>
       </c>
-      <c r="E56" s="6" t="n"/>
-      <c r="F56" s="18" t="inlineStr"/>
-      <c r="G56" s="18" t="inlineStr"/>
-      <c r="I56" s="31" t="n"/>
-      <c r="J56" s="15" t="inlineStr">
+      <c r="E61" s="5" t="n"/>
+      <c r="F61" s="17" t="inlineStr"/>
+      <c r="G61" s="17" t="inlineStr"/>
+      <c r="I61" s="30" t="n"/>
+      <c r="J61" s="14" t="inlineStr">
         <is>
           <t>Australië</t>
         </is>
       </c>
-      <c r="K56" s="32" t="n"/>
-      <c r="L56" s="17" t="inlineStr">
+      <c r="K61" s="31" t="n"/>
+      <c r="L61" s="16" t="inlineStr">
         <is>
           <t>Turkije</t>
         </is>
       </c>
-      <c r="M56" s="6" t="n"/>
-      <c r="N56" s="18" t="inlineStr"/>
-      <c r="O56" s="18" t="inlineStr"/>
-    </row>
-    <row r="57" ht="17" customHeight="1">
-      <c r="A57" s="25" t="n"/>
-      <c r="B57" s="15" t="inlineStr">
+      <c r="M61" s="5" t="n"/>
+      <c r="N61" s="17" t="inlineStr"/>
+      <c r="O61" s="17" t="inlineStr"/>
+    </row>
+    <row r="62" ht="17" customHeight="1">
+      <c r="A62" s="24" t="n"/>
+      <c r="B62" s="14" t="inlineStr">
         <is>
           <t>Brazilië</t>
         </is>
       </c>
-      <c r="C57" s="29" t="n"/>
-      <c r="D57" s="17" t="inlineStr">
+      <c r="C62" s="28" t="n"/>
+      <c r="D62" s="16" t="inlineStr">
         <is>
           <t>Haïti</t>
         </is>
       </c>
-      <c r="E57" s="6" t="n"/>
-      <c r="F57" s="18" t="inlineStr"/>
-      <c r="G57" s="18" t="inlineStr"/>
-      <c r="I57" s="27" t="n"/>
-      <c r="J57" s="15" t="inlineStr">
+      <c r="E62" s="5" t="n"/>
+      <c r="F62" s="17" t="inlineStr"/>
+      <c r="G62" s="17" t="inlineStr"/>
+      <c r="I62" s="26" t="n"/>
+      <c r="J62" s="14" t="inlineStr">
         <is>
           <t>Verenigde Staten</t>
         </is>
       </c>
-      <c r="K57" s="31" t="n"/>
-      <c r="L57" s="17" t="inlineStr">
+      <c r="K62" s="30" t="n"/>
+      <c r="L62" s="16" t="inlineStr">
         <is>
           <t>Australië</t>
         </is>
       </c>
-      <c r="M57" s="6" t="n"/>
-      <c r="N57" s="18" t="inlineStr"/>
-      <c r="O57" s="18" t="inlineStr"/>
-    </row>
-    <row r="58" ht="17" customHeight="1">
-      <c r="A58" s="30" t="n"/>
-      <c r="B58" s="15" t="inlineStr">
+      <c r="M62" s="5" t="n"/>
+      <c r="N62" s="17" t="inlineStr"/>
+      <c r="O62" s="17" t="inlineStr"/>
+    </row>
+    <row r="63" ht="17" customHeight="1">
+      <c r="A63" s="29" t="n"/>
+      <c r="B63" s="14" t="inlineStr">
         <is>
           <t>Schotland</t>
         </is>
       </c>
-      <c r="C58" s="26" t="n"/>
-      <c r="D58" s="17" t="inlineStr">
+      <c r="C63" s="25" t="n"/>
+      <c r="D63" s="16" t="inlineStr">
         <is>
           <t>Marokko</t>
         </is>
       </c>
-      <c r="E58" s="6" t="n"/>
-      <c r="F58" s="18" t="inlineStr"/>
-      <c r="G58" s="18" t="inlineStr"/>
-      <c r="I58" s="32" t="n"/>
-      <c r="J58" s="15" t="inlineStr">
+      <c r="E63" s="5" t="n"/>
+      <c r="F63" s="17" t="inlineStr"/>
+      <c r="G63" s="17" t="inlineStr"/>
+      <c r="I63" s="31" t="n"/>
+      <c r="J63" s="14" t="inlineStr">
         <is>
           <t>Turkije</t>
         </is>
       </c>
-      <c r="K58" s="28" t="n"/>
-      <c r="L58" s="17" t="inlineStr">
+      <c r="K63" s="27" t="n"/>
+      <c r="L63" s="16" t="inlineStr">
         <is>
           <t>Paraguay</t>
         </is>
       </c>
-      <c r="M58" s="6" t="n"/>
-      <c r="N58" s="18" t="inlineStr"/>
-      <c r="O58" s="18" t="inlineStr"/>
-    </row>
-    <row r="59" ht="17" customHeight="1">
-      <c r="A59" s="30" t="n"/>
-      <c r="B59" s="15" t="inlineStr">
+      <c r="M63" s="5" t="n"/>
+      <c r="N63" s="17" t="inlineStr"/>
+      <c r="O63" s="17" t="inlineStr"/>
+    </row>
+    <row r="64" ht="17" customHeight="1">
+      <c r="A64" s="29" t="n"/>
+      <c r="B64" s="14" t="inlineStr">
         <is>
           <t>Schotland</t>
         </is>
       </c>
-      <c r="C59" s="25" t="n"/>
-      <c r="D59" s="17" t="inlineStr">
+      <c r="C64" s="24" t="n"/>
+      <c r="D64" s="16" t="inlineStr">
         <is>
           <t>Brazilië</t>
         </is>
       </c>
-      <c r="E59" s="6" t="n"/>
-      <c r="F59" s="18" t="inlineStr"/>
-      <c r="G59" s="18" t="inlineStr"/>
-      <c r="I59" s="32" t="n"/>
-      <c r="J59" s="15" t="inlineStr">
+      <c r="E64" s="5" t="n"/>
+      <c r="F64" s="17" t="inlineStr"/>
+      <c r="G64" s="17" t="inlineStr"/>
+      <c r="I64" s="31" t="n"/>
+      <c r="J64" s="14" t="inlineStr">
         <is>
           <t>Turkije</t>
         </is>
       </c>
-      <c r="K59" s="27" t="n"/>
-      <c r="L59" s="17" t="inlineStr">
+      <c r="K64" s="26" t="n"/>
+      <c r="L64" s="16" t="inlineStr">
         <is>
           <t>Verenigde Staten</t>
         </is>
       </c>
-      <c r="M59" s="6" t="n"/>
-      <c r="N59" s="18" t="inlineStr"/>
-      <c r="O59" s="18" t="inlineStr"/>
-    </row>
-    <row r="60" ht="17" customHeight="1">
-      <c r="A60" s="26" t="n"/>
-      <c r="B60" s="15" t="inlineStr">
+      <c r="M64" s="5" t="n"/>
+      <c r="N64" s="17" t="inlineStr"/>
+      <c r="O64" s="17" t="inlineStr"/>
+    </row>
+    <row r="65" ht="17" customHeight="1">
+      <c r="A65" s="25" t="n"/>
+      <c r="B65" s="14" t="inlineStr">
         <is>
           <t>Marokko</t>
         </is>
       </c>
-      <c r="C60" s="29" t="n"/>
-      <c r="D60" s="17" t="inlineStr">
+      <c r="C65" s="28" t="n"/>
+      <c r="D65" s="16" t="inlineStr">
         <is>
           <t>Haïti</t>
         </is>
       </c>
-      <c r="E60" s="6" t="n"/>
-      <c r="F60" s="18" t="inlineStr"/>
-      <c r="G60" s="18" t="inlineStr"/>
-      <c r="I60" s="28" t="n"/>
-      <c r="J60" s="15" t="inlineStr">
+      <c r="E65" s="5" t="n"/>
+      <c r="F65" s="17" t="inlineStr"/>
+      <c r="G65" s="17" t="inlineStr"/>
+      <c r="I65" s="27" t="n"/>
+      <c r="J65" s="14" t="inlineStr">
         <is>
           <t>Paraguay</t>
         </is>
       </c>
-      <c r="K60" s="31" t="n"/>
-      <c r="L60" s="17" t="inlineStr">
+      <c r="K65" s="30" t="n"/>
+      <c r="L65" s="16" t="inlineStr">
         <is>
           <t>Australië</t>
         </is>
       </c>
-      <c r="M60" s="6" t="n"/>
-      <c r="N60" s="18" t="inlineStr"/>
-      <c r="O60" s="18" t="inlineStr"/>
-    </row>
-    <row r="61" ht="17" customHeight="1">
-      <c r="A61" s="5" t="inlineStr">
+      <c r="M65" s="5" t="n"/>
+      <c r="N65" s="17" t="inlineStr"/>
+      <c r="O65" s="17" t="inlineStr"/>
+    </row>
+    <row r="66" ht="17" customHeight="1">
+      <c r="A66" s="4" t="inlineStr">
         <is>
           <t>Groepswinnaar:</t>
         </is>
       </c>
-      <c r="E61" s="18" t="inlineStr">
+      <c r="E66" s="17" t="inlineStr">
         <is>
           <t>↳ niet invullen</t>
         </is>
       </c>
-      <c r="I61" s="5" t="inlineStr">
+      <c r="I66" s="4" t="inlineStr">
         <is>
           <t>Groepswinnaar:</t>
         </is>
       </c>
-      <c r="M61" s="18" t="inlineStr">
+      <c r="M66" s="17" t="inlineStr">
         <is>
           <t>↳ niet invullen</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="17" customHeight="1">
-      <c r="A62" s="5" t="inlineStr">
+    <row r="67" ht="17" customHeight="1">
+      <c r="A67" s="4" t="inlineStr">
         <is>
           <t>Runner-up:</t>
         </is>
       </c>
-      <c r="E62" s="18" t="inlineStr">
+      <c r="E67" s="17" t="inlineStr">
         <is>
           <t>↳ niet invullen</t>
         </is>
       </c>
-      <c r="I62" s="5" t="inlineStr">
+      <c r="I67" s="4" t="inlineStr">
         <is>
           <t>Runner-up:</t>
         </is>
       </c>
-      <c r="M62" s="18" t="inlineStr">
+      <c r="M67" s="17" t="inlineStr">
         <is>
           <t>↳ niet invullen</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="6" customHeight="1"/>
-    <row r="64" ht="16" customHeight="1">
-      <c r="A64" s="12" t="inlineStr">
+    <row r="68" ht="6" customHeight="1"/>
+    <row r="69" ht="16" customHeight="1">
+      <c r="A69" s="11" t="inlineStr">
         <is>
           <t>Groep E</t>
         </is>
       </c>
-      <c r="E64" s="13" t="inlineStr">
+      <c r="E69" s="12" t="inlineStr">
         <is>
           <t>voorsp.</t>
         </is>
       </c>
-      <c r="F64" s="13" t="inlineStr">
+      <c r="F69" s="12" t="inlineStr">
         <is>
           <t>uitslag</t>
         </is>
       </c>
-      <c r="G64" s="13" t="inlineStr">
+      <c r="G69" s="12" t="inlineStr">
         <is>
           <t>pt.</t>
         </is>
       </c>
-      <c r="I64" s="12" t="inlineStr">
+      <c r="I69" s="11" t="inlineStr">
         <is>
           <t>Groep F</t>
         </is>
       </c>
-      <c r="M64" s="13" t="inlineStr">
+      <c r="M69" s="12" t="inlineStr">
         <is>
           <t>voorsp.</t>
         </is>
       </c>
-      <c r="N64" s="13" t="inlineStr">
+      <c r="N69" s="12" t="inlineStr">
         <is>
           <t>uitslag</t>
         </is>
       </c>
-      <c r="O64" s="13" t="inlineStr">
+      <c r="O69" s="12" t="inlineStr">
         <is>
           <t>pt.</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="17" customHeight="1">
-      <c r="A65" s="20" t="n"/>
-      <c r="B65" s="15" t="inlineStr">
+    <row r="70" ht="17" customHeight="1">
+      <c r="A70" s="19" t="n"/>
+      <c r="B70" s="14" t="inlineStr">
         <is>
           <t>Duitsland</t>
         </is>
       </c>
-      <c r="C65" s="33" t="n"/>
-      <c r="D65" s="17" t="inlineStr">
+      <c r="C70" s="32" t="n"/>
+      <c r="D70" s="16" t="inlineStr">
         <is>
           <t>Curaçao</t>
         </is>
       </c>
-      <c r="E65" s="6" t="n"/>
-      <c r="F65" s="18" t="inlineStr"/>
-      <c r="G65" s="18" t="inlineStr"/>
-      <c r="I65" s="34" t="n"/>
-      <c r="J65" s="15" t="inlineStr">
+      <c r="E70" s="5" t="n"/>
+      <c r="F70" s="17" t="inlineStr"/>
+      <c r="G70" s="17" t="inlineStr"/>
+      <c r="I70" s="33" t="n"/>
+      <c r="J70" s="14" t="inlineStr">
         <is>
           <t>Nederland</t>
         </is>
       </c>
-      <c r="K65" s="35" t="n"/>
-      <c r="L65" s="17" t="inlineStr">
+      <c r="K70" s="34" t="n"/>
+      <c r="L70" s="16" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="M65" s="6" t="n"/>
-      <c r="N65" s="18" t="inlineStr"/>
-      <c r="O65" s="18" t="inlineStr"/>
-    </row>
-    <row r="66" ht="17" customHeight="1">
-      <c r="A66" s="36" t="n"/>
-      <c r="B66" s="15" t="inlineStr">
+      <c r="M70" s="5" t="n"/>
+      <c r="N70" s="17" t="inlineStr"/>
+      <c r="O70" s="17" t="inlineStr"/>
+    </row>
+    <row r="71" ht="17" customHeight="1">
+      <c r="A71" s="35" t="n"/>
+      <c r="B71" s="14" t="inlineStr">
         <is>
           <t>Ivoorkust</t>
         </is>
       </c>
-      <c r="C66" s="37" t="n"/>
-      <c r="D66" s="17" t="inlineStr">
+      <c r="C71" s="36" t="n"/>
+      <c r="D71" s="16" t="inlineStr">
         <is>
           <t>Ecuador</t>
         </is>
       </c>
-      <c r="E66" s="6" t="n"/>
-      <c r="F66" s="18" t="inlineStr"/>
-      <c r="G66" s="18" t="inlineStr"/>
-      <c r="I66" s="38" t="n"/>
-      <c r="J66" s="15" t="inlineStr">
+      <c r="E71" s="5" t="n"/>
+      <c r="F71" s="17" t="inlineStr"/>
+      <c r="G71" s="17" t="inlineStr"/>
+      <c r="I71" s="37" t="n"/>
+      <c r="J71" s="14" t="inlineStr">
         <is>
           <t>Zweden</t>
         </is>
       </c>
-      <c r="K66" s="32" t="n"/>
-      <c r="L66" s="17" t="inlineStr">
+      <c r="K71" s="31" t="n"/>
+      <c r="L71" s="16" t="inlineStr">
         <is>
           <t>Tunesië</t>
         </is>
       </c>
-      <c r="M66" s="6" t="n"/>
-      <c r="N66" s="18" t="inlineStr"/>
-      <c r="O66" s="18" t="inlineStr"/>
-    </row>
-    <row r="67" ht="17" customHeight="1">
-      <c r="A67" s="20" t="n"/>
-      <c r="B67" s="15" t="inlineStr">
+      <c r="M71" s="5" t="n"/>
+      <c r="N71" s="17" t="inlineStr"/>
+      <c r="O71" s="17" t="inlineStr"/>
+    </row>
+    <row r="72" ht="17" customHeight="1">
+      <c r="A72" s="19" t="n"/>
+      <c r="B72" s="14" t="inlineStr">
         <is>
           <t>Duitsland</t>
         </is>
       </c>
-      <c r="C67" s="36" t="n"/>
-      <c r="D67" s="17" t="inlineStr">
+      <c r="C72" s="35" t="n"/>
+      <c r="D72" s="16" t="inlineStr">
         <is>
           <t>Ivoorkust</t>
         </is>
       </c>
-      <c r="E67" s="6" t="n"/>
-      <c r="F67" s="18" t="inlineStr"/>
-      <c r="G67" s="18" t="inlineStr"/>
-      <c r="I67" s="34" t="n"/>
-      <c r="J67" s="15" t="inlineStr">
+      <c r="E72" s="5" t="n"/>
+      <c r="F72" s="17" t="inlineStr"/>
+      <c r="G72" s="17" t="inlineStr"/>
+      <c r="I72" s="33" t="n"/>
+      <c r="J72" s="14" t="inlineStr">
         <is>
           <t>Nederland</t>
         </is>
       </c>
-      <c r="K67" s="38" t="n"/>
-      <c r="L67" s="17" t="inlineStr">
+      <c r="K72" s="37" t="n"/>
+      <c r="L72" s="16" t="inlineStr">
         <is>
           <t>Zweden</t>
         </is>
       </c>
-      <c r="M67" s="6" t="n"/>
-      <c r="N67" s="18" t="inlineStr"/>
-      <c r="O67" s="18" t="inlineStr"/>
-    </row>
-    <row r="68" ht="17" customHeight="1">
-      <c r="A68" s="37" t="n"/>
-      <c r="B68" s="15" t="inlineStr">
+      <c r="M72" s="5" t="n"/>
+      <c r="N72" s="17" t="inlineStr"/>
+      <c r="O72" s="17" t="inlineStr"/>
+    </row>
+    <row r="73" ht="17" customHeight="1">
+      <c r="A73" s="36" t="n"/>
+      <c r="B73" s="14" t="inlineStr">
         <is>
           <t>Ecuador</t>
         </is>
       </c>
-      <c r="C68" s="33" t="n"/>
-      <c r="D68" s="17" t="inlineStr">
+      <c r="C73" s="32" t="n"/>
+      <c r="D73" s="16" t="inlineStr">
         <is>
           <t>Curaçao</t>
         </is>
       </c>
-      <c r="E68" s="6" t="n"/>
-      <c r="F68" s="18" t="inlineStr"/>
-      <c r="G68" s="18" t="inlineStr"/>
-      <c r="I68" s="32" t="n"/>
-      <c r="J68" s="15" t="inlineStr">
+      <c r="E73" s="5" t="n"/>
+      <c r="F73" s="17" t="inlineStr"/>
+      <c r="G73" s="17" t="inlineStr"/>
+      <c r="I73" s="31" t="n"/>
+      <c r="J73" s="14" t="inlineStr">
         <is>
           <t>Tunesië</t>
         </is>
       </c>
-      <c r="K68" s="35" t="n"/>
-      <c r="L68" s="17" t="inlineStr">
+      <c r="K73" s="34" t="n"/>
+      <c r="L73" s="16" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="M68" s="6" t="n"/>
-      <c r="N68" s="18" t="inlineStr"/>
-      <c r="O68" s="18" t="inlineStr"/>
-    </row>
-    <row r="69" ht="17" customHeight="1">
-      <c r="A69" s="37" t="n"/>
-      <c r="B69" s="15" t="inlineStr">
+      <c r="M73" s="5" t="n"/>
+      <c r="N73" s="17" t="inlineStr"/>
+      <c r="O73" s="17" t="inlineStr"/>
+    </row>
+    <row r="74" ht="17" customHeight="1">
+      <c r="A74" s="36" t="n"/>
+      <c r="B74" s="14" t="inlineStr">
         <is>
           <t>Ecuador</t>
         </is>
       </c>
-      <c r="C69" s="20" t="n"/>
-      <c r="D69" s="17" t="inlineStr">
+      <c r="C74" s="19" t="n"/>
+      <c r="D74" s="16" t="inlineStr">
         <is>
           <t>Duitsland</t>
         </is>
       </c>
-      <c r="E69" s="6" t="n"/>
-      <c r="F69" s="18" t="inlineStr"/>
-      <c r="G69" s="18" t="inlineStr"/>
-      <c r="I69" s="32" t="n"/>
-      <c r="J69" s="15" t="inlineStr">
+      <c r="E74" s="5" t="n"/>
+      <c r="F74" s="17" t="inlineStr"/>
+      <c r="G74" s="17" t="inlineStr"/>
+      <c r="I74" s="31" t="n"/>
+      <c r="J74" s="14" t="inlineStr">
         <is>
           <t>Tunesië</t>
         </is>
       </c>
-      <c r="K69" s="34" t="n"/>
-      <c r="L69" s="17" t="inlineStr">
+      <c r="K74" s="33" t="n"/>
+      <c r="L74" s="16" t="inlineStr">
         <is>
           <t>Nederland</t>
         </is>
       </c>
-      <c r="M69" s="6" t="n"/>
-      <c r="N69" s="18" t="inlineStr"/>
-      <c r="O69" s="18" t="inlineStr"/>
-    </row>
-    <row r="70" ht="17" customHeight="1">
-      <c r="A70" s="33" t="n"/>
-      <c r="B70" s="15" t="inlineStr">
+      <c r="M74" s="5" t="n"/>
+      <c r="N74" s="17" t="inlineStr"/>
+      <c r="O74" s="17" t="inlineStr"/>
+    </row>
+    <row r="75" ht="17" customHeight="1">
+      <c r="A75" s="32" t="n"/>
+      <c r="B75" s="14" t="inlineStr">
         <is>
           <t>Curaçao</t>
         </is>
       </c>
-      <c r="C70" s="36" t="n"/>
-      <c r="D70" s="17" t="inlineStr">
+      <c r="C75" s="35" t="n"/>
+      <c r="D75" s="16" t="inlineStr">
         <is>
           <t>Ivoorkust</t>
         </is>
       </c>
-      <c r="E70" s="6" t="n"/>
-      <c r="F70" s="18" t="inlineStr"/>
-      <c r="G70" s="18" t="inlineStr"/>
-      <c r="I70" s="35" t="n"/>
-      <c r="J70" s="15" t="inlineStr">
+      <c r="E75" s="5" t="n"/>
+      <c r="F75" s="17" t="inlineStr"/>
+      <c r="G75" s="17" t="inlineStr"/>
+      <c r="I75" s="34" t="n"/>
+      <c r="J75" s="14" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="K70" s="38" t="n"/>
-      <c r="L70" s="17" t="inlineStr">
+      <c r="K75" s="37" t="n"/>
+      <c r="L75" s="16" t="inlineStr">
         <is>
           <t>Zweden</t>
         </is>
       </c>
-      <c r="M70" s="6" t="n"/>
-      <c r="N70" s="18" t="inlineStr"/>
-      <c r="O70" s="18" t="inlineStr"/>
-    </row>
-    <row r="71" ht="17" customHeight="1">
-      <c r="A71" s="5" t="inlineStr">
+      <c r="M75" s="5" t="n"/>
+      <c r="N75" s="17" t="inlineStr"/>
+      <c r="O75" s="17" t="inlineStr"/>
+    </row>
+    <row r="76" ht="17" customHeight="1">
+      <c r="A76" s="4" t="inlineStr">
         <is>
           <t>Groepswinnaar:</t>
         </is>
       </c>
-      <c r="E71" s="18" t="inlineStr">
+      <c r="E76" s="17" t="inlineStr">
         <is>
           <t>↳ niet invullen</t>
         </is>
       </c>
-      <c r="I71" s="5" t="inlineStr">
+      <c r="I76" s="4" t="inlineStr">
         <is>
           <t>Groepswinnaar:</t>
         </is>
       </c>
-      <c r="M71" s="18" t="inlineStr">
+      <c r="M76" s="17" t="inlineStr">
         <is>
           <t>↳ niet invullen</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="17" customHeight="1">
-      <c r="A72" s="5" t="inlineStr">
+    <row r="77" ht="17" customHeight="1">
+      <c r="A77" s="4" t="inlineStr">
         <is>
           <t>Runner-up:</t>
         </is>
       </c>
-      <c r="E72" s="18" t="inlineStr">
+      <c r="E77" s="17" t="inlineStr">
         <is>
           <t>↳ niet invullen</t>
         </is>
       </c>
-      <c r="I72" s="5" t="inlineStr">
+      <c r="I77" s="4" t="inlineStr">
         <is>
           <t>Runner-up:</t>
         </is>
       </c>
-      <c r="M72" s="18" t="inlineStr">
+      <c r="M77" s="17" t="inlineStr">
         <is>
           <t>↳ niet invullen</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="6" customHeight="1"/>
-    <row r="74" ht="16" customHeight="1">
-      <c r="A74" s="12" t="inlineStr">
+    <row r="78" ht="6" customHeight="1"/>
+    <row r="79" ht="16" customHeight="1">
+      <c r="A79" s="11" t="inlineStr">
         <is>
           <t>Groep G</t>
         </is>
       </c>
-      <c r="E74" s="13" t="inlineStr">
+      <c r="E79" s="12" t="inlineStr">
         <is>
           <t>voorsp.</t>
         </is>
       </c>
-      <c r="F74" s="13" t="inlineStr">
+      <c r="F79" s="12" t="inlineStr">
         <is>
           <t>uitslag</t>
         </is>
       </c>
-      <c r="G74" s="13" t="inlineStr">
+      <c r="G79" s="12" t="inlineStr">
         <is>
           <t>pt.</t>
         </is>
       </c>
-      <c r="I74" s="12" t="inlineStr">
+      <c r="I79" s="11" t="inlineStr">
         <is>
           <t>Groep H</t>
         </is>
       </c>
-      <c r="M74" s="13" t="inlineStr">
+      <c r="M79" s="12" t="inlineStr">
         <is>
           <t>voorsp.</t>
         </is>
       </c>
-      <c r="N74" s="13" t="inlineStr">
+      <c r="N79" s="12" t="inlineStr">
         <is>
           <t>uitslag</t>
         </is>
       </c>
-      <c r="O74" s="13" t="inlineStr">
+      <c r="O79" s="12" t="inlineStr">
         <is>
           <t>pt.</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="17" customHeight="1">
-      <c r="A75" s="39" t="n"/>
-      <c r="B75" s="15" t="inlineStr">
+    <row r="80" ht="17" customHeight="1">
+      <c r="A80" s="38" t="n"/>
+      <c r="B80" s="14" t="inlineStr">
         <is>
           <t>België</t>
         </is>
       </c>
-      <c r="C75" s="40" t="n"/>
-      <c r="D75" s="17" t="inlineStr">
+      <c r="C80" s="39" t="n"/>
+      <c r="D80" s="16" t="inlineStr">
         <is>
           <t>Egypte</t>
         </is>
       </c>
-      <c r="E75" s="6" t="n"/>
-      <c r="F75" s="18" t="inlineStr"/>
-      <c r="G75" s="18" t="inlineStr"/>
-      <c r="I75" s="41" t="n"/>
-      <c r="J75" s="15" t="inlineStr">
+      <c r="E80" s="5" t="n"/>
+      <c r="F80" s="17" t="inlineStr"/>
+      <c r="G80" s="17" t="inlineStr"/>
+      <c r="I80" s="40" t="n"/>
+      <c r="J80" s="14" t="inlineStr">
         <is>
           <t>Spanje</t>
         </is>
       </c>
-      <c r="K75" s="42" t="n"/>
-      <c r="L75" s="17" t="inlineStr">
+      <c r="K80" s="41" t="n"/>
+      <c r="L80" s="16" t="inlineStr">
         <is>
           <t>Kaapverdië</t>
         </is>
       </c>
-      <c r="M75" s="6" t="n"/>
-      <c r="N75" s="18" t="inlineStr"/>
-      <c r="O75" s="18" t="inlineStr"/>
-    </row>
-    <row r="76" ht="17" customHeight="1">
-      <c r="A76" s="43" t="n"/>
-      <c r="B76" s="15" t="inlineStr">
+      <c r="M80" s="5" t="n"/>
+      <c r="N80" s="17" t="inlineStr"/>
+      <c r="O80" s="17" t="inlineStr"/>
+    </row>
+    <row r="81" ht="17" customHeight="1">
+      <c r="A81" s="42" t="n"/>
+      <c r="B81" s="14" t="inlineStr">
         <is>
           <t>Iran</t>
         </is>
       </c>
-      <c r="C76" s="44" t="n"/>
-      <c r="D76" s="17" t="inlineStr">
+      <c r="C81" s="43" t="n"/>
+      <c r="D81" s="16" t="inlineStr">
         <is>
           <t>Nieuw-Zeeland</t>
         </is>
       </c>
-      <c r="E76" s="6" t="n"/>
-      <c r="F76" s="18" t="inlineStr"/>
-      <c r="G76" s="18" t="inlineStr"/>
-      <c r="I76" s="45" t="n"/>
-      <c r="J76" s="15" t="inlineStr">
+      <c r="E81" s="5" t="n"/>
+      <c r="F81" s="17" t="inlineStr"/>
+      <c r="G81" s="17" t="inlineStr"/>
+      <c r="I81" s="44" t="n"/>
+      <c r="J81" s="14" t="inlineStr">
         <is>
           <t>Saoedi-Arabië</t>
         </is>
       </c>
-      <c r="K76" s="46" t="n"/>
-      <c r="L76" s="17" t="inlineStr">
+      <c r="K81" s="45" t="n"/>
+      <c r="L81" s="16" t="inlineStr">
         <is>
           <t>Uruguay</t>
         </is>
       </c>
-      <c r="M76" s="6" t="n"/>
-      <c r="N76" s="18" t="inlineStr"/>
-      <c r="O76" s="18" t="inlineStr"/>
-    </row>
-    <row r="77" ht="17" customHeight="1">
-      <c r="A77" s="39" t="n"/>
-      <c r="B77" s="15" t="inlineStr">
+      <c r="M81" s="5" t="n"/>
+      <c r="N81" s="17" t="inlineStr"/>
+      <c r="O81" s="17" t="inlineStr"/>
+    </row>
+    <row r="82" ht="17" customHeight="1">
+      <c r="A82" s="38" t="n"/>
+      <c r="B82" s="14" t="inlineStr">
         <is>
           <t>België</t>
         </is>
       </c>
-      <c r="C77" s="43" t="n"/>
-      <c r="D77" s="17" t="inlineStr">
+      <c r="C82" s="42" t="n"/>
+      <c r="D82" s="16" t="inlineStr">
         <is>
           <t>Iran</t>
         </is>
       </c>
-      <c r="E77" s="6" t="n"/>
-      <c r="F77" s="18" t="inlineStr"/>
-      <c r="G77" s="18" t="inlineStr"/>
-      <c r="I77" s="41" t="n"/>
-      <c r="J77" s="15" t="inlineStr">
+      <c r="E82" s="5" t="n"/>
+      <c r="F82" s="17" t="inlineStr"/>
+      <c r="G82" s="17" t="inlineStr"/>
+      <c r="I82" s="40" t="n"/>
+      <c r="J82" s="14" t="inlineStr">
         <is>
           <t>Spanje</t>
         </is>
       </c>
-      <c r="K77" s="45" t="n"/>
-      <c r="L77" s="17" t="inlineStr">
+      <c r="K82" s="44" t="n"/>
+      <c r="L82" s="16" t="inlineStr">
         <is>
           <t>Saoedi-Arabië</t>
         </is>
       </c>
-      <c r="M77" s="6" t="n"/>
-      <c r="N77" s="18" t="inlineStr"/>
-      <c r="O77" s="18" t="inlineStr"/>
-    </row>
-    <row r="78" ht="17" customHeight="1">
-      <c r="A78" s="44" t="n"/>
-      <c r="B78" s="15" t="inlineStr">
+      <c r="M82" s="5" t="n"/>
+      <c r="N82" s="17" t="inlineStr"/>
+      <c r="O82" s="17" t="inlineStr"/>
+    </row>
+    <row r="83" ht="17" customHeight="1">
+      <c r="A83" s="43" t="n"/>
+      <c r="B83" s="14" t="inlineStr">
         <is>
           <t>Nieuw-Zeeland</t>
         </is>
       </c>
-      <c r="C78" s="40" t="n"/>
-      <c r="D78" s="17" t="inlineStr">
+      <c r="C83" s="39" t="n"/>
+      <c r="D83" s="16" t="inlineStr">
         <is>
           <t>Egypte</t>
         </is>
       </c>
-      <c r="E78" s="6" t="n"/>
-      <c r="F78" s="18" t="inlineStr"/>
-      <c r="G78" s="18" t="inlineStr"/>
-      <c r="I78" s="46" t="n"/>
-      <c r="J78" s="15" t="inlineStr">
+      <c r="E83" s="5" t="n"/>
+      <c r="F83" s="17" t="inlineStr"/>
+      <c r="G83" s="17" t="inlineStr"/>
+      <c r="I83" s="45" t="n"/>
+      <c r="J83" s="14" t="inlineStr">
         <is>
           <t>Uruguay</t>
         </is>
       </c>
-      <c r="K78" s="42" t="n"/>
-      <c r="L78" s="17" t="inlineStr">
+      <c r="K83" s="41" t="n"/>
+      <c r="L83" s="16" t="inlineStr">
         <is>
           <t>Kaapverdië</t>
         </is>
       </c>
-      <c r="M78" s="6" t="n"/>
-      <c r="N78" s="18" t="inlineStr"/>
-      <c r="O78" s="18" t="inlineStr"/>
-    </row>
-    <row r="79" ht="17" customHeight="1">
-      <c r="A79" s="44" t="n"/>
-      <c r="B79" s="15" t="inlineStr">
+      <c r="M83" s="5" t="n"/>
+      <c r="N83" s="17" t="inlineStr"/>
+      <c r="O83" s="17" t="inlineStr"/>
+    </row>
+    <row r="84" ht="17" customHeight="1">
+      <c r="A84" s="43" t="n"/>
+      <c r="B84" s="14" t="inlineStr">
         <is>
           <t>Nieuw-Zeeland</t>
         </is>
       </c>
-      <c r="C79" s="39" t="n"/>
-      <c r="D79" s="17" t="inlineStr">
+      <c r="C84" s="38" t="n"/>
+      <c r="D84" s="16" t="inlineStr">
         <is>
           <t>België</t>
         </is>
       </c>
-      <c r="E79" s="6" t="n"/>
-      <c r="F79" s="18" t="inlineStr"/>
-      <c r="G79" s="18" t="inlineStr"/>
-      <c r="I79" s="46" t="n"/>
-      <c r="J79" s="15" t="inlineStr">
+      <c r="E84" s="5" t="n"/>
+      <c r="F84" s="17" t="inlineStr"/>
+      <c r="G84" s="17" t="inlineStr"/>
+      <c r="I84" s="45" t="n"/>
+      <c r="J84" s="14" t="inlineStr">
         <is>
           <t>Uruguay</t>
         </is>
       </c>
-      <c r="K79" s="41" t="n"/>
-      <c r="L79" s="17" t="inlineStr">
+      <c r="K84" s="40" t="n"/>
+      <c r="L84" s="16" t="inlineStr">
         <is>
           <t>Spanje</t>
         </is>
       </c>
-      <c r="M79" s="6" t="n"/>
-      <c r="N79" s="18" t="inlineStr"/>
-      <c r="O79" s="18" t="inlineStr"/>
-    </row>
-    <row r="80" ht="17" customHeight="1">
-      <c r="A80" s="40" t="n"/>
-      <c r="B80" s="15" t="inlineStr">
+      <c r="M84" s="5" t="n"/>
+      <c r="N84" s="17" t="inlineStr"/>
+      <c r="O84" s="17" t="inlineStr"/>
+    </row>
+    <row r="85" ht="17" customHeight="1">
+      <c r="A85" s="39" t="n"/>
+      <c r="B85" s="14" t="inlineStr">
         <is>
           <t>Egypte</t>
         </is>
       </c>
-      <c r="C80" s="43" t="n"/>
-      <c r="D80" s="17" t="inlineStr">
+      <c r="C85" s="42" t="n"/>
+      <c r="D85" s="16" t="inlineStr">
         <is>
           <t>Iran</t>
         </is>
       </c>
-      <c r="E80" s="6" t="n"/>
-      <c r="F80" s="18" t="inlineStr"/>
-      <c r="G80" s="18" t="inlineStr"/>
-      <c r="I80" s="42" t="n"/>
-      <c r="J80" s="15" t="inlineStr">
+      <c r="E85" s="5" t="n"/>
+      <c r="F85" s="17" t="inlineStr"/>
+      <c r="G85" s="17" t="inlineStr"/>
+      <c r="I85" s="41" t="n"/>
+      <c r="J85" s="14" t="inlineStr">
         <is>
           <t>Kaapverdië</t>
         </is>
       </c>
-      <c r="K80" s="45" t="n"/>
-      <c r="L80" s="17" t="inlineStr">
+      <c r="K85" s="44" t="n"/>
+      <c r="L85" s="16" t="inlineStr">
         <is>
           <t>Saoedi-Arabië</t>
         </is>
       </c>
-      <c r="M80" s="6" t="n"/>
-      <c r="N80" s="18" t="inlineStr"/>
-      <c r="O80" s="18" t="inlineStr"/>
-    </row>
-    <row r="81" ht="17" customHeight="1">
-      <c r="A81" s="5" t="inlineStr">
+      <c r="M85" s="5" t="n"/>
+      <c r="N85" s="17" t="inlineStr"/>
+      <c r="O85" s="17" t="inlineStr"/>
+    </row>
+    <row r="86" ht="17" customHeight="1">
+      <c r="A86" s="4" t="inlineStr">
         <is>
           <t>Groepswinnaar:</t>
         </is>
       </c>
-      <c r="E81" s="18" t="inlineStr">
+      <c r="E86" s="17" t="inlineStr">
         <is>
           <t>↳ niet invullen</t>
         </is>
       </c>
-      <c r="I81" s="5" t="inlineStr">
+      <c r="I86" s="4" t="inlineStr">
         <is>
           <t>Groepswinnaar:</t>
         </is>
       </c>
-      <c r="M81" s="18" t="inlineStr">
+      <c r="M86" s="17" t="inlineStr">
         <is>
           <t>↳ niet invullen</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="17" customHeight="1">
-      <c r="A82" s="5" t="inlineStr">
+    <row r="87" ht="17" customHeight="1">
+      <c r="A87" s="4" t="inlineStr">
         <is>
           <t>Runner-up:</t>
         </is>
       </c>
-      <c r="E82" s="18" t="inlineStr">
+      <c r="E87" s="17" t="inlineStr">
         <is>
           <t>↳ niet invullen</t>
         </is>
       </c>
-      <c r="I82" s="5" t="inlineStr">
+      <c r="I87" s="4" t="inlineStr">
         <is>
           <t>Runner-up:</t>
         </is>
       </c>
-      <c r="M82" s="18" t="inlineStr">
+      <c r="M87" s="17" t="inlineStr">
         <is>
           <t>↳ niet invullen</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="6" customHeight="1"/>
-    <row r="84" ht="16" customHeight="1">
-      <c r="A84" s="12" t="inlineStr">
+    <row r="88" ht="6" customHeight="1"/>
+    <row r="89" ht="16" customHeight="1">
+      <c r="A89" s="11" t="inlineStr">
         <is>
           <t>Groep I</t>
         </is>
       </c>
-      <c r="E84" s="13" t="inlineStr">
+      <c r="E89" s="12" t="inlineStr">
         <is>
           <t>voorsp.</t>
         </is>
       </c>
-      <c r="F84" s="13" t="inlineStr">
+      <c r="F89" s="12" t="inlineStr">
         <is>
           <t>uitslag</t>
         </is>
       </c>
-      <c r="G84" s="13" t="inlineStr">
+      <c r="G89" s="12" t="inlineStr">
         <is>
           <t>pt.</t>
         </is>
       </c>
-      <c r="I84" s="12" t="inlineStr">
+      <c r="I89" s="11" t="inlineStr">
         <is>
           <t>Groep J</t>
         </is>
       </c>
-      <c r="M84" s="13" t="inlineStr">
+      <c r="M89" s="12" t="inlineStr">
         <is>
           <t>voorsp.</t>
         </is>
       </c>
-      <c r="N84" s="13" t="inlineStr">
+      <c r="N89" s="12" t="inlineStr">
         <is>
           <t>uitslag</t>
         </is>
       </c>
-      <c r="O84" s="13" t="inlineStr">
+      <c r="O89" s="12" t="inlineStr">
         <is>
           <t>pt.</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="17" customHeight="1">
-      <c r="A85" s="47" t="n"/>
-      <c r="B85" s="15" t="inlineStr">
+    <row r="90" ht="17" customHeight="1">
+      <c r="A90" s="46" t="n"/>
+      <c r="B90" s="14" t="inlineStr">
         <is>
           <t>Frankrijk</t>
         </is>
       </c>
-      <c r="C85" s="48" t="n"/>
-      <c r="D85" s="17" t="inlineStr">
+      <c r="C90" s="47" t="n"/>
+      <c r="D90" s="16" t="inlineStr">
         <is>
           <t>Senegal</t>
         </is>
       </c>
-      <c r="E85" s="6" t="n"/>
-      <c r="F85" s="18" t="inlineStr"/>
-      <c r="G85" s="18" t="inlineStr"/>
-      <c r="I85" s="49" t="n"/>
-      <c r="J85" s="15" t="inlineStr">
+      <c r="E90" s="5" t="n"/>
+      <c r="F90" s="17" t="inlineStr"/>
+      <c r="G90" s="17" t="inlineStr"/>
+      <c r="I90" s="48" t="n"/>
+      <c r="J90" s="14" t="inlineStr">
         <is>
           <t>Argentinië</t>
         </is>
       </c>
-      <c r="K85" s="50" t="n"/>
-      <c r="L85" s="17" t="inlineStr">
+      <c r="K90" s="49" t="n"/>
+      <c r="L90" s="16" t="inlineStr">
         <is>
           <t>Algerije</t>
         </is>
       </c>
-      <c r="M85" s="6" t="n"/>
-      <c r="N85" s="18" t="inlineStr"/>
-      <c r="O85" s="18" t="inlineStr"/>
-    </row>
-    <row r="86" ht="17" customHeight="1">
-      <c r="A86" s="51" t="n"/>
-      <c r="B86" s="15" t="inlineStr">
+      <c r="M90" s="5" t="n"/>
+      <c r="N90" s="17" t="inlineStr"/>
+      <c r="O90" s="17" t="inlineStr"/>
+    </row>
+    <row r="91" ht="17" customHeight="1">
+      <c r="A91" s="50" t="n"/>
+      <c r="B91" s="14" t="inlineStr">
         <is>
           <t>Noorwegen</t>
         </is>
       </c>
-      <c r="C86" s="32" t="n"/>
-      <c r="D86" s="17" t="inlineStr">
+      <c r="C91" s="31" t="n"/>
+      <c r="D91" s="16" t="inlineStr">
         <is>
           <t>Irak</t>
         </is>
       </c>
-      <c r="E86" s="6" t="n"/>
-      <c r="F86" s="18" t="inlineStr"/>
-      <c r="G86" s="18" t="inlineStr"/>
-      <c r="I86" s="52" t="n"/>
-      <c r="J86" s="15" t="inlineStr">
+      <c r="E91" s="5" t="n"/>
+      <c r="F91" s="17" t="inlineStr"/>
+      <c r="G91" s="17" t="inlineStr"/>
+      <c r="I91" s="51" t="n"/>
+      <c r="J91" s="14" t="inlineStr">
         <is>
           <t>Oostenrijk</t>
         </is>
       </c>
-      <c r="K86" s="20" t="n"/>
-      <c r="L86" s="17" t="inlineStr">
+      <c r="K91" s="19" t="n"/>
+      <c r="L91" s="16" t="inlineStr">
         <is>
           <t>Jordanië</t>
         </is>
       </c>
-      <c r="M86" s="6" t="n"/>
-      <c r="N86" s="18" t="inlineStr"/>
-      <c r="O86" s="18" t="inlineStr"/>
-    </row>
-    <row r="87" ht="17" customHeight="1">
-      <c r="A87" s="47" t="n"/>
-      <c r="B87" s="15" t="inlineStr">
+      <c r="M91" s="5" t="n"/>
+      <c r="N91" s="17" t="inlineStr"/>
+      <c r="O91" s="17" t="inlineStr"/>
+    </row>
+    <row r="92" ht="17" customHeight="1">
+      <c r="A92" s="46" t="n"/>
+      <c r="B92" s="14" t="inlineStr">
         <is>
           <t>Frankrijk</t>
         </is>
       </c>
-      <c r="C87" s="51" t="n"/>
-      <c r="D87" s="17" t="inlineStr">
+      <c r="C92" s="50" t="n"/>
+      <c r="D92" s="16" t="inlineStr">
         <is>
           <t>Noorwegen</t>
         </is>
       </c>
-      <c r="E87" s="6" t="n"/>
-      <c r="F87" s="18" t="inlineStr"/>
-      <c r="G87" s="18" t="inlineStr"/>
-      <c r="I87" s="49" t="n"/>
-      <c r="J87" s="15" t="inlineStr">
+      <c r="E92" s="5" t="n"/>
+      <c r="F92" s="17" t="inlineStr"/>
+      <c r="G92" s="17" t="inlineStr"/>
+      <c r="I92" s="48" t="n"/>
+      <c r="J92" s="14" t="inlineStr">
         <is>
           <t>Argentinië</t>
         </is>
       </c>
-      <c r="K87" s="52" t="n"/>
-      <c r="L87" s="17" t="inlineStr">
+      <c r="K92" s="51" t="n"/>
+      <c r="L92" s="16" t="inlineStr">
         <is>
           <t>Oostenrijk</t>
         </is>
       </c>
-      <c r="M87" s="6" t="n"/>
-      <c r="N87" s="18" t="inlineStr"/>
-      <c r="O87" s="18" t="inlineStr"/>
-    </row>
-    <row r="88" ht="17" customHeight="1">
-      <c r="A88" s="32" t="n"/>
-      <c r="B88" s="15" t="inlineStr">
+      <c r="M92" s="5" t="n"/>
+      <c r="N92" s="17" t="inlineStr"/>
+      <c r="O92" s="17" t="inlineStr"/>
+    </row>
+    <row r="93" ht="17" customHeight="1">
+      <c r="A93" s="31" t="n"/>
+      <c r="B93" s="14" t="inlineStr">
         <is>
           <t>Irak</t>
         </is>
       </c>
-      <c r="C88" s="48" t="n"/>
-      <c r="D88" s="17" t="inlineStr">
+      <c r="C93" s="47" t="n"/>
+      <c r="D93" s="16" t="inlineStr">
         <is>
           <t>Senegal</t>
         </is>
       </c>
-      <c r="E88" s="6" t="n"/>
-      <c r="F88" s="18" t="inlineStr"/>
-      <c r="G88" s="18" t="inlineStr"/>
-      <c r="I88" s="20" t="n"/>
-      <c r="J88" s="15" t="inlineStr">
+      <c r="E93" s="5" t="n"/>
+      <c r="F93" s="17" t="inlineStr"/>
+      <c r="G93" s="17" t="inlineStr"/>
+      <c r="I93" s="19" t="n"/>
+      <c r="J93" s="14" t="inlineStr">
         <is>
           <t>Jordanië</t>
         </is>
       </c>
-      <c r="K88" s="50" t="n"/>
-      <c r="L88" s="17" t="inlineStr">
+      <c r="K93" s="49" t="n"/>
+      <c r="L93" s="16" t="inlineStr">
         <is>
           <t>Algerije</t>
         </is>
       </c>
-      <c r="M88" s="6" t="n"/>
-      <c r="N88" s="18" t="inlineStr"/>
-      <c r="O88" s="18" t="inlineStr"/>
-    </row>
-    <row r="89" ht="17" customHeight="1">
-      <c r="A89" s="32" t="n"/>
-      <c r="B89" s="15" t="inlineStr">
+      <c r="M93" s="5" t="n"/>
+      <c r="N93" s="17" t="inlineStr"/>
+      <c r="O93" s="17" t="inlineStr"/>
+    </row>
+    <row r="94" ht="17" customHeight="1">
+      <c r="A94" s="31" t="n"/>
+      <c r="B94" s="14" t="inlineStr">
         <is>
           <t>Irak</t>
         </is>
       </c>
-      <c r="C89" s="47" t="n"/>
-      <c r="D89" s="17" t="inlineStr">
+      <c r="C94" s="46" t="n"/>
+      <c r="D94" s="16" t="inlineStr">
         <is>
           <t>Frankrijk</t>
         </is>
       </c>
-      <c r="E89" s="6" t="n"/>
-      <c r="F89" s="18" t="inlineStr"/>
-      <c r="G89" s="18" t="inlineStr"/>
-      <c r="I89" s="20" t="n"/>
-      <c r="J89" s="15" t="inlineStr">
+      <c r="E94" s="5" t="n"/>
+      <c r="F94" s="17" t="inlineStr"/>
+      <c r="G94" s="17" t="inlineStr"/>
+      <c r="I94" s="19" t="n"/>
+      <c r="J94" s="14" t="inlineStr">
         <is>
           <t>Jordanië</t>
         </is>
       </c>
-      <c r="K89" s="49" t="n"/>
-      <c r="L89" s="17" t="inlineStr">
+      <c r="K94" s="48" t="n"/>
+      <c r="L94" s="16" t="inlineStr">
         <is>
           <t>Argentinië</t>
         </is>
       </c>
-      <c r="M89" s="6" t="n"/>
-      <c r="N89" s="18" t="inlineStr"/>
-      <c r="O89" s="18" t="inlineStr"/>
-    </row>
-    <row r="90" ht="17" customHeight="1">
-      <c r="A90" s="48" t="n"/>
-      <c r="B90" s="15" t="inlineStr">
+      <c r="M94" s="5" t="n"/>
+      <c r="N94" s="17" t="inlineStr"/>
+      <c r="O94" s="17" t="inlineStr"/>
+    </row>
+    <row r="95" ht="17" customHeight="1">
+      <c r="A95" s="47" t="n"/>
+      <c r="B95" s="14" t="inlineStr">
         <is>
           <t>Senegal</t>
         </is>
       </c>
-      <c r="C90" s="51" t="n"/>
-      <c r="D90" s="17" t="inlineStr">
+      <c r="C95" s="50" t="n"/>
+      <c r="D95" s="16" t="inlineStr">
         <is>
           <t>Noorwegen</t>
         </is>
       </c>
-      <c r="E90" s="6" t="n"/>
-      <c r="F90" s="18" t="inlineStr"/>
-      <c r="G90" s="18" t="inlineStr"/>
-      <c r="I90" s="50" t="n"/>
-      <c r="J90" s="15" t="inlineStr">
+      <c r="E95" s="5" t="n"/>
+      <c r="F95" s="17" t="inlineStr"/>
+      <c r="G95" s="17" t="inlineStr"/>
+      <c r="I95" s="49" t="n"/>
+      <c r="J95" s="14" t="inlineStr">
         <is>
           <t>Algerije</t>
         </is>
       </c>
-      <c r="K90" s="52" t="n"/>
-      <c r="L90" s="17" t="inlineStr">
+      <c r="K95" s="51" t="n"/>
+      <c r="L95" s="16" t="inlineStr">
         <is>
           <t>Oostenrijk</t>
         </is>
       </c>
-      <c r="M90" s="6" t="n"/>
-      <c r="N90" s="18" t="inlineStr"/>
-      <c r="O90" s="18" t="inlineStr"/>
-    </row>
-    <row r="91" ht="17" customHeight="1">
-      <c r="A91" s="5" t="inlineStr">
+      <c r="M95" s="5" t="n"/>
+      <c r="N95" s="17" t="inlineStr"/>
+      <c r="O95" s="17" t="inlineStr"/>
+    </row>
+    <row r="96" ht="17" customHeight="1">
+      <c r="A96" s="4" t="inlineStr">
         <is>
           <t>Groepswinnaar:</t>
         </is>
       </c>
-      <c r="E91" s="18" t="inlineStr">
+      <c r="E96" s="17" t="inlineStr">
         <is>
           <t>↳ niet invullen</t>
         </is>
       </c>
-      <c r="I91" s="5" t="inlineStr">
+      <c r="I96" s="4" t="inlineStr">
         <is>
           <t>Groepswinnaar:</t>
         </is>
       </c>
-      <c r="M91" s="18" t="inlineStr">
+      <c r="M96" s="17" t="inlineStr">
         <is>
           <t>↳ niet invullen</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="17" customHeight="1">
-      <c r="A92" s="5" t="inlineStr">
+    <row r="97" ht="17" customHeight="1">
+      <c r="A97" s="4" t="inlineStr">
         <is>
           <t>Runner-up:</t>
         </is>
       </c>
-      <c r="E92" s="18" t="inlineStr">
+      <c r="E97" s="17" t="inlineStr">
         <is>
           <t>↳ niet invullen</t>
         </is>
       </c>
-      <c r="I92" s="5" t="inlineStr">
+      <c r="I97" s="4" t="inlineStr">
         <is>
           <t>Runner-up:</t>
         </is>
       </c>
-      <c r="M92" s="18" t="inlineStr">
+      <c r="M97" s="17" t="inlineStr">
         <is>
           <t>↳ niet invullen</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="6" customHeight="1"/>
-    <row r="94" ht="16" customHeight="1">
-      <c r="A94" s="12" t="inlineStr">
+    <row r="98" ht="6" customHeight="1"/>
+    <row r="99" ht="16" customHeight="1">
+      <c r="A99" s="11" t="inlineStr">
         <is>
           <t>Groep K</t>
         </is>
       </c>
-      <c r="E94" s="13" t="inlineStr">
+      <c r="E99" s="12" t="inlineStr">
         <is>
           <t>voorsp.</t>
         </is>
       </c>
-      <c r="F94" s="13" t="inlineStr">
+      <c r="F99" s="12" t="inlineStr">
         <is>
           <t>uitslag</t>
         </is>
       </c>
-      <c r="G94" s="13" t="inlineStr">
+      <c r="G99" s="12" t="inlineStr">
         <is>
           <t>pt.</t>
         </is>
       </c>
-      <c r="I94" s="12" t="inlineStr">
+      <c r="I99" s="11" t="inlineStr">
         <is>
           <t>Groep L</t>
         </is>
       </c>
-      <c r="M94" s="13" t="inlineStr">
+      <c r="M99" s="12" t="inlineStr">
         <is>
           <t>voorsp.</t>
         </is>
       </c>
-      <c r="N94" s="13" t="inlineStr">
+      <c r="N99" s="12" t="inlineStr">
         <is>
           <t>uitslag</t>
         </is>
       </c>
-      <c r="O94" s="13" t="inlineStr">
+      <c r="O99" s="12" t="inlineStr">
         <is>
           <t>pt.</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="17" customHeight="1">
-      <c r="A95" s="53" t="n"/>
-      <c r="B95" s="15" t="inlineStr">
+    <row r="100" ht="17" customHeight="1">
+      <c r="A100" s="52" t="n"/>
+      <c r="B100" s="14" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="C95" s="54" t="n"/>
-      <c r="D95" s="17" t="inlineStr">
+      <c r="C100" s="53" t="n"/>
+      <c r="D100" s="16" t="inlineStr">
         <is>
           <t>DR Congo</t>
         </is>
       </c>
-      <c r="E95" s="6" t="n"/>
-      <c r="F95" s="18" t="inlineStr"/>
-      <c r="G95" s="18" t="inlineStr"/>
-      <c r="I95" s="55" t="n"/>
-      <c r="J95" s="15" t="inlineStr">
+      <c r="E100" s="5" t="n"/>
+      <c r="F100" s="17" t="inlineStr"/>
+      <c r="G100" s="17" t="inlineStr"/>
+      <c r="I100" s="54" t="n"/>
+      <c r="J100" s="14" t="inlineStr">
         <is>
           <t>Engeland</t>
         </is>
       </c>
-      <c r="K95" s="56" t="n"/>
-      <c r="L95" s="17" t="inlineStr">
+      <c r="K100" s="55" t="n"/>
+      <c r="L100" s="16" t="inlineStr">
         <is>
           <t>Kroatië</t>
         </is>
       </c>
-      <c r="M95" s="6" t="n"/>
-      <c r="N95" s="18" t="inlineStr"/>
-      <c r="O95" s="18" t="inlineStr"/>
-    </row>
-    <row r="96" ht="17" customHeight="1">
-      <c r="A96" s="57" t="n"/>
-      <c r="B96" s="15" t="inlineStr">
+      <c r="M100" s="5" t="n"/>
+      <c r="N100" s="17" t="inlineStr"/>
+      <c r="O100" s="17" t="inlineStr"/>
+    </row>
+    <row r="101" ht="17" customHeight="1">
+      <c r="A101" s="56" t="n"/>
+      <c r="B101" s="14" t="inlineStr">
         <is>
           <t>Oezbekistan</t>
         </is>
       </c>
-      <c r="C96" s="58" t="n"/>
-      <c r="D96" s="17" t="inlineStr">
+      <c r="C101" s="57" t="n"/>
+      <c r="D101" s="16" t="inlineStr">
         <is>
           <t>Colombia</t>
         </is>
       </c>
-      <c r="E96" s="6" t="n"/>
-      <c r="F96" s="18" t="inlineStr"/>
-      <c r="G96" s="18" t="inlineStr"/>
-      <c r="I96" s="59" t="n"/>
-      <c r="J96" s="15" t="inlineStr">
+      <c r="E101" s="5" t="n"/>
+      <c r="F101" s="17" t="inlineStr"/>
+      <c r="G101" s="17" t="inlineStr"/>
+      <c r="I101" s="58" t="n"/>
+      <c r="J101" s="14" t="inlineStr">
         <is>
           <t>Ghana</t>
         </is>
       </c>
-      <c r="K96" s="32" t="n"/>
-      <c r="L96" s="17" t="inlineStr">
+      <c r="K101" s="31" t="n"/>
+      <c r="L101" s="16" t="inlineStr">
         <is>
           <t>Panama</t>
         </is>
       </c>
-      <c r="M96" s="6" t="n"/>
-      <c r="N96" s="18" t="inlineStr"/>
-      <c r="O96" s="18" t="inlineStr"/>
-    </row>
-    <row r="97" ht="17" customHeight="1">
-      <c r="A97" s="53" t="n"/>
-      <c r="B97" s="15" t="inlineStr">
+      <c r="M101" s="5" t="n"/>
+      <c r="N101" s="17" t="inlineStr"/>
+      <c r="O101" s="17" t="inlineStr"/>
+    </row>
+    <row r="102" ht="17" customHeight="1">
+      <c r="A102" s="52" t="n"/>
+      <c r="B102" s="14" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="C97" s="57" t="n"/>
-      <c r="D97" s="17" t="inlineStr">
+      <c r="C102" s="56" t="n"/>
+      <c r="D102" s="16" t="inlineStr">
         <is>
           <t>Oezbekistan</t>
         </is>
       </c>
-      <c r="E97" s="6" t="n"/>
-      <c r="F97" s="18" t="inlineStr"/>
-      <c r="G97" s="18" t="inlineStr"/>
-      <c r="I97" s="55" t="n"/>
-      <c r="J97" s="15" t="inlineStr">
+      <c r="E102" s="5" t="n"/>
+      <c r="F102" s="17" t="inlineStr"/>
+      <c r="G102" s="17" t="inlineStr"/>
+      <c r="I102" s="54" t="n"/>
+      <c r="J102" s="14" t="inlineStr">
         <is>
           <t>Engeland</t>
         </is>
       </c>
-      <c r="K97" s="59" t="n"/>
-      <c r="L97" s="17" t="inlineStr">
+      <c r="K102" s="58" t="n"/>
+      <c r="L102" s="16" t="inlineStr">
         <is>
           <t>Ghana</t>
         </is>
       </c>
-      <c r="M97" s="6" t="n"/>
-      <c r="N97" s="18" t="inlineStr"/>
-      <c r="O97" s="18" t="inlineStr"/>
-    </row>
-    <row r="98" ht="17" customHeight="1">
-      <c r="A98" s="58" t="n"/>
-      <c r="B98" s="15" t="inlineStr">
+      <c r="M102" s="5" t="n"/>
+      <c r="N102" s="17" t="inlineStr"/>
+      <c r="O102" s="17" t="inlineStr"/>
+    </row>
+    <row r="103" ht="17" customHeight="1">
+      <c r="A103" s="57" t="n"/>
+      <c r="B103" s="14" t="inlineStr">
         <is>
           <t>Colombia</t>
         </is>
       </c>
-      <c r="C98" s="54" t="n"/>
-      <c r="D98" s="17" t="inlineStr">
+      <c r="C103" s="53" t="n"/>
+      <c r="D103" s="16" t="inlineStr">
         <is>
           <t>DR Congo</t>
         </is>
       </c>
-      <c r="E98" s="6" t="n"/>
-      <c r="F98" s="18" t="inlineStr"/>
-      <c r="G98" s="18" t="inlineStr"/>
-      <c r="I98" s="32" t="n"/>
-      <c r="J98" s="15" t="inlineStr">
+      <c r="E103" s="5" t="n"/>
+      <c r="F103" s="17" t="inlineStr"/>
+      <c r="G103" s="17" t="inlineStr"/>
+      <c r="I103" s="31" t="n"/>
+      <c r="J103" s="14" t="inlineStr">
         <is>
           <t>Panama</t>
         </is>
       </c>
-      <c r="K98" s="56" t="n"/>
-      <c r="L98" s="17" t="inlineStr">
+      <c r="K103" s="55" t="n"/>
+      <c r="L103" s="16" t="inlineStr">
         <is>
           <t>Kroatië</t>
         </is>
       </c>
-      <c r="M98" s="6" t="n"/>
-      <c r="N98" s="18" t="inlineStr"/>
-      <c r="O98" s="18" t="inlineStr"/>
-    </row>
-    <row r="99" ht="17" customHeight="1">
-      <c r="A99" s="58" t="n"/>
-      <c r="B99" s="15" t="inlineStr">
+      <c r="M103" s="5" t="n"/>
+      <c r="N103" s="17" t="inlineStr"/>
+      <c r="O103" s="17" t="inlineStr"/>
+    </row>
+    <row r="104" ht="17" customHeight="1">
+      <c r="A104" s="57" t="n"/>
+      <c r="B104" s="14" t="inlineStr">
         <is>
           <t>Colombia</t>
         </is>
       </c>
-      <c r="C99" s="53" t="n"/>
-      <c r="D99" s="17" t="inlineStr">
+      <c r="C104" s="52" t="n"/>
+      <c r="D104" s="16" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="E99" s="6" t="n"/>
-      <c r="F99" s="18" t="inlineStr"/>
-      <c r="G99" s="18" t="inlineStr"/>
-      <c r="I99" s="32" t="n"/>
-      <c r="J99" s="15" t="inlineStr">
+      <c r="E104" s="5" t="n"/>
+      <c r="F104" s="17" t="inlineStr"/>
+      <c r="G104" s="17" t="inlineStr"/>
+      <c r="I104" s="31" t="n"/>
+      <c r="J104" s="14" t="inlineStr">
         <is>
           <t>Panama</t>
         </is>
       </c>
-      <c r="K99" s="55" t="n"/>
-      <c r="L99" s="17" t="inlineStr">
+      <c r="K104" s="54" t="n"/>
+      <c r="L104" s="16" t="inlineStr">
         <is>
           <t>Engeland</t>
         </is>
       </c>
-      <c r="M99" s="6" t="n"/>
-      <c r="N99" s="18" t="inlineStr"/>
-      <c r="O99" s="18" t="inlineStr"/>
-    </row>
-    <row r="100" ht="17" customHeight="1">
-      <c r="A100" s="54" t="n"/>
-      <c r="B100" s="15" t="inlineStr">
+      <c r="M104" s="5" t="n"/>
+      <c r="N104" s="17" t="inlineStr"/>
+      <c r="O104" s="17" t="inlineStr"/>
+    </row>
+    <row r="105" ht="17" customHeight="1">
+      <c r="A105" s="53" t="n"/>
+      <c r="B105" s="14" t="inlineStr">
         <is>
           <t>DR Congo</t>
         </is>
       </c>
-      <c r="C100" s="57" t="n"/>
-      <c r="D100" s="17" t="inlineStr">
+      <c r="C105" s="56" t="n"/>
+      <c r="D105" s="16" t="inlineStr">
         <is>
           <t>Oezbekistan</t>
         </is>
       </c>
-      <c r="E100" s="6" t="n"/>
-      <c r="F100" s="18" t="inlineStr"/>
-      <c r="G100" s="18" t="inlineStr"/>
-      <c r="I100" s="56" t="n"/>
-      <c r="J100" s="15" t="inlineStr">
+      <c r="E105" s="5" t="n"/>
+      <c r="F105" s="17" t="inlineStr"/>
+      <c r="G105" s="17" t="inlineStr"/>
+      <c r="I105" s="55" t="n"/>
+      <c r="J105" s="14" t="inlineStr">
         <is>
           <t>Kroatië</t>
         </is>
       </c>
-      <c r="K100" s="59" t="n"/>
-      <c r="L100" s="17" t="inlineStr">
+      <c r="K105" s="58" t="n"/>
+      <c r="L105" s="16" t="inlineStr">
         <is>
           <t>Ghana</t>
         </is>
       </c>
-      <c r="M100" s="6" t="n"/>
-      <c r="N100" s="18" t="inlineStr"/>
-      <c r="O100" s="18" t="inlineStr"/>
-    </row>
-    <row r="101" ht="17" customHeight="1">
-      <c r="A101" s="5" t="inlineStr">
+      <c r="M105" s="5" t="n"/>
+      <c r="N105" s="17" t="inlineStr"/>
+      <c r="O105" s="17" t="inlineStr"/>
+    </row>
+    <row r="106" ht="17" customHeight="1">
+      <c r="A106" s="4" t="inlineStr">
         <is>
           <t>Groepswinnaar:</t>
         </is>
       </c>
-      <c r="E101" s="18" t="inlineStr">
+      <c r="E106" s="17" t="inlineStr">
         <is>
           <t>↳ niet invullen</t>
         </is>
       </c>
-      <c r="I101" s="5" t="inlineStr">
+      <c r="I106" s="4" t="inlineStr">
         <is>
           <t>Groepswinnaar:</t>
         </is>
       </c>
-      <c r="M101" s="18" t="inlineStr">
+      <c r="M106" s="17" t="inlineStr">
         <is>
           <t>↳ niet invullen</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="17" customHeight="1">
-      <c r="A102" s="5" t="inlineStr">
+    <row r="107" ht="17" customHeight="1">
+      <c r="A107" s="4" t="inlineStr">
         <is>
           <t>Runner-up:</t>
         </is>
       </c>
-      <c r="E102" s="18" t="inlineStr">
+      <c r="E107" s="17" t="inlineStr">
         <is>
           <t>↳ niet invullen</t>
         </is>
       </c>
-      <c r="I102" s="5" t="inlineStr">
+      <c r="I107" s="4" t="inlineStr">
         <is>
           <t>Runner-up:</t>
         </is>
       </c>
-      <c r="M102" s="18" t="inlineStr">
+      <c r="M107" s="17" t="inlineStr">
         <is>
           <t>↳ niet invullen</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="6" customHeight="1"/>
-    <row r="104" ht="8" customHeight="1"/>
-    <row r="105" ht="18" customHeight="1">
-      <c r="A105" s="4" t="inlineStr">
+    <row r="108" ht="6" customHeight="1"/>
+    <row r="109" ht="8" customHeight="1"/>
+    <row r="110" ht="18" customHeight="1">
+      <c r="A110" s="3" t="inlineStr">
         <is>
           <t>▶  BESTE 8 NUMMERS 3  ·  niet invullen — wordt na inlevering door de agent berekend</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="40" customHeight="1">
-      <c r="A106" s="60" t="inlineStr">
+    <row r="111" ht="40" customHeight="1">
+      <c r="A111" s="59" t="inlineStr">
         <is>
           <t>De 8 beste nummers 3 worden na inlevering van dit formulier automatisch berekend op basis van de punten en het doelsaldo van de nummer-3-landen in jouw groepsscores. De Excel zelf rekent dit NIET uit — je hoeft hier niets in te vullen.</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="8" customHeight="1"/>
-    <row r="108" ht="18" customHeight="1">
-      <c r="A108" s="4" t="inlineStr">
+    <row r="112" ht="8" customHeight="1"/>
+    <row r="113" ht="18" customHeight="1">
+      <c r="A113" s="3" t="inlineStr">
         <is>
           <t>▶  KNOCK-OUT  ·  grijze vakjes — invullen na de groepsfase, vóór elke ronde</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="16" customHeight="1">
-      <c r="A109" s="10" t="inlineStr">
+    <row r="114" ht="16" customHeight="1">
+      <c r="A114" s="9" t="inlineStr">
         <is>
           <t>Ronde van 32  ·  toto 5 pt / exact +3 pt</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="14" customHeight="1">
-      <c r="E110" s="13" t="inlineStr">
+    <row r="115" ht="14" customHeight="1">
+      <c r="E115" s="12" t="inlineStr">
         <is>
           <t>voorsp.</t>
         </is>
       </c>
-      <c r="F110" s="13" t="inlineStr">
+      <c r="F115" s="12" t="inlineStr">
         <is>
           <t>uitslag</t>
         </is>
       </c>
-      <c r="G110" s="13" t="inlineStr">
+      <c r="G115" s="12" t="inlineStr">
         <is>
           <t>pt.</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="16" customHeight="1">
-      <c r="A111" s="61" t="inlineStr">
+    <row r="116" ht="16" customHeight="1">
+      <c r="A116" s="60" t="inlineStr">
         <is>
           <t>2A  –  2B</t>
         </is>
       </c>
-      <c r="E111" s="18" t="inlineStr"/>
-      <c r="F111" s="18" t="inlineStr"/>
-      <c r="G111" s="18" t="inlineStr"/>
-    </row>
-    <row r="112" ht="16" customHeight="1">
-      <c r="A112" s="61" t="inlineStr">
+      <c r="E116" s="17" t="inlineStr"/>
+      <c r="F116" s="17" t="inlineStr"/>
+      <c r="G116" s="17" t="inlineStr"/>
+    </row>
+    <row r="117" ht="16" customHeight="1">
+      <c r="A117" s="60" t="inlineStr">
         <is>
           <t>1E  –  3e (A/B/C/D/F)</t>
         </is>
       </c>
-      <c r="E112" s="18" t="inlineStr"/>
-      <c r="F112" s="18" t="inlineStr"/>
-      <c r="G112" s="18" t="inlineStr"/>
-    </row>
-    <row r="113" ht="16" customHeight="1">
-      <c r="A113" s="61" t="inlineStr">
+      <c r="E117" s="17" t="inlineStr"/>
+      <c r="F117" s="17" t="inlineStr"/>
+      <c r="G117" s="17" t="inlineStr"/>
+    </row>
+    <row r="118" ht="16" customHeight="1">
+      <c r="A118" s="60" t="inlineStr">
         <is>
           <t>1F  –  2C</t>
         </is>
       </c>
-      <c r="E113" s="18" t="inlineStr"/>
-      <c r="F113" s="18" t="inlineStr"/>
-      <c r="G113" s="18" t="inlineStr"/>
-    </row>
-    <row r="114" ht="16" customHeight="1">
-      <c r="A114" s="61" t="inlineStr">
+      <c r="E118" s="17" t="inlineStr"/>
+      <c r="F118" s="17" t="inlineStr"/>
+      <c r="G118" s="17" t="inlineStr"/>
+    </row>
+    <row r="119" ht="16" customHeight="1">
+      <c r="A119" s="60" t="inlineStr">
         <is>
           <t>1C  –  2F</t>
         </is>
       </c>
-      <c r="E114" s="18" t="inlineStr"/>
-      <c r="F114" s="18" t="inlineStr"/>
-      <c r="G114" s="18" t="inlineStr"/>
-    </row>
-    <row r="115" ht="16" customHeight="1">
-      <c r="A115" s="61" t="inlineStr">
+      <c r="E119" s="17" t="inlineStr"/>
+      <c r="F119" s="17" t="inlineStr"/>
+      <c r="G119" s="17" t="inlineStr"/>
+    </row>
+    <row r="120" ht="16" customHeight="1">
+      <c r="A120" s="60" t="inlineStr">
         <is>
           <t>1I  –  3e (C/D/F/G/H)</t>
         </is>
       </c>
-      <c r="E115" s="18" t="inlineStr"/>
-      <c r="F115" s="18" t="inlineStr"/>
-      <c r="G115" s="18" t="inlineStr"/>
-    </row>
-    <row r="116" ht="16" customHeight="1">
-      <c r="A116" s="61" t="inlineStr">
+      <c r="E120" s="17" t="inlineStr"/>
+      <c r="F120" s="17" t="inlineStr"/>
+      <c r="G120" s="17" t="inlineStr"/>
+    </row>
+    <row r="121" ht="16" customHeight="1">
+      <c r="A121" s="60" t="inlineStr">
         <is>
           <t>2E  –  2I</t>
         </is>
       </c>
-      <c r="E116" s="18" t="inlineStr"/>
-      <c r="F116" s="18" t="inlineStr"/>
-      <c r="G116" s="18" t="inlineStr"/>
-    </row>
-    <row r="117" ht="16" customHeight="1">
-      <c r="A117" s="61" t="inlineStr">
+      <c r="E121" s="17" t="inlineStr"/>
+      <c r="F121" s="17" t="inlineStr"/>
+      <c r="G121" s="17" t="inlineStr"/>
+    </row>
+    <row r="122" ht="16" customHeight="1">
+      <c r="A122" s="60" t="inlineStr">
         <is>
           <t>1A  –  3e (C/E/F/H/I)</t>
         </is>
       </c>
-      <c r="E117" s="18" t="inlineStr"/>
-      <c r="F117" s="18" t="inlineStr"/>
-      <c r="G117" s="18" t="inlineStr"/>
-    </row>
-    <row r="118" ht="16" customHeight="1">
-      <c r="A118" s="61" t="inlineStr">
+      <c r="E122" s="17" t="inlineStr"/>
+      <c r="F122" s="17" t="inlineStr"/>
+      <c r="G122" s="17" t="inlineStr"/>
+    </row>
+    <row r="123" ht="16" customHeight="1">
+      <c r="A123" s="60" t="inlineStr">
         <is>
           <t>1L  –  3e (E/H/I/J/K)</t>
         </is>
       </c>
-      <c r="E118" s="18" t="inlineStr"/>
-      <c r="F118" s="18" t="inlineStr"/>
-      <c r="G118" s="18" t="inlineStr"/>
-    </row>
-    <row r="119" ht="16" customHeight="1">
-      <c r="A119" s="61" t="inlineStr">
+      <c r="E123" s="17" t="inlineStr"/>
+      <c r="F123" s="17" t="inlineStr"/>
+      <c r="G123" s="17" t="inlineStr"/>
+    </row>
+    <row r="124" ht="16" customHeight="1">
+      <c r="A124" s="60" t="inlineStr">
         <is>
           <t>1D  –  3e (B/E/F/I/J)</t>
         </is>
       </c>
-      <c r="E119" s="18" t="inlineStr"/>
-      <c r="F119" s="18" t="inlineStr"/>
-      <c r="G119" s="18" t="inlineStr"/>
-    </row>
-    <row r="120" ht="16" customHeight="1">
-      <c r="A120" s="61" t="inlineStr">
+      <c r="E124" s="17" t="inlineStr"/>
+      <c r="F124" s="17" t="inlineStr"/>
+      <c r="G124" s="17" t="inlineStr"/>
+    </row>
+    <row r="125" ht="16" customHeight="1">
+      <c r="A125" s="60" t="inlineStr">
         <is>
           <t>1G  –  3e (A/E/H/I/J)</t>
         </is>
       </c>
-      <c r="E120" s="18" t="inlineStr"/>
-      <c r="F120" s="18" t="inlineStr"/>
-      <c r="G120" s="18" t="inlineStr"/>
-    </row>
-    <row r="121" ht="16" customHeight="1">
-      <c r="A121" s="61" t="inlineStr">
+      <c r="E125" s="17" t="inlineStr"/>
+      <c r="F125" s="17" t="inlineStr"/>
+      <c r="G125" s="17" t="inlineStr"/>
+    </row>
+    <row r="126" ht="16" customHeight="1">
+      <c r="A126" s="60" t="inlineStr">
         <is>
           <t>2K  –  2L</t>
         </is>
       </c>
-      <c r="E121" s="18" t="inlineStr"/>
-      <c r="F121" s="18" t="inlineStr"/>
-      <c r="G121" s="18" t="inlineStr"/>
-    </row>
-    <row r="122" ht="16" customHeight="1">
-      <c r="A122" s="61" t="inlineStr">
+      <c r="E126" s="17" t="inlineStr"/>
+      <c r="F126" s="17" t="inlineStr"/>
+      <c r="G126" s="17" t="inlineStr"/>
+    </row>
+    <row r="127" ht="16" customHeight="1">
+      <c r="A127" s="60" t="inlineStr">
         <is>
           <t>1H  –  2J</t>
         </is>
       </c>
-      <c r="E122" s="18" t="inlineStr"/>
-      <c r="F122" s="18" t="inlineStr"/>
-      <c r="G122" s="18" t="inlineStr"/>
-    </row>
-    <row r="123" ht="16" customHeight="1">
-      <c r="A123" s="61" t="inlineStr">
+      <c r="E127" s="17" t="inlineStr"/>
+      <c r="F127" s="17" t="inlineStr"/>
+      <c r="G127" s="17" t="inlineStr"/>
+    </row>
+    <row r="128" ht="16" customHeight="1">
+      <c r="A128" s="60" t="inlineStr">
         <is>
           <t>1B  –  3e (E/F/G/I/J)</t>
         </is>
       </c>
-      <c r="E123" s="18" t="inlineStr"/>
-      <c r="F123" s="18" t="inlineStr"/>
-      <c r="G123" s="18" t="inlineStr"/>
-    </row>
-    <row r="124" ht="16" customHeight="1">
-      <c r="A124" s="61" t="inlineStr">
+      <c r="E128" s="17" t="inlineStr"/>
+      <c r="F128" s="17" t="inlineStr"/>
+      <c r="G128" s="17" t="inlineStr"/>
+    </row>
+    <row r="129" ht="16" customHeight="1">
+      <c r="A129" s="60" t="inlineStr">
         <is>
           <t>1J  –  2H</t>
         </is>
       </c>
-      <c r="E124" s="18" t="inlineStr"/>
-      <c r="F124" s="18" t="inlineStr"/>
-      <c r="G124" s="18" t="inlineStr"/>
-    </row>
-    <row r="125" ht="16" customHeight="1">
-      <c r="A125" s="61" t="inlineStr">
+      <c r="E129" s="17" t="inlineStr"/>
+      <c r="F129" s="17" t="inlineStr"/>
+      <c r="G129" s="17" t="inlineStr"/>
+    </row>
+    <row r="130" ht="16" customHeight="1">
+      <c r="A130" s="60" t="inlineStr">
         <is>
           <t>1K  –  3e (D/E/I/J/L)</t>
         </is>
       </c>
-      <c r="E125" s="18" t="inlineStr"/>
-      <c r="F125" s="18" t="inlineStr"/>
-      <c r="G125" s="18" t="inlineStr"/>
-    </row>
-    <row r="126" ht="16" customHeight="1">
-      <c r="A126" s="61" t="inlineStr">
+      <c r="E130" s="17" t="inlineStr"/>
+      <c r="F130" s="17" t="inlineStr"/>
+      <c r="G130" s="17" t="inlineStr"/>
+    </row>
+    <row r="131" ht="16" customHeight="1">
+      <c r="A131" s="60" t="inlineStr">
         <is>
           <t>2D  –  2G</t>
         </is>
       </c>
-      <c r="E126" s="18" t="inlineStr"/>
-      <c r="F126" s="18" t="inlineStr"/>
-      <c r="G126" s="18" t="inlineStr"/>
-    </row>
-    <row r="127" ht="6" customHeight="1"/>
-    <row r="128" ht="16" customHeight="1">
-      <c r="A128" s="10" t="inlineStr">
+      <c r="E131" s="17" t="inlineStr"/>
+      <c r="F131" s="17" t="inlineStr"/>
+      <c r="G131" s="17" t="inlineStr"/>
+    </row>
+    <row r="132" ht="6" customHeight="1"/>
+    <row r="133" ht="16" customHeight="1">
+      <c r="A133" s="9" t="inlineStr">
         <is>
           <t>Ronde van 16  ·  toto 7 pt / exact +4 pt</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="14" customHeight="1">
-      <c r="E129" s="13" t="inlineStr">
+    <row r="134" ht="14" customHeight="1">
+      <c r="E134" s="12" t="inlineStr">
         <is>
           <t>voorsp.</t>
         </is>
       </c>
-      <c r="F129" s="13" t="inlineStr">
+      <c r="F134" s="12" t="inlineStr">
         <is>
           <t>uitslag</t>
         </is>
       </c>
-      <c r="G129" s="13" t="inlineStr">
+      <c r="G134" s="12" t="inlineStr">
         <is>
           <t>pt.</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="16" customHeight="1">
-      <c r="A130" s="61" t="inlineStr">
+    <row r="135" ht="16" customHeight="1">
+      <c r="A135" s="60" t="inlineStr">
         <is>
           <t>W32-2  –  W32-5</t>
         </is>
       </c>
-      <c r="E130" s="18" t="inlineStr"/>
-      <c r="F130" s="18" t="inlineStr"/>
-      <c r="G130" s="18" t="inlineStr"/>
-    </row>
-    <row r="131" ht="16" customHeight="1">
-      <c r="A131" s="61" t="inlineStr">
+      <c r="E135" s="17" t="inlineStr"/>
+      <c r="F135" s="17" t="inlineStr"/>
+      <c r="G135" s="17" t="inlineStr"/>
+    </row>
+    <row r="136" ht="16" customHeight="1">
+      <c r="A136" s="60" t="inlineStr">
         <is>
           <t>W32-1  –  W32-3</t>
         </is>
       </c>
-      <c r="E131" s="18" t="inlineStr"/>
-      <c r="F131" s="18" t="inlineStr"/>
-      <c r="G131" s="18" t="inlineStr"/>
-    </row>
-    <row r="132" ht="16" customHeight="1">
-      <c r="A132" s="61" t="inlineStr">
+      <c r="E136" s="17" t="inlineStr"/>
+      <c r="F136" s="17" t="inlineStr"/>
+      <c r="G136" s="17" t="inlineStr"/>
+    </row>
+    <row r="137" ht="16" customHeight="1">
+      <c r="A137" s="60" t="inlineStr">
         <is>
           <t>W32-4  –  W32-6</t>
         </is>
       </c>
-      <c r="E132" s="18" t="inlineStr"/>
-      <c r="F132" s="18" t="inlineStr"/>
-      <c r="G132" s="18" t="inlineStr"/>
-    </row>
-    <row r="133" ht="16" customHeight="1">
-      <c r="A133" s="61" t="inlineStr">
+      <c r="E137" s="17" t="inlineStr"/>
+      <c r="F137" s="17" t="inlineStr"/>
+      <c r="G137" s="17" t="inlineStr"/>
+    </row>
+    <row r="138" ht="16" customHeight="1">
+      <c r="A138" s="60" t="inlineStr">
         <is>
           <t>W32-7  –  W32-8</t>
         </is>
       </c>
-      <c r="E133" s="18" t="inlineStr"/>
-      <c r="F133" s="18" t="inlineStr"/>
-      <c r="G133" s="18" t="inlineStr"/>
-    </row>
-    <row r="134" ht="16" customHeight="1">
-      <c r="A134" s="61" t="inlineStr">
+      <c r="E138" s="17" t="inlineStr"/>
+      <c r="F138" s="17" t="inlineStr"/>
+      <c r="G138" s="17" t="inlineStr"/>
+    </row>
+    <row r="139" ht="16" customHeight="1">
+      <c r="A139" s="60" t="inlineStr">
         <is>
           <t>W32-11  –  W32-12</t>
         </is>
       </c>
-      <c r="E134" s="18" t="inlineStr"/>
-      <c r="F134" s="18" t="inlineStr"/>
-      <c r="G134" s="18" t="inlineStr"/>
-    </row>
-    <row r="135" ht="16" customHeight="1">
-      <c r="A135" s="61" t="inlineStr">
+      <c r="E139" s="17" t="inlineStr"/>
+      <c r="F139" s="17" t="inlineStr"/>
+      <c r="G139" s="17" t="inlineStr"/>
+    </row>
+    <row r="140" ht="16" customHeight="1">
+      <c r="A140" s="60" t="inlineStr">
         <is>
           <t>W32-9  –  W32-10</t>
         </is>
       </c>
-      <c r="E135" s="18" t="inlineStr"/>
-      <c r="F135" s="18" t="inlineStr"/>
-      <c r="G135" s="18" t="inlineStr"/>
-    </row>
-    <row r="136" ht="16" customHeight="1">
-      <c r="A136" s="61" t="inlineStr">
+      <c r="E140" s="17" t="inlineStr"/>
+      <c r="F140" s="17" t="inlineStr"/>
+      <c r="G140" s="17" t="inlineStr"/>
+    </row>
+    <row r="141" ht="16" customHeight="1">
+      <c r="A141" s="60" t="inlineStr">
         <is>
           <t>W32-14  –  W32-16</t>
         </is>
       </c>
-      <c r="E136" s="18" t="inlineStr"/>
-      <c r="F136" s="18" t="inlineStr"/>
-      <c r="G136" s="18" t="inlineStr"/>
-    </row>
-    <row r="137" ht="16" customHeight="1">
-      <c r="A137" s="61" t="inlineStr">
+      <c r="E141" s="17" t="inlineStr"/>
+      <c r="F141" s="17" t="inlineStr"/>
+      <c r="G141" s="17" t="inlineStr"/>
+    </row>
+    <row r="142" ht="16" customHeight="1">
+      <c r="A142" s="60" t="inlineStr">
         <is>
           <t>W32-13  –  W32-15</t>
         </is>
       </c>
-      <c r="E137" s="18" t="inlineStr"/>
-      <c r="F137" s="18" t="inlineStr"/>
-      <c r="G137" s="18" t="inlineStr"/>
-    </row>
-    <row r="138" ht="6" customHeight="1"/>
-    <row r="139" ht="16" customHeight="1">
-      <c r="A139" s="10" t="inlineStr">
+      <c r="E142" s="17" t="inlineStr"/>
+      <c r="F142" s="17" t="inlineStr"/>
+      <c r="G142" s="17" t="inlineStr"/>
+    </row>
+    <row r="143" ht="6" customHeight="1"/>
+    <row r="144" ht="16" customHeight="1">
+      <c r="A144" s="9" t="inlineStr">
         <is>
           <t>Kwartfinales  ·  toto 9 pt / exact +5 pt</t>
         </is>
       </c>
     </row>
-    <row r="140" ht="14" customHeight="1">
-      <c r="E140" s="13" t="inlineStr">
+    <row r="145" ht="14" customHeight="1">
+      <c r="E145" s="12" t="inlineStr">
         <is>
           <t>voorsp.</t>
         </is>
       </c>
-      <c r="F140" s="13" t="inlineStr">
+      <c r="F145" s="12" t="inlineStr">
         <is>
           <t>uitslag</t>
         </is>
       </c>
-      <c r="G140" s="13" t="inlineStr">
+      <c r="G145" s="12" t="inlineStr">
         <is>
           <t>pt.</t>
         </is>
       </c>
     </row>
-    <row r="141" ht="16" customHeight="1">
-      <c r="A141" s="61" t="inlineStr">
+    <row r="146" ht="16" customHeight="1">
+      <c r="A146" s="60" t="inlineStr">
         <is>
           <t>W16-1  –  W16-2</t>
         </is>
       </c>
-      <c r="E141" s="18" t="inlineStr"/>
-      <c r="F141" s="18" t="inlineStr"/>
-      <c r="G141" s="18" t="inlineStr"/>
-    </row>
-    <row r="142" ht="16" customHeight="1">
-      <c r="A142" s="61" t="inlineStr">
+      <c r="E146" s="17" t="inlineStr"/>
+      <c r="F146" s="17" t="inlineStr"/>
+      <c r="G146" s="17" t="inlineStr"/>
+    </row>
+    <row r="147" ht="16" customHeight="1">
+      <c r="A147" s="60" t="inlineStr">
         <is>
           <t>W16-5  –  W16-6</t>
         </is>
       </c>
-      <c r="E142" s="18" t="inlineStr"/>
-      <c r="F142" s="18" t="inlineStr"/>
-      <c r="G142" s="18" t="inlineStr"/>
-    </row>
-    <row r="143" ht="16" customHeight="1">
-      <c r="A143" s="61" t="inlineStr">
+      <c r="E147" s="17" t="inlineStr"/>
+      <c r="F147" s="17" t="inlineStr"/>
+      <c r="G147" s="17" t="inlineStr"/>
+    </row>
+    <row r="148" ht="16" customHeight="1">
+      <c r="A148" s="60" t="inlineStr">
         <is>
           <t>W16-3  –  W16-4</t>
         </is>
       </c>
-      <c r="E143" s="18" t="inlineStr"/>
-      <c r="F143" s="18" t="inlineStr"/>
-      <c r="G143" s="18" t="inlineStr"/>
-    </row>
-    <row r="144" ht="16" customHeight="1">
-      <c r="A144" s="61" t="inlineStr">
+      <c r="E148" s="17" t="inlineStr"/>
+      <c r="F148" s="17" t="inlineStr"/>
+      <c r="G148" s="17" t="inlineStr"/>
+    </row>
+    <row r="149" ht="16" customHeight="1">
+      <c r="A149" s="60" t="inlineStr">
         <is>
           <t>W16-7  –  W16-8</t>
         </is>
       </c>
-      <c r="E144" s="18" t="inlineStr"/>
-      <c r="F144" s="18" t="inlineStr"/>
-      <c r="G144" s="18" t="inlineStr"/>
-    </row>
-    <row r="145" ht="6" customHeight="1"/>
-    <row r="146" ht="16" customHeight="1">
-      <c r="A146" s="10" t="inlineStr">
-        <is>
-          <t>Halve finales  ·  toto 11 pt / exact +6 pt</t>
-        </is>
-      </c>
-    </row>
-    <row r="147" ht="14" customHeight="1">
-      <c r="E147" s="13" t="inlineStr">
-        <is>
-          <t>voorsp.</t>
-        </is>
-      </c>
-      <c r="F147" s="13" t="inlineStr">
-        <is>
-          <t>uitslag</t>
-        </is>
-      </c>
-      <c r="G147" s="13" t="inlineStr">
-        <is>
-          <t>pt.</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" ht="16" customHeight="1">
-      <c r="A148" s="61" t="inlineStr">
-        <is>
-          <t>WKF-1  –  WKF-2</t>
-        </is>
-      </c>
-      <c r="E148" s="18" t="inlineStr"/>
-      <c r="F148" s="18" t="inlineStr"/>
-      <c r="G148" s="18" t="inlineStr"/>
-    </row>
-    <row r="149" ht="16" customHeight="1">
-      <c r="A149" s="61" t="inlineStr">
-        <is>
-          <t>WKF-3  –  WKF-4</t>
-        </is>
-      </c>
-      <c r="E149" s="18" t="inlineStr"/>
-      <c r="F149" s="18" t="inlineStr"/>
-      <c r="G149" s="18" t="inlineStr"/>
+      <c r="E149" s="17" t="inlineStr"/>
+      <c r="F149" s="17" t="inlineStr"/>
+      <c r="G149" s="17" t="inlineStr"/>
     </row>
     <row r="150" ht="6" customHeight="1"/>
     <row r="151" ht="16" customHeight="1">
-      <c r="A151" s="10" t="inlineStr">
+      <c r="A151" s="9" t="inlineStr">
+        <is>
+          <t>Halve finales  ·  toto 11 pt / exact +6 pt</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="14" customHeight="1">
+      <c r="E152" s="12" t="inlineStr">
+        <is>
+          <t>voorsp.</t>
+        </is>
+      </c>
+      <c r="F152" s="12" t="inlineStr">
+        <is>
+          <t>uitslag</t>
+        </is>
+      </c>
+      <c r="G152" s="12" t="inlineStr">
+        <is>
+          <t>pt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="16" customHeight="1">
+      <c r="A153" s="60" t="inlineStr">
+        <is>
+          <t>WKF-1  –  WKF-2</t>
+        </is>
+      </c>
+      <c r="E153" s="17" t="inlineStr"/>
+      <c r="F153" s="17" t="inlineStr"/>
+      <c r="G153" s="17" t="inlineStr"/>
+    </row>
+    <row r="154" ht="16" customHeight="1">
+      <c r="A154" s="60" t="inlineStr">
+        <is>
+          <t>WKF-3  –  WKF-4</t>
+        </is>
+      </c>
+      <c r="E154" s="17" t="inlineStr"/>
+      <c r="F154" s="17" t="inlineStr"/>
+      <c r="G154" s="17" t="inlineStr"/>
+    </row>
+    <row r="155" ht="6" customHeight="1"/>
+    <row r="156" ht="16" customHeight="1">
+      <c r="A156" s="9" t="inlineStr">
         <is>
           <t>Finale  ·  toto 13 pt / exact +7 pt</t>
         </is>
       </c>
     </row>
-    <row r="152" ht="14" customHeight="1">
-      <c r="E152" s="13" t="inlineStr">
+    <row r="157" ht="14" customHeight="1">
+      <c r="E157" s="12" t="inlineStr">
         <is>
           <t>voorsp.</t>
         </is>
       </c>
-      <c r="F152" s="13" t="inlineStr">
+      <c r="F157" s="12" t="inlineStr">
         <is>
           <t>uitslag</t>
         </is>
       </c>
-      <c r="G152" s="13" t="inlineStr">
+      <c r="G157" s="12" t="inlineStr">
         <is>
           <t>pt.</t>
         </is>
       </c>
     </row>
-    <row r="153" ht="16" customHeight="1">
-      <c r="A153" s="61" t="inlineStr">
+    <row r="158" ht="16" customHeight="1">
+      <c r="A158" s="60" t="inlineStr">
         <is>
           <t>WHF-1  –  WHF-2</t>
         </is>
       </c>
-      <c r="E153" s="18" t="inlineStr"/>
-      <c r="F153" s="18" t="inlineStr"/>
-      <c r="G153" s="18" t="inlineStr"/>
-    </row>
-    <row r="154" ht="6" customHeight="1"/>
-    <row r="155" ht="8" customHeight="1"/>
-    <row r="156" ht="18" customHeight="1">
-      <c r="A156" s="4" t="inlineStr">
+      <c r="E158" s="17" t="inlineStr"/>
+      <c r="F158" s="17" t="inlineStr"/>
+      <c r="G158" s="17" t="inlineStr"/>
+    </row>
+    <row r="159" ht="6" customHeight="1"/>
+    <row r="160" ht="8" customHeight="1"/>
+    <row r="161" ht="18" customHeight="1">
+      <c r="A161" s="3" t="inlineStr">
         <is>
           <t>▶  VERRASSING — kies een land BUITEN de top-12 · punten schalen met ranking en ronde</t>
         </is>
       </c>
     </row>
-    <row r="157" ht="14" customHeight="1">
-      <c r="A157" s="13" t="inlineStr">
+    <row r="162" ht="14" customHeight="1">
+      <c r="A162" s="12" t="inlineStr">
         <is>
           <t>Land (outsider)</t>
         </is>
       </c>
-      <c r="E157" s="13" t="inlineStr">
+      <c r="E162" s="12" t="inlineStr">
         <is>
           <t>R16</t>
         </is>
       </c>
-      <c r="F157" s="13" t="inlineStr">
+      <c r="F162" s="12" t="inlineStr">
         <is>
           <t>KF</t>
         </is>
       </c>
-      <c r="G157" s="13" t="inlineStr">
+      <c r="G162" s="12" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="H157" s="13" t="inlineStr">
+      <c r="H162" s="12" t="inlineStr">
         <is>
           <t>Finale</t>
         </is>
       </c>
-      <c r="I157" s="13" t="inlineStr">
+      <c r="I162" s="12" t="inlineStr">
         <is>
           <t>Winnaar</t>
         </is>
       </c>
     </row>
-    <row r="158" ht="15" customHeight="1">
-      <c r="A158" s="15" t="inlineStr">
+    <row r="163" ht="15" customHeight="1">
+      <c r="A163" s="14" t="inlineStr">
         <is>
           <t>Senegal</t>
         </is>
       </c>
-      <c r="E158" s="62" t="n">
+      <c r="E163" s="61" t="n">
         <v>7</v>
       </c>
-      <c r="F158" s="62" t="n">
+      <c r="F163" s="61" t="n">
         <v>12</v>
       </c>
-      <c r="G158" s="62" t="n">
+      <c r="G163" s="61" t="n">
         <v>19</v>
       </c>
-      <c r="H158" s="62" t="n">
+      <c r="H163" s="61" t="n">
         <v>26</v>
       </c>
-      <c r="I158" s="62" t="n">
+      <c r="I163" s="61" t="n">
         <v>34</v>
       </c>
     </row>
-    <row r="159" ht="15" customHeight="1">
-      <c r="A159" s="15" t="inlineStr">
+    <row r="164" ht="15" customHeight="1">
+      <c r="A164" s="14" t="inlineStr">
         <is>
           <t>Mexico</t>
         </is>
       </c>
-      <c r="E159" s="62" t="n">
+      <c r="E164" s="61" t="n">
         <v>7</v>
       </c>
-      <c r="F159" s="62" t="n">
+      <c r="F164" s="61" t="n">
         <v>13</v>
       </c>
-      <c r="G159" s="62" t="n">
+      <c r="G164" s="61" t="n">
         <v>19</v>
       </c>
-      <c r="H159" s="62" t="n">
+      <c r="H164" s="61" t="n">
         <v>27</v>
       </c>
-      <c r="I159" s="62" t="n">
+      <c r="I164" s="61" t="n">
         <v>35</v>
       </c>
     </row>
-    <row r="160" ht="15" customHeight="1">
-      <c r="A160" s="15" t="inlineStr">
+    <row r="165" ht="15" customHeight="1">
+      <c r="A165" s="14" t="inlineStr">
         <is>
           <t>Verenigde Staten</t>
         </is>
       </c>
-      <c r="E160" s="62" t="n">
+      <c r="E165" s="61" t="n">
         <v>8</v>
       </c>
-      <c r="F160" s="62" t="n">
+      <c r="F165" s="61" t="n">
         <v>13</v>
       </c>
-      <c r="G160" s="62" t="n">
+      <c r="G165" s="61" t="n">
         <v>20</v>
       </c>
-      <c r="H160" s="62" t="n">
+      <c r="H165" s="61" t="n">
         <v>27</v>
       </c>
-      <c r="I160" s="62" t="n">
+      <c r="I165" s="61" t="n">
         <v>36</v>
       </c>
     </row>
-    <row r="161" ht="15" customHeight="1">
-      <c r="A161" s="15" t="inlineStr">
+    <row r="166" ht="15" customHeight="1">
+      <c r="A166" s="14" t="inlineStr">
         <is>
           <t>Uruguay</t>
         </is>
       </c>
-      <c r="E161" s="62" t="n">
+      <c r="E166" s="61" t="n">
         <v>8</v>
       </c>
-      <c r="F161" s="62" t="n">
+      <c r="F166" s="61" t="n">
         <v>14</v>
       </c>
-      <c r="G161" s="62" t="n">
+      <c r="G166" s="61" t="n">
         <v>20</v>
       </c>
-      <c r="H161" s="62" t="n">
+      <c r="H166" s="61" t="n">
         <v>28</v>
       </c>
-      <c r="I161" s="62" t="n">
+      <c r="I166" s="61" t="n">
         <v>37</v>
       </c>
     </row>
-    <row r="162" ht="15" customHeight="1">
-      <c r="A162" s="15" t="inlineStr">
+    <row r="167" ht="15" customHeight="1">
+      <c r="A167" s="14" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="E162" s="62" t="n">
+      <c r="E167" s="61" t="n">
         <v>8</v>
       </c>
-      <c r="F162" s="62" t="n">
+      <c r="F167" s="61" t="n">
         <v>14</v>
       </c>
-      <c r="G162" s="62" t="n">
+      <c r="G167" s="61" t="n">
         <v>21</v>
       </c>
-      <c r="H162" s="62" t="n">
+      <c r="H167" s="61" t="n">
         <v>29</v>
       </c>
-      <c r="I162" s="62" t="n">
+      <c r="I167" s="61" t="n">
         <v>38</v>
       </c>
     </row>
-    <row r="163" ht="15" customHeight="1">
-      <c r="A163" s="15" t="inlineStr">
+    <row r="168" ht="15" customHeight="1">
+      <c r="A168" s="14" t="inlineStr">
         <is>
           <t>Zwitserland</t>
         </is>
       </c>
-      <c r="E163" s="62" t="n">
+      <c r="E168" s="61" t="n">
         <v>8</v>
       </c>
-      <c r="F163" s="62" t="n">
+      <c r="F168" s="61" t="n">
         <v>14</v>
       </c>
-      <c r="G163" s="62" t="n">
+      <c r="G168" s="61" t="n">
         <v>21</v>
       </c>
-      <c r="H163" s="62" t="n">
+      <c r="H168" s="61" t="n">
         <v>30</v>
       </c>
-      <c r="I163" s="62" t="n">
+      <c r="I168" s="61" t="n">
         <v>39</v>
       </c>
     </row>
-    <row r="164" ht="15" customHeight="1">
-      <c r="A164" s="15" t="inlineStr">
+    <row r="169" ht="15" customHeight="1">
+      <c r="A169" s="14" t="inlineStr">
         <is>
           <t>Iran</t>
         </is>
       </c>
-      <c r="E164" s="62" t="n">
+      <c r="E169" s="61" t="n">
         <v>9</v>
       </c>
-      <c r="F164" s="62" t="n">
+      <c r="F169" s="61" t="n">
         <v>15</v>
       </c>
-      <c r="G164" s="62" t="n">
+      <c r="G169" s="61" t="n">
         <v>22</v>
       </c>
-      <c r="H164" s="62" t="n">
+      <c r="H169" s="61" t="n">
         <v>31</v>
       </c>
-      <c r="I164" s="62" t="n">
+      <c r="I169" s="61" t="n">
         <v>41</v>
       </c>
     </row>
-    <row r="165" ht="15" customHeight="1">
-      <c r="A165" s="15" t="inlineStr">
+    <row r="170" ht="15" customHeight="1">
+      <c r="A170" s="14" t="inlineStr">
         <is>
           <t>Oostenrijk</t>
         </is>
       </c>
-      <c r="E165" s="62" t="n">
+      <c r="E170" s="61" t="n">
         <v>9</v>
       </c>
-      <c r="F165" s="62" t="n">
+      <c r="F170" s="61" t="n">
         <v>15</v>
       </c>
-      <c r="G165" s="62" t="n">
+      <c r="G170" s="61" t="n">
         <v>23</v>
       </c>
-      <c r="H165" s="62" t="n">
+      <c r="H170" s="61" t="n">
         <v>32</v>
       </c>
-      <c r="I165" s="62" t="n">
+      <c r="I170" s="61" t="n">
         <v>42</v>
       </c>
     </row>
-    <row r="166" ht="15" customHeight="1">
-      <c r="A166" s="15" t="inlineStr">
+    <row r="171" ht="15" customHeight="1">
+      <c r="A171" s="14" t="inlineStr">
         <is>
           <t>Zuid-Korea</t>
         </is>
       </c>
-      <c r="E166" s="62" t="n">
+      <c r="E171" s="61" t="n">
         <v>9</v>
       </c>
-      <c r="F166" s="62" t="n">
+      <c r="F171" s="61" t="n">
         <v>16</v>
       </c>
-      <c r="G166" s="62" t="n">
+      <c r="G171" s="61" t="n">
         <v>23</v>
       </c>
-      <c r="H166" s="62" t="n">
+      <c r="H171" s="61" t="n">
         <v>32</v>
       </c>
-      <c r="I166" s="62" t="n">
+      <c r="I171" s="61" t="n">
         <v>43</v>
       </c>
     </row>
-    <row r="167" ht="15" customHeight="1">
-      <c r="A167" s="15" t="inlineStr">
+    <row r="172" ht="15" customHeight="1">
+      <c r="A172" s="14" t="inlineStr">
         <is>
           <t>Australië</t>
         </is>
       </c>
-      <c r="E167" s="62" t="n">
+      <c r="E172" s="61" t="n">
         <v>9</v>
       </c>
-      <c r="F167" s="62" t="n">
+      <c r="F172" s="61" t="n">
         <v>16</v>
       </c>
-      <c r="G167" s="62" t="n">
+      <c r="G172" s="61" t="n">
         <v>24</v>
       </c>
-      <c r="H167" s="62" t="n">
+      <c r="H172" s="61" t="n">
         <v>33</v>
       </c>
-      <c r="I167" s="62" t="n">
+      <c r="I172" s="61" t="n">
         <v>43</v>
       </c>
     </row>
-    <row r="168" ht="15" customHeight="1">
-      <c r="A168" s="15" t="inlineStr">
+    <row r="173" ht="15" customHeight="1">
+      <c r="A173" s="14" t="inlineStr">
         <is>
           <t>Ecuador</t>
         </is>
       </c>
-      <c r="E168" s="62" t="n">
+      <c r="E173" s="61" t="n">
         <v>9</v>
       </c>
-      <c r="F168" s="62" t="n">
+      <c r="F173" s="61" t="n">
         <v>16</v>
       </c>
-      <c r="G168" s="62" t="n">
+      <c r="G173" s="61" t="n">
         <v>24</v>
       </c>
-      <c r="H168" s="62" t="n">
+      <c r="H173" s="61" t="n">
         <v>34</v>
       </c>
-      <c r="I168" s="62" t="n">
+      <c r="I173" s="61" t="n">
         <v>44</v>
       </c>
     </row>
-    <row r="169" ht="15" customHeight="1">
-      <c r="A169" s="15" t="inlineStr">
+    <row r="174" ht="15" customHeight="1">
+      <c r="A174" s="14" t="inlineStr">
         <is>
           <t>Noorwegen</t>
         </is>
       </c>
-      <c r="E169" s="62" t="n">
+      <c r="E174" s="61" t="n">
         <v>10</v>
       </c>
-      <c r="F169" s="62" t="n">
+      <c r="F174" s="61" t="n">
         <v>16</v>
       </c>
-      <c r="G169" s="62" t="n">
+      <c r="G174" s="61" t="n">
         <v>25</v>
       </c>
-      <c r="H169" s="62" t="n">
+      <c r="H174" s="61" t="n">
         <v>34</v>
       </c>
-      <c r="I169" s="62" t="n">
+      <c r="I174" s="61" t="n">
         <v>45</v>
       </c>
     </row>
-    <row r="170" ht="15" customHeight="1">
-      <c r="A170" s="15" t="inlineStr">
+    <row r="175" ht="15" customHeight="1">
+      <c r="A175" s="14" t="inlineStr">
         <is>
           <t>Panama</t>
         </is>
       </c>
-      <c r="E170" s="62" t="n">
+      <c r="E175" s="61" t="n">
         <v>10</v>
       </c>
-      <c r="F170" s="62" t="n">
+      <c r="F175" s="61" t="n">
         <v>17</v>
       </c>
-      <c r="G170" s="62" t="n">
+      <c r="G175" s="61" t="n">
         <v>26</v>
       </c>
-      <c r="H170" s="62" t="n">
+      <c r="H175" s="61" t="n">
         <v>36</v>
       </c>
-      <c r="I170" s="62" t="n">
+      <c r="I175" s="61" t="n">
         <v>48</v>
       </c>
     </row>
-    <row r="171" ht="15" customHeight="1">
-      <c r="A171" s="15" t="inlineStr">
+    <row r="176" ht="15" customHeight="1">
+      <c r="A176" s="14" t="inlineStr">
         <is>
           <t>Egypte</t>
         </is>
       </c>
-      <c r="E171" s="62" t="n">
+      <c r="E176" s="61" t="n">
         <v>10</v>
       </c>
-      <c r="F171" s="62" t="n">
+      <c r="F176" s="61" t="n">
         <v>18</v>
       </c>
-      <c r="G171" s="62" t="n">
+      <c r="G176" s="61" t="n">
         <v>27</v>
       </c>
-      <c r="H171" s="62" t="n">
+      <c r="H176" s="61" t="n">
         <v>37</v>
       </c>
-      <c r="I171" s="62" t="n">
+      <c r="I176" s="61" t="n">
         <v>49</v>
       </c>
     </row>
-    <row r="172" ht="15" customHeight="1">
-      <c r="A172" s="15" t="inlineStr">
+    <row r="177" ht="15" customHeight="1">
+      <c r="A177" s="14" t="inlineStr">
         <is>
           <t>Algerije</t>
         </is>
       </c>
-      <c r="E172" s="62" t="n">
+      <c r="E177" s="61" t="n">
         <v>11</v>
       </c>
-      <c r="F172" s="62" t="n">
+      <c r="F177" s="61" t="n">
         <v>19</v>
       </c>
-      <c r="G172" s="62" t="n">
+      <c r="G177" s="61" t="n">
         <v>28</v>
       </c>
-      <c r="H172" s="62" t="n">
+      <c r="H177" s="61" t="n">
         <v>40</v>
       </c>
-      <c r="I172" s="62" t="n">
+      <c r="I177" s="61" t="n">
         <v>52</v>
       </c>
     </row>
-    <row r="173" ht="15" customHeight="1">
-      <c r="A173" s="15" t="inlineStr">
+    <row r="178" ht="15" customHeight="1">
+      <c r="A178" s="14" t="inlineStr">
         <is>
           <t>Paraguay</t>
         </is>
       </c>
-      <c r="E173" s="62" t="n">
+      <c r="E178" s="61" t="n">
         <v>11</v>
       </c>
-      <c r="F173" s="62" t="n">
+      <c r="F178" s="61" t="n">
         <v>19</v>
       </c>
-      <c r="G173" s="62" t="n">
+      <c r="G178" s="61" t="n">
         <v>29</v>
       </c>
-      <c r="H173" s="62" t="n">
+      <c r="H178" s="61" t="n">
         <v>41</v>
       </c>
-      <c r="I173" s="62" t="n">
+      <c r="I178" s="61" t="n">
         <v>53</v>
       </c>
     </row>
-    <row r="174" ht="15" customHeight="1">
-      <c r="A174" s="15" t="inlineStr">
+    <row r="179" ht="15" customHeight="1">
+      <c r="A179" s="14" t="inlineStr">
         <is>
           <t>Ivoorkust</t>
         </is>
       </c>
-      <c r="E174" s="62" t="n">
+      <c r="E179" s="61" t="n">
         <v>12</v>
       </c>
-      <c r="F174" s="62" t="n">
+      <c r="F179" s="61" t="n">
         <v>20</v>
       </c>
-      <c r="G174" s="62" t="n">
+      <c r="G179" s="61" t="n">
         <v>30</v>
       </c>
-      <c r="H174" s="62" t="n">
+      <c r="H179" s="61" t="n">
         <v>41</v>
       </c>
-      <c r="I174" s="62" t="n">
+      <c r="I179" s="61" t="n">
         <v>55</v>
       </c>
     </row>
-    <row r="175" ht="15" customHeight="1">
-      <c r="A175" s="15" t="inlineStr">
+    <row r="180" ht="15" customHeight="1">
+      <c r="A180" s="14" t="inlineStr">
         <is>
           <t>Tunesië</t>
         </is>
       </c>
-      <c r="E175" s="62" t="n">
+      <c r="E180" s="61" t="n">
         <v>12</v>
       </c>
-      <c r="F175" s="62" t="n">
+      <c r="F180" s="61" t="n">
         <v>20</v>
       </c>
-      <c r="G175" s="62" t="n">
+      <c r="G180" s="61" t="n">
         <v>30</v>
       </c>
-      <c r="H175" s="62" t="n">
+      <c r="H180" s="61" t="n">
         <v>42</v>
       </c>
-      <c r="I175" s="62" t="n">
+      <c r="I180" s="61" t="n">
         <v>55</v>
       </c>
     </row>
-    <row r="176" ht="15" customHeight="1">
-      <c r="A176" s="15" t="inlineStr">
+    <row r="181" ht="15" customHeight="1">
+      <c r="A181" s="14" t="inlineStr">
         <is>
           <t>Schotland</t>
         </is>
       </c>
-      <c r="E176" s="62" t="n">
+      <c r="E181" s="61" t="n">
         <v>12</v>
       </c>
-      <c r="F176" s="62" t="n">
+      <c r="F181" s="61" t="n">
         <v>20</v>
       </c>
-      <c r="G176" s="62" t="n">
+      <c r="G181" s="61" t="n">
         <v>31</v>
       </c>
-      <c r="H176" s="62" t="n">
+      <c r="H181" s="61" t="n">
         <v>42</v>
       </c>
-      <c r="I176" s="62" t="n">
+      <c r="I181" s="61" t="n">
         <v>56</v>
       </c>
     </row>
-    <row r="177" ht="15" customHeight="1">
-      <c r="A177" s="15" t="inlineStr">
+    <row r="182" ht="15" customHeight="1">
+      <c r="A182" s="14" t="inlineStr">
         <is>
           <t>Zweden</t>
         </is>
       </c>
-      <c r="E177" s="62" t="n">
+      <c r="E182" s="61" t="n">
         <v>12</v>
       </c>
-      <c r="F177" s="62" t="n">
+      <c r="F182" s="61" t="n">
         <v>21</v>
       </c>
-      <c r="G177" s="62" t="n">
+      <c r="G182" s="61" t="n">
         <v>31</v>
       </c>
-      <c r="H177" s="62" t="n">
+      <c r="H182" s="61" t="n">
         <v>43</v>
       </c>
-      <c r="I177" s="62" t="n">
+      <c r="I182" s="61" t="n">
         <v>57</v>
       </c>
     </row>
-    <row r="178" ht="15" customHeight="1">
-      <c r="A178" s="15" t="inlineStr">
+    <row r="183" ht="15" customHeight="1">
+      <c r="A183" s="14" t="inlineStr">
         <is>
           <t>Tsjechië</t>
         </is>
       </c>
-      <c r="E178" s="62" t="n">
+      <c r="E183" s="61" t="n">
         <v>12</v>
       </c>
-      <c r="F178" s="62" t="n">
+      <c r="F183" s="61" t="n">
         <v>21</v>
       </c>
-      <c r="G178" s="62" t="n">
+      <c r="G183" s="61" t="n">
         <v>31</v>
       </c>
-      <c r="H178" s="62" t="n">
+      <c r="H183" s="61" t="n">
         <v>43</v>
       </c>
-      <c r="I178" s="62" t="n">
+      <c r="I183" s="61" t="n">
         <v>57</v>
       </c>
     </row>
-    <row r="179" ht="15" customHeight="1">
-      <c r="A179" s="15" t="inlineStr">
+    <row r="184" ht="15" customHeight="1">
+      <c r="A184" s="14" t="inlineStr">
         <is>
           <t>Qatar</t>
         </is>
       </c>
-      <c r="E179" s="62" t="n">
+      <c r="E184" s="61" t="n">
         <v>13</v>
       </c>
-      <c r="F179" s="62" t="n">
+      <c r="F184" s="61" t="n">
         <v>22</v>
       </c>
-      <c r="G179" s="62" t="n">
+      <c r="G184" s="61" t="n">
         <v>33</v>
       </c>
-      <c r="H179" s="62" t="n">
+      <c r="H184" s="61" t="n">
         <v>46</v>
       </c>
-      <c r="I179" s="62" t="n">
+      <c r="I184" s="61" t="n">
         <v>61</v>
       </c>
     </row>
-    <row r="180" ht="15" customHeight="1">
-      <c r="A180" s="15" t="inlineStr">
+    <row r="185" ht="15" customHeight="1">
+      <c r="A185" s="14" t="inlineStr">
         <is>
           <t>Oezbekistan</t>
         </is>
       </c>
-      <c r="E180" s="62" t="n">
+      <c r="E185" s="61" t="n">
         <v>13</v>
       </c>
-      <c r="F180" s="62" t="n">
+      <c r="F185" s="61" t="n">
         <v>23</v>
       </c>
-      <c r="G180" s="62" t="n">
+      <c r="G185" s="61" t="n">
         <v>34</v>
       </c>
-      <c r="H180" s="62" t="n">
+      <c r="H185" s="61" t="n">
         <v>47</v>
       </c>
-      <c r="I180" s="62" t="n">
+      <c r="I185" s="61" t="n">
         <v>63</v>
       </c>
     </row>
-    <row r="181" ht="15" customHeight="1">
-      <c r="A181" s="15" t="inlineStr">
+    <row r="186" ht="15" customHeight="1">
+      <c r="A186" s="14" t="inlineStr">
         <is>
           <t>DR Congo</t>
         </is>
       </c>
-      <c r="E181" s="62" t="n">
+      <c r="E186" s="61" t="n">
         <v>14</v>
       </c>
-      <c r="F181" s="62" t="n">
+      <c r="F186" s="61" t="n">
         <v>23</v>
       </c>
-      <c r="G181" s="62" t="n">
+      <c r="G186" s="61" t="n">
         <v>35</v>
       </c>
-      <c r="H181" s="62" t="n">
+      <c r="H186" s="61" t="n">
         <v>48</v>
       </c>
-      <c r="I181" s="62" t="n">
+      <c r="I186" s="61" t="n">
         <v>64</v>
       </c>
     </row>
-    <row r="182" ht="15" customHeight="1">
-      <c r="A182" s="15" t="inlineStr">
+    <row r="187" ht="15" customHeight="1">
+      <c r="A187" s="14" t="inlineStr">
         <is>
           <t>Saoedi-Arabië</t>
         </is>
       </c>
-      <c r="E182" s="62" t="n">
+      <c r="E187" s="61" t="n">
         <v>14</v>
       </c>
-      <c r="F182" s="62" t="n">
+      <c r="F187" s="61" t="n">
         <v>24</v>
       </c>
-      <c r="G182" s="62" t="n">
+      <c r="G187" s="61" t="n">
         <v>35</v>
       </c>
-      <c r="H182" s="62" t="n">
+      <c r="H187" s="61" t="n">
         <v>49</v>
       </c>
-      <c r="I182" s="62" t="n">
+      <c r="I187" s="61" t="n">
         <v>65</v>
       </c>
     </row>
-    <row r="183" ht="15" customHeight="1">
-      <c r="A183" s="15" t="inlineStr">
+    <row r="188" ht="15" customHeight="1">
+      <c r="A188" s="14" t="inlineStr">
         <is>
           <t>Irak</t>
         </is>
       </c>
-      <c r="E183" s="62" t="n">
+      <c r="E188" s="61" t="n">
         <v>14</v>
       </c>
-      <c r="F183" s="62" t="n">
+      <c r="F188" s="61" t="n">
         <v>24</v>
       </c>
-      <c r="G183" s="62" t="n">
+      <c r="G188" s="61" t="n">
         <v>36</v>
       </c>
-      <c r="H183" s="62" t="n">
+      <c r="H188" s="61" t="n">
         <v>49</v>
       </c>
-      <c r="I183" s="62" t="n">
+      <c r="I188" s="61" t="n">
         <v>65</v>
       </c>
     </row>
-    <row r="184" ht="15" customHeight="1">
-      <c r="A184" s="15" t="inlineStr">
+    <row r="189" ht="15" customHeight="1">
+      <c r="A189" s="14" t="inlineStr">
         <is>
           <t>Zuid-Afrika</t>
         </is>
       </c>
-      <c r="E184" s="62" t="n">
+      <c r="E189" s="61" t="n">
         <v>14</v>
       </c>
-      <c r="F184" s="62" t="n">
+      <c r="F189" s="61" t="n">
         <v>24</v>
       </c>
-      <c r="G184" s="62" t="n">
+      <c r="G189" s="61" t="n">
         <v>36</v>
       </c>
-      <c r="H184" s="62" t="n">
+      <c r="H189" s="61" t="n">
         <v>50</v>
       </c>
-      <c r="I184" s="62" t="n">
+      <c r="I189" s="61" t="n">
         <v>66</v>
       </c>
     </row>
-    <row r="185" ht="15" customHeight="1">
-      <c r="A185" s="15" t="inlineStr">
+    <row r="190" ht="15" customHeight="1">
+      <c r="A190" s="14" t="inlineStr">
         <is>
           <t>Jordanië</t>
         </is>
       </c>
-      <c r="E185" s="62" t="n">
+      <c r="E190" s="61" t="n">
         <v>14</v>
       </c>
-      <c r="F185" s="62" t="n">
+      <c r="F190" s="61" t="n">
         <v>25</v>
       </c>
-      <c r="G185" s="62" t="n">
+      <c r="G190" s="61" t="n">
         <v>37</v>
       </c>
-      <c r="H185" s="62" t="n">
+      <c r="H190" s="61" t="n">
         <v>51</v>
       </c>
-      <c r="I185" s="62" t="n">
+      <c r="I190" s="61" t="n">
         <v>68</v>
       </c>
     </row>
-    <row r="186" ht="15" customHeight="1">
-      <c r="A186" s="15" t="inlineStr">
+    <row r="191" ht="15" customHeight="1">
+      <c r="A191" s="14" t="inlineStr">
         <is>
           <t>Kaapverdië</t>
         </is>
       </c>
-      <c r="E186" s="62" t="n">
+      <c r="E191" s="61" t="n">
         <v>15</v>
       </c>
-      <c r="F186" s="62" t="n">
+      <c r="F191" s="61" t="n">
         <v>26</v>
       </c>
-      <c r="G186" s="62" t="n">
+      <c r="G191" s="61" t="n">
         <v>38</v>
       </c>
-      <c r="H186" s="62" t="n">
+      <c r="H191" s="61" t="n">
         <v>53</v>
       </c>
-      <c r="I186" s="62" t="n">
+      <c r="I191" s="61" t="n">
         <v>70</v>
       </c>
     </row>
-    <row r="187" ht="15" customHeight="1">
-      <c r="A187" s="15" t="inlineStr">
+    <row r="192" ht="15" customHeight="1">
+      <c r="A192" s="14" t="inlineStr">
         <is>
           <t>Ghana</t>
         </is>
       </c>
-      <c r="E187" s="62" t="n">
+      <c r="E192" s="61" t="n">
         <v>15</v>
       </c>
-      <c r="F187" s="62" t="n">
+      <c r="F192" s="61" t="n">
         <v>26</v>
       </c>
-      <c r="G187" s="62" t="n">
+      <c r="G192" s="61" t="n">
         <v>39</v>
       </c>
-      <c r="H187" s="62" t="n">
+      <c r="H192" s="61" t="n">
         <v>54</v>
       </c>
-      <c r="I187" s="62" t="n">
+      <c r="I192" s="61" t="n">
         <v>72</v>
       </c>
     </row>
-    <row r="188" ht="15" customHeight="1">
-      <c r="A188" s="15" t="inlineStr">
+    <row r="193" ht="15" customHeight="1">
+      <c r="A193" s="14" t="inlineStr">
         <is>
           <t>Bosnië-Herzegovina</t>
         </is>
       </c>
-      <c r="E188" s="62" t="n">
+      <c r="E193" s="61" t="n">
         <v>15</v>
       </c>
-      <c r="F188" s="62" t="n">
+      <c r="F193" s="61" t="n">
         <v>26</v>
       </c>
-      <c r="G188" s="62" t="n">
+      <c r="G193" s="61" t="n">
         <v>39</v>
       </c>
-      <c r="H188" s="62" t="n">
+      <c r="H193" s="61" t="n">
         <v>55</v>
       </c>
-      <c r="I188" s="62" t="n">
+      <c r="I193" s="61" t="n">
         <v>72</v>
       </c>
     </row>
-    <row r="189" ht="15" customHeight="1">
-      <c r="A189" s="15" t="inlineStr">
+    <row r="194" ht="15" customHeight="1">
+      <c r="A194" s="14" t="inlineStr">
         <is>
           <t>Haïti</t>
         </is>
       </c>
-      <c r="E189" s="62" t="n">
+      <c r="E194" s="61" t="n">
         <v>16</v>
       </c>
-      <c r="F189" s="62" t="n">
+      <c r="F194" s="61" t="n">
         <v>28</v>
       </c>
-      <c r="G189" s="62" t="n">
+      <c r="G194" s="61" t="n">
         <v>41</v>
       </c>
-      <c r="H189" s="62" t="n">
+      <c r="H194" s="61" t="n">
         <v>58</v>
       </c>
-      <c r="I189" s="62" t="n">
+      <c r="I194" s="61" t="n">
         <v>76</v>
       </c>
     </row>
-    <row r="190" ht="15" customHeight="1">
-      <c r="A190" s="15" t="inlineStr">
+    <row r="195" ht="15" customHeight="1">
+      <c r="A195" s="14" t="inlineStr">
         <is>
           <t>Nieuw-Zeeland</t>
         </is>
       </c>
-      <c r="E190" s="62" t="n">
+      <c r="E195" s="61" t="n">
         <v>16</v>
       </c>
-      <c r="F190" s="62" t="n">
+      <c r="F195" s="61" t="n">
         <v>28</v>
       </c>
-      <c r="G190" s="62" t="n">
+      <c r="G195" s="61" t="n">
         <v>42</v>
       </c>
-      <c r="H190" s="62" t="n">
+      <c r="H195" s="61" t="n">
         <v>59</v>
       </c>
-      <c r="I190" s="62" t="n">
+      <c r="I195" s="61" t="n">
         <v>77</v>
       </c>
     </row>
-    <row r="191" ht="15" customHeight="1">
-      <c r="A191" s="15" t="inlineStr">
+    <row r="196" ht="15" customHeight="1">
+      <c r="A196" s="14" t="inlineStr">
         <is>
           <t>Curaçao</t>
         </is>
       </c>
-      <c r="E191" s="62" t="n">
+      <c r="E196" s="61" t="n">
         <v>17</v>
       </c>
-      <c r="F191" s="62" t="n">
+      <c r="F196" s="61" t="n">
         <v>29</v>
       </c>
-      <c r="G191" s="62" t="n">
+      <c r="G196" s="61" t="n">
         <v>43</v>
       </c>
-      <c r="H191" s="62" t="n">
+      <c r="H196" s="61" t="n">
         <v>60</v>
       </c>
-      <c r="I191" s="62" t="n">
+      <c r="I196" s="61" t="n">
         <v>79</v>
       </c>
     </row>
-    <row r="192" ht="15" customHeight="1">
-      <c r="A192" s="15" t="inlineStr">
+    <row r="197" ht="15" customHeight="1">
+      <c r="A197" s="14" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="E192" s="62" t="n">
+      <c r="E197" s="61" t="n">
         <v>13</v>
       </c>
-      <c r="F192" s="62" t="n">
+      <c r="F197" s="61" t="n">
         <v>22</v>
       </c>
-      <c r="G192" s="62" t="n">
+      <c r="G197" s="61" t="n">
         <v>33</v>
       </c>
-      <c r="H192" s="62" t="n">
+      <c r="H197" s="61" t="n">
         <v>46</v>
       </c>
-      <c r="I192" s="62" t="n">
+      <c r="I197" s="61" t="n">
         <v>61</v>
       </c>
     </row>
-    <row r="193" ht="15" customHeight="1">
-      <c r="A193" s="15" t="inlineStr">
+    <row r="198" ht="15" customHeight="1">
+      <c r="A198" s="14" t="inlineStr">
         <is>
           <t>Turkije</t>
         </is>
       </c>
-      <c r="E193" s="62" t="n">
+      <c r="E198" s="61" t="n">
         <v>13</v>
       </c>
-      <c r="F193" s="62" t="n">
+      <c r="F198" s="61" t="n">
         <v>22</v>
       </c>
-      <c r="G193" s="62" t="n">
+      <c r="G198" s="61" t="n">
         <v>33</v>
       </c>
-      <c r="H193" s="62" t="n">
+      <c r="H198" s="61" t="n">
         <v>46</v>
       </c>
-      <c r="I193" s="62" t="n">
+      <c r="I198" s="61" t="n">
         <v>61</v>
       </c>
     </row>
-    <row r="194" ht="8" customHeight="1"/>
-    <row r="195" ht="18" customHeight="1">
-      <c r="A195" s="4" t="inlineStr">
+    <row r="199" ht="8" customHeight="1"/>
+    <row r="200" ht="18" customHeight="1">
+      <c r="A200" s="3" t="inlineStr">
         <is>
           <t>▶  DECEPTIE — kies een land UIT de top-12 · punten schalen met ranking en uitvalsronde</t>
         </is>
       </c>
     </row>
-    <row r="196" ht="14" customHeight="1">
-      <c r="A196" s="13" t="inlineStr">
+    <row r="201" ht="14" customHeight="1">
+      <c r="A201" s="12" t="inlineStr">
         <is>
           <t>Land (favoriet)</t>
         </is>
       </c>
-      <c r="E196" s="13" t="inlineStr">
+      <c r="E201" s="12" t="inlineStr">
         <is>
           <t>KF</t>
         </is>
       </c>
-      <c r="F196" s="13" t="inlineStr">
+      <c r="F201" s="12" t="inlineStr">
         <is>
           <t>R16</t>
         </is>
       </c>
-      <c r="G196" s="13" t="inlineStr">
+      <c r="G201" s="12" t="inlineStr">
         <is>
           <t>R32</t>
         </is>
       </c>
-      <c r="H196" s="13" t="inlineStr">
+      <c r="H201" s="12" t="inlineStr">
         <is>
           <t>Groep eruit</t>
         </is>
       </c>
     </row>
-    <row r="197" ht="15" customHeight="1">
-      <c r="A197" s="15" t="inlineStr">
+    <row r="202" ht="15" customHeight="1">
+      <c r="A202" s="14" t="inlineStr">
         <is>
           <t>Frankrijk</t>
         </is>
       </c>
-      <c r="E197" s="62" t="n">
+      <c r="E202" s="61" t="n">
         <v>8</v>
       </c>
-      <c r="F197" s="62" t="n">
+      <c r="F202" s="61" t="n">
         <v>14</v>
       </c>
-      <c r="G197" s="62" t="n">
+      <c r="G202" s="61" t="n">
         <v>20</v>
       </c>
-      <c r="H197" s="62" t="n">
+      <c r="H202" s="61" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="198" ht="15" customHeight="1">
-      <c r="A198" s="15" t="inlineStr">
+    <row r="203" ht="15" customHeight="1">
+      <c r="A203" s="14" t="inlineStr">
         <is>
           <t>Spanje</t>
         </is>
       </c>
-      <c r="E198" s="62" t="n">
+      <c r="E203" s="61" t="n">
         <v>7</v>
       </c>
-      <c r="F198" s="62" t="n">
+      <c r="F203" s="61" t="n">
         <v>13</v>
       </c>
-      <c r="G198" s="62" t="n">
+      <c r="G203" s="61" t="n">
         <v>19</v>
       </c>
-      <c r="H198" s="62" t="n">
+      <c r="H203" s="61" t="n">
         <v>28</v>
       </c>
     </row>
-    <row r="199" ht="15" customHeight="1">
-      <c r="A199" s="15" t="inlineStr">
+    <row r="204" ht="15" customHeight="1">
+      <c r="A204" s="14" t="inlineStr">
         <is>
           <t>Argentinië</t>
         </is>
       </c>
-      <c r="E199" s="62" t="n">
+      <c r="E204" s="61" t="n">
         <v>6</v>
       </c>
-      <c r="F199" s="62" t="n">
+      <c r="F204" s="61" t="n">
         <v>12</v>
       </c>
-      <c r="G199" s="62" t="n">
+      <c r="G204" s="61" t="n">
         <v>17</v>
       </c>
-      <c r="H199" s="62" t="n">
+      <c r="H204" s="61" t="n">
         <v>26</v>
       </c>
     </row>
-    <row r="200" ht="15" customHeight="1">
-      <c r="A200" s="15" t="inlineStr">
+    <row r="205" ht="15" customHeight="1">
+      <c r="A205" s="14" t="inlineStr">
         <is>
           <t>Engeland</t>
         </is>
       </c>
-      <c r="E200" s="62" t="n">
+      <c r="E205" s="61" t="n">
         <v>6</v>
       </c>
-      <c r="F200" s="62" t="n">
+      <c r="F205" s="61" t="n">
         <v>11</v>
       </c>
-      <c r="G200" s="62" t="n">
+      <c r="G205" s="61" t="n">
         <v>16</v>
       </c>
-      <c r="H200" s="62" t="n">
+      <c r="H205" s="61" t="n">
         <v>24</v>
       </c>
     </row>
-    <row r="201" ht="15" customHeight="1">
-      <c r="A201" s="15" t="inlineStr">
+    <row r="206" ht="15" customHeight="1">
+      <c r="A206" s="14" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="E201" s="62" t="n">
+      <c r="E206" s="61" t="n">
         <v>6</v>
       </c>
-      <c r="F201" s="62" t="n">
+      <c r="F206" s="61" t="n">
         <v>10</v>
       </c>
-      <c r="G201" s="62" t="n">
+      <c r="G206" s="61" t="n">
         <v>15</v>
       </c>
-      <c r="H201" s="62" t="n">
+      <c r="H206" s="61" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="202" ht="15" customHeight="1">
-      <c r="A202" s="15" t="inlineStr">
+    <row r="207" ht="15" customHeight="1">
+      <c r="A207" s="14" t="inlineStr">
         <is>
           <t>Brazilië</t>
         </is>
       </c>
-      <c r="E202" s="62" t="n">
+      <c r="E207" s="61" t="n">
         <v>5</v>
       </c>
-      <c r="F202" s="62" t="n">
+      <c r="F207" s="61" t="n">
         <v>9</v>
       </c>
-      <c r="G202" s="62" t="n">
+      <c r="G207" s="61" t="n">
         <v>13</v>
       </c>
-      <c r="H202" s="62" t="n">
+      <c r="H207" s="61" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="203" ht="15" customHeight="1">
-      <c r="A203" s="15" t="inlineStr">
+    <row r="208" ht="15" customHeight="1">
+      <c r="A208" s="14" t="inlineStr">
         <is>
           <t>Nederland</t>
         </is>
       </c>
-      <c r="E203" s="62" t="n">
+      <c r="E208" s="61" t="n">
         <v>4</v>
       </c>
-      <c r="F203" s="62" t="n">
+      <c r="F208" s="61" t="n">
         <v>8</v>
       </c>
-      <c r="G203" s="62" t="n">
+      <c r="G208" s="61" t="n">
         <v>12</v>
       </c>
-      <c r="H203" s="62" t="n">
+      <c r="H208" s="61" t="n">
         <v>18</v>
       </c>
     </row>
-    <row r="204" ht="15" customHeight="1">
-      <c r="A204" s="15" t="inlineStr">
+    <row r="209" ht="15" customHeight="1">
+      <c r="A209" s="14" t="inlineStr">
         <is>
           <t>Marokko</t>
         </is>
       </c>
-      <c r="E204" s="62" t="n">
+      <c r="E209" s="61" t="n">
         <v>4</v>
       </c>
-      <c r="F204" s="62" t="n">
+      <c r="F209" s="61" t="n">
         <v>7</v>
       </c>
-      <c r="G204" s="62" t="n">
+      <c r="G209" s="61" t="n">
         <v>11</v>
       </c>
-      <c r="H204" s="62" t="n">
+      <c r="H209" s="61" t="n">
         <v>16</v>
       </c>
     </row>
-    <row r="205" ht="15" customHeight="1">
-      <c r="A205" s="15" t="inlineStr">
+    <row r="210" ht="15" customHeight="1">
+      <c r="A210" s="14" t="inlineStr">
         <is>
           <t>België</t>
         </is>
       </c>
-      <c r="E205" s="62" t="n">
+      <c r="E210" s="61" t="n">
         <v>4</v>
       </c>
-      <c r="F205" s="62" t="n">
+      <c r="F210" s="61" t="n">
         <v>6</v>
       </c>
-      <c r="G205" s="62" t="n">
+      <c r="G210" s="61" t="n">
         <v>9</v>
       </c>
-      <c r="H205" s="62" t="n">
+      <c r="H210" s="61" t="n">
         <v>14</v>
       </c>
     </row>
-    <row r="206" ht="15" customHeight="1">
-      <c r="A206" s="15" t="inlineStr">
+    <row r="211" ht="15" customHeight="1">
+      <c r="A211" s="14" t="inlineStr">
         <is>
           <t>Duitsland</t>
         </is>
       </c>
-      <c r="E206" s="62" t="n">
+      <c r="E211" s="61" t="n">
         <v>3</v>
       </c>
-      <c r="F206" s="62" t="n">
+      <c r="F211" s="61" t="n">
         <v>6</v>
       </c>
-      <c r="G206" s="62" t="n">
+      <c r="G211" s="61" t="n">
         <v>8</v>
       </c>
-      <c r="H206" s="62" t="n">
+      <c r="H211" s="61" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="207" ht="15" customHeight="1">
-      <c r="A207" s="15" t="inlineStr">
+    <row r="212" ht="15" customHeight="1">
+      <c r="A212" s="14" t="inlineStr">
         <is>
           <t>Kroatië</t>
         </is>
       </c>
-      <c r="E207" s="62" t="n">
+      <c r="E212" s="61" t="n">
         <v>2</v>
       </c>
-      <c r="F207" s="62" t="n">
+      <c r="F212" s="61" t="n">
         <v>5</v>
       </c>
-      <c r="G207" s="62" t="n">
+      <c r="G212" s="61" t="n">
         <v>7</v>
       </c>
-      <c r="H207" s="62" t="n">
+      <c r="H212" s="61" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="208" ht="15" customHeight="1">
-      <c r="A208" s="15" t="inlineStr">
+    <row r="213" ht="15" customHeight="1">
+      <c r="A213" s="14" t="inlineStr">
         <is>
           <t>Colombia</t>
         </is>
       </c>
-      <c r="E208" s="62" t="n">
+      <c r="E213" s="61" t="n">
         <v>2</v>
       </c>
-      <c r="F208" s="62" t="n">
+      <c r="F213" s="61" t="n">
         <v>3</v>
       </c>
-      <c r="G208" s="62" t="n">
+      <c r="G213" s="61" t="n">
         <v>4</v>
       </c>
-      <c r="H208" s="62" t="n">
+      <c r="H213" s="61" t="n">
         <v>6</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="200">
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="B41:O41"/>
-    <mergeCell ref="B35:O35"/>
-    <mergeCell ref="A144:D144"/>
-    <mergeCell ref="A159:D159"/>
+  <mergeCells count="199">
+    <mergeCell ref="E13:G13"/>
     <mergeCell ref="A122:D122"/>
-    <mergeCell ref="A72:D72"/>
-    <mergeCell ref="B25:O25"/>
-    <mergeCell ref="A134:D134"/>
-    <mergeCell ref="A200:D200"/>
-    <mergeCell ref="A81:D81"/>
-    <mergeCell ref="A112:D112"/>
+    <mergeCell ref="A97:D97"/>
+    <mergeCell ref="A133:O133"/>
     <mergeCell ref="A121:D121"/>
-    <mergeCell ref="M81:O81"/>
-    <mergeCell ref="A161:D161"/>
-    <mergeCell ref="A3:O3"/>
-    <mergeCell ref="A44:D44"/>
-    <mergeCell ref="B27:O27"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="A13:D13"/>
     <mergeCell ref="A202:D202"/>
     <mergeCell ref="A176:D176"/>
-    <mergeCell ref="A114:D114"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A64:D64"/>
-    <mergeCell ref="I81:L81"/>
-    <mergeCell ref="A32:O32"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="E57:G57"/>
     <mergeCell ref="A186:D186"/>
-    <mergeCell ref="A51:D51"/>
+    <mergeCell ref="M106:O106"/>
+    <mergeCell ref="A107:D107"/>
     <mergeCell ref="A178:D178"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="A106:O106"/>
-    <mergeCell ref="E81:G81"/>
-    <mergeCell ref="A38:O38"/>
-    <mergeCell ref="A13:O13"/>
+    <mergeCell ref="M76:O76"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="A29:O29"/>
+    <mergeCell ref="A200:O200"/>
+    <mergeCell ref="B44:O44"/>
+    <mergeCell ref="A161:O161"/>
+    <mergeCell ref="M66:O66"/>
+    <mergeCell ref="I106:L106"/>
     <mergeCell ref="A124:D124"/>
-    <mergeCell ref="B29:O29"/>
-    <mergeCell ref="A54:D54"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="B37:O37"/>
+    <mergeCell ref="A31:O31"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="I76:L76"/>
     <mergeCell ref="A172:D172"/>
-    <mergeCell ref="A40:O40"/>
+    <mergeCell ref="A99:D99"/>
     <mergeCell ref="A164:D164"/>
-    <mergeCell ref="A15:O15"/>
+    <mergeCell ref="E106:G106"/>
+    <mergeCell ref="A212:D212"/>
+    <mergeCell ref="I66:L66"/>
+    <mergeCell ref="A56:D56"/>
     <mergeCell ref="A24:O24"/>
+    <mergeCell ref="A154:D154"/>
     <mergeCell ref="A149:D149"/>
-    <mergeCell ref="M52:O52"/>
     <mergeCell ref="A163:D163"/>
-    <mergeCell ref="A101:D101"/>
-    <mergeCell ref="E92:G92"/>
+    <mergeCell ref="M67:O67"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A195:D195"/>
     <mergeCell ref="A204:D204"/>
-    <mergeCell ref="A146:O146"/>
-    <mergeCell ref="I52:L52"/>
+    <mergeCell ref="E107:G107"/>
     <mergeCell ref="A188:D188"/>
     <mergeCell ref="A126:D126"/>
     <mergeCell ref="A141:D141"/>
-    <mergeCell ref="A16:O16"/>
     <mergeCell ref="A135:D135"/>
     <mergeCell ref="A206:D206"/>
-    <mergeCell ref="I44:L44"/>
-    <mergeCell ref="A62:D62"/>
-    <mergeCell ref="A108:O108"/>
+    <mergeCell ref="A27:O27"/>
     <mergeCell ref="A125:D125"/>
     <mergeCell ref="A190:D190"/>
     <mergeCell ref="A18:O18"/>
-    <mergeCell ref="I94:L94"/>
     <mergeCell ref="A117:D117"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="A111:D111"/>
-    <mergeCell ref="A199:D199"/>
+    <mergeCell ref="E77:G77"/>
+    <mergeCell ref="M86:O86"/>
     <mergeCell ref="A9:D9"/>
-    <mergeCell ref="I84:L84"/>
+    <mergeCell ref="E86:G86"/>
+    <mergeCell ref="A127:D127"/>
     <mergeCell ref="A167:D167"/>
     <mergeCell ref="A151:O151"/>
-    <mergeCell ref="E61:G61"/>
+    <mergeCell ref="A59:D59"/>
+    <mergeCell ref="I77:L77"/>
     <mergeCell ref="A142:D142"/>
+    <mergeCell ref="M57:O57"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="A22:O22"/>
+    <mergeCell ref="B42:O42"/>
+    <mergeCell ref="I86:L86"/>
+    <mergeCell ref="M97:O97"/>
+    <mergeCell ref="A144:O144"/>
+    <mergeCell ref="A169:D169"/>
+    <mergeCell ref="I89:L89"/>
     <mergeCell ref="A182:D182"/>
     <mergeCell ref="A191:D191"/>
-    <mergeCell ref="A169:D169"/>
-    <mergeCell ref="M72:O72"/>
-    <mergeCell ref="I61:L61"/>
-    <mergeCell ref="E72:G72"/>
-    <mergeCell ref="A61:D61"/>
-    <mergeCell ref="A28:O28"/>
+    <mergeCell ref="A20:O20"/>
+    <mergeCell ref="A79:D79"/>
+    <mergeCell ref="E97:G97"/>
+    <mergeCell ref="I57:L57"/>
     <mergeCell ref="A153:D153"/>
     <mergeCell ref="A162:D162"/>
-    <mergeCell ref="M71:O71"/>
-    <mergeCell ref="I54:L54"/>
-    <mergeCell ref="I72:L72"/>
+    <mergeCell ref="M56:O56"/>
+    <mergeCell ref="E56:G56"/>
+    <mergeCell ref="E96:G96"/>
+    <mergeCell ref="B34:O34"/>
+    <mergeCell ref="A128:D128"/>
+    <mergeCell ref="B28:O28"/>
     <mergeCell ref="A137:D137"/>
     <mergeCell ref="A177:D177"/>
+    <mergeCell ref="A48:O48"/>
     <mergeCell ref="A208:D208"/>
-    <mergeCell ref="A30:O30"/>
-    <mergeCell ref="E71:G71"/>
+    <mergeCell ref="A114:O114"/>
     <mergeCell ref="A136:D136"/>
+    <mergeCell ref="I56:L56"/>
+    <mergeCell ref="I96:L96"/>
+    <mergeCell ref="M107:O107"/>
     <mergeCell ref="A192:D192"/>
-    <mergeCell ref="I71:L71"/>
-    <mergeCell ref="A74:D74"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="G1:K1"/>
+    <mergeCell ref="B30:O30"/>
+    <mergeCell ref="A139:D139"/>
+    <mergeCell ref="A210:D210"/>
     <mergeCell ref="A179:D179"/>
-    <mergeCell ref="A71:D71"/>
-    <mergeCell ref="E82:G82"/>
-    <mergeCell ref="A203:D203"/>
+    <mergeCell ref="A129:D129"/>
+    <mergeCell ref="A194:D194"/>
+    <mergeCell ref="A76:D76"/>
+    <mergeCell ref="I107:L107"/>
     <mergeCell ref="A116:D116"/>
     <mergeCell ref="A181:D181"/>
     <mergeCell ref="E10:G10"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A91:D91"/>
+    <mergeCell ref="A203:D203"/>
     <mergeCell ref="A184:D184"/>
     <mergeCell ref="A131:D131"/>
-    <mergeCell ref="I82:L82"/>
+    <mergeCell ref="A41:O41"/>
+    <mergeCell ref="A140:D140"/>
     <mergeCell ref="A171:D171"/>
-    <mergeCell ref="A52:D52"/>
     <mergeCell ref="A165:D165"/>
+    <mergeCell ref="A180:D180"/>
     <mergeCell ref="E9:G9"/>
-    <mergeCell ref="A180:D180"/>
-    <mergeCell ref="B31:O31"/>
     <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A115:D115"/>
-    <mergeCell ref="A139:O139"/>
-    <mergeCell ref="A102:D102"/>
+    <mergeCell ref="B46:O46"/>
+    <mergeCell ref="I59:L59"/>
+    <mergeCell ref="I99:L99"/>
     <mergeCell ref="A173:D173"/>
+    <mergeCell ref="M77:O77"/>
     <mergeCell ref="E11:G11"/>
-    <mergeCell ref="I74:L74"/>
-    <mergeCell ref="B39:O39"/>
-    <mergeCell ref="A195:O195"/>
-    <mergeCell ref="A143:D143"/>
-    <mergeCell ref="A92:D92"/>
-    <mergeCell ref="A157:D157"/>
+    <mergeCell ref="A77:D77"/>
+    <mergeCell ref="I69:L69"/>
+    <mergeCell ref="A33:O33"/>
     <mergeCell ref="A166:D166"/>
-    <mergeCell ref="M61:O61"/>
-    <mergeCell ref="A17:O17"/>
-    <mergeCell ref="B23:O23"/>
-    <mergeCell ref="M62:O62"/>
+    <mergeCell ref="A8:O8"/>
+    <mergeCell ref="A49:D49"/>
     <mergeCell ref="A207:D207"/>
-    <mergeCell ref="A109:O109"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A94:D94"/>
+    <mergeCell ref="A35:O35"/>
     <mergeCell ref="A168:D168"/>
-    <mergeCell ref="E102:G102"/>
+    <mergeCell ref="A69:D69"/>
     <mergeCell ref="A19:O19"/>
     <mergeCell ref="A205:D205"/>
-    <mergeCell ref="A34:O34"/>
-    <mergeCell ref="A133:D133"/>
+    <mergeCell ref="A87:D87"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="A111:O111"/>
+    <mergeCell ref="M87:O87"/>
+    <mergeCell ref="M96:O96"/>
     <mergeCell ref="A193:D193"/>
-    <mergeCell ref="E62:G62"/>
+    <mergeCell ref="A39:O39"/>
+    <mergeCell ref="I97:L97"/>
+    <mergeCell ref="A89:D89"/>
     <mergeCell ref="A120:D120"/>
-    <mergeCell ref="A36:O36"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="A113:D113"/>
-    <mergeCell ref="I62:L62"/>
-    <mergeCell ref="M51:O51"/>
-    <mergeCell ref="M82:O82"/>
-    <mergeCell ref="E51:G51"/>
+    <mergeCell ref="E14:G14"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="I87:L87"/>
+    <mergeCell ref="A45:O45"/>
+    <mergeCell ref="A57:D57"/>
+    <mergeCell ref="B36:O36"/>
+    <mergeCell ref="E87:G87"/>
+    <mergeCell ref="A14:D14"/>
     <mergeCell ref="A185:D185"/>
-    <mergeCell ref="I64:L64"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A128:O128"/>
-    <mergeCell ref="I51:L51"/>
+    <mergeCell ref="A106:D106"/>
+    <mergeCell ref="I79:L79"/>
+    <mergeCell ref="A96:D96"/>
+    <mergeCell ref="A209:D209"/>
+    <mergeCell ref="A147:D147"/>
+    <mergeCell ref="A37:O37"/>
     <mergeCell ref="A170:D170"/>
     <mergeCell ref="A21:O21"/>
-    <mergeCell ref="A105:O105"/>
+    <mergeCell ref="A211:D211"/>
     <mergeCell ref="A26:O26"/>
+    <mergeCell ref="A67:D67"/>
+    <mergeCell ref="A113:O113"/>
     <mergeCell ref="A130:D130"/>
-    <mergeCell ref="A14:O14"/>
-    <mergeCell ref="M101:O101"/>
     <mergeCell ref="A201:D201"/>
     <mergeCell ref="A148:D148"/>
-    <mergeCell ref="A82:D82"/>
-    <mergeCell ref="E101:G101"/>
-    <mergeCell ref="M91:O91"/>
-    <mergeCell ref="E91:G91"/>
+    <mergeCell ref="A23:O23"/>
+    <mergeCell ref="E76:G76"/>
+    <mergeCell ref="I49:L49"/>
     <mergeCell ref="A123:D123"/>
-    <mergeCell ref="A132:D132"/>
+    <mergeCell ref="A138:D138"/>
     <mergeCell ref="A197:D197"/>
     <mergeCell ref="A43:O43"/>
+    <mergeCell ref="A146:D146"/>
     <mergeCell ref="A156:O156"/>
-    <mergeCell ref="I101:L101"/>
-    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="E66:G66"/>
     <mergeCell ref="A119:D119"/>
-    <mergeCell ref="I91:L91"/>
-    <mergeCell ref="M102:O102"/>
+    <mergeCell ref="B38:O38"/>
     <mergeCell ref="A187:D187"/>
+    <mergeCell ref="D6:J6"/>
     <mergeCell ref="A196:D196"/>
     <mergeCell ref="A174:D174"/>
     <mergeCell ref="A183:D183"/>
-    <mergeCell ref="A84:D84"/>
-    <mergeCell ref="M92:O92"/>
+    <mergeCell ref="A66:D66"/>
+    <mergeCell ref="B40:O40"/>
     <mergeCell ref="A118:D118"/>
     <mergeCell ref="A189:D189"/>
     <mergeCell ref="A158:D158"/>
-    <mergeCell ref="E52:G52"/>
-    <mergeCell ref="I102:L102"/>
     <mergeCell ref="A198:D198"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="B33:O33"/>
-    <mergeCell ref="I92:L92"/>
-    <mergeCell ref="A160:D160"/>
+    <mergeCell ref="E67:G67"/>
+    <mergeCell ref="A86:D86"/>
+    <mergeCell ref="A110:O110"/>
+    <mergeCell ref="A213:D213"/>
     <mergeCell ref="A175:D175"/>
+    <mergeCell ref="I67:L67"/>
+    <mergeCell ref="B32:O32"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation sqref="E4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Landen!$A$1:$A$48</formula1>
     </dataValidation>
-    <dataValidation sqref="E5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Landen!$B$1:$B$36</formula1>
     </dataValidation>
-    <dataValidation sqref="E6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Landen!$C$1:$C$12</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/tempetoto2026_invulformulier.xlsx
+++ b/tempetoto2026_invulformulier.xlsx
@@ -421,7 +421,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -514,6 +514,7 @@
     <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3521,6 +3522,11 @@
       </c>
     </row>
     <row r="115" ht="14" customHeight="1">
+      <c r="A115" s="12" t="inlineStr">
+        <is>
+          <t>Wedstrijd</t>
+        </is>
+      </c>
       <c r="E115" s="12" t="inlineStr">
         <is>
           <t>voorsp.</t>
@@ -3536,9 +3542,17 @@
           <t>pt.</t>
         </is>
       </c>
+      <c r="H115" s="60" t="n"/>
+      <c r="I115" s="60" t="n"/>
+      <c r="J115" s="60" t="n"/>
+      <c r="K115" s="60" t="n"/>
+      <c r="L115" s="60" t="n"/>
+      <c r="M115" s="60" t="n"/>
+      <c r="N115" s="60" t="n"/>
+      <c r="O115" s="60" t="n"/>
     </row>
     <row r="116" ht="16" customHeight="1">
-      <c r="A116" s="60" t="inlineStr">
+      <c r="A116" s="61" t="inlineStr">
         <is>
           <t>2A  –  2B</t>
         </is>
@@ -3548,7 +3562,7 @@
       <c r="G116" s="17" t="inlineStr"/>
     </row>
     <row r="117" ht="16" customHeight="1">
-      <c r="A117" s="60" t="inlineStr">
+      <c r="A117" s="61" t="inlineStr">
         <is>
           <t>1E  –  3e (A/B/C/D/F)</t>
         </is>
@@ -3558,7 +3572,7 @@
       <c r="G117" s="17" t="inlineStr"/>
     </row>
     <row r="118" ht="16" customHeight="1">
-      <c r="A118" s="60" t="inlineStr">
+      <c r="A118" s="61" t="inlineStr">
         <is>
           <t>1F  –  2C</t>
         </is>
@@ -3568,7 +3582,7 @@
       <c r="G118" s="17" t="inlineStr"/>
     </row>
     <row r="119" ht="16" customHeight="1">
-      <c r="A119" s="60" t="inlineStr">
+      <c r="A119" s="61" t="inlineStr">
         <is>
           <t>1C  –  2F</t>
         </is>
@@ -3578,7 +3592,7 @@
       <c r="G119" s="17" t="inlineStr"/>
     </row>
     <row r="120" ht="16" customHeight="1">
-      <c r="A120" s="60" t="inlineStr">
+      <c r="A120" s="61" t="inlineStr">
         <is>
           <t>1I  –  3e (C/D/F/G/H)</t>
         </is>
@@ -3588,7 +3602,7 @@
       <c r="G120" s="17" t="inlineStr"/>
     </row>
     <row r="121" ht="16" customHeight="1">
-      <c r="A121" s="60" t="inlineStr">
+      <c r="A121" s="61" t="inlineStr">
         <is>
           <t>2E  –  2I</t>
         </is>
@@ -3598,7 +3612,7 @@
       <c r="G121" s="17" t="inlineStr"/>
     </row>
     <row r="122" ht="16" customHeight="1">
-      <c r="A122" s="60" t="inlineStr">
+      <c r="A122" s="61" t="inlineStr">
         <is>
           <t>1A  –  3e (C/E/F/H/I)</t>
         </is>
@@ -3608,7 +3622,7 @@
       <c r="G122" s="17" t="inlineStr"/>
     </row>
     <row r="123" ht="16" customHeight="1">
-      <c r="A123" s="60" t="inlineStr">
+      <c r="A123" s="61" t="inlineStr">
         <is>
           <t>1L  –  3e (E/H/I/J/K)</t>
         </is>
@@ -3618,7 +3632,7 @@
       <c r="G123" s="17" t="inlineStr"/>
     </row>
     <row r="124" ht="16" customHeight="1">
-      <c r="A124" s="60" t="inlineStr">
+      <c r="A124" s="61" t="inlineStr">
         <is>
           <t>1D  –  3e (B/E/F/I/J)</t>
         </is>
@@ -3628,7 +3642,7 @@
       <c r="G124" s="17" t="inlineStr"/>
     </row>
     <row r="125" ht="16" customHeight="1">
-      <c r="A125" s="60" t="inlineStr">
+      <c r="A125" s="61" t="inlineStr">
         <is>
           <t>1G  –  3e (A/E/H/I/J)</t>
         </is>
@@ -3638,7 +3652,7 @@
       <c r="G125" s="17" t="inlineStr"/>
     </row>
     <row r="126" ht="16" customHeight="1">
-      <c r="A126" s="60" t="inlineStr">
+      <c r="A126" s="61" t="inlineStr">
         <is>
           <t>2K  –  2L</t>
         </is>
@@ -3648,7 +3662,7 @@
       <c r="G126" s="17" t="inlineStr"/>
     </row>
     <row r="127" ht="16" customHeight="1">
-      <c r="A127" s="60" t="inlineStr">
+      <c r="A127" s="61" t="inlineStr">
         <is>
           <t>1H  –  2J</t>
         </is>
@@ -3658,7 +3672,7 @@
       <c r="G127" s="17" t="inlineStr"/>
     </row>
     <row r="128" ht="16" customHeight="1">
-      <c r="A128" s="60" t="inlineStr">
+      <c r="A128" s="61" t="inlineStr">
         <is>
           <t>1B  –  3e (E/F/G/I/J)</t>
         </is>
@@ -3668,7 +3682,7 @@
       <c r="G128" s="17" t="inlineStr"/>
     </row>
     <row r="129" ht="16" customHeight="1">
-      <c r="A129" s="60" t="inlineStr">
+      <c r="A129" s="61" t="inlineStr">
         <is>
           <t>1J  –  2H</t>
         </is>
@@ -3678,7 +3692,7 @@
       <c r="G129" s="17" t="inlineStr"/>
     </row>
     <row r="130" ht="16" customHeight="1">
-      <c r="A130" s="60" t="inlineStr">
+      <c r="A130" s="61" t="inlineStr">
         <is>
           <t>1K  –  3e (D/E/I/J/L)</t>
         </is>
@@ -3688,7 +3702,7 @@
       <c r="G130" s="17" t="inlineStr"/>
     </row>
     <row r="131" ht="16" customHeight="1">
-      <c r="A131" s="60" t="inlineStr">
+      <c r="A131" s="61" t="inlineStr">
         <is>
           <t>2D  –  2G</t>
         </is>
@@ -3706,6 +3720,11 @@
       </c>
     </row>
     <row r="134" ht="14" customHeight="1">
+      <c r="A134" s="12" t="inlineStr">
+        <is>
+          <t>Wedstrijd</t>
+        </is>
+      </c>
       <c r="E134" s="12" t="inlineStr">
         <is>
           <t>voorsp.</t>
@@ -3721,9 +3740,17 @@
           <t>pt.</t>
         </is>
       </c>
+      <c r="H134" s="60" t="n"/>
+      <c r="I134" s="60" t="n"/>
+      <c r="J134" s="60" t="n"/>
+      <c r="K134" s="60" t="n"/>
+      <c r="L134" s="60" t="n"/>
+      <c r="M134" s="60" t="n"/>
+      <c r="N134" s="60" t="n"/>
+      <c r="O134" s="60" t="n"/>
     </row>
     <row r="135" ht="16" customHeight="1">
-      <c r="A135" s="60" t="inlineStr">
+      <c r="A135" s="61" t="inlineStr">
         <is>
           <t>W32-2  –  W32-5</t>
         </is>
@@ -3733,7 +3760,7 @@
       <c r="G135" s="17" t="inlineStr"/>
     </row>
     <row r="136" ht="16" customHeight="1">
-      <c r="A136" s="60" t="inlineStr">
+      <c r="A136" s="61" t="inlineStr">
         <is>
           <t>W32-1  –  W32-3</t>
         </is>
@@ -3743,7 +3770,7 @@
       <c r="G136" s="17" t="inlineStr"/>
     </row>
     <row r="137" ht="16" customHeight="1">
-      <c r="A137" s="60" t="inlineStr">
+      <c r="A137" s="61" t="inlineStr">
         <is>
           <t>W32-4  –  W32-6</t>
         </is>
@@ -3753,7 +3780,7 @@
       <c r="G137" s="17" t="inlineStr"/>
     </row>
     <row r="138" ht="16" customHeight="1">
-      <c r="A138" s="60" t="inlineStr">
+      <c r="A138" s="61" t="inlineStr">
         <is>
           <t>W32-7  –  W32-8</t>
         </is>
@@ -3763,7 +3790,7 @@
       <c r="G138" s="17" t="inlineStr"/>
     </row>
     <row r="139" ht="16" customHeight="1">
-      <c r="A139" s="60" t="inlineStr">
+      <c r="A139" s="61" t="inlineStr">
         <is>
           <t>W32-11  –  W32-12</t>
         </is>
@@ -3773,7 +3800,7 @@
       <c r="G139" s="17" t="inlineStr"/>
     </row>
     <row r="140" ht="16" customHeight="1">
-      <c r="A140" s="60" t="inlineStr">
+      <c r="A140" s="61" t="inlineStr">
         <is>
           <t>W32-9  –  W32-10</t>
         </is>
@@ -3783,7 +3810,7 @@
       <c r="G140" s="17" t="inlineStr"/>
     </row>
     <row r="141" ht="16" customHeight="1">
-      <c r="A141" s="60" t="inlineStr">
+      <c r="A141" s="61" t="inlineStr">
         <is>
           <t>W32-14  –  W32-16</t>
         </is>
@@ -3793,7 +3820,7 @@
       <c r="G141" s="17" t="inlineStr"/>
     </row>
     <row r="142" ht="16" customHeight="1">
-      <c r="A142" s="60" t="inlineStr">
+      <c r="A142" s="61" t="inlineStr">
         <is>
           <t>W32-13  –  W32-15</t>
         </is>
@@ -3811,6 +3838,11 @@
       </c>
     </row>
     <row r="145" ht="14" customHeight="1">
+      <c r="A145" s="12" t="inlineStr">
+        <is>
+          <t>Wedstrijd</t>
+        </is>
+      </c>
       <c r="E145" s="12" t="inlineStr">
         <is>
           <t>voorsp.</t>
@@ -3826,9 +3858,17 @@
           <t>pt.</t>
         </is>
       </c>
+      <c r="H145" s="60" t="n"/>
+      <c r="I145" s="60" t="n"/>
+      <c r="J145" s="60" t="n"/>
+      <c r="K145" s="60" t="n"/>
+      <c r="L145" s="60" t="n"/>
+      <c r="M145" s="60" t="n"/>
+      <c r="N145" s="60" t="n"/>
+      <c r="O145" s="60" t="n"/>
     </row>
     <row r="146" ht="16" customHeight="1">
-      <c r="A146" s="60" t="inlineStr">
+      <c r="A146" s="61" t="inlineStr">
         <is>
           <t>W16-1  –  W16-2</t>
         </is>
@@ -3838,7 +3878,7 @@
       <c r="G146" s="17" t="inlineStr"/>
     </row>
     <row r="147" ht="16" customHeight="1">
-      <c r="A147" s="60" t="inlineStr">
+      <c r="A147" s="61" t="inlineStr">
         <is>
           <t>W16-5  –  W16-6</t>
         </is>
@@ -3848,7 +3888,7 @@
       <c r="G147" s="17" t="inlineStr"/>
     </row>
     <row r="148" ht="16" customHeight="1">
-      <c r="A148" s="60" t="inlineStr">
+      <c r="A148" s="61" t="inlineStr">
         <is>
           <t>W16-3  –  W16-4</t>
         </is>
@@ -3858,7 +3898,7 @@
       <c r="G148" s="17" t="inlineStr"/>
     </row>
     <row r="149" ht="16" customHeight="1">
-      <c r="A149" s="60" t="inlineStr">
+      <c r="A149" s="61" t="inlineStr">
         <is>
           <t>W16-7  –  W16-8</t>
         </is>
@@ -3876,6 +3916,11 @@
       </c>
     </row>
     <row r="152" ht="14" customHeight="1">
+      <c r="A152" s="12" t="inlineStr">
+        <is>
+          <t>Wedstrijd</t>
+        </is>
+      </c>
       <c r="E152" s="12" t="inlineStr">
         <is>
           <t>voorsp.</t>
@@ -3891,9 +3936,17 @@
           <t>pt.</t>
         </is>
       </c>
+      <c r="H152" s="60" t="n"/>
+      <c r="I152" s="60" t="n"/>
+      <c r="J152" s="60" t="n"/>
+      <c r="K152" s="60" t="n"/>
+      <c r="L152" s="60" t="n"/>
+      <c r="M152" s="60" t="n"/>
+      <c r="N152" s="60" t="n"/>
+      <c r="O152" s="60" t="n"/>
     </row>
     <row r="153" ht="16" customHeight="1">
-      <c r="A153" s="60" t="inlineStr">
+      <c r="A153" s="61" t="inlineStr">
         <is>
           <t>WKF-1  –  WKF-2</t>
         </is>
@@ -3903,7 +3956,7 @@
       <c r="G153" s="17" t="inlineStr"/>
     </row>
     <row r="154" ht="16" customHeight="1">
-      <c r="A154" s="60" t="inlineStr">
+      <c r="A154" s="61" t="inlineStr">
         <is>
           <t>WKF-3  –  WKF-4</t>
         </is>
@@ -3921,6 +3974,11 @@
       </c>
     </row>
     <row r="157" ht="14" customHeight="1">
+      <c r="A157" s="12" t="inlineStr">
+        <is>
+          <t>Wedstrijd</t>
+        </is>
+      </c>
       <c r="E157" s="12" t="inlineStr">
         <is>
           <t>voorsp.</t>
@@ -3936,9 +3994,17 @@
           <t>pt.</t>
         </is>
       </c>
+      <c r="H157" s="60" t="n"/>
+      <c r="I157" s="60" t="n"/>
+      <c r="J157" s="60" t="n"/>
+      <c r="K157" s="60" t="n"/>
+      <c r="L157" s="60" t="n"/>
+      <c r="M157" s="60" t="n"/>
+      <c r="N157" s="60" t="n"/>
+      <c r="O157" s="60" t="n"/>
     </row>
     <row r="158" ht="16" customHeight="1">
-      <c r="A158" s="60" t="inlineStr">
+      <c r="A158" s="61" t="inlineStr">
         <is>
           <t>WHF-1  –  WHF-2</t>
         </is>
@@ -3994,19 +4060,19 @@
           <t>Senegal</t>
         </is>
       </c>
-      <c r="E163" s="61" t="n">
+      <c r="E163" s="62" t="n">
         <v>7</v>
       </c>
-      <c r="F163" s="61" t="n">
+      <c r="F163" s="62" t="n">
         <v>12</v>
       </c>
-      <c r="G163" s="61" t="n">
+      <c r="G163" s="62" t="n">
         <v>19</v>
       </c>
-      <c r="H163" s="61" t="n">
+      <c r="H163" s="62" t="n">
         <v>26</v>
       </c>
-      <c r="I163" s="61" t="n">
+      <c r="I163" s="62" t="n">
         <v>34</v>
       </c>
     </row>
@@ -4016,19 +4082,19 @@
           <t>Mexico</t>
         </is>
       </c>
-      <c r="E164" s="61" t="n">
+      <c r="E164" s="62" t="n">
         <v>7</v>
       </c>
-      <c r="F164" s="61" t="n">
+      <c r="F164" s="62" t="n">
         <v>13</v>
       </c>
-      <c r="G164" s="61" t="n">
+      <c r="G164" s="62" t="n">
         <v>19</v>
       </c>
-      <c r="H164" s="61" t="n">
+      <c r="H164" s="62" t="n">
         <v>27</v>
       </c>
-      <c r="I164" s="61" t="n">
+      <c r="I164" s="62" t="n">
         <v>35</v>
       </c>
     </row>
@@ -4038,19 +4104,19 @@
           <t>Verenigde Staten</t>
         </is>
       </c>
-      <c r="E165" s="61" t="n">
+      <c r="E165" s="62" t="n">
         <v>8</v>
       </c>
-      <c r="F165" s="61" t="n">
+      <c r="F165" s="62" t="n">
         <v>13</v>
       </c>
-      <c r="G165" s="61" t="n">
+      <c r="G165" s="62" t="n">
         <v>20</v>
       </c>
-      <c r="H165" s="61" t="n">
+      <c r="H165" s="62" t="n">
         <v>27</v>
       </c>
-      <c r="I165" s="61" t="n">
+      <c r="I165" s="62" t="n">
         <v>36</v>
       </c>
     </row>
@@ -4060,19 +4126,19 @@
           <t>Uruguay</t>
         </is>
       </c>
-      <c r="E166" s="61" t="n">
+      <c r="E166" s="62" t="n">
         <v>8</v>
       </c>
-      <c r="F166" s="61" t="n">
+      <c r="F166" s="62" t="n">
         <v>14</v>
       </c>
-      <c r="G166" s="61" t="n">
+      <c r="G166" s="62" t="n">
         <v>20</v>
       </c>
-      <c r="H166" s="61" t="n">
+      <c r="H166" s="62" t="n">
         <v>28</v>
       </c>
-      <c r="I166" s="61" t="n">
+      <c r="I166" s="62" t="n">
         <v>37</v>
       </c>
     </row>
@@ -4082,19 +4148,19 @@
           <t>Japan</t>
         </is>
       </c>
-      <c r="E167" s="61" t="n">
+      <c r="E167" s="62" t="n">
         <v>8</v>
       </c>
-      <c r="F167" s="61" t="n">
+      <c r="F167" s="62" t="n">
         <v>14</v>
       </c>
-      <c r="G167" s="61" t="n">
+      <c r="G167" s="62" t="n">
         <v>21</v>
       </c>
-      <c r="H167" s="61" t="n">
+      <c r="H167" s="62" t="n">
         <v>29</v>
       </c>
-      <c r="I167" s="61" t="n">
+      <c r="I167" s="62" t="n">
         <v>38</v>
       </c>
     </row>
@@ -4104,19 +4170,19 @@
           <t>Zwitserland</t>
         </is>
       </c>
-      <c r="E168" s="61" t="n">
+      <c r="E168" s="62" t="n">
         <v>8</v>
       </c>
-      <c r="F168" s="61" t="n">
+      <c r="F168" s="62" t="n">
         <v>14</v>
       </c>
-      <c r="G168" s="61" t="n">
+      <c r="G168" s="62" t="n">
         <v>21</v>
       </c>
-      <c r="H168" s="61" t="n">
+      <c r="H168" s="62" t="n">
         <v>30</v>
       </c>
-      <c r="I168" s="61" t="n">
+      <c r="I168" s="62" t="n">
         <v>39</v>
       </c>
     </row>
@@ -4126,19 +4192,19 @@
           <t>Iran</t>
         </is>
       </c>
-      <c r="E169" s="61" t="n">
+      <c r="E169" s="62" t="n">
         <v>9</v>
       </c>
-      <c r="F169" s="61" t="n">
+      <c r="F169" s="62" t="n">
         <v>15</v>
       </c>
-      <c r="G169" s="61" t="n">
+      <c r="G169" s="62" t="n">
         <v>22</v>
       </c>
-      <c r="H169" s="61" t="n">
+      <c r="H169" s="62" t="n">
         <v>31</v>
       </c>
-      <c r="I169" s="61" t="n">
+      <c r="I169" s="62" t="n">
         <v>41</v>
       </c>
     </row>
@@ -4148,19 +4214,19 @@
           <t>Oostenrijk</t>
         </is>
       </c>
-      <c r="E170" s="61" t="n">
+      <c r="E170" s="62" t="n">
         <v>9</v>
       </c>
-      <c r="F170" s="61" t="n">
+      <c r="F170" s="62" t="n">
         <v>15</v>
       </c>
-      <c r="G170" s="61" t="n">
+      <c r="G170" s="62" t="n">
         <v>23</v>
       </c>
-      <c r="H170" s="61" t="n">
+      <c r="H170" s="62" t="n">
         <v>32</v>
       </c>
-      <c r="I170" s="61" t="n">
+      <c r="I170" s="62" t="n">
         <v>42</v>
       </c>
     </row>
@@ -4170,19 +4236,19 @@
           <t>Zuid-Korea</t>
         </is>
       </c>
-      <c r="E171" s="61" t="n">
+      <c r="E171" s="62" t="n">
         <v>9</v>
       </c>
-      <c r="F171" s="61" t="n">
+      <c r="F171" s="62" t="n">
         <v>16</v>
       </c>
-      <c r="G171" s="61" t="n">
+      <c r="G171" s="62" t="n">
         <v>23</v>
       </c>
-      <c r="H171" s="61" t="n">
+      <c r="H171" s="62" t="n">
         <v>32</v>
       </c>
-      <c r="I171" s="61" t="n">
+      <c r="I171" s="62" t="n">
         <v>43</v>
       </c>
     </row>
@@ -4192,19 +4258,19 @@
           <t>Australië</t>
         </is>
       </c>
-      <c r="E172" s="61" t="n">
+      <c r="E172" s="62" t="n">
         <v>9</v>
       </c>
-      <c r="F172" s="61" t="n">
+      <c r="F172" s="62" t="n">
         <v>16</v>
       </c>
-      <c r="G172" s="61" t="n">
+      <c r="G172" s="62" t="n">
         <v>24</v>
       </c>
-      <c r="H172" s="61" t="n">
+      <c r="H172" s="62" t="n">
         <v>33</v>
       </c>
-      <c r="I172" s="61" t="n">
+      <c r="I172" s="62" t="n">
         <v>43</v>
       </c>
     </row>
@@ -4214,19 +4280,19 @@
           <t>Ecuador</t>
         </is>
       </c>
-      <c r="E173" s="61" t="n">
+      <c r="E173" s="62" t="n">
         <v>9</v>
       </c>
-      <c r="F173" s="61" t="n">
+      <c r="F173" s="62" t="n">
         <v>16</v>
       </c>
-      <c r="G173" s="61" t="n">
+      <c r="G173" s="62" t="n">
         <v>24</v>
       </c>
-      <c r="H173" s="61" t="n">
+      <c r="H173" s="62" t="n">
         <v>34</v>
       </c>
-      <c r="I173" s="61" t="n">
+      <c r="I173" s="62" t="n">
         <v>44</v>
       </c>
     </row>
@@ -4236,19 +4302,19 @@
           <t>Noorwegen</t>
         </is>
       </c>
-      <c r="E174" s="61" t="n">
+      <c r="E174" s="62" t="n">
         <v>10</v>
       </c>
-      <c r="F174" s="61" t="n">
+      <c r="F174" s="62" t="n">
         <v>16</v>
       </c>
-      <c r="G174" s="61" t="n">
+      <c r="G174" s="62" t="n">
         <v>25</v>
       </c>
-      <c r="H174" s="61" t="n">
+      <c r="H174" s="62" t="n">
         <v>34</v>
       </c>
-      <c r="I174" s="61" t="n">
+      <c r="I174" s="62" t="n">
         <v>45</v>
       </c>
     </row>
@@ -4258,19 +4324,19 @@
           <t>Panama</t>
         </is>
       </c>
-      <c r="E175" s="61" t="n">
+      <c r="E175" s="62" t="n">
         <v>10</v>
       </c>
-      <c r="F175" s="61" t="n">
+      <c r="F175" s="62" t="n">
         <v>17</v>
       </c>
-      <c r="G175" s="61" t="n">
+      <c r="G175" s="62" t="n">
         <v>26</v>
       </c>
-      <c r="H175" s="61" t="n">
+      <c r="H175" s="62" t="n">
         <v>36</v>
       </c>
-      <c r="I175" s="61" t="n">
+      <c r="I175" s="62" t="n">
         <v>48</v>
       </c>
     </row>
@@ -4280,19 +4346,19 @@
           <t>Egypte</t>
         </is>
       </c>
-      <c r="E176" s="61" t="n">
+      <c r="E176" s="62" t="n">
         <v>10</v>
       </c>
-      <c r="F176" s="61" t="n">
+      <c r="F176" s="62" t="n">
         <v>18</v>
       </c>
-      <c r="G176" s="61" t="n">
+      <c r="G176" s="62" t="n">
         <v>27</v>
       </c>
-      <c r="H176" s="61" t="n">
+      <c r="H176" s="62" t="n">
         <v>37</v>
       </c>
-      <c r="I176" s="61" t="n">
+      <c r="I176" s="62" t="n">
         <v>49</v>
       </c>
     </row>
@@ -4302,19 +4368,19 @@
           <t>Algerije</t>
         </is>
       </c>
-      <c r="E177" s="61" t="n">
+      <c r="E177" s="62" t="n">
         <v>11</v>
       </c>
-      <c r="F177" s="61" t="n">
+      <c r="F177" s="62" t="n">
         <v>19</v>
       </c>
-      <c r="G177" s="61" t="n">
+      <c r="G177" s="62" t="n">
         <v>28</v>
       </c>
-      <c r="H177" s="61" t="n">
+      <c r="H177" s="62" t="n">
         <v>40</v>
       </c>
-      <c r="I177" s="61" t="n">
+      <c r="I177" s="62" t="n">
         <v>52</v>
       </c>
     </row>
@@ -4324,19 +4390,19 @@
           <t>Paraguay</t>
         </is>
       </c>
-      <c r="E178" s="61" t="n">
+      <c r="E178" s="62" t="n">
         <v>11</v>
       </c>
-      <c r="F178" s="61" t="n">
+      <c r="F178" s="62" t="n">
         <v>19</v>
       </c>
-      <c r="G178" s="61" t="n">
+      <c r="G178" s="62" t="n">
         <v>29</v>
       </c>
-      <c r="H178" s="61" t="n">
+      <c r="H178" s="62" t="n">
         <v>41</v>
       </c>
-      <c r="I178" s="61" t="n">
+      <c r="I178" s="62" t="n">
         <v>53</v>
       </c>
     </row>
@@ -4346,19 +4412,19 @@
           <t>Ivoorkust</t>
         </is>
       </c>
-      <c r="E179" s="61" t="n">
+      <c r="E179" s="62" t="n">
         <v>12</v>
       </c>
-      <c r="F179" s="61" t="n">
+      <c r="F179" s="62" t="n">
         <v>20</v>
       </c>
-      <c r="G179" s="61" t="n">
+      <c r="G179" s="62" t="n">
         <v>30</v>
       </c>
-      <c r="H179" s="61" t="n">
+      <c r="H179" s="62" t="n">
         <v>41</v>
       </c>
-      <c r="I179" s="61" t="n">
+      <c r="I179" s="62" t="n">
         <v>55</v>
       </c>
     </row>
@@ -4368,19 +4434,19 @@
           <t>Tunesië</t>
         </is>
       </c>
-      <c r="E180" s="61" t="n">
+      <c r="E180" s="62" t="n">
         <v>12</v>
       </c>
-      <c r="F180" s="61" t="n">
+      <c r="F180" s="62" t="n">
         <v>20</v>
       </c>
-      <c r="G180" s="61" t="n">
+      <c r="G180" s="62" t="n">
         <v>30</v>
       </c>
-      <c r="H180" s="61" t="n">
+      <c r="H180" s="62" t="n">
         <v>42</v>
       </c>
-      <c r="I180" s="61" t="n">
+      <c r="I180" s="62" t="n">
         <v>55</v>
       </c>
     </row>
@@ -4390,19 +4456,19 @@
           <t>Schotland</t>
         </is>
       </c>
-      <c r="E181" s="61" t="n">
+      <c r="E181" s="62" t="n">
         <v>12</v>
       </c>
-      <c r="F181" s="61" t="n">
+      <c r="F181" s="62" t="n">
         <v>20</v>
       </c>
-      <c r="G181" s="61" t="n">
+      <c r="G181" s="62" t="n">
         <v>31</v>
       </c>
-      <c r="H181" s="61" t="n">
+      <c r="H181" s="62" t="n">
         <v>42</v>
       </c>
-      <c r="I181" s="61" t="n">
+      <c r="I181" s="62" t="n">
         <v>56</v>
       </c>
     </row>
@@ -4412,19 +4478,19 @@
           <t>Zweden</t>
         </is>
       </c>
-      <c r="E182" s="61" t="n">
+      <c r="E182" s="62" t="n">
         <v>12</v>
       </c>
-      <c r="F182" s="61" t="n">
+      <c r="F182" s="62" t="n">
         <v>21</v>
       </c>
-      <c r="G182" s="61" t="n">
+      <c r="G182" s="62" t="n">
         <v>31</v>
       </c>
-      <c r="H182" s="61" t="n">
+      <c r="H182" s="62" t="n">
         <v>43</v>
       </c>
-      <c r="I182" s="61" t="n">
+      <c r="I182" s="62" t="n">
         <v>57</v>
       </c>
     </row>
@@ -4434,19 +4500,19 @@
           <t>Tsjechië</t>
         </is>
       </c>
-      <c r="E183" s="61" t="n">
+      <c r="E183" s="62" t="n">
         <v>12</v>
       </c>
-      <c r="F183" s="61" t="n">
+      <c r="F183" s="62" t="n">
         <v>21</v>
       </c>
-      <c r="G183" s="61" t="n">
+      <c r="G183" s="62" t="n">
         <v>31</v>
       </c>
-      <c r="H183" s="61" t="n">
+      <c r="H183" s="62" t="n">
         <v>43</v>
       </c>
-      <c r="I183" s="61" t="n">
+      <c r="I183" s="62" t="n">
         <v>57</v>
       </c>
     </row>
@@ -4456,19 +4522,19 @@
           <t>Qatar</t>
         </is>
       </c>
-      <c r="E184" s="61" t="n">
+      <c r="E184" s="62" t="n">
         <v>13</v>
       </c>
-      <c r="F184" s="61" t="n">
+      <c r="F184" s="62" t="n">
         <v>22</v>
       </c>
-      <c r="G184" s="61" t="n">
+      <c r="G184" s="62" t="n">
         <v>33</v>
       </c>
-      <c r="H184" s="61" t="n">
+      <c r="H184" s="62" t="n">
         <v>46</v>
       </c>
-      <c r="I184" s="61" t="n">
+      <c r="I184" s="62" t="n">
         <v>61</v>
       </c>
     </row>
@@ -4478,19 +4544,19 @@
           <t>Oezbekistan</t>
         </is>
       </c>
-      <c r="E185" s="61" t="n">
+      <c r="E185" s="62" t="n">
         <v>13</v>
       </c>
-      <c r="F185" s="61" t="n">
+      <c r="F185" s="62" t="n">
         <v>23</v>
       </c>
-      <c r="G185" s="61" t="n">
+      <c r="G185" s="62" t="n">
         <v>34</v>
       </c>
-      <c r="H185" s="61" t="n">
+      <c r="H185" s="62" t="n">
         <v>47</v>
       </c>
-      <c r="I185" s="61" t="n">
+      <c r="I185" s="62" t="n">
         <v>63</v>
       </c>
     </row>
@@ -4500,19 +4566,19 @@
           <t>DR Congo</t>
         </is>
       </c>
-      <c r="E186" s="61" t="n">
+      <c r="E186" s="62" t="n">
         <v>14</v>
       </c>
-      <c r="F186" s="61" t="n">
+      <c r="F186" s="62" t="n">
         <v>23</v>
       </c>
-      <c r="G186" s="61" t="n">
+      <c r="G186" s="62" t="n">
         <v>35</v>
       </c>
-      <c r="H186" s="61" t="n">
+      <c r="H186" s="62" t="n">
         <v>48</v>
       </c>
-      <c r="I186" s="61" t="n">
+      <c r="I186" s="62" t="n">
         <v>64</v>
       </c>
     </row>
@@ -4522,19 +4588,19 @@
           <t>Saoedi-Arabië</t>
         </is>
       </c>
-      <c r="E187" s="61" t="n">
+      <c r="E187" s="62" t="n">
         <v>14</v>
       </c>
-      <c r="F187" s="61" t="n">
+      <c r="F187" s="62" t="n">
         <v>24</v>
       </c>
-      <c r="G187" s="61" t="n">
+      <c r="G187" s="62" t="n">
         <v>35</v>
       </c>
-      <c r="H187" s="61" t="n">
+      <c r="H187" s="62" t="n">
         <v>49</v>
       </c>
-      <c r="I187" s="61" t="n">
+      <c r="I187" s="62" t="n">
         <v>65</v>
       </c>
     </row>
@@ -4544,19 +4610,19 @@
           <t>Irak</t>
         </is>
       </c>
-      <c r="E188" s="61" t="n">
+      <c r="E188" s="62" t="n">
         <v>14</v>
       </c>
-      <c r="F188" s="61" t="n">
+      <c r="F188" s="62" t="n">
         <v>24</v>
       </c>
-      <c r="G188" s="61" t="n">
+      <c r="G188" s="62" t="n">
         <v>36</v>
       </c>
-      <c r="H188" s="61" t="n">
+      <c r="H188" s="62" t="n">
         <v>49</v>
       </c>
-      <c r="I188" s="61" t="n">
+      <c r="I188" s="62" t="n">
         <v>65</v>
       </c>
     </row>
@@ -4566,19 +4632,19 @@
           <t>Zuid-Afrika</t>
         </is>
       </c>
-      <c r="E189" s="61" t="n">
+      <c r="E189" s="62" t="n">
         <v>14</v>
       </c>
-      <c r="F189" s="61" t="n">
+      <c r="F189" s="62" t="n">
         <v>24</v>
       </c>
-      <c r="G189" s="61" t="n">
+      <c r="G189" s="62" t="n">
         <v>36</v>
       </c>
-      <c r="H189" s="61" t="n">
+      <c r="H189" s="62" t="n">
         <v>50</v>
       </c>
-      <c r="I189" s="61" t="n">
+      <c r="I189" s="62" t="n">
         <v>66</v>
       </c>
     </row>
@@ -4588,19 +4654,19 @@
           <t>Jordanië</t>
         </is>
       </c>
-      <c r="E190" s="61" t="n">
+      <c r="E190" s="62" t="n">
         <v>14</v>
       </c>
-      <c r="F190" s="61" t="n">
+      <c r="F190" s="62" t="n">
         <v>25</v>
       </c>
-      <c r="G190" s="61" t="n">
+      <c r="G190" s="62" t="n">
         <v>37</v>
       </c>
-      <c r="H190" s="61" t="n">
+      <c r="H190" s="62" t="n">
         <v>51</v>
       </c>
-      <c r="I190" s="61" t="n">
+      <c r="I190" s="62" t="n">
         <v>68</v>
       </c>
     </row>
@@ -4610,19 +4676,19 @@
           <t>Kaapverdië</t>
         </is>
       </c>
-      <c r="E191" s="61" t="n">
+      <c r="E191" s="62" t="n">
         <v>15</v>
       </c>
-      <c r="F191" s="61" t="n">
+      <c r="F191" s="62" t="n">
         <v>26</v>
       </c>
-      <c r="G191" s="61" t="n">
+      <c r="G191" s="62" t="n">
         <v>38</v>
       </c>
-      <c r="H191" s="61" t="n">
+      <c r="H191" s="62" t="n">
         <v>53</v>
       </c>
-      <c r="I191" s="61" t="n">
+      <c r="I191" s="62" t="n">
         <v>70</v>
       </c>
     </row>
@@ -4632,19 +4698,19 @@
           <t>Ghana</t>
         </is>
       </c>
-      <c r="E192" s="61" t="n">
+      <c r="E192" s="62" t="n">
         <v>15</v>
       </c>
-      <c r="F192" s="61" t="n">
+      <c r="F192" s="62" t="n">
         <v>26</v>
       </c>
-      <c r="G192" s="61" t="n">
+      <c r="G192" s="62" t="n">
         <v>39</v>
       </c>
-      <c r="H192" s="61" t="n">
+      <c r="H192" s="62" t="n">
         <v>54</v>
       </c>
-      <c r="I192" s="61" t="n">
+      <c r="I192" s="62" t="n">
         <v>72</v>
       </c>
     </row>
@@ -4654,19 +4720,19 @@
           <t>Bosnië-Herzegovina</t>
         </is>
       </c>
-      <c r="E193" s="61" t="n">
+      <c r="E193" s="62" t="n">
         <v>15</v>
       </c>
-      <c r="F193" s="61" t="n">
+      <c r="F193" s="62" t="n">
         <v>26</v>
       </c>
-      <c r="G193" s="61" t="n">
+      <c r="G193" s="62" t="n">
         <v>39</v>
       </c>
-      <c r="H193" s="61" t="n">
+      <c r="H193" s="62" t="n">
         <v>55</v>
       </c>
-      <c r="I193" s="61" t="n">
+      <c r="I193" s="62" t="n">
         <v>72</v>
       </c>
     </row>
@@ -4676,19 +4742,19 @@
           <t>Haïti</t>
         </is>
       </c>
-      <c r="E194" s="61" t="n">
+      <c r="E194" s="62" t="n">
         <v>16</v>
       </c>
-      <c r="F194" s="61" t="n">
+      <c r="F194" s="62" t="n">
         <v>28</v>
       </c>
-      <c r="G194" s="61" t="n">
+      <c r="G194" s="62" t="n">
         <v>41</v>
       </c>
-      <c r="H194" s="61" t="n">
+      <c r="H194" s="62" t="n">
         <v>58</v>
       </c>
-      <c r="I194" s="61" t="n">
+      <c r="I194" s="62" t="n">
         <v>76</v>
       </c>
     </row>
@@ -4698,19 +4764,19 @@
           <t>Nieuw-Zeeland</t>
         </is>
       </c>
-      <c r="E195" s="61" t="n">
+      <c r="E195" s="62" t="n">
         <v>16</v>
       </c>
-      <c r="F195" s="61" t="n">
+      <c r="F195" s="62" t="n">
         <v>28</v>
       </c>
-      <c r="G195" s="61" t="n">
+      <c r="G195" s="62" t="n">
         <v>42</v>
       </c>
-      <c r="H195" s="61" t="n">
+      <c r="H195" s="62" t="n">
         <v>59</v>
       </c>
-      <c r="I195" s="61" t="n">
+      <c r="I195" s="62" t="n">
         <v>77</v>
       </c>
     </row>
@@ -4720,19 +4786,19 @@
           <t>Curaçao</t>
         </is>
       </c>
-      <c r="E196" s="61" t="n">
+      <c r="E196" s="62" t="n">
         <v>17</v>
       </c>
-      <c r="F196" s="61" t="n">
+      <c r="F196" s="62" t="n">
         <v>29</v>
       </c>
-      <c r="G196" s="61" t="n">
+      <c r="G196" s="62" t="n">
         <v>43</v>
       </c>
-      <c r="H196" s="61" t="n">
+      <c r="H196" s="62" t="n">
         <v>60</v>
       </c>
-      <c r="I196" s="61" t="n">
+      <c r="I196" s="62" t="n">
         <v>79</v>
       </c>
     </row>
@@ -4742,19 +4808,19 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="E197" s="61" t="n">
+      <c r="E197" s="62" t="n">
         <v>13</v>
       </c>
-      <c r="F197" s="61" t="n">
+      <c r="F197" s="62" t="n">
         <v>22</v>
       </c>
-      <c r="G197" s="61" t="n">
+      <c r="G197" s="62" t="n">
         <v>33</v>
       </c>
-      <c r="H197" s="61" t="n">
+      <c r="H197" s="62" t="n">
         <v>46</v>
       </c>
-      <c r="I197" s="61" t="n">
+      <c r="I197" s="62" t="n">
         <v>61</v>
       </c>
     </row>
@@ -4764,19 +4830,19 @@
           <t>Turkije</t>
         </is>
       </c>
-      <c r="E198" s="61" t="n">
+      <c r="E198" s="62" t="n">
         <v>13</v>
       </c>
-      <c r="F198" s="61" t="n">
+      <c r="F198" s="62" t="n">
         <v>22</v>
       </c>
-      <c r="G198" s="61" t="n">
+      <c r="G198" s="62" t="n">
         <v>33</v>
       </c>
-      <c r="H198" s="61" t="n">
+      <c r="H198" s="62" t="n">
         <v>46</v>
       </c>
-      <c r="I198" s="61" t="n">
+      <c r="I198" s="62" t="n">
         <v>61</v>
       </c>
     </row>
@@ -4821,16 +4887,16 @@
           <t>Frankrijk</t>
         </is>
       </c>
-      <c r="E202" s="61" t="n">
+      <c r="E202" s="62" t="n">
         <v>8</v>
       </c>
-      <c r="F202" s="61" t="n">
+      <c r="F202" s="62" t="n">
         <v>14</v>
       </c>
-      <c r="G202" s="61" t="n">
+      <c r="G202" s="62" t="n">
         <v>20</v>
       </c>
-      <c r="H202" s="61" t="n">
+      <c r="H202" s="62" t="n">
         <v>30</v>
       </c>
     </row>
@@ -4840,16 +4906,16 @@
           <t>Spanje</t>
         </is>
       </c>
-      <c r="E203" s="61" t="n">
+      <c r="E203" s="62" t="n">
         <v>7</v>
       </c>
-      <c r="F203" s="61" t="n">
+      <c r="F203" s="62" t="n">
         <v>13</v>
       </c>
-      <c r="G203" s="61" t="n">
+      <c r="G203" s="62" t="n">
         <v>19</v>
       </c>
-      <c r="H203" s="61" t="n">
+      <c r="H203" s="62" t="n">
         <v>28</v>
       </c>
     </row>
@@ -4859,16 +4925,16 @@
           <t>Argentinië</t>
         </is>
       </c>
-      <c r="E204" s="61" t="n">
+      <c r="E204" s="62" t="n">
         <v>6</v>
       </c>
-      <c r="F204" s="61" t="n">
+      <c r="F204" s="62" t="n">
         <v>12</v>
       </c>
-      <c r="G204" s="61" t="n">
+      <c r="G204" s="62" t="n">
         <v>17</v>
       </c>
-      <c r="H204" s="61" t="n">
+      <c r="H204" s="62" t="n">
         <v>26</v>
       </c>
     </row>
@@ -4878,16 +4944,16 @@
           <t>Engeland</t>
         </is>
       </c>
-      <c r="E205" s="61" t="n">
+      <c r="E205" s="62" t="n">
         <v>6</v>
       </c>
-      <c r="F205" s="61" t="n">
+      <c r="F205" s="62" t="n">
         <v>11</v>
       </c>
-      <c r="G205" s="61" t="n">
+      <c r="G205" s="62" t="n">
         <v>16</v>
       </c>
-      <c r="H205" s="61" t="n">
+      <c r="H205" s="62" t="n">
         <v>24</v>
       </c>
     </row>
@@ -4897,16 +4963,16 @@
           <t>Portugal</t>
         </is>
       </c>
-      <c r="E206" s="61" t="n">
+      <c r="E206" s="62" t="n">
         <v>6</v>
       </c>
-      <c r="F206" s="61" t="n">
+      <c r="F206" s="62" t="n">
         <v>10</v>
       </c>
-      <c r="G206" s="61" t="n">
+      <c r="G206" s="62" t="n">
         <v>15</v>
       </c>
-      <c r="H206" s="61" t="n">
+      <c r="H206" s="62" t="n">
         <v>22</v>
       </c>
     </row>
@@ -4916,16 +4982,16 @@
           <t>Brazilië</t>
         </is>
       </c>
-      <c r="E207" s="61" t="n">
+      <c r="E207" s="62" t="n">
         <v>5</v>
       </c>
-      <c r="F207" s="61" t="n">
+      <c r="F207" s="62" t="n">
         <v>9</v>
       </c>
-      <c r="G207" s="61" t="n">
+      <c r="G207" s="62" t="n">
         <v>13</v>
       </c>
-      <c r="H207" s="61" t="n">
+      <c r="H207" s="62" t="n">
         <v>20</v>
       </c>
     </row>
@@ -4935,16 +5001,16 @@
           <t>Nederland</t>
         </is>
       </c>
-      <c r="E208" s="61" t="n">
+      <c r="E208" s="62" t="n">
         <v>4</v>
       </c>
-      <c r="F208" s="61" t="n">
+      <c r="F208" s="62" t="n">
         <v>8</v>
       </c>
-      <c r="G208" s="61" t="n">
+      <c r="G208" s="62" t="n">
         <v>12</v>
       </c>
-      <c r="H208" s="61" t="n">
+      <c r="H208" s="62" t="n">
         <v>18</v>
       </c>
     </row>
@@ -4954,16 +5020,16 @@
           <t>Marokko</t>
         </is>
       </c>
-      <c r="E209" s="61" t="n">
+      <c r="E209" s="62" t="n">
         <v>4</v>
       </c>
-      <c r="F209" s="61" t="n">
+      <c r="F209" s="62" t="n">
         <v>7</v>
       </c>
-      <c r="G209" s="61" t="n">
+      <c r="G209" s="62" t="n">
         <v>11</v>
       </c>
-      <c r="H209" s="61" t="n">
+      <c r="H209" s="62" t="n">
         <v>16</v>
       </c>
     </row>
@@ -4973,16 +5039,16 @@
           <t>België</t>
         </is>
       </c>
-      <c r="E210" s="61" t="n">
+      <c r="E210" s="62" t="n">
         <v>4</v>
       </c>
-      <c r="F210" s="61" t="n">
+      <c r="F210" s="62" t="n">
         <v>6</v>
       </c>
-      <c r="G210" s="61" t="n">
+      <c r="G210" s="62" t="n">
         <v>9</v>
       </c>
-      <c r="H210" s="61" t="n">
+      <c r="H210" s="62" t="n">
         <v>14</v>
       </c>
     </row>
@@ -4992,16 +5058,16 @@
           <t>Duitsland</t>
         </is>
       </c>
-      <c r="E211" s="61" t="n">
+      <c r="E211" s="62" t="n">
         <v>3</v>
       </c>
-      <c r="F211" s="61" t="n">
+      <c r="F211" s="62" t="n">
         <v>6</v>
       </c>
-      <c r="G211" s="61" t="n">
+      <c r="G211" s="62" t="n">
         <v>8</v>
       </c>
-      <c r="H211" s="61" t="n">
+      <c r="H211" s="62" t="n">
         <v>12</v>
       </c>
     </row>
@@ -5011,16 +5077,16 @@
           <t>Kroatië</t>
         </is>
       </c>
-      <c r="E212" s="61" t="n">
+      <c r="E212" s="62" t="n">
         <v>2</v>
       </c>
-      <c r="F212" s="61" t="n">
+      <c r="F212" s="62" t="n">
         <v>5</v>
       </c>
-      <c r="G212" s="61" t="n">
+      <c r="G212" s="62" t="n">
         <v>7</v>
       </c>
-      <c r="H212" s="61" t="n">
+      <c r="H212" s="62" t="n">
         <v>10</v>
       </c>
     </row>
@@ -5030,25 +5096,27 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="E213" s="61" t="n">
+      <c r="E213" s="62" t="n">
         <v>2</v>
       </c>
-      <c r="F213" s="61" t="n">
+      <c r="F213" s="62" t="n">
         <v>3</v>
       </c>
-      <c r="G213" s="61" t="n">
+      <c r="G213" s="62" t="n">
         <v>4</v>
       </c>
-      <c r="H213" s="61" t="n">
+      <c r="H213" s="62" t="n">
         <v>6</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="199">
+  <mergeCells count="204">
     <mergeCell ref="E13:G13"/>
     <mergeCell ref="A122:D122"/>
     <mergeCell ref="A97:D97"/>
     <mergeCell ref="A133:O133"/>
+    <mergeCell ref="A134:D134"/>
+    <mergeCell ref="A152:D152"/>
     <mergeCell ref="A121:D121"/>
     <mergeCell ref="E15:G15"/>
     <mergeCell ref="A13:D13"/>
@@ -5140,6 +5208,7 @@
     <mergeCell ref="I56:L56"/>
     <mergeCell ref="I96:L96"/>
     <mergeCell ref="M107:O107"/>
+    <mergeCell ref="A145:D145"/>
     <mergeCell ref="A192:D192"/>
     <mergeCell ref="B30:O30"/>
     <mergeCell ref="A139:D139"/>
@@ -5163,6 +5232,7 @@
     <mergeCell ref="E9:G9"/>
     <mergeCell ref="A10:D10"/>
     <mergeCell ref="B46:O46"/>
+    <mergeCell ref="A115:D115"/>
     <mergeCell ref="I59:L59"/>
     <mergeCell ref="I99:L99"/>
     <mergeCell ref="A173:D173"/>
@@ -5171,6 +5241,7 @@
     <mergeCell ref="A77:D77"/>
     <mergeCell ref="I69:L69"/>
     <mergeCell ref="A33:O33"/>
+    <mergeCell ref="A157:D157"/>
     <mergeCell ref="A166:D166"/>
     <mergeCell ref="A8:O8"/>
     <mergeCell ref="A49:D49"/>

--- a/tempetoto2026_invulformulier.xlsx
+++ b/tempetoto2026_invulformulier.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -87,12 +87,6 @@
       <name val="Calibri"/>
       <i val="1"/>
       <color rgb="00888888"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="00555555"/>
       <sz val="10"/>
     </font>
     <font>
@@ -421,7 +415,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -511,14 +505,11 @@
     <xf numFmtId="0" fontId="0" fillId="47" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="48" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="49" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="50" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="50" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -916,7 +907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:O48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -935,6 +926,66 @@
           <t>Frankrijk</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Brazilië</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Verenigde Staten</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Duitsland</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Nederland</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>België</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Spanje</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Frankrijk</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Argentinië</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Engeland</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -952,6 +1003,66 @@
           <t>Spanje</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Zuid-Afrika</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Zwitserland</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Marokko</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Curaçao</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Egypte</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Kaapverdië</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Senegal</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Algerije</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>DR Congo</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Kroatië</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -969,6 +1080,66 @@
           <t>Argentinië</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Zuid-Korea</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Haïti</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Australië</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Ivoorkust</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Zweden</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Iran</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Saoedi-Arabië</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Noorwegen</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Oostenrijk</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Oezbekistan</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -984,6 +1155,66 @@
       <c r="C4" t="inlineStr">
         <is>
           <t>Engeland</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Tsjechië</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Bosnië-Herzegovina</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Schotland</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Turkije</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Tunesië</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Nieuw-Zeeland</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Uruguay</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Irak</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Jordanië</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Panama</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A6:O213"/>
+  <dimension ref="A6:O214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1636,7 +1867,7 @@
     <row r="21" ht="40" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>3.  Groepswinnaar, runner-up en beste nummers 3 worden AUTOMATISCH berekend uit je scores — je hoeft die niet in te vullen.</t>
+          <t>3.  Na je wedstrijdscores vul je per groep de groepswinnaar en runner-up in, én de 8 beste nummers 3. Dit zijn vrije voorspellingen — ze mogen afwijken van wat je scores logisch opleveren.</t>
         </is>
       </c>
     </row>
@@ -2057,21 +2288,17 @@
           <t>Groepswinnaar:</t>
         </is>
       </c>
-      <c r="E56" s="17" t="inlineStr">
-        <is>
-          <t>↳ niet invullen</t>
-        </is>
-      </c>
+      <c r="E56" s="5" t="n"/>
+      <c r="F56" s="17" t="inlineStr"/>
+      <c r="G56" s="17" t="inlineStr"/>
       <c r="I56" s="4" t="inlineStr">
         <is>
           <t>Groepswinnaar:</t>
         </is>
       </c>
-      <c r="M56" s="17" t="inlineStr">
-        <is>
-          <t>↳ niet invullen</t>
-        </is>
-      </c>
+      <c r="M56" s="5" t="n"/>
+      <c r="N56" s="17" t="inlineStr"/>
+      <c r="O56" s="17" t="inlineStr"/>
     </row>
     <row r="57" ht="17" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
@@ -2079,21 +2306,17 @@
           <t>Runner-up:</t>
         </is>
       </c>
-      <c r="E57" s="17" t="inlineStr">
-        <is>
-          <t>↳ niet invullen</t>
-        </is>
-      </c>
+      <c r="E57" s="5" t="n"/>
+      <c r="F57" s="17" t="inlineStr"/>
+      <c r="G57" s="17" t="inlineStr"/>
       <c r="I57" s="4" t="inlineStr">
         <is>
           <t>Runner-up:</t>
         </is>
       </c>
-      <c r="M57" s="17" t="inlineStr">
-        <is>
-          <t>↳ niet invullen</t>
-        </is>
-      </c>
+      <c r="M57" s="5" t="n"/>
+      <c r="N57" s="17" t="inlineStr"/>
+      <c r="O57" s="17" t="inlineStr"/>
     </row>
     <row r="58" ht="6" customHeight="1"/>
     <row r="59" ht="16" customHeight="1">
@@ -2336,21 +2559,17 @@
           <t>Groepswinnaar:</t>
         </is>
       </c>
-      <c r="E66" s="17" t="inlineStr">
-        <is>
-          <t>↳ niet invullen</t>
-        </is>
-      </c>
+      <c r="E66" s="5" t="n"/>
+      <c r="F66" s="17" t="inlineStr"/>
+      <c r="G66" s="17" t="inlineStr"/>
       <c r="I66" s="4" t="inlineStr">
         <is>
           <t>Groepswinnaar:</t>
         </is>
       </c>
-      <c r="M66" s="17" t="inlineStr">
-        <is>
-          <t>↳ niet invullen</t>
-        </is>
-      </c>
+      <c r="M66" s="5" t="n"/>
+      <c r="N66" s="17" t="inlineStr"/>
+      <c r="O66" s="17" t="inlineStr"/>
     </row>
     <row r="67" ht="17" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
@@ -2358,21 +2577,17 @@
           <t>Runner-up:</t>
         </is>
       </c>
-      <c r="E67" s="17" t="inlineStr">
-        <is>
-          <t>↳ niet invullen</t>
-        </is>
-      </c>
+      <c r="E67" s="5" t="n"/>
+      <c r="F67" s="17" t="inlineStr"/>
+      <c r="G67" s="17" t="inlineStr"/>
       <c r="I67" s="4" t="inlineStr">
         <is>
           <t>Runner-up:</t>
         </is>
       </c>
-      <c r="M67" s="17" t="inlineStr">
-        <is>
-          <t>↳ niet invullen</t>
-        </is>
-      </c>
+      <c r="M67" s="5" t="n"/>
+      <c r="N67" s="17" t="inlineStr"/>
+      <c r="O67" s="17" t="inlineStr"/>
     </row>
     <row r="68" ht="6" customHeight="1"/>
     <row r="69" ht="16" customHeight="1">
@@ -2615,21 +2830,17 @@
           <t>Groepswinnaar:</t>
         </is>
       </c>
-      <c r="E76" s="17" t="inlineStr">
-        <is>
-          <t>↳ niet invullen</t>
-        </is>
-      </c>
+      <c r="E76" s="5" t="n"/>
+      <c r="F76" s="17" t="inlineStr"/>
+      <c r="G76" s="17" t="inlineStr"/>
       <c r="I76" s="4" t="inlineStr">
         <is>
           <t>Groepswinnaar:</t>
         </is>
       </c>
-      <c r="M76" s="17" t="inlineStr">
-        <is>
-          <t>↳ niet invullen</t>
-        </is>
-      </c>
+      <c r="M76" s="5" t="n"/>
+      <c r="N76" s="17" t="inlineStr"/>
+      <c r="O76" s="17" t="inlineStr"/>
     </row>
     <row r="77" ht="17" customHeight="1">
       <c r="A77" s="4" t="inlineStr">
@@ -2637,21 +2848,17 @@
           <t>Runner-up:</t>
         </is>
       </c>
-      <c r="E77" s="17" t="inlineStr">
-        <is>
-          <t>↳ niet invullen</t>
-        </is>
-      </c>
+      <c r="E77" s="5" t="n"/>
+      <c r="F77" s="17" t="inlineStr"/>
+      <c r="G77" s="17" t="inlineStr"/>
       <c r="I77" s="4" t="inlineStr">
         <is>
           <t>Runner-up:</t>
         </is>
       </c>
-      <c r="M77" s="17" t="inlineStr">
-        <is>
-          <t>↳ niet invullen</t>
-        </is>
-      </c>
+      <c r="M77" s="5" t="n"/>
+      <c r="N77" s="17" t="inlineStr"/>
+      <c r="O77" s="17" t="inlineStr"/>
     </row>
     <row r="78" ht="6" customHeight="1"/>
     <row r="79" ht="16" customHeight="1">
@@ -2894,21 +3101,17 @@
           <t>Groepswinnaar:</t>
         </is>
       </c>
-      <c r="E86" s="17" t="inlineStr">
-        <is>
-          <t>↳ niet invullen</t>
-        </is>
-      </c>
+      <c r="E86" s="5" t="n"/>
+      <c r="F86" s="17" t="inlineStr"/>
+      <c r="G86" s="17" t="inlineStr"/>
       <c r="I86" s="4" t="inlineStr">
         <is>
           <t>Groepswinnaar:</t>
         </is>
       </c>
-      <c r="M86" s="17" t="inlineStr">
-        <is>
-          <t>↳ niet invullen</t>
-        </is>
-      </c>
+      <c r="M86" s="5" t="n"/>
+      <c r="N86" s="17" t="inlineStr"/>
+      <c r="O86" s="17" t="inlineStr"/>
     </row>
     <row r="87" ht="17" customHeight="1">
       <c r="A87" s="4" t="inlineStr">
@@ -2916,21 +3119,17 @@
           <t>Runner-up:</t>
         </is>
       </c>
-      <c r="E87" s="17" t="inlineStr">
-        <is>
-          <t>↳ niet invullen</t>
-        </is>
-      </c>
+      <c r="E87" s="5" t="n"/>
+      <c r="F87" s="17" t="inlineStr"/>
+      <c r="G87" s="17" t="inlineStr"/>
       <c r="I87" s="4" t="inlineStr">
         <is>
           <t>Runner-up:</t>
         </is>
       </c>
-      <c r="M87" s="17" t="inlineStr">
-        <is>
-          <t>↳ niet invullen</t>
-        </is>
-      </c>
+      <c r="M87" s="5" t="n"/>
+      <c r="N87" s="17" t="inlineStr"/>
+      <c r="O87" s="17" t="inlineStr"/>
     </row>
     <row r="88" ht="6" customHeight="1"/>
     <row r="89" ht="16" customHeight="1">
@@ -3173,21 +3372,17 @@
           <t>Groepswinnaar:</t>
         </is>
       </c>
-      <c r="E96" s="17" t="inlineStr">
-        <is>
-          <t>↳ niet invullen</t>
-        </is>
-      </c>
+      <c r="E96" s="5" t="n"/>
+      <c r="F96" s="17" t="inlineStr"/>
+      <c r="G96" s="17" t="inlineStr"/>
       <c r="I96" s="4" t="inlineStr">
         <is>
           <t>Groepswinnaar:</t>
         </is>
       </c>
-      <c r="M96" s="17" t="inlineStr">
-        <is>
-          <t>↳ niet invullen</t>
-        </is>
-      </c>
+      <c r="M96" s="5" t="n"/>
+      <c r="N96" s="17" t="inlineStr"/>
+      <c r="O96" s="17" t="inlineStr"/>
     </row>
     <row r="97" ht="17" customHeight="1">
       <c r="A97" s="4" t="inlineStr">
@@ -3195,21 +3390,17 @@
           <t>Runner-up:</t>
         </is>
       </c>
-      <c r="E97" s="17" t="inlineStr">
-        <is>
-          <t>↳ niet invullen</t>
-        </is>
-      </c>
+      <c r="E97" s="5" t="n"/>
+      <c r="F97" s="17" t="inlineStr"/>
+      <c r="G97" s="17" t="inlineStr"/>
       <c r="I97" s="4" t="inlineStr">
         <is>
           <t>Runner-up:</t>
         </is>
       </c>
-      <c r="M97" s="17" t="inlineStr">
-        <is>
-          <t>↳ niet invullen</t>
-        </is>
-      </c>
+      <c r="M97" s="5" t="n"/>
+      <c r="N97" s="17" t="inlineStr"/>
+      <c r="O97" s="17" t="inlineStr"/>
     </row>
     <row r="98" ht="6" customHeight="1"/>
     <row r="99" ht="16" customHeight="1">
@@ -3452,21 +3643,17 @@
           <t>Groepswinnaar:</t>
         </is>
       </c>
-      <c r="E106" s="17" t="inlineStr">
-        <is>
-          <t>↳ niet invullen</t>
-        </is>
-      </c>
+      <c r="E106" s="5" t="n"/>
+      <c r="F106" s="17" t="inlineStr"/>
+      <c r="G106" s="17" t="inlineStr"/>
       <c r="I106" s="4" t="inlineStr">
         <is>
           <t>Groepswinnaar:</t>
         </is>
       </c>
-      <c r="M106" s="17" t="inlineStr">
-        <is>
-          <t>↳ niet invullen</t>
-        </is>
-      </c>
+      <c r="M106" s="5" t="n"/>
+      <c r="N106" s="17" t="inlineStr"/>
+      <c r="O106" s="17" t="inlineStr"/>
     </row>
     <row r="107" ht="17" customHeight="1">
       <c r="A107" s="4" t="inlineStr">
@@ -3474,97 +3661,128 @@
           <t>Runner-up:</t>
         </is>
       </c>
-      <c r="E107" s="17" t="inlineStr">
-        <is>
-          <t>↳ niet invullen</t>
-        </is>
-      </c>
+      <c r="E107" s="5" t="n"/>
+      <c r="F107" s="17" t="inlineStr"/>
+      <c r="G107" s="17" t="inlineStr"/>
       <c r="I107" s="4" t="inlineStr">
         <is>
           <t>Runner-up:</t>
         </is>
       </c>
-      <c r="M107" s="17" t="inlineStr">
-        <is>
-          <t>↳ niet invullen</t>
-        </is>
-      </c>
+      <c r="M107" s="5" t="n"/>
+      <c r="N107" s="17" t="inlineStr"/>
+      <c r="O107" s="17" t="inlineStr"/>
     </row>
     <row r="108" ht="6" customHeight="1"/>
     <row r="109" ht="8" customHeight="1"/>
     <row r="110" ht="18" customHeight="1">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>▶  BESTE 8 NUMMERS 3  ·  niet invullen — wordt na inlevering door de agent berekend</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="40" customHeight="1">
-      <c r="A111" s="59" t="inlineStr">
-        <is>
-          <t>De 8 beste nummers 3 worden na inlevering van dit formulier automatisch berekend op basis van de punten en het doelsaldo van de nummer-3-landen in jouw groepsscores. De Excel zelf rekent dit NIET uit — je hoeft hier niets in te vullen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="8" customHeight="1"/>
-    <row r="113" ht="18" customHeight="1">
-      <c r="A113" s="3" t="inlineStr">
+          <t>▶  BESTE 8 NUMMERS 3  ·  vul in welke 8 nummers 3 jij verwacht dat doorgaan</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="18" customHeight="1">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>#1:</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="n"/>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>#2:</t>
+        </is>
+      </c>
+      <c r="G111" s="5" t="n"/>
+      <c r="I111" s="4" t="inlineStr">
+        <is>
+          <t>#3:</t>
+        </is>
+      </c>
+      <c r="K111" s="5" t="n"/>
+      <c r="M111" s="4" t="inlineStr">
+        <is>
+          <t>#4:</t>
+        </is>
+      </c>
+      <c r="O111" s="5" t="n"/>
+    </row>
+    <row r="112" ht="18" customHeight="1">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>#5:</t>
+        </is>
+      </c>
+      <c r="C112" s="5" t="n"/>
+      <c r="E112" s="4" t="inlineStr">
+        <is>
+          <t>#6:</t>
+        </is>
+      </c>
+      <c r="G112" s="5" t="n"/>
+      <c r="I112" s="4" t="inlineStr">
+        <is>
+          <t>#7:</t>
+        </is>
+      </c>
+      <c r="K112" s="5" t="n"/>
+      <c r="M112" s="4" t="inlineStr">
+        <is>
+          <t>#8:</t>
+        </is>
+      </c>
+      <c r="O112" s="5" t="n"/>
+    </row>
+    <row r="113" ht="8" customHeight="1"/>
+    <row r="114" ht="18" customHeight="1">
+      <c r="A114" s="3" t="inlineStr">
         <is>
           <t>▶  KNOCK-OUT  ·  grijze vakjes — invullen na de groepsfase, vóór elke ronde</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="16" customHeight="1">
-      <c r="A114" s="9" t="inlineStr">
+    <row r="115" ht="16" customHeight="1">
+      <c r="A115" s="9" t="inlineStr">
         <is>
           <t>Ronde van 32  ·  toto 5 pt / exact +3 pt</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="14" customHeight="1">
-      <c r="A115" s="12" t="inlineStr">
+    <row r="116" ht="14" customHeight="1">
+      <c r="A116" s="12" t="inlineStr">
         <is>
           <t>Wedstrijd</t>
         </is>
       </c>
-      <c r="E115" s="12" t="inlineStr">
+      <c r="E116" s="12" t="inlineStr">
         <is>
           <t>voorsp.</t>
         </is>
       </c>
-      <c r="F115" s="12" t="inlineStr">
+      <c r="F116" s="12" t="inlineStr">
         <is>
           <t>uitslag</t>
         </is>
       </c>
-      <c r="G115" s="12" t="inlineStr">
+      <c r="G116" s="12" t="inlineStr">
         <is>
           <t>pt.</t>
         </is>
       </c>
-      <c r="H115" s="60" t="n"/>
-      <c r="I115" s="60" t="n"/>
-      <c r="J115" s="60" t="n"/>
-      <c r="K115" s="60" t="n"/>
-      <c r="L115" s="60" t="n"/>
-      <c r="M115" s="60" t="n"/>
-      <c r="N115" s="60" t="n"/>
-      <c r="O115" s="60" t="n"/>
-    </row>
-    <row r="116" ht="16" customHeight="1">
-      <c r="A116" s="61" t="inlineStr">
+      <c r="H116" s="59" t="n"/>
+      <c r="I116" s="59" t="n"/>
+      <c r="J116" s="59" t="n"/>
+      <c r="K116" s="59" t="n"/>
+      <c r="L116" s="59" t="n"/>
+      <c r="M116" s="59" t="n"/>
+      <c r="N116" s="59" t="n"/>
+      <c r="O116" s="59" t="n"/>
+    </row>
+    <row r="117" ht="16" customHeight="1">
+      <c r="A117" s="60" t="inlineStr">
         <is>
           <t>2A  –  2B</t>
-        </is>
-      </c>
-      <c r="E116" s="17" t="inlineStr"/>
-      <c r="F116" s="17" t="inlineStr"/>
-      <c r="G116" s="17" t="inlineStr"/>
-    </row>
-    <row r="117" ht="16" customHeight="1">
-      <c r="A117" s="61" t="inlineStr">
-        <is>
-          <t>1E  –  3e (A/B/C/D/F)</t>
         </is>
       </c>
       <c r="E117" s="17" t="inlineStr"/>
@@ -3572,9 +3790,9 @@
       <c r="G117" s="17" t="inlineStr"/>
     </row>
     <row r="118" ht="16" customHeight="1">
-      <c r="A118" s="61" t="inlineStr">
-        <is>
-          <t>1F  –  2C</t>
+      <c r="A118" s="60" t="inlineStr">
+        <is>
+          <t>1E  –  3e (A/B/C/D/F)</t>
         </is>
       </c>
       <c r="E118" s="17" t="inlineStr"/>
@@ -3582,9 +3800,9 @@
       <c r="G118" s="17" t="inlineStr"/>
     </row>
     <row r="119" ht="16" customHeight="1">
-      <c r="A119" s="61" t="inlineStr">
-        <is>
-          <t>1C  –  2F</t>
+      <c r="A119" s="60" t="inlineStr">
+        <is>
+          <t>1F  –  2C</t>
         </is>
       </c>
       <c r="E119" s="17" t="inlineStr"/>
@@ -3592,9 +3810,9 @@
       <c r="G119" s="17" t="inlineStr"/>
     </row>
     <row r="120" ht="16" customHeight="1">
-      <c r="A120" s="61" t="inlineStr">
-        <is>
-          <t>1I  –  3e (C/D/F/G/H)</t>
+      <c r="A120" s="60" t="inlineStr">
+        <is>
+          <t>1C  –  2F</t>
         </is>
       </c>
       <c r="E120" s="17" t="inlineStr"/>
@@ -3602,9 +3820,9 @@
       <c r="G120" s="17" t="inlineStr"/>
     </row>
     <row r="121" ht="16" customHeight="1">
-      <c r="A121" s="61" t="inlineStr">
-        <is>
-          <t>2E  –  2I</t>
+      <c r="A121" s="60" t="inlineStr">
+        <is>
+          <t>1I  –  3e (C/D/F/G/H)</t>
         </is>
       </c>
       <c r="E121" s="17" t="inlineStr"/>
@@ -3612,9 +3830,9 @@
       <c r="G121" s="17" t="inlineStr"/>
     </row>
     <row r="122" ht="16" customHeight="1">
-      <c r="A122" s="61" t="inlineStr">
-        <is>
-          <t>1A  –  3e (C/E/F/H/I)</t>
+      <c r="A122" s="60" t="inlineStr">
+        <is>
+          <t>2E  –  2I</t>
         </is>
       </c>
       <c r="E122" s="17" t="inlineStr"/>
@@ -3622,9 +3840,9 @@
       <c r="G122" s="17" t="inlineStr"/>
     </row>
     <row r="123" ht="16" customHeight="1">
-      <c r="A123" s="61" t="inlineStr">
-        <is>
-          <t>1L  –  3e (E/H/I/J/K)</t>
+      <c r="A123" s="60" t="inlineStr">
+        <is>
+          <t>1A  –  3e (C/E/F/H/I)</t>
         </is>
       </c>
       <c r="E123" s="17" t="inlineStr"/>
@@ -3632,9 +3850,9 @@
       <c r="G123" s="17" t="inlineStr"/>
     </row>
     <row r="124" ht="16" customHeight="1">
-      <c r="A124" s="61" t="inlineStr">
-        <is>
-          <t>1D  –  3e (B/E/F/I/J)</t>
+      <c r="A124" s="60" t="inlineStr">
+        <is>
+          <t>1L  –  3e (E/H/I/J/K)</t>
         </is>
       </c>
       <c r="E124" s="17" t="inlineStr"/>
@@ -3642,9 +3860,9 @@
       <c r="G124" s="17" t="inlineStr"/>
     </row>
     <row r="125" ht="16" customHeight="1">
-      <c r="A125" s="61" t="inlineStr">
-        <is>
-          <t>1G  –  3e (A/E/H/I/J)</t>
+      <c r="A125" s="60" t="inlineStr">
+        <is>
+          <t>1D  –  3e (B/E/F/I/J)</t>
         </is>
       </c>
       <c r="E125" s="17" t="inlineStr"/>
@@ -3652,9 +3870,9 @@
       <c r="G125" s="17" t="inlineStr"/>
     </row>
     <row r="126" ht="16" customHeight="1">
-      <c r="A126" s="61" t="inlineStr">
-        <is>
-          <t>2K  –  2L</t>
+      <c r="A126" s="60" t="inlineStr">
+        <is>
+          <t>1G  –  3e (A/E/H/I/J)</t>
         </is>
       </c>
       <c r="E126" s="17" t="inlineStr"/>
@@ -3662,9 +3880,9 @@
       <c r="G126" s="17" t="inlineStr"/>
     </row>
     <row r="127" ht="16" customHeight="1">
-      <c r="A127" s="61" t="inlineStr">
-        <is>
-          <t>1H  –  2J</t>
+      <c r="A127" s="60" t="inlineStr">
+        <is>
+          <t>2K  –  2L</t>
         </is>
       </c>
       <c r="E127" s="17" t="inlineStr"/>
@@ -3672,9 +3890,9 @@
       <c r="G127" s="17" t="inlineStr"/>
     </row>
     <row r="128" ht="16" customHeight="1">
-      <c r="A128" s="61" t="inlineStr">
-        <is>
-          <t>1B  –  3e (E/F/G/I/J)</t>
+      <c r="A128" s="60" t="inlineStr">
+        <is>
+          <t>1H  –  2J</t>
         </is>
       </c>
       <c r="E128" s="17" t="inlineStr"/>
@@ -3682,9 +3900,9 @@
       <c r="G128" s="17" t="inlineStr"/>
     </row>
     <row r="129" ht="16" customHeight="1">
-      <c r="A129" s="61" t="inlineStr">
-        <is>
-          <t>1J  –  2H</t>
+      <c r="A129" s="60" t="inlineStr">
+        <is>
+          <t>1B  –  3e (E/F/G/I/J)</t>
         </is>
       </c>
       <c r="E129" s="17" t="inlineStr"/>
@@ -3692,9 +3910,9 @@
       <c r="G129" s="17" t="inlineStr"/>
     </row>
     <row r="130" ht="16" customHeight="1">
-      <c r="A130" s="61" t="inlineStr">
-        <is>
-          <t>1K  –  3e (D/E/I/J/L)</t>
+      <c r="A130" s="60" t="inlineStr">
+        <is>
+          <t>1J  –  2H</t>
         </is>
       </c>
       <c r="E130" s="17" t="inlineStr"/>
@@ -3702,67 +3920,67 @@
       <c r="G130" s="17" t="inlineStr"/>
     </row>
     <row r="131" ht="16" customHeight="1">
-      <c r="A131" s="61" t="inlineStr">
-        <is>
-          <t>2D  –  2G</t>
+      <c r="A131" s="60" t="inlineStr">
+        <is>
+          <t>1K  –  3e (D/E/I/J/L)</t>
         </is>
       </c>
       <c r="E131" s="17" t="inlineStr"/>
       <c r="F131" s="17" t="inlineStr"/>
       <c r="G131" s="17" t="inlineStr"/>
     </row>
-    <row r="132" ht="6" customHeight="1"/>
-    <row r="133" ht="16" customHeight="1">
-      <c r="A133" s="9" t="inlineStr">
+    <row r="132" ht="16" customHeight="1">
+      <c r="A132" s="60" t="inlineStr">
+        <is>
+          <t>2D  –  2G</t>
+        </is>
+      </c>
+      <c r="E132" s="17" t="inlineStr"/>
+      <c r="F132" s="17" t="inlineStr"/>
+      <c r="G132" s="17" t="inlineStr"/>
+    </row>
+    <row r="133" ht="6" customHeight="1"/>
+    <row r="134" ht="16" customHeight="1">
+      <c r="A134" s="9" t="inlineStr">
         <is>
           <t>Ronde van 16  ·  toto 7 pt / exact +4 pt</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="14" customHeight="1">
-      <c r="A134" s="12" t="inlineStr">
+    <row r="135" ht="14" customHeight="1">
+      <c r="A135" s="12" t="inlineStr">
         <is>
           <t>Wedstrijd</t>
         </is>
       </c>
-      <c r="E134" s="12" t="inlineStr">
+      <c r="E135" s="12" t="inlineStr">
         <is>
           <t>voorsp.</t>
         </is>
       </c>
-      <c r="F134" s="12" t="inlineStr">
+      <c r="F135" s="12" t="inlineStr">
         <is>
           <t>uitslag</t>
         </is>
       </c>
-      <c r="G134" s="12" t="inlineStr">
+      <c r="G135" s="12" t="inlineStr">
         <is>
           <t>pt.</t>
         </is>
       </c>
-      <c r="H134" s="60" t="n"/>
-      <c r="I134" s="60" t="n"/>
-      <c r="J134" s="60" t="n"/>
-      <c r="K134" s="60" t="n"/>
-      <c r="L134" s="60" t="n"/>
-      <c r="M134" s="60" t="n"/>
-      <c r="N134" s="60" t="n"/>
-      <c r="O134" s="60" t="n"/>
-    </row>
-    <row r="135" ht="16" customHeight="1">
-      <c r="A135" s="61" t="inlineStr">
+      <c r="H135" s="59" t="n"/>
+      <c r="I135" s="59" t="n"/>
+      <c r="J135" s="59" t="n"/>
+      <c r="K135" s="59" t="n"/>
+      <c r="L135" s="59" t="n"/>
+      <c r="M135" s="59" t="n"/>
+      <c r="N135" s="59" t="n"/>
+      <c r="O135" s="59" t="n"/>
+    </row>
+    <row r="136" ht="16" customHeight="1">
+      <c r="A136" s="60" t="inlineStr">
         <is>
           <t>W32-2  –  W32-5</t>
-        </is>
-      </c>
-      <c r="E135" s="17" t="inlineStr"/>
-      <c r="F135" s="17" t="inlineStr"/>
-      <c r="G135" s="17" t="inlineStr"/>
-    </row>
-    <row r="136" ht="16" customHeight="1">
-      <c r="A136" s="61" t="inlineStr">
-        <is>
-          <t>W32-1  –  W32-3</t>
         </is>
       </c>
       <c r="E136" s="17" t="inlineStr"/>
@@ -3770,9 +3988,9 @@
       <c r="G136" s="17" t="inlineStr"/>
     </row>
     <row r="137" ht="16" customHeight="1">
-      <c r="A137" s="61" t="inlineStr">
-        <is>
-          <t>W32-4  –  W32-6</t>
+      <c r="A137" s="60" t="inlineStr">
+        <is>
+          <t>W32-1  –  W32-3</t>
         </is>
       </c>
       <c r="E137" s="17" t="inlineStr"/>
@@ -3780,9 +3998,9 @@
       <c r="G137" s="17" t="inlineStr"/>
     </row>
     <row r="138" ht="16" customHeight="1">
-      <c r="A138" s="61" t="inlineStr">
-        <is>
-          <t>W32-7  –  W32-8</t>
+      <c r="A138" s="60" t="inlineStr">
+        <is>
+          <t>W32-4  –  W32-6</t>
         </is>
       </c>
       <c r="E138" s="17" t="inlineStr"/>
@@ -3790,9 +4008,9 @@
       <c r="G138" s="17" t="inlineStr"/>
     </row>
     <row r="139" ht="16" customHeight="1">
-      <c r="A139" s="61" t="inlineStr">
-        <is>
-          <t>W32-11  –  W32-12</t>
+      <c r="A139" s="60" t="inlineStr">
+        <is>
+          <t>W32-7  –  W32-8</t>
         </is>
       </c>
       <c r="E139" s="17" t="inlineStr"/>
@@ -3800,9 +4018,9 @@
       <c r="G139" s="17" t="inlineStr"/>
     </row>
     <row r="140" ht="16" customHeight="1">
-      <c r="A140" s="61" t="inlineStr">
-        <is>
-          <t>W32-9  –  W32-10</t>
+      <c r="A140" s="60" t="inlineStr">
+        <is>
+          <t>W32-11  –  W32-12</t>
         </is>
       </c>
       <c r="E140" s="17" t="inlineStr"/>
@@ -3810,9 +4028,9 @@
       <c r="G140" s="17" t="inlineStr"/>
     </row>
     <row r="141" ht="16" customHeight="1">
-      <c r="A141" s="61" t="inlineStr">
-        <is>
-          <t>W32-14  –  W32-16</t>
+      <c r="A141" s="60" t="inlineStr">
+        <is>
+          <t>W32-9  –  W32-10</t>
         </is>
       </c>
       <c r="E141" s="17" t="inlineStr"/>
@@ -3820,67 +4038,67 @@
       <c r="G141" s="17" t="inlineStr"/>
     </row>
     <row r="142" ht="16" customHeight="1">
-      <c r="A142" s="61" t="inlineStr">
-        <is>
-          <t>W32-13  –  W32-15</t>
+      <c r="A142" s="60" t="inlineStr">
+        <is>
+          <t>W32-14  –  W32-16</t>
         </is>
       </c>
       <c r="E142" s="17" t="inlineStr"/>
       <c r="F142" s="17" t="inlineStr"/>
       <c r="G142" s="17" t="inlineStr"/>
     </row>
-    <row r="143" ht="6" customHeight="1"/>
-    <row r="144" ht="16" customHeight="1">
-      <c r="A144" s="9" t="inlineStr">
+    <row r="143" ht="16" customHeight="1">
+      <c r="A143" s="60" t="inlineStr">
+        <is>
+          <t>W32-13  –  W32-15</t>
+        </is>
+      </c>
+      <c r="E143" s="17" t="inlineStr"/>
+      <c r="F143" s="17" t="inlineStr"/>
+      <c r="G143" s="17" t="inlineStr"/>
+    </row>
+    <row r="144" ht="6" customHeight="1"/>
+    <row r="145" ht="16" customHeight="1">
+      <c r="A145" s="9" t="inlineStr">
         <is>
           <t>Kwartfinales  ·  toto 9 pt / exact +5 pt</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="14" customHeight="1">
-      <c r="A145" s="12" t="inlineStr">
+    <row r="146" ht="14" customHeight="1">
+      <c r="A146" s="12" t="inlineStr">
         <is>
           <t>Wedstrijd</t>
         </is>
       </c>
-      <c r="E145" s="12" t="inlineStr">
+      <c r="E146" s="12" t="inlineStr">
         <is>
           <t>voorsp.</t>
         </is>
       </c>
-      <c r="F145" s="12" t="inlineStr">
+      <c r="F146" s="12" t="inlineStr">
         <is>
           <t>uitslag</t>
         </is>
       </c>
-      <c r="G145" s="12" t="inlineStr">
+      <c r="G146" s="12" t="inlineStr">
         <is>
           <t>pt.</t>
         </is>
       </c>
-      <c r="H145" s="60" t="n"/>
-      <c r="I145" s="60" t="n"/>
-      <c r="J145" s="60" t="n"/>
-      <c r="K145" s="60" t="n"/>
-      <c r="L145" s="60" t="n"/>
-      <c r="M145" s="60" t="n"/>
-      <c r="N145" s="60" t="n"/>
-      <c r="O145" s="60" t="n"/>
-    </row>
-    <row r="146" ht="16" customHeight="1">
-      <c r="A146" s="61" t="inlineStr">
+      <c r="H146" s="59" t="n"/>
+      <c r="I146" s="59" t="n"/>
+      <c r="J146" s="59" t="n"/>
+      <c r="K146" s="59" t="n"/>
+      <c r="L146" s="59" t="n"/>
+      <c r="M146" s="59" t="n"/>
+      <c r="N146" s="59" t="n"/>
+      <c r="O146" s="59" t="n"/>
+    </row>
+    <row r="147" ht="16" customHeight="1">
+      <c r="A147" s="60" t="inlineStr">
         <is>
           <t>W16-1  –  W16-2</t>
-        </is>
-      </c>
-      <c r="E146" s="17" t="inlineStr"/>
-      <c r="F146" s="17" t="inlineStr"/>
-      <c r="G146" s="17" t="inlineStr"/>
-    </row>
-    <row r="147" ht="16" customHeight="1">
-      <c r="A147" s="61" t="inlineStr">
-        <is>
-          <t>W16-5  –  W16-6</t>
         </is>
       </c>
       <c r="E147" s="17" t="inlineStr"/>
@@ -3888,9 +4106,9 @@
       <c r="G147" s="17" t="inlineStr"/>
     </row>
     <row r="148" ht="16" customHeight="1">
-      <c r="A148" s="61" t="inlineStr">
-        <is>
-          <t>W16-3  –  W16-4</t>
+      <c r="A148" s="60" t="inlineStr">
+        <is>
+          <t>W16-5  –  W16-6</t>
         </is>
       </c>
       <c r="E148" s="17" t="inlineStr"/>
@@ -3898,1243 +4116,1249 @@
       <c r="G148" s="17" t="inlineStr"/>
     </row>
     <row r="149" ht="16" customHeight="1">
-      <c r="A149" s="61" t="inlineStr">
-        <is>
-          <t>W16-7  –  W16-8</t>
+      <c r="A149" s="60" t="inlineStr">
+        <is>
+          <t>W16-3  –  W16-4</t>
         </is>
       </c>
       <c r="E149" s="17" t="inlineStr"/>
       <c r="F149" s="17" t="inlineStr"/>
       <c r="G149" s="17" t="inlineStr"/>
     </row>
-    <row r="150" ht="6" customHeight="1"/>
-    <row r="151" ht="16" customHeight="1">
-      <c r="A151" s="9" t="inlineStr">
+    <row r="150" ht="16" customHeight="1">
+      <c r="A150" s="60" t="inlineStr">
+        <is>
+          <t>W16-7  –  W16-8</t>
+        </is>
+      </c>
+      <c r="E150" s="17" t="inlineStr"/>
+      <c r="F150" s="17" t="inlineStr"/>
+      <c r="G150" s="17" t="inlineStr"/>
+    </row>
+    <row r="151" ht="6" customHeight="1"/>
+    <row r="152" ht="16" customHeight="1">
+      <c r="A152" s="9" t="inlineStr">
         <is>
           <t>Halve finales  ·  toto 11 pt / exact +6 pt</t>
         </is>
       </c>
     </row>
-    <row r="152" ht="14" customHeight="1">
-      <c r="A152" s="12" t="inlineStr">
+    <row r="153" ht="14" customHeight="1">
+      <c r="A153" s="12" t="inlineStr">
         <is>
           <t>Wedstrijd</t>
         </is>
       </c>
-      <c r="E152" s="12" t="inlineStr">
+      <c r="E153" s="12" t="inlineStr">
         <is>
           <t>voorsp.</t>
         </is>
       </c>
-      <c r="F152" s="12" t="inlineStr">
+      <c r="F153" s="12" t="inlineStr">
         <is>
           <t>uitslag</t>
         </is>
       </c>
-      <c r="G152" s="12" t="inlineStr">
+      <c r="G153" s="12" t="inlineStr">
         <is>
           <t>pt.</t>
         </is>
       </c>
-      <c r="H152" s="60" t="n"/>
-      <c r="I152" s="60" t="n"/>
-      <c r="J152" s="60" t="n"/>
-      <c r="K152" s="60" t="n"/>
-      <c r="L152" s="60" t="n"/>
-      <c r="M152" s="60" t="n"/>
-      <c r="N152" s="60" t="n"/>
-      <c r="O152" s="60" t="n"/>
-    </row>
-    <row r="153" ht="16" customHeight="1">
-      <c r="A153" s="61" t="inlineStr">
+      <c r="H153" s="59" t="n"/>
+      <c r="I153" s="59" t="n"/>
+      <c r="J153" s="59" t="n"/>
+      <c r="K153" s="59" t="n"/>
+      <c r="L153" s="59" t="n"/>
+      <c r="M153" s="59" t="n"/>
+      <c r="N153" s="59" t="n"/>
+      <c r="O153" s="59" t="n"/>
+    </row>
+    <row r="154" ht="16" customHeight="1">
+      <c r="A154" s="60" t="inlineStr">
         <is>
           <t>WKF-1  –  WKF-2</t>
-        </is>
-      </c>
-      <c r="E153" s="17" t="inlineStr"/>
-      <c r="F153" s="17" t="inlineStr"/>
-      <c r="G153" s="17" t="inlineStr"/>
-    </row>
-    <row r="154" ht="16" customHeight="1">
-      <c r="A154" s="61" t="inlineStr">
-        <is>
-          <t>WKF-3  –  WKF-4</t>
         </is>
       </c>
       <c r="E154" s="17" t="inlineStr"/>
       <c r="F154" s="17" t="inlineStr"/>
       <c r="G154" s="17" t="inlineStr"/>
     </row>
-    <row r="155" ht="6" customHeight="1"/>
-    <row r="156" ht="16" customHeight="1">
-      <c r="A156" s="9" t="inlineStr">
+    <row r="155" ht="16" customHeight="1">
+      <c r="A155" s="60" t="inlineStr">
+        <is>
+          <t>WKF-3  –  WKF-4</t>
+        </is>
+      </c>
+      <c r="E155" s="17" t="inlineStr"/>
+      <c r="F155" s="17" t="inlineStr"/>
+      <c r="G155" s="17" t="inlineStr"/>
+    </row>
+    <row r="156" ht="6" customHeight="1"/>
+    <row r="157" ht="16" customHeight="1">
+      <c r="A157" s="9" t="inlineStr">
         <is>
           <t>Finale  ·  toto 13 pt / exact +7 pt</t>
         </is>
       </c>
     </row>
-    <row r="157" ht="14" customHeight="1">
-      <c r="A157" s="12" t="inlineStr">
+    <row r="158" ht="14" customHeight="1">
+      <c r="A158" s="12" t="inlineStr">
         <is>
           <t>Wedstrijd</t>
         </is>
       </c>
-      <c r="E157" s="12" t="inlineStr">
+      <c r="E158" s="12" t="inlineStr">
         <is>
           <t>voorsp.</t>
         </is>
       </c>
-      <c r="F157" s="12" t="inlineStr">
+      <c r="F158" s="12" t="inlineStr">
         <is>
           <t>uitslag</t>
         </is>
       </c>
-      <c r="G157" s="12" t="inlineStr">
+      <c r="G158" s="12" t="inlineStr">
         <is>
           <t>pt.</t>
         </is>
       </c>
-      <c r="H157" s="60" t="n"/>
-      <c r="I157" s="60" t="n"/>
-      <c r="J157" s="60" t="n"/>
-      <c r="K157" s="60" t="n"/>
-      <c r="L157" s="60" t="n"/>
-      <c r="M157" s="60" t="n"/>
-      <c r="N157" s="60" t="n"/>
-      <c r="O157" s="60" t="n"/>
-    </row>
-    <row r="158" ht="16" customHeight="1">
-      <c r="A158" s="61" t="inlineStr">
+      <c r="H158" s="59" t="n"/>
+      <c r="I158" s="59" t="n"/>
+      <c r="J158" s="59" t="n"/>
+      <c r="K158" s="59" t="n"/>
+      <c r="L158" s="59" t="n"/>
+      <c r="M158" s="59" t="n"/>
+      <c r="N158" s="59" t="n"/>
+      <c r="O158" s="59" t="n"/>
+    </row>
+    <row r="159" ht="16" customHeight="1">
+      <c r="A159" s="60" t="inlineStr">
         <is>
           <t>WHF-1  –  WHF-2</t>
         </is>
       </c>
-      <c r="E158" s="17" t="inlineStr"/>
-      <c r="F158" s="17" t="inlineStr"/>
-      <c r="G158" s="17" t="inlineStr"/>
-    </row>
-    <row r="159" ht="6" customHeight="1"/>
-    <row r="160" ht="8" customHeight="1"/>
-    <row r="161" ht="18" customHeight="1">
-      <c r="A161" s="3" t="inlineStr">
+      <c r="E159" s="17" t="inlineStr"/>
+      <c r="F159" s="17" t="inlineStr"/>
+      <c r="G159" s="17" t="inlineStr"/>
+    </row>
+    <row r="160" ht="6" customHeight="1"/>
+    <row r="161" ht="8" customHeight="1"/>
+    <row r="162" ht="18" customHeight="1">
+      <c r="A162" s="3" t="inlineStr">
         <is>
           <t>▶  VERRASSING — kies een land BUITEN de top-12 · punten schalen met ranking en ronde</t>
         </is>
       </c>
     </row>
-    <row r="162" ht="14" customHeight="1">
-      <c r="A162" s="12" t="inlineStr">
+    <row r="163" ht="14" customHeight="1">
+      <c r="A163" s="12" t="inlineStr">
         <is>
           <t>Land (outsider)</t>
         </is>
       </c>
-      <c r="E162" s="12" t="inlineStr">
+      <c r="E163" s="12" t="inlineStr">
         <is>
           <t>R16</t>
         </is>
       </c>
-      <c r="F162" s="12" t="inlineStr">
+      <c r="F163" s="12" t="inlineStr">
         <is>
           <t>KF</t>
         </is>
       </c>
-      <c r="G162" s="12" t="inlineStr">
+      <c r="G163" s="12" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="H162" s="12" t="inlineStr">
+      <c r="H163" s="12" t="inlineStr">
         <is>
           <t>Finale</t>
         </is>
       </c>
-      <c r="I162" s="12" t="inlineStr">
+      <c r="I163" s="12" t="inlineStr">
         <is>
           <t>Winnaar</t>
         </is>
-      </c>
-    </row>
-    <row r="163" ht="15" customHeight="1">
-      <c r="A163" s="14" t="inlineStr">
-        <is>
-          <t>Senegal</t>
-        </is>
-      </c>
-      <c r="E163" s="62" t="n">
-        <v>7</v>
-      </c>
-      <c r="F163" s="62" t="n">
-        <v>12</v>
-      </c>
-      <c r="G163" s="62" t="n">
-        <v>19</v>
-      </c>
-      <c r="H163" s="62" t="n">
-        <v>26</v>
-      </c>
-      <c r="I163" s="62" t="n">
-        <v>34</v>
       </c>
     </row>
     <row r="164" ht="15" customHeight="1">
       <c r="A164" s="14" t="inlineStr">
         <is>
-          <t>Mexico</t>
-        </is>
-      </c>
-      <c r="E164" s="62" t="n">
+          <t>Senegal</t>
+        </is>
+      </c>
+      <c r="E164" s="61" t="n">
         <v>7</v>
       </c>
-      <c r="F164" s="62" t="n">
-        <v>13</v>
-      </c>
-      <c r="G164" s="62" t="n">
+      <c r="F164" s="61" t="n">
+        <v>12</v>
+      </c>
+      <c r="G164" s="61" t="n">
         <v>19</v>
       </c>
-      <c r="H164" s="62" t="n">
-        <v>27</v>
-      </c>
-      <c r="I164" s="62" t="n">
-        <v>35</v>
+      <c r="H164" s="61" t="n">
+        <v>26</v>
+      </c>
+      <c r="I164" s="61" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="165" ht="15" customHeight="1">
       <c r="A165" s="14" t="inlineStr">
         <is>
-          <t>Verenigde Staten</t>
-        </is>
-      </c>
-      <c r="E165" s="62" t="n">
-        <v>8</v>
-      </c>
-      <c r="F165" s="62" t="n">
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="E165" s="61" t="n">
+        <v>7</v>
+      </c>
+      <c r="F165" s="61" t="n">
         <v>13</v>
       </c>
-      <c r="G165" s="62" t="n">
-        <v>20</v>
-      </c>
-      <c r="H165" s="62" t="n">
+      <c r="G165" s="61" t="n">
+        <v>19</v>
+      </c>
+      <c r="H165" s="61" t="n">
         <v>27</v>
       </c>
-      <c r="I165" s="62" t="n">
-        <v>36</v>
+      <c r="I165" s="61" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="166" ht="15" customHeight="1">
       <c r="A166" s="14" t="inlineStr">
         <is>
-          <t>Uruguay</t>
-        </is>
-      </c>
-      <c r="E166" s="62" t="n">
+          <t>Verenigde Staten</t>
+        </is>
+      </c>
+      <c r="E166" s="61" t="n">
         <v>8</v>
       </c>
-      <c r="F166" s="62" t="n">
-        <v>14</v>
-      </c>
-      <c r="G166" s="62" t="n">
+      <c r="F166" s="61" t="n">
+        <v>13</v>
+      </c>
+      <c r="G166" s="61" t="n">
         <v>20</v>
       </c>
-      <c r="H166" s="62" t="n">
-        <v>28</v>
-      </c>
-      <c r="I166" s="62" t="n">
-        <v>37</v>
+      <c r="H166" s="61" t="n">
+        <v>27</v>
+      </c>
+      <c r="I166" s="61" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="167" ht="15" customHeight="1">
       <c r="A167" s="14" t="inlineStr">
         <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="E167" s="62" t="n">
+          <t>Uruguay</t>
+        </is>
+      </c>
+      <c r="E167" s="61" t="n">
         <v>8</v>
       </c>
-      <c r="F167" s="62" t="n">
+      <c r="F167" s="61" t="n">
         <v>14</v>
       </c>
-      <c r="G167" s="62" t="n">
-        <v>21</v>
-      </c>
-      <c r="H167" s="62" t="n">
-        <v>29</v>
-      </c>
-      <c r="I167" s="62" t="n">
-        <v>38</v>
+      <c r="G167" s="61" t="n">
+        <v>20</v>
+      </c>
+      <c r="H167" s="61" t="n">
+        <v>28</v>
+      </c>
+      <c r="I167" s="61" t="n">
+        <v>37</v>
       </c>
     </row>
     <row r="168" ht="15" customHeight="1">
       <c r="A168" s="14" t="inlineStr">
         <is>
-          <t>Zwitserland</t>
-        </is>
-      </c>
-      <c r="E168" s="62" t="n">
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E168" s="61" t="n">
         <v>8</v>
       </c>
-      <c r="F168" s="62" t="n">
+      <c r="F168" s="61" t="n">
         <v>14</v>
       </c>
-      <c r="G168" s="62" t="n">
+      <c r="G168" s="61" t="n">
         <v>21</v>
       </c>
-      <c r="H168" s="62" t="n">
-        <v>30</v>
-      </c>
-      <c r="I168" s="62" t="n">
-        <v>39</v>
+      <c r="H168" s="61" t="n">
+        <v>29</v>
+      </c>
+      <c r="I168" s="61" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="169" ht="15" customHeight="1">
       <c r="A169" s="14" t="inlineStr">
         <is>
-          <t>Iran</t>
-        </is>
-      </c>
-      <c r="E169" s="62" t="n">
-        <v>9</v>
-      </c>
-      <c r="F169" s="62" t="n">
-        <v>15</v>
-      </c>
-      <c r="G169" s="62" t="n">
-        <v>22</v>
-      </c>
-      <c r="H169" s="62" t="n">
-        <v>31</v>
-      </c>
-      <c r="I169" s="62" t="n">
-        <v>41</v>
+          <t>Zwitserland</t>
+        </is>
+      </c>
+      <c r="E169" s="61" t="n">
+        <v>8</v>
+      </c>
+      <c r="F169" s="61" t="n">
+        <v>14</v>
+      </c>
+      <c r="G169" s="61" t="n">
+        <v>21</v>
+      </c>
+      <c r="H169" s="61" t="n">
+        <v>30</v>
+      </c>
+      <c r="I169" s="61" t="n">
+        <v>39</v>
       </c>
     </row>
     <row r="170" ht="15" customHeight="1">
       <c r="A170" s="14" t="inlineStr">
         <is>
-          <t>Oostenrijk</t>
-        </is>
-      </c>
-      <c r="E170" s="62" t="n">
+          <t>Iran</t>
+        </is>
+      </c>
+      <c r="E170" s="61" t="n">
         <v>9</v>
       </c>
-      <c r="F170" s="62" t="n">
+      <c r="F170" s="61" t="n">
         <v>15</v>
       </c>
-      <c r="G170" s="62" t="n">
-        <v>23</v>
-      </c>
-      <c r="H170" s="62" t="n">
-        <v>32</v>
-      </c>
-      <c r="I170" s="62" t="n">
-        <v>42</v>
+      <c r="G170" s="61" t="n">
+        <v>22</v>
+      </c>
+      <c r="H170" s="61" t="n">
+        <v>31</v>
+      </c>
+      <c r="I170" s="61" t="n">
+        <v>41</v>
       </c>
     </row>
     <row r="171" ht="15" customHeight="1">
       <c r="A171" s="14" t="inlineStr">
         <is>
-          <t>Zuid-Korea</t>
-        </is>
-      </c>
-      <c r="E171" s="62" t="n">
+          <t>Oostenrijk</t>
+        </is>
+      </c>
+      <c r="E171" s="61" t="n">
         <v>9</v>
       </c>
-      <c r="F171" s="62" t="n">
-        <v>16</v>
-      </c>
-      <c r="G171" s="62" t="n">
+      <c r="F171" s="61" t="n">
+        <v>15</v>
+      </c>
+      <c r="G171" s="61" t="n">
         <v>23</v>
       </c>
-      <c r="H171" s="62" t="n">
+      <c r="H171" s="61" t="n">
         <v>32</v>
       </c>
-      <c r="I171" s="62" t="n">
-        <v>43</v>
+      <c r="I171" s="61" t="n">
+        <v>42</v>
       </c>
     </row>
     <row r="172" ht="15" customHeight="1">
       <c r="A172" s="14" t="inlineStr">
         <is>
-          <t>Australië</t>
-        </is>
-      </c>
-      <c r="E172" s="62" t="n">
+          <t>Zuid-Korea</t>
+        </is>
+      </c>
+      <c r="E172" s="61" t="n">
         <v>9</v>
       </c>
-      <c r="F172" s="62" t="n">
+      <c r="F172" s="61" t="n">
         <v>16</v>
       </c>
-      <c r="G172" s="62" t="n">
-        <v>24</v>
-      </c>
-      <c r="H172" s="62" t="n">
-        <v>33</v>
-      </c>
-      <c r="I172" s="62" t="n">
+      <c r="G172" s="61" t="n">
+        <v>23</v>
+      </c>
+      <c r="H172" s="61" t="n">
+        <v>32</v>
+      </c>
+      <c r="I172" s="61" t="n">
         <v>43</v>
       </c>
     </row>
     <row r="173" ht="15" customHeight="1">
       <c r="A173" s="14" t="inlineStr">
         <is>
-          <t>Ecuador</t>
-        </is>
-      </c>
-      <c r="E173" s="62" t="n">
+          <t>Australië</t>
+        </is>
+      </c>
+      <c r="E173" s="61" t="n">
         <v>9</v>
       </c>
-      <c r="F173" s="62" t="n">
+      <c r="F173" s="61" t="n">
         <v>16</v>
       </c>
-      <c r="G173" s="62" t="n">
+      <c r="G173" s="61" t="n">
         <v>24</v>
       </c>
-      <c r="H173" s="62" t="n">
-        <v>34</v>
-      </c>
-      <c r="I173" s="62" t="n">
-        <v>44</v>
+      <c r="H173" s="61" t="n">
+        <v>33</v>
+      </c>
+      <c r="I173" s="61" t="n">
+        <v>43</v>
       </c>
     </row>
     <row r="174" ht="15" customHeight="1">
       <c r="A174" s="14" t="inlineStr">
         <is>
-          <t>Noorwegen</t>
-        </is>
-      </c>
-      <c r="E174" s="62" t="n">
-        <v>10</v>
-      </c>
-      <c r="F174" s="62" t="n">
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="E174" s="61" t="n">
+        <v>9</v>
+      </c>
+      <c r="F174" s="61" t="n">
         <v>16</v>
       </c>
-      <c r="G174" s="62" t="n">
-        <v>25</v>
-      </c>
-      <c r="H174" s="62" t="n">
+      <c r="G174" s="61" t="n">
+        <v>24</v>
+      </c>
+      <c r="H174" s="61" t="n">
         <v>34</v>
       </c>
-      <c r="I174" s="62" t="n">
-        <v>45</v>
+      <c r="I174" s="61" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="175" ht="15" customHeight="1">
       <c r="A175" s="14" t="inlineStr">
         <is>
-          <t>Panama</t>
-        </is>
-      </c>
-      <c r="E175" s="62" t="n">
+          <t>Noorwegen</t>
+        </is>
+      </c>
+      <c r="E175" s="61" t="n">
         <v>10</v>
       </c>
-      <c r="F175" s="62" t="n">
-        <v>17</v>
-      </c>
-      <c r="G175" s="62" t="n">
-        <v>26</v>
-      </c>
-      <c r="H175" s="62" t="n">
-        <v>36</v>
-      </c>
-      <c r="I175" s="62" t="n">
-        <v>48</v>
+      <c r="F175" s="61" t="n">
+        <v>16</v>
+      </c>
+      <c r="G175" s="61" t="n">
+        <v>25</v>
+      </c>
+      <c r="H175" s="61" t="n">
+        <v>34</v>
+      </c>
+      <c r="I175" s="61" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="176" ht="15" customHeight="1">
       <c r="A176" s="14" t="inlineStr">
         <is>
-          <t>Egypte</t>
-        </is>
-      </c>
-      <c r="E176" s="62" t="n">
+          <t>Panama</t>
+        </is>
+      </c>
+      <c r="E176" s="61" t="n">
         <v>10</v>
       </c>
-      <c r="F176" s="62" t="n">
-        <v>18</v>
-      </c>
-      <c r="G176" s="62" t="n">
-        <v>27</v>
-      </c>
-      <c r="H176" s="62" t="n">
-        <v>37</v>
-      </c>
-      <c r="I176" s="62" t="n">
-        <v>49</v>
+      <c r="F176" s="61" t="n">
+        <v>17</v>
+      </c>
+      <c r="G176" s="61" t="n">
+        <v>26</v>
+      </c>
+      <c r="H176" s="61" t="n">
+        <v>36</v>
+      </c>
+      <c r="I176" s="61" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="177" ht="15" customHeight="1">
       <c r="A177" s="14" t="inlineStr">
         <is>
-          <t>Algerije</t>
-        </is>
-      </c>
-      <c r="E177" s="62" t="n">
-        <v>11</v>
-      </c>
-      <c r="F177" s="62" t="n">
-        <v>19</v>
-      </c>
-      <c r="G177" s="62" t="n">
-        <v>28</v>
-      </c>
-      <c r="H177" s="62" t="n">
-        <v>40</v>
-      </c>
-      <c r="I177" s="62" t="n">
-        <v>52</v>
+          <t>Egypte</t>
+        </is>
+      </c>
+      <c r="E177" s="61" t="n">
+        <v>10</v>
+      </c>
+      <c r="F177" s="61" t="n">
+        <v>18</v>
+      </c>
+      <c r="G177" s="61" t="n">
+        <v>27</v>
+      </c>
+      <c r="H177" s="61" t="n">
+        <v>37</v>
+      </c>
+      <c r="I177" s="61" t="n">
+        <v>49</v>
       </c>
     </row>
     <row r="178" ht="15" customHeight="1">
       <c r="A178" s="14" t="inlineStr">
         <is>
-          <t>Paraguay</t>
-        </is>
-      </c>
-      <c r="E178" s="62" t="n">
+          <t>Algerije</t>
+        </is>
+      </c>
+      <c r="E178" s="61" t="n">
         <v>11</v>
       </c>
-      <c r="F178" s="62" t="n">
+      <c r="F178" s="61" t="n">
         <v>19</v>
       </c>
-      <c r="G178" s="62" t="n">
-        <v>29</v>
-      </c>
-      <c r="H178" s="62" t="n">
-        <v>41</v>
-      </c>
-      <c r="I178" s="62" t="n">
-        <v>53</v>
+      <c r="G178" s="61" t="n">
+        <v>28</v>
+      </c>
+      <c r="H178" s="61" t="n">
+        <v>40</v>
+      </c>
+      <c r="I178" s="61" t="n">
+        <v>52</v>
       </c>
     </row>
     <row r="179" ht="15" customHeight="1">
       <c r="A179" s="14" t="inlineStr">
         <is>
-          <t>Ivoorkust</t>
-        </is>
-      </c>
-      <c r="E179" s="62" t="n">
-        <v>12</v>
-      </c>
-      <c r="F179" s="62" t="n">
-        <v>20</v>
-      </c>
-      <c r="G179" s="62" t="n">
-        <v>30</v>
-      </c>
-      <c r="H179" s="62" t="n">
+          <t>Paraguay</t>
+        </is>
+      </c>
+      <c r="E179" s="61" t="n">
+        <v>11</v>
+      </c>
+      <c r="F179" s="61" t="n">
+        <v>19</v>
+      </c>
+      <c r="G179" s="61" t="n">
+        <v>29</v>
+      </c>
+      <c r="H179" s="61" t="n">
         <v>41</v>
       </c>
-      <c r="I179" s="62" t="n">
-        <v>55</v>
+      <c r="I179" s="61" t="n">
+        <v>53</v>
       </c>
     </row>
     <row r="180" ht="15" customHeight="1">
       <c r="A180" s="14" t="inlineStr">
         <is>
-          <t>Tunesië</t>
-        </is>
-      </c>
-      <c r="E180" s="62" t="n">
+          <t>Ivoorkust</t>
+        </is>
+      </c>
+      <c r="E180" s="61" t="n">
         <v>12</v>
       </c>
-      <c r="F180" s="62" t="n">
+      <c r="F180" s="61" t="n">
         <v>20</v>
       </c>
-      <c r="G180" s="62" t="n">
+      <c r="G180" s="61" t="n">
         <v>30</v>
       </c>
-      <c r="H180" s="62" t="n">
-        <v>42</v>
-      </c>
-      <c r="I180" s="62" t="n">
+      <c r="H180" s="61" t="n">
+        <v>41</v>
+      </c>
+      <c r="I180" s="61" t="n">
         <v>55</v>
       </c>
     </row>
     <row r="181" ht="15" customHeight="1">
       <c r="A181" s="14" t="inlineStr">
         <is>
-          <t>Schotland</t>
-        </is>
-      </c>
-      <c r="E181" s="62" t="n">
+          <t>Tunesië</t>
+        </is>
+      </c>
+      <c r="E181" s="61" t="n">
         <v>12</v>
       </c>
-      <c r="F181" s="62" t="n">
+      <c r="F181" s="61" t="n">
         <v>20</v>
       </c>
-      <c r="G181" s="62" t="n">
-        <v>31</v>
-      </c>
-      <c r="H181" s="62" t="n">
+      <c r="G181" s="61" t="n">
+        <v>30</v>
+      </c>
+      <c r="H181" s="61" t="n">
         <v>42</v>
       </c>
-      <c r="I181" s="62" t="n">
-        <v>56</v>
+      <c r="I181" s="61" t="n">
+        <v>55</v>
       </c>
     </row>
     <row r="182" ht="15" customHeight="1">
       <c r="A182" s="14" t="inlineStr">
         <is>
-          <t>Zweden</t>
-        </is>
-      </c>
-      <c r="E182" s="62" t="n">
+          <t>Schotland</t>
+        </is>
+      </c>
+      <c r="E182" s="61" t="n">
         <v>12</v>
       </c>
-      <c r="F182" s="62" t="n">
-        <v>21</v>
-      </c>
-      <c r="G182" s="62" t="n">
+      <c r="F182" s="61" t="n">
+        <v>20</v>
+      </c>
+      <c r="G182" s="61" t="n">
         <v>31</v>
       </c>
-      <c r="H182" s="62" t="n">
-        <v>43</v>
-      </c>
-      <c r="I182" s="62" t="n">
-        <v>57</v>
+      <c r="H182" s="61" t="n">
+        <v>42</v>
+      </c>
+      <c r="I182" s="61" t="n">
+        <v>56</v>
       </c>
     </row>
     <row r="183" ht="15" customHeight="1">
       <c r="A183" s="14" t="inlineStr">
         <is>
-          <t>Tsjechië</t>
-        </is>
-      </c>
-      <c r="E183" s="62" t="n">
+          <t>Zweden</t>
+        </is>
+      </c>
+      <c r="E183" s="61" t="n">
         <v>12</v>
       </c>
-      <c r="F183" s="62" t="n">
+      <c r="F183" s="61" t="n">
         <v>21</v>
       </c>
-      <c r="G183" s="62" t="n">
+      <c r="G183" s="61" t="n">
         <v>31</v>
       </c>
-      <c r="H183" s="62" t="n">
+      <c r="H183" s="61" t="n">
         <v>43</v>
       </c>
-      <c r="I183" s="62" t="n">
+      <c r="I183" s="61" t="n">
         <v>57</v>
       </c>
     </row>
     <row r="184" ht="15" customHeight="1">
       <c r="A184" s="14" t="inlineStr">
         <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="E184" s="62" t="n">
-        <v>13</v>
-      </c>
-      <c r="F184" s="62" t="n">
-        <v>22</v>
-      </c>
-      <c r="G184" s="62" t="n">
-        <v>33</v>
-      </c>
-      <c r="H184" s="62" t="n">
-        <v>46</v>
-      </c>
-      <c r="I184" s="62" t="n">
-        <v>61</v>
+          <t>Tsjechië</t>
+        </is>
+      </c>
+      <c r="E184" s="61" t="n">
+        <v>12</v>
+      </c>
+      <c r="F184" s="61" t="n">
+        <v>21</v>
+      </c>
+      <c r="G184" s="61" t="n">
+        <v>31</v>
+      </c>
+      <c r="H184" s="61" t="n">
+        <v>43</v>
+      </c>
+      <c r="I184" s="61" t="n">
+        <v>57</v>
       </c>
     </row>
     <row r="185" ht="15" customHeight="1">
       <c r="A185" s="14" t="inlineStr">
         <is>
-          <t>Oezbekistan</t>
-        </is>
-      </c>
-      <c r="E185" s="62" t="n">
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="E185" s="61" t="n">
         <v>13</v>
       </c>
-      <c r="F185" s="62" t="n">
-        <v>23</v>
-      </c>
-      <c r="G185" s="62" t="n">
-        <v>34</v>
-      </c>
-      <c r="H185" s="62" t="n">
-        <v>47</v>
-      </c>
-      <c r="I185" s="62" t="n">
-        <v>63</v>
+      <c r="F185" s="61" t="n">
+        <v>22</v>
+      </c>
+      <c r="G185" s="61" t="n">
+        <v>33</v>
+      </c>
+      <c r="H185" s="61" t="n">
+        <v>46</v>
+      </c>
+      <c r="I185" s="61" t="n">
+        <v>61</v>
       </c>
     </row>
     <row r="186" ht="15" customHeight="1">
       <c r="A186" s="14" t="inlineStr">
         <is>
-          <t>DR Congo</t>
-        </is>
-      </c>
-      <c r="E186" s="62" t="n">
-        <v>14</v>
-      </c>
-      <c r="F186" s="62" t="n">
+          <t>Oezbekistan</t>
+        </is>
+      </c>
+      <c r="E186" s="61" t="n">
+        <v>13</v>
+      </c>
+      <c r="F186" s="61" t="n">
         <v>23</v>
       </c>
-      <c r="G186" s="62" t="n">
-        <v>35</v>
-      </c>
-      <c r="H186" s="62" t="n">
-        <v>48</v>
-      </c>
-      <c r="I186" s="62" t="n">
-        <v>64</v>
+      <c r="G186" s="61" t="n">
+        <v>34</v>
+      </c>
+      <c r="H186" s="61" t="n">
+        <v>47</v>
+      </c>
+      <c r="I186" s="61" t="n">
+        <v>63</v>
       </c>
     </row>
     <row r="187" ht="15" customHeight="1">
       <c r="A187" s="14" t="inlineStr">
         <is>
-          <t>Saoedi-Arabië</t>
-        </is>
-      </c>
-      <c r="E187" s="62" t="n">
+          <t>DR Congo</t>
+        </is>
+      </c>
+      <c r="E187" s="61" t="n">
         <v>14</v>
       </c>
-      <c r="F187" s="62" t="n">
-        <v>24</v>
-      </c>
-      <c r="G187" s="62" t="n">
+      <c r="F187" s="61" t="n">
+        <v>23</v>
+      </c>
+      <c r="G187" s="61" t="n">
         <v>35</v>
       </c>
-      <c r="H187" s="62" t="n">
-        <v>49</v>
-      </c>
-      <c r="I187" s="62" t="n">
-        <v>65</v>
+      <c r="H187" s="61" t="n">
+        <v>48</v>
+      </c>
+      <c r="I187" s="61" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="188" ht="15" customHeight="1">
       <c r="A188" s="14" t="inlineStr">
         <is>
-          <t>Irak</t>
-        </is>
-      </c>
-      <c r="E188" s="62" t="n">
+          <t>Saoedi-Arabië</t>
+        </is>
+      </c>
+      <c r="E188" s="61" t="n">
         <v>14</v>
       </c>
-      <c r="F188" s="62" t="n">
+      <c r="F188" s="61" t="n">
         <v>24</v>
       </c>
-      <c r="G188" s="62" t="n">
-        <v>36</v>
-      </c>
-      <c r="H188" s="62" t="n">
+      <c r="G188" s="61" t="n">
+        <v>35</v>
+      </c>
+      <c r="H188" s="61" t="n">
         <v>49</v>
       </c>
-      <c r="I188" s="62" t="n">
+      <c r="I188" s="61" t="n">
         <v>65</v>
       </c>
     </row>
     <row r="189" ht="15" customHeight="1">
       <c r="A189" s="14" t="inlineStr">
         <is>
-          <t>Zuid-Afrika</t>
-        </is>
-      </c>
-      <c r="E189" s="62" t="n">
+          <t>Irak</t>
+        </is>
+      </c>
+      <c r="E189" s="61" t="n">
         <v>14</v>
       </c>
-      <c r="F189" s="62" t="n">
+      <c r="F189" s="61" t="n">
         <v>24</v>
       </c>
-      <c r="G189" s="62" t="n">
+      <c r="G189" s="61" t="n">
         <v>36</v>
       </c>
-      <c r="H189" s="62" t="n">
-        <v>50</v>
-      </c>
-      <c r="I189" s="62" t="n">
-        <v>66</v>
+      <c r="H189" s="61" t="n">
+        <v>49</v>
+      </c>
+      <c r="I189" s="61" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="190" ht="15" customHeight="1">
       <c r="A190" s="14" t="inlineStr">
         <is>
-          <t>Jordanië</t>
-        </is>
-      </c>
-      <c r="E190" s="62" t="n">
+          <t>Zuid-Afrika</t>
+        </is>
+      </c>
+      <c r="E190" s="61" t="n">
         <v>14</v>
       </c>
-      <c r="F190" s="62" t="n">
-        <v>25</v>
-      </c>
-      <c r="G190" s="62" t="n">
-        <v>37</v>
-      </c>
-      <c r="H190" s="62" t="n">
-        <v>51</v>
-      </c>
-      <c r="I190" s="62" t="n">
-        <v>68</v>
+      <c r="F190" s="61" t="n">
+        <v>24</v>
+      </c>
+      <c r="G190" s="61" t="n">
+        <v>36</v>
+      </c>
+      <c r="H190" s="61" t="n">
+        <v>50</v>
+      </c>
+      <c r="I190" s="61" t="n">
+        <v>66</v>
       </c>
     </row>
     <row r="191" ht="15" customHeight="1">
       <c r="A191" s="14" t="inlineStr">
         <is>
-          <t>Kaapverdië</t>
-        </is>
-      </c>
-      <c r="E191" s="62" t="n">
-        <v>15</v>
-      </c>
-      <c r="F191" s="62" t="n">
-        <v>26</v>
-      </c>
-      <c r="G191" s="62" t="n">
-        <v>38</v>
-      </c>
-      <c r="H191" s="62" t="n">
-        <v>53</v>
-      </c>
-      <c r="I191" s="62" t="n">
-        <v>70</v>
+          <t>Jordanië</t>
+        </is>
+      </c>
+      <c r="E191" s="61" t="n">
+        <v>14</v>
+      </c>
+      <c r="F191" s="61" t="n">
+        <v>25</v>
+      </c>
+      <c r="G191" s="61" t="n">
+        <v>37</v>
+      </c>
+      <c r="H191" s="61" t="n">
+        <v>51</v>
+      </c>
+      <c r="I191" s="61" t="n">
+        <v>68</v>
       </c>
     </row>
     <row r="192" ht="15" customHeight="1">
       <c r="A192" s="14" t="inlineStr">
         <is>
-          <t>Ghana</t>
-        </is>
-      </c>
-      <c r="E192" s="62" t="n">
+          <t>Kaapverdië</t>
+        </is>
+      </c>
+      <c r="E192" s="61" t="n">
         <v>15</v>
       </c>
-      <c r="F192" s="62" t="n">
+      <c r="F192" s="61" t="n">
         <v>26</v>
       </c>
-      <c r="G192" s="62" t="n">
-        <v>39</v>
-      </c>
-      <c r="H192" s="62" t="n">
-        <v>54</v>
-      </c>
-      <c r="I192" s="62" t="n">
-        <v>72</v>
+      <c r="G192" s="61" t="n">
+        <v>38</v>
+      </c>
+      <c r="H192" s="61" t="n">
+        <v>53</v>
+      </c>
+      <c r="I192" s="61" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="193" ht="15" customHeight="1">
       <c r="A193" s="14" t="inlineStr">
         <is>
-          <t>Bosnië-Herzegovina</t>
-        </is>
-      </c>
-      <c r="E193" s="62" t="n">
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="E193" s="61" t="n">
         <v>15</v>
       </c>
-      <c r="F193" s="62" t="n">
+      <c r="F193" s="61" t="n">
         <v>26</v>
       </c>
-      <c r="G193" s="62" t="n">
+      <c r="G193" s="61" t="n">
         <v>39</v>
       </c>
-      <c r="H193" s="62" t="n">
-        <v>55</v>
-      </c>
-      <c r="I193" s="62" t="n">
+      <c r="H193" s="61" t="n">
+        <v>54</v>
+      </c>
+      <c r="I193" s="61" t="n">
         <v>72</v>
       </c>
     </row>
     <row r="194" ht="15" customHeight="1">
       <c r="A194" s="14" t="inlineStr">
         <is>
-          <t>Haïti</t>
-        </is>
-      </c>
-      <c r="E194" s="62" t="n">
-        <v>16</v>
-      </c>
-      <c r="F194" s="62" t="n">
-        <v>28</v>
-      </c>
-      <c r="G194" s="62" t="n">
-        <v>41</v>
-      </c>
-      <c r="H194" s="62" t="n">
-        <v>58</v>
-      </c>
-      <c r="I194" s="62" t="n">
-        <v>76</v>
+          <t>Bosnië-Herzegovina</t>
+        </is>
+      </c>
+      <c r="E194" s="61" t="n">
+        <v>15</v>
+      </c>
+      <c r="F194" s="61" t="n">
+        <v>26</v>
+      </c>
+      <c r="G194" s="61" t="n">
+        <v>39</v>
+      </c>
+      <c r="H194" s="61" t="n">
+        <v>55</v>
+      </c>
+      <c r="I194" s="61" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="195" ht="15" customHeight="1">
       <c r="A195" s="14" t="inlineStr">
         <is>
-          <t>Nieuw-Zeeland</t>
-        </is>
-      </c>
-      <c r="E195" s="62" t="n">
+          <t>Haïti</t>
+        </is>
+      </c>
+      <c r="E195" s="61" t="n">
         <v>16</v>
       </c>
-      <c r="F195" s="62" t="n">
+      <c r="F195" s="61" t="n">
         <v>28</v>
       </c>
-      <c r="G195" s="62" t="n">
-        <v>42</v>
-      </c>
-      <c r="H195" s="62" t="n">
-        <v>59</v>
-      </c>
-      <c r="I195" s="62" t="n">
-        <v>77</v>
+      <c r="G195" s="61" t="n">
+        <v>41</v>
+      </c>
+      <c r="H195" s="61" t="n">
+        <v>58</v>
+      </c>
+      <c r="I195" s="61" t="n">
+        <v>76</v>
       </c>
     </row>
     <row r="196" ht="15" customHeight="1">
       <c r="A196" s="14" t="inlineStr">
         <is>
-          <t>Curaçao</t>
-        </is>
-      </c>
-      <c r="E196" s="62" t="n">
-        <v>17</v>
-      </c>
-      <c r="F196" s="62" t="n">
-        <v>29</v>
-      </c>
-      <c r="G196" s="62" t="n">
-        <v>43</v>
-      </c>
-      <c r="H196" s="62" t="n">
-        <v>60</v>
-      </c>
-      <c r="I196" s="62" t="n">
-        <v>79</v>
+          <t>Nieuw-Zeeland</t>
+        </is>
+      </c>
+      <c r="E196" s="61" t="n">
+        <v>16</v>
+      </c>
+      <c r="F196" s="61" t="n">
+        <v>28</v>
+      </c>
+      <c r="G196" s="61" t="n">
+        <v>42</v>
+      </c>
+      <c r="H196" s="61" t="n">
+        <v>59</v>
+      </c>
+      <c r="I196" s="61" t="n">
+        <v>77</v>
       </c>
     </row>
     <row r="197" ht="15" customHeight="1">
       <c r="A197" s="14" t="inlineStr">
         <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="E197" s="62" t="n">
-        <v>13</v>
-      </c>
-      <c r="F197" s="62" t="n">
-        <v>22</v>
-      </c>
-      <c r="G197" s="62" t="n">
-        <v>33</v>
-      </c>
-      <c r="H197" s="62" t="n">
-        <v>46</v>
-      </c>
-      <c r="I197" s="62" t="n">
-        <v>61</v>
+          <t>Curaçao</t>
+        </is>
+      </c>
+      <c r="E197" s="61" t="n">
+        <v>17</v>
+      </c>
+      <c r="F197" s="61" t="n">
+        <v>29</v>
+      </c>
+      <c r="G197" s="61" t="n">
+        <v>43</v>
+      </c>
+      <c r="H197" s="61" t="n">
+        <v>60</v>
+      </c>
+      <c r="I197" s="61" t="n">
+        <v>79</v>
       </c>
     </row>
     <row r="198" ht="15" customHeight="1">
       <c r="A198" s="14" t="inlineStr">
         <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="E198" s="61" t="n">
+        <v>13</v>
+      </c>
+      <c r="F198" s="61" t="n">
+        <v>22</v>
+      </c>
+      <c r="G198" s="61" t="n">
+        <v>33</v>
+      </c>
+      <c r="H198" s="61" t="n">
+        <v>46</v>
+      </c>
+      <c r="I198" s="61" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="199" ht="15" customHeight="1">
+      <c r="A199" s="14" t="inlineStr">
+        <is>
           <t>Turkije</t>
         </is>
       </c>
-      <c r="E198" s="62" t="n">
+      <c r="E199" s="61" t="n">
         <v>13</v>
       </c>
-      <c r="F198" s="62" t="n">
+      <c r="F199" s="61" t="n">
         <v>22</v>
       </c>
-      <c r="G198" s="62" t="n">
+      <c r="G199" s="61" t="n">
         <v>33</v>
       </c>
-      <c r="H198" s="62" t="n">
+      <c r="H199" s="61" t="n">
         <v>46</v>
       </c>
-      <c r="I198" s="62" t="n">
+      <c r="I199" s="61" t="n">
         <v>61</v>
       </c>
     </row>
-    <row r="199" ht="8" customHeight="1"/>
-    <row r="200" ht="18" customHeight="1">
-      <c r="A200" s="3" t="inlineStr">
+    <row r="200" ht="8" customHeight="1"/>
+    <row r="201" ht="18" customHeight="1">
+      <c r="A201" s="3" t="inlineStr">
         <is>
           <t>▶  DECEPTIE — kies een land UIT de top-12 · punten schalen met ranking en uitvalsronde</t>
         </is>
       </c>
     </row>
-    <row r="201" ht="14" customHeight="1">
-      <c r="A201" s="12" t="inlineStr">
+    <row r="202" ht="14" customHeight="1">
+      <c r="A202" s="12" t="inlineStr">
         <is>
           <t>Land (favoriet)</t>
         </is>
       </c>
-      <c r="E201" s="12" t="inlineStr">
+      <c r="E202" s="12" t="inlineStr">
         <is>
           <t>KF</t>
         </is>
       </c>
-      <c r="F201" s="12" t="inlineStr">
+      <c r="F202" s="12" t="inlineStr">
         <is>
           <t>R16</t>
         </is>
       </c>
-      <c r="G201" s="12" t="inlineStr">
+      <c r="G202" s="12" t="inlineStr">
         <is>
           <t>R32</t>
         </is>
       </c>
-      <c r="H201" s="12" t="inlineStr">
+      <c r="H202" s="12" t="inlineStr">
         <is>
           <t>Groep eruit</t>
         </is>
-      </c>
-    </row>
-    <row r="202" ht="15" customHeight="1">
-      <c r="A202" s="14" t="inlineStr">
-        <is>
-          <t>Frankrijk</t>
-        </is>
-      </c>
-      <c r="E202" s="62" t="n">
-        <v>8</v>
-      </c>
-      <c r="F202" s="62" t="n">
-        <v>14</v>
-      </c>
-      <c r="G202" s="62" t="n">
-        <v>20</v>
-      </c>
-      <c r="H202" s="62" t="n">
-        <v>30</v>
       </c>
     </row>
     <row r="203" ht="15" customHeight="1">
       <c r="A203" s="14" t="inlineStr">
         <is>
-          <t>Spanje</t>
-        </is>
-      </c>
-      <c r="E203" s="62" t="n">
-        <v>7</v>
-      </c>
-      <c r="F203" s="62" t="n">
-        <v>13</v>
-      </c>
-      <c r="G203" s="62" t="n">
-        <v>19</v>
-      </c>
-      <c r="H203" s="62" t="n">
-        <v>28</v>
+          <t>Frankrijk</t>
+        </is>
+      </c>
+      <c r="E203" s="61" t="n">
+        <v>8</v>
+      </c>
+      <c r="F203" s="61" t="n">
+        <v>14</v>
+      </c>
+      <c r="G203" s="61" t="n">
+        <v>20</v>
+      </c>
+      <c r="H203" s="61" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="204" ht="15" customHeight="1">
       <c r="A204" s="14" t="inlineStr">
         <is>
-          <t>Argentinië</t>
-        </is>
-      </c>
-      <c r="E204" s="62" t="n">
-        <v>6</v>
-      </c>
-      <c r="F204" s="62" t="n">
-        <v>12</v>
-      </c>
-      <c r="G204" s="62" t="n">
-        <v>17</v>
-      </c>
-      <c r="H204" s="62" t="n">
-        <v>26</v>
+          <t>Spanje</t>
+        </is>
+      </c>
+      <c r="E204" s="61" t="n">
+        <v>7</v>
+      </c>
+      <c r="F204" s="61" t="n">
+        <v>13</v>
+      </c>
+      <c r="G204" s="61" t="n">
+        <v>19</v>
+      </c>
+      <c r="H204" s="61" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="205" ht="15" customHeight="1">
       <c r="A205" s="14" t="inlineStr">
         <is>
-          <t>Engeland</t>
-        </is>
-      </c>
-      <c r="E205" s="62" t="n">
+          <t>Argentinië</t>
+        </is>
+      </c>
+      <c r="E205" s="61" t="n">
         <v>6</v>
       </c>
-      <c r="F205" s="62" t="n">
-        <v>11</v>
-      </c>
-      <c r="G205" s="62" t="n">
-        <v>16</v>
-      </c>
-      <c r="H205" s="62" t="n">
-        <v>24</v>
+      <c r="F205" s="61" t="n">
+        <v>12</v>
+      </c>
+      <c r="G205" s="61" t="n">
+        <v>17</v>
+      </c>
+      <c r="H205" s="61" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="206" ht="15" customHeight="1">
       <c r="A206" s="14" t="inlineStr">
         <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="E206" s="62" t="n">
+          <t>Engeland</t>
+        </is>
+      </c>
+      <c r="E206" s="61" t="n">
         <v>6</v>
       </c>
-      <c r="F206" s="62" t="n">
-        <v>10</v>
-      </c>
-      <c r="G206" s="62" t="n">
-        <v>15</v>
-      </c>
-      <c r="H206" s="62" t="n">
-        <v>22</v>
+      <c r="F206" s="61" t="n">
+        <v>11</v>
+      </c>
+      <c r="G206" s="61" t="n">
+        <v>16</v>
+      </c>
+      <c r="H206" s="61" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="207" ht="15" customHeight="1">
       <c r="A207" s="14" t="inlineStr">
         <is>
-          <t>Brazilië</t>
-        </is>
-      </c>
-      <c r="E207" s="62" t="n">
-        <v>5</v>
-      </c>
-      <c r="F207" s="62" t="n">
-        <v>9</v>
-      </c>
-      <c r="G207" s="62" t="n">
-        <v>13</v>
-      </c>
-      <c r="H207" s="62" t="n">
-        <v>20</v>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E207" s="61" t="n">
+        <v>6</v>
+      </c>
+      <c r="F207" s="61" t="n">
+        <v>10</v>
+      </c>
+      <c r="G207" s="61" t="n">
+        <v>15</v>
+      </c>
+      <c r="H207" s="61" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="208" ht="15" customHeight="1">
       <c r="A208" s="14" t="inlineStr">
         <is>
-          <t>Nederland</t>
-        </is>
-      </c>
-      <c r="E208" s="62" t="n">
-        <v>4</v>
-      </c>
-      <c r="F208" s="62" t="n">
-        <v>8</v>
-      </c>
-      <c r="G208" s="62" t="n">
-        <v>12</v>
-      </c>
-      <c r="H208" s="62" t="n">
-        <v>18</v>
+          <t>Brazilië</t>
+        </is>
+      </c>
+      <c r="E208" s="61" t="n">
+        <v>5</v>
+      </c>
+      <c r="F208" s="61" t="n">
+        <v>9</v>
+      </c>
+      <c r="G208" s="61" t="n">
+        <v>13</v>
+      </c>
+      <c r="H208" s="61" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="209" ht="15" customHeight="1">
       <c r="A209" s="14" t="inlineStr">
         <is>
-          <t>Marokko</t>
-        </is>
-      </c>
-      <c r="E209" s="62" t="n">
+          <t>Nederland</t>
+        </is>
+      </c>
+      <c r="E209" s="61" t="n">
         <v>4</v>
       </c>
-      <c r="F209" s="62" t="n">
-        <v>7</v>
-      </c>
-      <c r="G209" s="62" t="n">
-        <v>11</v>
-      </c>
-      <c r="H209" s="62" t="n">
-        <v>16</v>
+      <c r="F209" s="61" t="n">
+        <v>8</v>
+      </c>
+      <c r="G209" s="61" t="n">
+        <v>12</v>
+      </c>
+      <c r="H209" s="61" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="210" ht="15" customHeight="1">
       <c r="A210" s="14" t="inlineStr">
         <is>
-          <t>België</t>
-        </is>
-      </c>
-      <c r="E210" s="62" t="n">
+          <t>Marokko</t>
+        </is>
+      </c>
+      <c r="E210" s="61" t="n">
         <v>4</v>
       </c>
-      <c r="F210" s="62" t="n">
-        <v>6</v>
-      </c>
-      <c r="G210" s="62" t="n">
-        <v>9</v>
-      </c>
-      <c r="H210" s="62" t="n">
-        <v>14</v>
+      <c r="F210" s="61" t="n">
+        <v>7</v>
+      </c>
+      <c r="G210" s="61" t="n">
+        <v>11</v>
+      </c>
+      <c r="H210" s="61" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="211" ht="15" customHeight="1">
       <c r="A211" s="14" t="inlineStr">
         <is>
-          <t>Duitsland</t>
-        </is>
-      </c>
-      <c r="E211" s="62" t="n">
-        <v>3</v>
-      </c>
-      <c r="F211" s="62" t="n">
+          <t>België</t>
+        </is>
+      </c>
+      <c r="E211" s="61" t="n">
+        <v>4</v>
+      </c>
+      <c r="F211" s="61" t="n">
         <v>6</v>
       </c>
-      <c r="G211" s="62" t="n">
-        <v>8</v>
-      </c>
-      <c r="H211" s="62" t="n">
-        <v>12</v>
+      <c r="G211" s="61" t="n">
+        <v>9</v>
+      </c>
+      <c r="H211" s="61" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="212" ht="15" customHeight="1">
       <c r="A212" s="14" t="inlineStr">
         <is>
-          <t>Kroatië</t>
-        </is>
-      </c>
-      <c r="E212" s="62" t="n">
-        <v>2</v>
-      </c>
-      <c r="F212" s="62" t="n">
-        <v>5</v>
-      </c>
-      <c r="G212" s="62" t="n">
-        <v>7</v>
-      </c>
-      <c r="H212" s="62" t="n">
-        <v>10</v>
+          <t>Duitsland</t>
+        </is>
+      </c>
+      <c r="E212" s="61" t="n">
+        <v>3</v>
+      </c>
+      <c r="F212" s="61" t="n">
+        <v>6</v>
+      </c>
+      <c r="G212" s="61" t="n">
+        <v>8</v>
+      </c>
+      <c r="H212" s="61" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="213" ht="15" customHeight="1">
       <c r="A213" s="14" t="inlineStr">
         <is>
+          <t>Kroatië</t>
+        </is>
+      </c>
+      <c r="E213" s="61" t="n">
+        <v>2</v>
+      </c>
+      <c r="F213" s="61" t="n">
+        <v>5</v>
+      </c>
+      <c r="G213" s="61" t="n">
+        <v>7</v>
+      </c>
+      <c r="H213" s="61" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="214" ht="15" customHeight="1">
+      <c r="A214" s="14" t="inlineStr">
+        <is>
           <t>Colombia</t>
         </is>
       </c>
-      <c r="E213" s="62" t="n">
+      <c r="E214" s="61" t="n">
         <v>2</v>
       </c>
-      <c r="F213" s="62" t="n">
+      <c r="F214" s="61" t="n">
         <v>3</v>
       </c>
-      <c r="G213" s="62" t="n">
+      <c r="G214" s="61" t="n">
         <v>4</v>
       </c>
-      <c r="H213" s="62" t="n">
+      <c r="H214" s="61" t="n">
         <v>6</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="204">
+  <mergeCells count="187">
+    <mergeCell ref="A150:D150"/>
     <mergeCell ref="E13:G13"/>
     <mergeCell ref="A122:D122"/>
     <mergeCell ref="A97:D97"/>
-    <mergeCell ref="A133:O133"/>
-    <mergeCell ref="A134:D134"/>
-    <mergeCell ref="A152:D152"/>
+    <mergeCell ref="A159:D159"/>
+    <mergeCell ref="M111:N111"/>
+    <mergeCell ref="E111:F111"/>
     <mergeCell ref="A121:D121"/>
     <mergeCell ref="E15:G15"/>
     <mergeCell ref="A13:D13"/>
     <mergeCell ref="A202:D202"/>
     <mergeCell ref="A176:D176"/>
     <mergeCell ref="A15:D15"/>
-    <mergeCell ref="E57:G57"/>
     <mergeCell ref="A186:D186"/>
-    <mergeCell ref="M106:O106"/>
     <mergeCell ref="A107:D107"/>
     <mergeCell ref="A178:D178"/>
-    <mergeCell ref="M76:O76"/>
     <mergeCell ref="E16:G16"/>
     <mergeCell ref="A29:O29"/>
-    <mergeCell ref="A200:O200"/>
     <mergeCell ref="B44:O44"/>
-    <mergeCell ref="A161:O161"/>
-    <mergeCell ref="M66:O66"/>
+    <mergeCell ref="A152:O152"/>
     <mergeCell ref="I106:L106"/>
     <mergeCell ref="A124:D124"/>
     <mergeCell ref="A31:O31"/>
@@ -5143,19 +5367,18 @@
     <mergeCell ref="A172:D172"/>
     <mergeCell ref="A99:D99"/>
     <mergeCell ref="A164:D164"/>
-    <mergeCell ref="E106:G106"/>
     <mergeCell ref="A212:D212"/>
     <mergeCell ref="I66:L66"/>
     <mergeCell ref="A56:D56"/>
     <mergeCell ref="A24:O24"/>
     <mergeCell ref="A154:D154"/>
     <mergeCell ref="A149:D149"/>
+    <mergeCell ref="A214:D214"/>
     <mergeCell ref="A163:D163"/>
-    <mergeCell ref="M67:O67"/>
     <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A111:B111"/>
     <mergeCell ref="A195:D195"/>
     <mergeCell ref="A204:D204"/>
-    <mergeCell ref="E107:G107"/>
     <mergeCell ref="A188:D188"/>
     <mergeCell ref="A126:D126"/>
     <mergeCell ref="A141:D141"/>
@@ -5166,36 +5389,28 @@
     <mergeCell ref="A190:D190"/>
     <mergeCell ref="A18:O18"/>
     <mergeCell ref="A117:D117"/>
-    <mergeCell ref="E77:G77"/>
-    <mergeCell ref="M86:O86"/>
+    <mergeCell ref="A199:D199"/>
     <mergeCell ref="A9:D9"/>
-    <mergeCell ref="E86:G86"/>
     <mergeCell ref="A127:D127"/>
     <mergeCell ref="A167:D167"/>
-    <mergeCell ref="A151:O151"/>
+    <mergeCell ref="I112:J112"/>
     <mergeCell ref="A59:D59"/>
     <mergeCell ref="I77:L77"/>
     <mergeCell ref="A142:D142"/>
-    <mergeCell ref="M57:O57"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="A22:O22"/>
     <mergeCell ref="B42:O42"/>
     <mergeCell ref="I86:L86"/>
-    <mergeCell ref="M97:O97"/>
-    <mergeCell ref="A144:O144"/>
+    <mergeCell ref="A182:D182"/>
+    <mergeCell ref="A191:D191"/>
     <mergeCell ref="A169:D169"/>
     <mergeCell ref="I89:L89"/>
-    <mergeCell ref="A182:D182"/>
-    <mergeCell ref="A191:D191"/>
     <mergeCell ref="A20:O20"/>
     <mergeCell ref="A79:D79"/>
-    <mergeCell ref="E97:G97"/>
+    <mergeCell ref="A134:O134"/>
+    <mergeCell ref="I111:J111"/>
     <mergeCell ref="I57:L57"/>
     <mergeCell ref="A153:D153"/>
-    <mergeCell ref="A162:D162"/>
-    <mergeCell ref="M56:O56"/>
-    <mergeCell ref="E56:G56"/>
-    <mergeCell ref="E96:G96"/>
     <mergeCell ref="B34:O34"/>
     <mergeCell ref="A128:D128"/>
     <mergeCell ref="B28:O28"/>
@@ -5207,8 +5422,6 @@
     <mergeCell ref="A136:D136"/>
     <mergeCell ref="I56:L56"/>
     <mergeCell ref="I96:L96"/>
-    <mergeCell ref="M107:O107"/>
-    <mergeCell ref="A145:D145"/>
     <mergeCell ref="A192:D192"/>
     <mergeCell ref="B30:O30"/>
     <mergeCell ref="A139:D139"/>
@@ -5217,6 +5430,7 @@
     <mergeCell ref="A129:D129"/>
     <mergeCell ref="A194:D194"/>
     <mergeCell ref="A76:D76"/>
+    <mergeCell ref="A162:O162"/>
     <mergeCell ref="I107:L107"/>
     <mergeCell ref="A116:D116"/>
     <mergeCell ref="A181:D181"/>
@@ -5232,16 +5446,16 @@
     <mergeCell ref="E9:G9"/>
     <mergeCell ref="A10:D10"/>
     <mergeCell ref="B46:O46"/>
-    <mergeCell ref="A115:D115"/>
+    <mergeCell ref="A145:O145"/>
+    <mergeCell ref="A155:D155"/>
     <mergeCell ref="I59:L59"/>
     <mergeCell ref="I99:L99"/>
     <mergeCell ref="A173:D173"/>
-    <mergeCell ref="M77:O77"/>
     <mergeCell ref="E11:G11"/>
     <mergeCell ref="A77:D77"/>
     <mergeCell ref="I69:L69"/>
+    <mergeCell ref="A143:D143"/>
     <mergeCell ref="A33:O33"/>
-    <mergeCell ref="A157:D157"/>
     <mergeCell ref="A166:D166"/>
     <mergeCell ref="A8:O8"/>
     <mergeCell ref="A49:D49"/>
@@ -5249,13 +5463,11 @@
     <mergeCell ref="A35:O35"/>
     <mergeCell ref="A168:D168"/>
     <mergeCell ref="A69:D69"/>
+    <mergeCell ref="A115:O115"/>
     <mergeCell ref="A19:O19"/>
     <mergeCell ref="A205:D205"/>
     <mergeCell ref="A87:D87"/>
     <mergeCell ref="E12:G12"/>
-    <mergeCell ref="A111:O111"/>
-    <mergeCell ref="M87:O87"/>
-    <mergeCell ref="M96:O96"/>
     <mergeCell ref="A193:D193"/>
     <mergeCell ref="A39:O39"/>
     <mergeCell ref="I97:L97"/>
@@ -5264,10 +5476,10 @@
     <mergeCell ref="E14:G14"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="I87:L87"/>
+    <mergeCell ref="E112:F112"/>
     <mergeCell ref="A45:O45"/>
     <mergeCell ref="A57:D57"/>
     <mergeCell ref="B36:O36"/>
-    <mergeCell ref="E87:G87"/>
     <mergeCell ref="A14:D14"/>
     <mergeCell ref="A185:D185"/>
     <mergeCell ref="A106:D106"/>
@@ -5281,20 +5493,16 @@
     <mergeCell ref="A211:D211"/>
     <mergeCell ref="A26:O26"/>
     <mergeCell ref="A67:D67"/>
-    <mergeCell ref="A113:O113"/>
     <mergeCell ref="A130:D130"/>
-    <mergeCell ref="A201:D201"/>
     <mergeCell ref="A148:D148"/>
     <mergeCell ref="A23:O23"/>
-    <mergeCell ref="E76:G76"/>
     <mergeCell ref="I49:L49"/>
     <mergeCell ref="A123:D123"/>
     <mergeCell ref="A138:D138"/>
+    <mergeCell ref="A132:D132"/>
     <mergeCell ref="A197:D197"/>
     <mergeCell ref="A43:O43"/>
     <mergeCell ref="A146:D146"/>
-    <mergeCell ref="A156:O156"/>
-    <mergeCell ref="E66:G66"/>
     <mergeCell ref="A119:D119"/>
     <mergeCell ref="B38:O38"/>
     <mergeCell ref="A187:D187"/>
@@ -5303,20 +5511,23 @@
     <mergeCell ref="A174:D174"/>
     <mergeCell ref="A183:D183"/>
     <mergeCell ref="A66:D66"/>
+    <mergeCell ref="A201:O201"/>
     <mergeCell ref="B40:O40"/>
     <mergeCell ref="A118:D118"/>
     <mergeCell ref="A189:D189"/>
+    <mergeCell ref="A157:O157"/>
     <mergeCell ref="A158:D158"/>
     <mergeCell ref="A198:D198"/>
-    <mergeCell ref="E67:G67"/>
+    <mergeCell ref="A112:B112"/>
     <mergeCell ref="A86:D86"/>
+    <mergeCell ref="M112:N112"/>
     <mergeCell ref="A110:O110"/>
     <mergeCell ref="A213:D213"/>
     <mergeCell ref="A175:D175"/>
     <mergeCell ref="I67:L67"/>
     <mergeCell ref="B32:O32"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="35">
     <dataValidation sqref="E9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Landen!$A$1:$A$48</formula1>
     </dataValidation>
@@ -5326,6 +5537,102 @@
     <dataValidation sqref="E11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Landen!$C$1:$C$12</formula1>
     </dataValidation>
+    <dataValidation sqref="E56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Landen!$D$1:$D$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="M56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Landen!$E$1:$E$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="E57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Landen!$D$1:$D$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="M57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Landen!$E$1:$E$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="E66" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Landen!$F$1:$F$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="M66" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Landen!$G$1:$G$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="E67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Landen!$F$1:$F$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="M67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Landen!$G$1:$G$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="E76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Landen!$H$1:$H$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="M76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Landen!$I$1:$I$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="E77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Landen!$H$1:$H$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="M77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Landen!$I$1:$I$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="E86" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Landen!$J$1:$J$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="M86" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Landen!$K$1:$K$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="E87" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Landen!$J$1:$J$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="M87" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Landen!$K$1:$K$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="E96" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Landen!$L$1:$L$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="M96" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Landen!$M$1:$M$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="E97" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Landen!$L$1:$L$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="M97" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Landen!$M$1:$M$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="E106" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Landen!$N$1:$N$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="M106" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Landen!$O$1:$O$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="E107" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Landen!$N$1:$N$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="M107" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Landen!$O$1:$O$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="C111" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Landen!$A$1:$A$48</formula1>
+    </dataValidation>
+    <dataValidation sqref="G111" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Landen!$A$1:$A$48</formula1>
+    </dataValidation>
+    <dataValidation sqref="K111" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Landen!$A$1:$A$48</formula1>
+    </dataValidation>
+    <dataValidation sqref="O111" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Landen!$A$1:$A$48</formula1>
+    </dataValidation>
+    <dataValidation sqref="C112" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Landen!$A$1:$A$48</formula1>
+    </dataValidation>
+    <dataValidation sqref="G112" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Landen!$A$1:$A$48</formula1>
+    </dataValidation>
+    <dataValidation sqref="K112" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Landen!$A$1:$A$48</formula1>
+    </dataValidation>
+    <dataValidation sqref="O112" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Landen!$A$1:$A$48</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
